--- a/docs/testing/PROJECT TEST CASES CAA 031026.xlsx
+++ b/docs/testing/PROJECT TEST CASES CAA 031026.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J265"/>
+  <dimension ref="A1:J275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6633,22 +6633,23 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>Setup time and Turnaround time both read 0; every Confirmed, Tentative and Blocked period on the calendar matches the advertised times exactly, with no buffer portion shown, so TC_E05S03_01 to TC_E05S03_05 continue to pass unchanged</t>
+          <t>Setup time and Turnaround time both read 0; every Confirmed, Tentative and Blocked period on the calendar matches the advertised times exactly, with no buffer portion shown, so TC_E05S03_01 to TC_E05S03_05 continue to pass unchanged
+## E05-S06</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>E06-S01</t>
+          <t>E05-S06</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>E06-S01 - Scenario 1 (Matching venues listed)</t>
+          <t>E05-S06 — Scenario 1 (Unavailability recorded with a reason)</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -6658,150 +6659,159 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>TC_E06S01_01</t>
+          <t>TC_E05S06_01</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Verify that running a search where multiple criteria match an available venue should list it with its capacity, layouts and facilities</t>
+          <t>Verify that marking a venue unavailable with a reason category over a period with no bookings should save and show the period as Blocked</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Venue "Grand Ballroom" is available on 15/11/2026, capacity 300, supports Theatre layout, has Wheelchair Access, and has no other confirmed/blocked booking for that date</t>
+          <t>venue_staff_1@connectsphere.com is signed in; venue "Riverside Hall" has no bookings on 20/01/2027</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>1. Log in as an Event Coordinator
- 2. Search venues with Date: 15/11/2026, Expected Attendance: 250, Layout: Theatre, Accessibility: Wheelchair Access</t>
+          <t>1. Open venue "Riverside Hall" and click "Mark unavailable"
+  2. Enter period 20/01/2027 08:00 to 20/01/2027 18:00
+  3. Choose reason category "Equipment failure" and note "Projector rig fault"
+  4. Click "Save"
+  5. Open the venue availability calendar for 20/01/2027</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>Date: 15/11/2026 | Attendance: 250 | Layout: Theatre | Accessibility: Wheelchair Access</t>
+          <t>Period: 20/01/2027 08:00-18:00 | Category: Equipment failure | Note: Projector rig fault</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>"Grand Ballroom" appears in the results, listed with its capacity (300), supported layouts, and facilities</t>
+          <t>The unavailability is saved with period, category, note and venue_staff_1 as recorder; the calendar shows 20/01/2027 08:00-18:00 as Blocked</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>E06-S01</t>
+          <t>E05-S06</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>E06-S01 - Scenario 2 (Near matches show failing criteria)</t>
+          <t>E05-S06 — Scenario 2 (Overlapping bookings become Conflicting, not released); Scenario 3 (The event itself is untouched); assumes O-24</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>2 - Happy Path</t>
+          <t>4 - Negative (business rule)</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>TC_E06S01_02</t>
+          <t>TC_E05S06_02</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Verify that when no venue matches every criterion, near matches should be returned instead of an empty result</t>
+          <t>Verify that marking a venue unavailable over a Pending request and a Confirmed booking should mark both Conflicting, list the affected events on save and release neither</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>No venue fully meets Date: 15/11/2026, Attendance: 250, Accessibility: Hearing Loop (no venue currently has a hearing loop)</t>
+          <t>Venue "Riverside Hall" has a Confirmed booking for "Charity Run" (status Confirmed, coordinator_1) on 15/01/2027 10:00-12:00 and a Pending request for "Alumni Dinner" (coordinator_2) on 15/01/2027 14:00-16:00; venue_staff_1@connectsphere.com is signed in</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>1. Log in as an Event Coordinator
- 2. Search venues with Date: 15/11/2026, Attendance: 250, Accessibility: Hearing Loop</t>
+          <t>1. Open venue "Riverside Hall" and click "Mark unavailable"
+  2. Enter period 15/01/2027 00:00 to 16/01/2027 00:00, category "Safety concern", note "Ceiling inspection"
+  3. Click "Save"
+  4. Open event "Charity Run"
+  5. Open the venue availability calendar for 15/01/2027</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Date: 15/11/2026 | Attendance: 250 | Accessibility: Hearing Loop (no exact match exists)</t>
+          <t>Two bookings inside the period: Charity Run (Confirmed), Alumni Dinner (Pending)</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>The search returns near-matching venues (e.g. "Grand Ballroom" without a hearing loop) rather than an empty list, with the failing criterion (Hearing Loop) indicated for each</t>
+          <t>The save succeeds and lists "Charity Run" and "Alumni Dinner" as affected; both bookings are marked Conflicting and neither is released or cancelled; "Charity Run" still shows status Confirmed with all other arrangements intact and a venue-conflict flag reading "Safety concern"; the calendar shows the period Blocked with the two Conflicting bookings visible</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>E06-S01</t>
+          <t>E05-S06</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>E06-S01 - Scenario 3 (Undersized venue marked unsuitable)</t>
+          <t>E05-S06 — Scenario 4 (Affected Coordinators informed); assumes O-25</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>4 - Negative</t>
+          <t>3 - Cross-cutting (notification consistency)</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>TC_E06S01_03</t>
+          <t>TC_E05S06_03</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Verify that a venue available but with capacity below the event's expected attendance should be excluded or marked unsuitable</t>
+          <t>Verify that each Coordinator whose booking became Conflicting should receive an in-app and email notification naming the venue, period, reason and event</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Venue "Small Room" (capacity 50) is available on 15/11/2026; the event's expected attendance is 100</t>
+          <t>As TC_E05S06_02, with the notification outbox relay enabled against the intercepted email provider</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>1. Log in as an Event Coordinator
-  2. Search venues with Date: 15/11/2026, Expected Attendance: 100</t>
+          <t>1. Perform TC_E05S06_02 steps 1-3
+  2. Sign in as coordinator_1@connectsphere.com and open the inbox
+  3. Sign in as coordinator_2@connectsphere.com and open the inbox
+  4. Inspect the intercepted outbound emails
+  5. Sign in as the Organiser of "Charity Run" and open the inbox</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>Small Room capacity: 50 | Required attendance: 100</t>
+          <t>Expected recipients: coordinator_1, coordinator_2 | Not expected: the Organiser, registered Attendees</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>"Small Room" is excluded from the results or clearly marked unsuitable due to insufficient capacity</t>
+          <t>Each Coordinator has exactly one in-app notification and one email naming "Riverside Hall", 15/01/2027, "Safety concern" and their event, stating that alternative arrangements are required; the Organiser has no notification about the venue loss</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>E06-S01</t>
+          <t>E05-S06</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>E06-S01 - Scenario 4 (Blocked or booked venues excluded)</t>
+          <t>E05-S06 — Scenario 5 (End date required and extendable); assumes O-23</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -6811,33 +6821,34 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>TC_E06S01_04</t>
+          <t>TC_E05S06_04</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Verify that a venue that is blocked or already confirmed for the requested period should not appear as available</t>
+          <t>Verify that an unavailability with no end date and time should be refused</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Venue "Grand Ballroom" is Confirmed for another event on 15/11/2026</t>
+          <t>venue_staff_1@connectsphere.com is signed in on venue "Riverside Hall"</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>1. Log in as an Event Coordinator
-  2. Search venues with Date: 15/11/2026</t>
+          <t>1. Click "Mark unavailable"
+  2. Enter start 20/01/2027 08:00, leave the end empty, choose "Renovation"
+  3. Click "Save"</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>Date: 15/11/2026 | Grand Ballroom status: Confirmed (for another event)</t>
+          <t>Start: 20/01/2027 08:00 | End: (empty)</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>"Grand Ballroom" does not appear as available in the results for 15/11/2026</t>
+          <t>The save is refused with a message that an end date and time is required; nothing is recorded and the calendar is unchanged</t>
         </is>
       </c>
     </row>
@@ -6847,295 +6858,603 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
+          <t>E05-S06</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>E05-S06 — Scenario 5 (End date required and extendable); Scenario 6 (Unavailability shortened or ended early); assumes O-26</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>5 - Boundary (exactly at)</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>TC_E05S06_05</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Verify that extending an unavailability should flag bookings newly inside the longer period and that shortening it should clear the flag on bookings it no longer touches</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Venue "Riverside Hall" has an unavailability 15/01/2027 08:00-12:00 and a Confirmed booking for "Alumni Dinner" 15/01/2027 12:00-14:00 that is not Conflicting; venue_staff_1@connectsphere.com is signed in</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>1. Edit the unavailability and set the end to 15/01/2027 12:01; save
+  2. Open event "Alumni Dinner"
+  3. Edit the unavailability and set the end back to 15/01/2027 12:00; save
+  4. Open event "Alumni Dinner" again</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>Booking: 12:00-14:00 | End at 12:00 = adjacent, no overlap | End at 12:01 = one minute of overlap</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>After step 1 the booking is Conflicting and coordinator_2 is notified; after step 3 the Conflicting flag has cleared and the booking stands as Confirmed with no further action by the Coordinator</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>E05-S06</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>E05-S06 — Checklist (E05-S04 regression per T-74)</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>3 - Integration / regression</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>TC_E05S06_06</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Verify that E05-S04's block, shorten and remove behaviour still works for periods with no bookings after this story</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Venue "Riverside Hall" has no bookings 05/01/2027-07/01/2027; venue_staff_1@connectsphere.com is signed in</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>1. Re-run TC_E05S04_01 (block a free period)
+  2. Re-run TC_E05S04_04 (shorten and remove the block)</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>As TC_E05S04_01 and TC_E05S04_04</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>Both cases pass unchanged: a block over a free period makes the venue unavailable, and shortening or removing it restores availability; the only E05-S04 behaviour this story changes is the refusal in TC_E05S04_02, which is superseded by TC_E05S06_02</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>E06-S01</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>E06-S01 - Scenario 1 (Matching venues listed)</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>TC_E06S01_01</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Verify that running a search where multiple criteria match an available venue should list it with its capacity, layouts and facilities</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Venue "Grand Ballroom" is available on 15/11/2026, capacity 300, supports Theatre layout, has Wheelchair Access, and has no other confirmed/blocked booking for that date</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in as an Event Coordinator
+ 2. Search venues with Date: 15/11/2026, Expected Attendance: 250, Layout: Theatre, Accessibility: Wheelchair Access</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>Date: 15/11/2026 | Attendance: 250 | Layout: Theatre | Accessibility: Wheelchair Access</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>"Grand Ballroom" appears in the results, listed with its capacity (300), supported layouts, and facilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>E06-S01</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>E06-S01 - Scenario 2 (Near matches show failing criteria)</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>TC_E06S01_02</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Verify that when no venue matches every criterion, near matches should be returned instead of an empty result</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>No venue fully meets Date: 15/11/2026, Attendance: 250, Accessibility: Hearing Loop (no venue currently has a hearing loop)</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in as an Event Coordinator
+ 2. Search venues with Date: 15/11/2026, Attendance: 250, Accessibility: Hearing Loop</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Date: 15/11/2026 | Attendance: 250 | Accessibility: Hearing Loop (no exact match exists)</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>The search returns near-matching venues (e.g. "Grand Ballroom" without a hearing loop) rather than an empty list, with the failing criterion (Hearing Loop) indicated for each</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>E06-S01</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>E06-S01 - Scenario 3 (Undersized venue marked unsuitable)</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>4 - Negative</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>TC_E06S01_03</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Verify that a venue available but with capacity below the event's expected attendance should be excluded or marked unsuitable</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Venue "Small Room" (capacity 50) is available on 15/11/2026; the event's expected attendance is 100</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in as an Event Coordinator
+  2. Search venues with Date: 15/11/2026, Expected Attendance: 100</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>Small Room capacity: 50 | Required attendance: 100</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>"Small Room" is excluded from the results or clearly marked unsuitable due to insufficient capacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>E06-S01</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>E06-S01 - Scenario 4 (Blocked or booked venues excluded)</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>4 - Negative</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>TC_E06S01_04</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Verify that a venue that is blocked or already confirmed for the requested period should not appear as available</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Venue "Grand Ballroom" is Confirmed for another event on 15/11/2026</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in as an Event Coordinator
+  2. Search venues with Date: 15/11/2026</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>Date: 15/11/2026 | Grand Ballroom status: Confirmed (for another event)</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>"Grand Ballroom" does not appear as available in the results for 15/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>E06-S01</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
         <is>
           <t>E06-S01 — Scenario 5 (Buffered occupancy excludes a venue)</t>
         </is>
       </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>4 - Negative (business rule)</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>TC_E06S01_05</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Verify that a venue whose existing booking overlaps the event only once its setup and turnaround time are applied should not appear as available in search</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>Venue "Riverside Hall" has Setup time 30 and Turnaround time 45 and a Confirmed booking 15/01/2027 10:00-12:00; coordinator_1@connectsphere.com is signed in with an Approved event on 15/01/2027 12:30-14:00</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>1. Open venue search for the event
   2. Search for "Riverside"
   3. Inspect the result for "Riverside Hall"</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
+      <c r="I129" s="2" t="inlineStr">
         <is>
           <t>Existing booking buffered window: 09:30-12:45 | Event period: 12:30-14:00</t>
         </is>
       </c>
-      <c r="J123" s="2" t="inlineStr">
+      <c r="J129" s="2" t="inlineStr">
         <is>
           <t>"Riverside Hall" is not offered as available for the event; where it is listed its unavailability names the 12:30-12:45 overlap with the other booking's turnaround
 ## E06-S02</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="n">
+    <row r="130">
+      <c r="A130" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>E06-S02</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
         <is>
           <t>E06-S02 - Scenario 1 (Suitability shown for the event)</t>
         </is>
       </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>TC_E06S02_01</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Verify that viewing a venue in the context of a event with recorded requirements should show a suitability status for that event</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>A event of "Tech Conference 2026" has recorded requirements: Theatre layout, Wheelchair Access, 100 attendees</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open venue "Riverside Hall" in the context of this event
   3. Check the suitability status shown</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr">
+      <c r="I130" s="2" t="inlineStr">
         <is>
           <t>Event requirements: Theatre layout, Wheelchair Access, 100 attendees</t>
         </is>
       </c>
-      <c r="J124" s="2" t="inlineStr">
+      <c r="J130" s="2" t="inlineStr">
         <is>
           <t>A suitability status (Suitable or Unsuitable) is shown for "Riverside Hall" specifically against this event's requirements</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="n">
+    <row r="131">
+      <c r="A131" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>E06-S02</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
         <is>
           <t>E06-S02 - Scenario 2 (Failing requirements named)</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>TC_E06S02_02</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Verify that a venue failing one or more recorded requirements should be marked unsuitable with every failing requirement named</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>The event requires Wheelchair Access and a capacity of 150; "Riverside Hall" has no wheelchair access and a capacity of 120</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. View "Riverside Hall" in the context of this event</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr">
+      <c r="I131" s="2" t="inlineStr">
         <is>
           <t>Event requires: Wheelchair Access, 150 capacity | Riverside Hall: no wheelchair access, 120 capacity</t>
         </is>
       </c>
-      <c r="J125" s="2" t="inlineStr">
+      <c r="J131" s="2" t="inlineStr">
         <is>
           <t>"Riverside Hall" is marked "Unsuitable", with both failing requirements named: "No wheelchair access" and "Capacity below 150"</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="n">
+    <row r="132">
+      <c r="A132" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>E06-S02</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
         <is>
           <t>E06-S02 - Scenario 3 (All requirements met)</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>TC_E06S02_03</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Verify that a venue meeting all recorded requirements for the event should be marked suitable</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>The event requires Theatre layout and a capacity of 100; "Riverside Hall" supports Theatre layout with capacity 150</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. View "Riverside Hall" in the context of this event</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr">
+      <c r="I132" s="2" t="inlineStr">
         <is>
           <t>Event requires: Theatre layout, 100 capacity | Riverside Hall: Theatre layout, 150 capacity</t>
         </is>
       </c>
-      <c r="J126" s="2" t="inlineStr">
+      <c r="J132" s="2" t="inlineStr">
         <is>
           <t>"Riverside Hall" is marked "Suitable"</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="n">
+    <row r="133">
+      <c r="A133" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>E06-S02</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
         <is>
           <t>E06-S02 - Scenario 4 (Unsuitable venue may still be requested)</t>
         </is>
       </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>TC_E06S02_04</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting a booking request for a venue marked unsuitable should still be accepted, with the unsuitability shown to Venue Staff</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>"Riverside Hall" is marked "Unsuitable" for the event (missing Wheelchair Access)</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Submit a booking request for "Riverside Hall" for this event anyway
   3. Log in as venue_staff_1@connectsphere.com and open the request</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr">
+      <c r="I133" s="2" t="inlineStr">
         <is>
           <t>Venue: Riverside Hall (marked Unsuitable)</t>
         </is>
       </c>
-      <c r="J127" s="2" t="inlineStr">
+      <c r="J133" s="2" t="inlineStr">
         <is>
           <t>The booking request is accepted (not blocked); venue_staff_1@connectsphere.com sees the unsuitability flag on the request when deciding
 ## E06-S03</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="n">
+    <row r="134">
+      <c r="A134" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>E06-S03</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
         <is>
           <t>E06-S03 - Scenario 1 (Request created as Pending)</t>
         </is>
       </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>TC_E06S03_01</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting a booking request for a event with no existing pending request should create it as Pending and notify Venue Staff</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>Request "Charity Run" has status "Approved"; its event has recorded requirements and no pending booking request</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open request "Charity Run"
@@ -7144,52 +7463,52 @@
   5. Check venue_staff_1@connectsphere.com's notifications</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr">
         <is>
           <t>Event: Charity Run | Venue: Riverside Hall</t>
         </is>
       </c>
-      <c r="J128" s="2" t="inlineStr">
+      <c r="J134" s="2" t="inlineStr">
         <is>
           <t>The booking request is created with status "Pending"; "Riverside Hall"'s calendar shows the requested period as Pending; venue_staff_1@connectsphere.com is notified</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="n">
+    <row r="135">
+      <c r="A135" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>E06-S03</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
         <is>
           <t>E06-S03 - Scenario 2 (First request moves event to Planning)</t>
         </is>
       </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>TC_E06S03_02</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting the first booking request for an Approved event should move its status to Planning</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has status "Approved" and has no venue booking requests yet</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Charity Run"
@@ -7197,259 +7516,259 @@
   4. Check the event's status</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr">
+      <c r="I135" s="2" t="inlineStr">
         <is>
           <t>Event: Charity Run (status: Approved, first booking request)</t>
         </is>
       </c>
-      <c r="J129" s="2" t="inlineStr">
+      <c r="J135" s="2" t="inlineStr">
         <is>
           <t>The event status changes from "Approved" to "Planning"</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="n">
+    <row r="136">
+      <c r="A136" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>E06-S03</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
         <is>
           <t>E06-S03 - Scenario 3 (Second request for same event blocked)</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>TC_E06S03_03</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting a second booking request for a event that already has a pending request should be blocked with the existing request identified</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>The event for "Charity Run" already has a pending booking request for "Riverside Hall"</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the same event of "Charity Run"
   3. Attempt to submit a second booking request for a different venue, "Grand Ballroom"</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr">
         <is>
           <t>Existing pending request: Riverside Hall | New attempted request: Grand Ballroom</t>
         </is>
       </c>
-      <c r="J130" s="2" t="inlineStr">
+      <c r="J136" s="2" t="inlineStr">
         <is>
           <t>Submission is blocked; the message identifies the existing pending request for "Riverside Hall" as the reason</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="n">
+    <row r="137">
+      <c r="A137" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>E06-S03</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
         <is>
           <t>E06-S03 - Scenario 4 (Venue taken by another event blocked)</t>
         </is>
       </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>TC_E06S03_04</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting a request for a venue already Pending or Confirmed for another event over the same period should be blocked with the conflict explained</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>Venue "Riverside Hall" is already Confirmed for event "Tech Conference 2026" on 15/01/2027</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Attempt to submit a booking request for "Riverside Hall" for a different event also on 15/01/2027</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr">
+      <c r="I137" s="2" t="inlineStr">
         <is>
           <t>Venue: Riverside Hall | Date: 15/01/2027 (already Confirmed for another event)</t>
         </is>
       </c>
-      <c r="J131" s="2" t="inlineStr">
+      <c r="J137" s="2" t="inlineStr">
         <is>
           <t>Submission is blocked with a message explaining that "Riverside Hall" is already committed to "Tech Conference 2026" for that period</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="n">
+    <row r="138">
+      <c r="A138" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>E06-S03</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
         <is>
           <t>E06-S03 (checklist: view status of own booking requests)</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>TC_E06S03_05</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Coordinator should be able to view the status of each of their own booking requests</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>coordinator_1@connectsphere.com has 2 booking requests: Riverside Hall (Pending) and Grand Ballroom (Confirmed)</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Navigate to "My Booking Requests"</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr">
         <is>
           <t>Requests: Riverside Hall (Pending), Grand Ballroom (Confirmed)</t>
         </is>
       </c>
-      <c r="J132" s="2" t="inlineStr">
+      <c r="J138" s="2" t="inlineStr">
         <is>
           <t>Both requests are listed with their correct current status: Riverside Hall = Pending, Grand Ballroom = Confirmed</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="n">
+    <row r="139">
+      <c r="A139" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>E06-S03</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
         <is>
           <t>E06-S03 — Scenario 5 (Request conflicts through the buffer)</t>
         </is>
       </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>4 - Negative (business rule)</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>TC_E06S03_06</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Verify that a booking request whose period overlaps another event's buffered window should be blocked with the buffered window named</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>Venue "Riverside Hall" has Turnaround time 45 and a Confirmed booking for "Charity Run" 15/01/2027 10:00-12:00; coordinator_2@connectsphere.com is signed in with Approved event "Alumni Dinner"</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>1. Open "Alumni Dinner" and start a venue booking request for "Riverside Hall"
   2. Enter 15/01/2027 12:30-14:00
   3. Submit</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr">
         <is>
           <t>Existing booking: 10:00-12:00, buffered to 12:45 | Request: 12:30-14:00</t>
         </is>
       </c>
-      <c r="J133" s="2" t="inlineStr">
+      <c r="J139" s="2" t="inlineStr">
         <is>
           <t>Submission is blocked; the message identifies "Charity Run" and its buffered window 09:30-12:45; no Pending request is created
 ## E06-S04</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="n">
+    <row r="140">
+      <c r="A140" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>E06-S04</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
         <is>
           <t>E06-S04 - Scenario 1 (Request approved and confirmed)</t>
         </is>
       </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>TC_E06S04_01</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Verify that approving a pending request for a venue that is free for the period should confirm the booking, update the calendar, and notify the Coordinator</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>Booking request for "Riverside Hall" (event "Charity Run") is Pending; the venue is free for the requested period</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>1. Log in as venue_staff_1@connectsphere.com
   2. Open the pending request for "Riverside Hall" / "Charity Run"
@@ -7457,52 +7776,52 @@
   4. Check "Riverside Hall"'s calendar and coordinator_1@connectsphere.com's notifications</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr">
         <is>
           <t>Request: Riverside Hall for Charity Run</t>
         </is>
       </c>
-      <c r="J134" s="2" t="inlineStr">
+      <c r="J140" s="2" t="inlineStr">
         <is>
           <t>The booking becomes "Confirmed"; the calendar shows the period as Confirmed; coordinator_1@connectsphere.com is notified of the approval</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="n">
+    <row r="141">
+      <c r="A141" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>E06-S04</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
         <is>
           <t>E06-S04 - Scenario 2 (Rejected with reason and alternative)</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>TC_E06S04_02</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Verify that rejecting a request with a recorded reason and a suggested alternative venue should notify the Coordinator with both, allowing them to amend without restarting the search</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>Booking request for "Small Room" (event "Product Expo 2026") is Pending</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>1. Log in as venue_staff_1@connectsphere.com
   2. Open the pending request for "Small Room"
@@ -7512,52 +7831,52 @@
   6. Log in as the assigned Coordinator and check the notification and request</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr">
+      <c r="I141" s="2" t="inlineStr">
         <is>
           <t>Rejection reason: "Capacity too small for expected attendance" | Suggested alternative: Riverside Hall</t>
         </is>
       </c>
-      <c r="J135" s="2" t="inlineStr">
+      <c r="J141" s="2" t="inlineStr">
         <is>
           <t>The Coordinator is notified with both the reason and the suggested alternative, and can amend the existing request directly to "Riverside Hall" without starting a new search</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
+    <row r="142">
+      <c r="A142" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>E06-S04</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
         <is>
           <t>E06-S04 - Scenario 3 (Rejection without reason blocked)</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>TC_E06S04_03</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to reject a request without recording a reason should be blocked</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>Booking request for "Riverside Hall" (event "Charity Run") is Pending</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>1. Log in as venue_staff_1@connectsphere.com
   2. Open the pending request
@@ -7566,156 +7885,156 @@
   5. Click "Confirm"</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr">
+      <c r="I142" s="2" t="inlineStr">
         <is>
           <t>Rejection reason: (blank)</t>
         </is>
       </c>
-      <c r="J136" s="2" t="inlineStr">
+      <c r="J142" s="2" t="inlineStr">
         <is>
           <t>The rejection is blocked with a message that a reason is required; the request remains Pending</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
+    <row r="143">
+      <c r="A143" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>E06-S04</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
         <is>
           <t>E06-S04 — Scenario 4 (Approval checks the buffered window)</t>
         </is>
       </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>4 - Negative (business rule)</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>TC_E06S04_04</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Verify that approving a request whose buffered window overlaps another confirmed booking's buffered window should be blocked even when the advertised times do not overlap</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>Venue "Riverside Hall" has Setup time 30 and Turnaround time 45; "Charity Run" is Confirmed 15/01/2027 10:00-12:00; a Pending request for "Alumni Dinner" 15/01/2027 12:30-14:00 was created before the buffers were set; venue_staff_1@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>1. Open the pending request for "Alumni Dinner"
   2. Click "Approve"</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr">
         <is>
           <t>Charity Run buffered: 09:30-12:45 | Alumni Dinner buffered: 12:00-14:45</t>
         </is>
       </c>
-      <c r="J137" s="2" t="inlineStr">
+      <c r="J143" s="2" t="inlineStr">
         <is>
           <t>Approval is blocked; "Charity Run" is identified as the conflicting booking with its buffered window; the request stays Pending
 ## E06-S05</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
+    <row r="144">
+      <c r="A144" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>E06-S05</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
         <is>
           <t>E06-S05 · Scenario 2 (Slot already held or booked)</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>4 - Negative (business rule)</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>TC_E06S05_01</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Verify that a second tentative hold on the same venue and period is refused</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>Orchid Hall has an active tentative hold for 2026-12-01 09:00 to 11:00 against event EVT-1005. Coordinator coord_b@connectsphere.com is planning event EVT-1006</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as coord_b@connectsphere.com
  2. Open the venue calendar for Orchid Hall on 2026-12-01
  3. Attempt to place a tentative hold for 09:00–11:00 against EVT-1006</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr">
         <is>
           <t>Existing hold: EVT-1005, 09:00–11:00 · Requested: EVT-1006, same period</t>
         </is>
       </c>
-      <c r="J138" s="2" t="inlineStr">
+      <c r="J144" s="2" t="inlineStr">
         <is>
           <t>The hold is refused and the existing hold against EVT-1005 is identified. The calendar continues to show the period as Tentative for one event only</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
+    <row r="145">
+      <c r="A145" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>E06-S05</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
         <is>
           <t>E06-S05 — Scenario 5 (Hold occupies the buffered window)</t>
         </is>
       </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>TC_E06S05_02</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Verify that a tentative hold should occupy the venue's buffered window so that an overlapping hold or request is refused</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>Venue "Riverside Hall" has Setup time 30 and Turnaround time 45 and is Free on 15/01/2027; coordinator_1@connectsphere.com and coordinator_2@connectsphere.com each have an Approved event</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>1. As coordinator_1, place a tentative hold on "Riverside Hall" for 15/01/2027 10:00-12:00
   2. Open the availability calendar for 15/01/2027
@@ -7723,363 +8042,363 @@
   4. As coordinator_2, attempt a booking request for "Riverside Hall" for 15/01/2027 13:15-14:00</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr">
+      <c r="I145" s="2" t="inlineStr">
         <is>
           <t>Hold: 10:00-12:00 (buffered 09:30-12:45) | Attempt A: 12:30-13:30 | Attempt B: 13:15-14:00 (buffered 12:45-14:45)</t>
         </is>
       </c>
-      <c r="J139" s="2" t="inlineStr">
+      <c r="J145" s="2" t="inlineStr">
         <is>
           <t>The calendar shows Tentative from 09:30 to 12:45 with the buffer portions marked; Attempt A is refused naming coordinator_1's hold; Attempt B is accepted because its own buffered window starts at exactly 12:45, when the hold's ends
 ## E06-S06</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="n">
+    <row r="146">
+      <c r="A146" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
         <is>
           <t>E06-S06 - Scenario 1 (Overlapping approval blocked)</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_01</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to approve a request that overlaps an existing confirmed booking for the same venue should be blocked with the conflicting booking identified</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>"Riverside Hall" has a confirmed booking for "Charity Run" on 15/01/2027, 09:00-17:00. A second pending request for "Riverside Hall" on 15/01/2027, 14:00-18:00 exists for event "Product Expo 2026"</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>1. Log in as venue_staff_1@connectsphere.com
   2. Open the pending request for "Product Expo 2026"
   3. Attempt to click "Approve"</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr">
+      <c r="I146" s="2" t="inlineStr">
         <is>
           <t>Existing confirmed booking: Charity Run, 15/01/2027 09:00-17:00 | Conflicting request: Product Expo 2026, 15/01/2027 14:00-18:00</t>
         </is>
       </c>
-      <c r="J140" s="2" t="inlineStr">
+      <c r="J146" s="2" t="inlineStr">
         <is>
           <t>Approval is blocked, and the message identifies the existing confirmed "Charity Run" booking as the conflict</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="n">
+    <row r="147">
+      <c r="A147" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
         <is>
           <t>E06-S06 - Scenario 2 (Competing request flagged)</t>
         </is>
       </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_02</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Verify that approving one of two pending requests for the same venue and overlapping times should flag the other as conflicting</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>Two pending requests exist for "Riverside Hall" on 20/01/2027, both 09:00-12:00: Request A ("Tech Conference 2026") and Request B ("Product Expo 2026")</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>1. Log in as venue_staff_1@connectsphere.com
   2. Approve Request A ("Tech Conference 2026")
   3. Open Request B ("Product Expo 2026")</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr">
         <is>
           <t>Request A: Tech Conference 2026 (approved) | Request B: Product Expo 2026 (same venue, overlapping time)</t>
         </is>
       </c>
-      <c r="J141" s="2" t="inlineStr">
+      <c r="J147" s="2" t="inlineStr">
         <is>
           <t>Request B is now flagged as conflicting and cannot be approved until the conflict is resolved</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="n">
+    <row r="148">
+      <c r="A148" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
         <is>
           <t>E06-S06 - Scenario 3 (Simultaneous approval fails safely)</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_03</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Verify that if another Venue Staff member approves a conflicting request moments earlier, a simultaneous approval attempt should fail safely and inform the user the venue has just been taken</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>Two pending requests exist for "Riverside Hall" on 25/01/2027, overlapping times. venue_staff_2@connectsphere.com approves one of them a moment before venue_staff_1@connectsphere.com processes the other</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>1. As venue_staff_2@connectsphere.com, approve Request A for "Riverside Hall" on 25/01/2027
   2. Immediately as venue_staff_1@connectsphere.com, attempt to approve the conflicting Request B for the same venue and overlapping time</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr">
         <is>
           <t>Request A approved by venue_staff_2@connectsphere.com just before venue_staff_1@connectsphere.com's attempt on Request B</t>
         </is>
       </c>
-      <c r="J142" s="2" t="inlineStr">
+      <c r="J148" s="2" t="inlineStr">
         <is>
           <t>venue_staff_1@connectsphere.com's approval attempt fails safely, with a message stating the venue has just been taken by another approval</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="n">
+    <row r="149">
+      <c r="A149" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>E06-S06 · Scenario 1 (Overlapping approval blocked)</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (adjacent, must not conflict)</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_04</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Verify that a booking beginning exactly when another ends is not treated as a conflict</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>Venue Orchid Hall has a confirmed booking for 2026-11-10 09:00:00 to 2026-11-10 11:00:00. A pending request exists for the same venue for 2026-11-10 11:00:00 to 2026-11-10 13:00:00</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Venue Staff
  2. Open the pending request for 11:00–13:00
  3. Approve it</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr">
         <is>
           <t>Existing: 09:00–11:00 · Requested: 11:00–13:00 · Shared boundary: 11:00</t>
         </is>
       </c>
-      <c r="J143" s="2" t="inlineStr">
+      <c r="J149" s="2" t="inlineStr">
         <is>
           <t>The approval succeeds and both bookings show as Confirmed on the venue calendar. Ranges are half-open, so touching at the boundary is not an overlap</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="n">
+    <row r="150">
+      <c r="A150" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t>E06-S06 · Scenario 1 (Overlapping approval blocked)</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (one minute of overlap, must conflict)</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_05</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Verify that a booking overlapping an existing one by a single minute is blocked</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>Venue Orchid Hall has a confirmed booking for 2026-11-10 09:00:00 to 2026-11-10 11:00:00. A pending request exists for the same venue for 2026-11-10 10:59:00 to 2026-11-10 13:00:00</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Venue Staff
  2. Open the pending request for 10:59–13:00
  3. Attempt to approve it</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr">
         <is>
           <t>Existing: 09:00–11:00 · Requested: 10:59–13:00 · Overlap: 1 minute</t>
         </is>
       </c>
-      <c r="J144" s="2" t="inlineStr">
+      <c r="J150" s="2" t="inlineStr">
         <is>
           <t>Approval is blocked and the conflicting 09:00–11:00 booking is identified. The venue never holds two confirmed bookings over the same period</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="n">
+    <row r="151">
+      <c r="A151" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
         <is>
           <t>E06-S06 — Scenario 4 (Buffered windows are what must not overlap)</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>3 - Integration / regression</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_06</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Verify that two approvals whose advertised times do not overlap but whose buffered windows do should let at most one succeed when processed at the same moment</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>Venue "Riverside Hall" has Setup time 30 and Turnaround time 45; two Pending requests exist on it for 15/01/2027: "Charity Run" 10:00-12:00 and "Alumni Dinner" 12:30-14:00; two Venue Staff accounts are signed in; TEST_DATABASE_URL points at the disposable test schema</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>1. Trigger approval of both requests concurrently (integration test issues both approvals in parallel transactions)
   2. Read back both bookings and the venue calendar</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr">
         <is>
           <t>Charity Run buffered: 09:30-12:45 | Alumni Dinner buffered: 12:00-14:45 (advertised times do not overlap; buffered windows overlap 12:00-12:45)</t>
         </is>
       </c>
-      <c r="J145" s="2" t="inlineStr">
+      <c r="J151" s="2" t="inlineStr">
         <is>
           <t>Exactly one booking is Confirmed; the other approval fails with the conflict identified and its request remains Pending; the database exclusion constraint rejected the second write on the buffered range (ADR-003), so TC_E06S06_04 (adjacent, must not conflict) and TC_E06S06_05 (one minute of overlap) continue to hold on buffered windows</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="n">
+    <row r="152">
+      <c r="A152" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t>E07-S01 - Scenario 1 (Item added and reservable)</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>TC_E07S01_01</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Verify that saving a new equipment item with its full details should make it available for reservation</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>tech_support_1@connectsphere.com is signed in; equipment item "Wireless Microphone" does not yet exist</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to "Add Equipment"
   2. Enter Type: "Wireless Microphone", Description: "Handheld, UHF", Quantity: 10, Location: "Main Storage", Operational Status: "Working"
@@ -8087,52 +8406,52 @@
   4. Log in as an Event Coordinator and check equipment availability for "Wireless Microphone"</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr">
         <is>
           <t>Item: Wireless Microphone | Quantity: 10 | Location: Main Storage | Status: Working</t>
         </is>
       </c>
-      <c r="J146" s="2" t="inlineStr">
+      <c r="J152" s="2" t="inlineStr">
         <is>
           <t>The item is saved and appears as available for reservation, with 10 units free</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="n">
+    <row r="153">
+      <c r="A153" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
         <is>
           <t>E07-S01 - Scenario 2 (Quantity drop flags reservations)</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>TC_E07S01_02</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Verify that reducing an item's quantity below the amount already reserved for upcoming events should flag the affected reservations and notify the relevant Coordinators</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>"Wireless Microphone" (quantity 10) has 6 units reserved for an upcoming event of "Tech Conference 2026", assigned to coordinator_1@connectsphere.com</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "Wireless Microphone"
@@ -8140,52 +8459,52 @@
   4. Save</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr">
         <is>
           <t>Quantity: 10 -&gt; 4 | Existing reservation: 6 units</t>
         </is>
       </c>
-      <c r="J147" s="2" t="inlineStr">
+      <c r="J153" s="2" t="inlineStr">
         <is>
           <t>The 6-unit reservation is flagged for review since it now exceeds total stock, and coordinator_1@connectsphere.com is notified</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="n">
+    <row r="154">
+      <c r="A154" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
         <is>
           <t>E07-S01 - Scenario 3 (Item retired)</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>TC_E07S01_03</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Verify that retiring an item with no future reservations should remove it from availability checks while retaining its past reservations</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>Equipment item "Old Projector" has no future reservations; it has 2 past (completed) reservations on record</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "Old Projector"
@@ -8194,52 +8513,52 @@
   5. Check availability for "Old Projector" as an Event Coordinator</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr">
         <is>
           <t>Item: Old Projector (no future reservations)</t>
         </is>
       </c>
-      <c r="J148" s="2" t="inlineStr">
+      <c r="J154" s="2" t="inlineStr">
         <is>
           <t>"Old Projector" no longer appears in availability checks; its 2 past reservations remain retained and viewable in historical records</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="n">
+    <row r="155">
+      <c r="A155" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
         <is>
           <t>E07-S01 (checklist: update equipment attributes)</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>TC_E07S01_04</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Verify that updating an existing equipment item's attributes should save the changes</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>Equipment item "Wireless Microphone" exists with Location: "Main Storage"</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "Wireless Microphone"
@@ -8247,53 +8566,53 @@
   4. Click "Save"</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr">
         <is>
           <t>Location: Main Storage -&gt; Annex Storage</t>
         </is>
       </c>
-      <c r="J149" s="2" t="inlineStr">
+      <c r="J155" s="2" t="inlineStr">
         <is>
           <t>The updated Location value is saved and shown when the item record is reopened
 ## E07-S02</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="n">
+    <row r="156">
+      <c r="A156" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
         <is>
           <t>E07-S02 - Scenario 1 (Equipment recorded against an event)</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>TC_E07S02_01</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Verify that adding equipment items with quantities to a event of an approved event should save the request and notify Technical Support Staff</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" is Approved; the event has no equipment requested yet</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the event of "Tech Conference 2026"
@@ -8302,52 +8621,52 @@
   5. Check tech_support_1@connectsphere.com's notifications</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr">
         <is>
           <t>the event equipment: Wireless Microphone x2, Projector x1</t>
         </is>
       </c>
-      <c r="J150" s="2" t="inlineStr">
+      <c r="J156" s="2" t="inlineStr">
         <is>
           <t>The equipment request is saved against the event, and tech_support_1@connectsphere.com is notified</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="n">
+    <row r="157">
+      <c r="A157" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
         <is>
           <t>E07-S02 - Scenario 2 (Request exceeds total stock)</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>TC_E07S02_02</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Verify that requesting more of an item than ConnectSphere owns in total should warn that the request cannot be met from existing stock</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>"Wireless Microphone" has a total stock of 10 units</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open a event of "Tech Conference 2026"
@@ -8355,52 +8674,52 @@
   4. Save</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr">
         <is>
           <t>Requested quantity: 15 | Total stock: 10</t>
         </is>
       </c>
-      <c r="J151" s="2" t="inlineStr">
+      <c r="J157" s="2" t="inlineStr">
         <is>
           <t>A warning is shown that the request (15 units) cannot be met from existing stock (10 units)</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="n">
+    <row r="158">
+      <c r="A158" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
         <is>
           <t>E07-S02 - Scenario 3 (Events independent of each other)</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>TC_E07S02_03</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Verify that recording equipment for one event should leave a different event's equipment unaffected</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>Coordinator coordinator_1@connectsphere.com manages two separate events, "Tech Conference 2026" and "Charity Run", neither with equipment requested yet</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open "Tech Conference 2026" and add "Projector" x 1
@@ -8408,52 +8727,52 @@
   4. Open "Charity Run" and check its equipment list</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr">
         <is>
           <t>"Tech Conference 2026": Projector x1 added | "Charity Run": unchanged</t>
         </is>
       </c>
-      <c r="J152" s="2" t="inlineStr">
+      <c r="J158" s="2" t="inlineStr">
         <is>
           <t>"Tech Conference 2026" shows "Projector x1"; "Charity Run"'s equipment list remains empty, unaffected by the other event's request</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="n">
+    <row r="159">
+      <c r="A159" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
         <is>
           <t>E07-S02 (checklist: amend or remove equipment request before reservation)</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>TC_E07S02_04</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Verify that amending or removing an equipment request before it is reserved should update or clear the request accordingly</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" has an unreserved equipment request: "Wireless Microphone" x 2</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the event's equipment request
@@ -8462,208 +8781,208 @@
   5. Save</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr">
         <is>
           <t>Quantity change: 2 -&gt; 3, then removed entirely</t>
         </is>
       </c>
-      <c r="J153" s="2" t="inlineStr">
+      <c r="J159" s="2" t="inlineStr">
         <is>
           <t>After step 3, the request shows "Wireless Microphone x3"; after step 5, the request no longer includes "Wireless Microphone"
 ## E07-S03</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="n">
+    <row r="160">
+      <c r="A160" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
         <is>
           <t>E07-S03 - Scenario 1 (Reserved and faulty stock excluded)</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>TC_E07S03_01</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Verify that checking availability for a period with other reservations should exclude those reservations and any damaged or under-maintenance items from the free quantity</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>"Wireless Microphone" has total stock 10; 3 units are reserved for another event on 15/11/2026, 09:00-12:00; 2 units are marked damaged</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Check availability for "Wireless Microphone" on 15/11/2026, 09:00-12:00</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr">
         <is>
           <t>Total stock: 10 | Reserved: 3 | Damaged: 2</t>
         </is>
       </c>
-      <c r="J154" s="2" t="inlineStr">
+      <c r="J160" s="2" t="inlineStr">
         <is>
           <t>The free quantity shown is 5 (10 minus 3 reserved minus 2 damaged)</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="n">
+    <row r="161">
+      <c r="A161" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
         <is>
           <t>E07-S03 - Scenario 2 (Location does not affect availability)</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>TC_E07S03_02</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Verify that an item free for the requested date and time but located at another venue should still be shown as available, with no transport allowance applied</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>"Projector" is free for 15/11/2026, 09:00-12:00, but is currently located at "Grand Ballroom" rather than the requested venue</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Check availability for "Projector" on 15/11/2026, 09:00-12:00 for a event at "Riverside Hall"</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr">
         <is>
           <t>Item location: Grand Ballroom | Requested venue: Riverside Hall</t>
         </is>
       </c>
-      <c r="J155" s="2" t="inlineStr">
+      <c r="J161" s="2" t="inlineStr">
         <is>
           <t>"Projector" is shown as available with its full free quantity; no transport time or allowance is added to the availability check</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="n">
+    <row r="162">
+      <c r="A162" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
         <is>
           <t>E07-S03 - Scenario 3 (Non-overlapping events share an item)</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>TC_E07S03_03</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Verify that two events requiring the same item at non-overlapping times on the same day should both show it as free</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>"Tech Conference 2026" the event (09:00-12:00) and the event (14:00-17:00) both require "Wireless Microphone", with no other reservations that day</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Check availability for "Wireless Microphone" during the event's time (09:00-12:00)
   3. Check availability for "Wireless Microphone" during the event's time (14:00-17:00)</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr">
         <is>
           <t>the event: 09:00-12:00 | the event: 14:00-17:00 (same day, non-overlapping)</t>
         </is>
       </c>
-      <c r="J156" s="2" t="inlineStr">
+      <c r="J162" s="2" t="inlineStr">
         <is>
           <t>"Wireless Microphone" shows its full free quantity for both the event's and the event's time windows
 ## E07-S04</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="n">
+    <row r="163">
+      <c r="A163" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
         <is>
           <t>E07-S04 - Scenario 1 (Full reservation recorded)</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_01</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Verify that reserving the requested quantity when sufficient equipment is free should record the reservation and notify the Event Coordinator</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" requested "Wireless Microphone" x 2; 5 units are free for that period</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the equipment request for the event
@@ -8672,52 +8991,52 @@
   5. Check coordinator_1@connectsphere.com's notifications</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr">
         <is>
           <t>Reserved: Wireless Microphone x2 (5 free)</t>
         </is>
       </c>
-      <c r="J157" s="2" t="inlineStr">
+      <c r="J163" s="2" t="inlineStr">
         <is>
           <t>The reservation is recorded against the event, and coordinator_1@connectsphere.com receives a confirmation showing the event's date/time, item, and quantity</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="n">
+    <row r="164">
+      <c r="A164" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
         <is>
           <t>E07-S04 - Scenario 2 (Partial reservation and shortfall)</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_02</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Verify that recording a partial reservation when only part of the requested quantity is free should notify the Coordinator of the shortfall</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" requested "Projector" x 3; only 2 units are free for that period</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the equipment request for the event
@@ -8725,103 +9044,103 @@
   4. Confirm</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr">
         <is>
           <t>Requested: 3 | Reserved (partial): 2 | Shortfall: 1</t>
         </is>
       </c>
-      <c r="J158" s="2" t="inlineStr">
+      <c r="J164" s="2" t="inlineStr">
         <is>
           <t>coordinator_1@connectsphere.com is notified of the shortfall, showing 2 reserved and 1 outstanding unit of "Projector"</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="n">
+    <row r="165">
+      <c r="A165" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
         <is>
           <t>E07-S04 - Scenario 3 (Fully committed item shows nothing free)</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_03</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Verify that once an item becomes fully committed, a subsequent availability check for that period should show no free quantity</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>"Portable Stage" (total stock 2) has both units fully reserved for the period 20/11/2026, 09:00-17:00</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Check availability for "Portable Stage" on 20/11/2026, 09:00-17:00</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr">
+      <c r="I165" s="2" t="inlineStr">
         <is>
           <t>Portable Stage: 2 total, 2 reserved</t>
         </is>
       </c>
-      <c r="J159" s="2" t="inlineStr">
+      <c r="J165" s="2" t="inlineStr">
         <is>
           <t>The availability check shows 0 free units of "Portable Stage" for that period</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="n">
+    <row r="166">
+      <c r="A166" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
         <is>
           <t>E07-S04 - Scenario 4 (Reservation released)</t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_04</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Verify that releasing a reservation when a event is cancelled or the equipment is no longer required should return the quantity to the available pool</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" has a reservation of "Wireless Microphone" x 2</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the reservation for the event
@@ -8830,52 +9149,52 @@
   5. Check availability for "Wireless Microphone" for that period</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr">
+      <c r="I166" s="2" t="inlineStr">
         <is>
           <t>Released reservation: Wireless Microphone x2</t>
         </is>
       </c>
-      <c r="J160" s="2" t="inlineStr">
+      <c r="J166" s="2" t="inlineStr">
         <is>
           <t>The 2 units are returned to the available pool, increasing the free quantity for that period by 2</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="n">
+    <row r="167">
+      <c r="A167" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
         <is>
           <t>E07-S04 · Scenario 1 (Full reservation recorded)</t>
         </is>
       </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (just below)</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_05</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Verify that requesting one fewer than the free quantity produces a full reservation and leaves the remainder free</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>Equipment Projector-HD has total quantity 10. Six units are reserved for other events overlapping EVT-1003, leaving 4 free. Event EVT-1003 has an equipment request for 3 units</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Technical Support Staff
  2. Open the equipment request for EVT-1003
@@ -8883,52 +9202,52 @@
  4. Re-check availability for the same period</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr">
+      <c r="I167" s="2" t="inlineStr">
         <is>
           <t>Free quantity: 4 · Requested: 3</t>
         </is>
       </c>
-      <c r="J161" s="2" t="inlineStr">
+      <c r="J167" s="2" t="inlineStr">
         <is>
           <t>A reservation of 3 is recorded with status Reserved, not Partial. Availability for the period now shows 1 free. Confirmation of the event is not blocked by this reservation</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="n">
+    <row r="168">
+      <c r="A168" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
         <is>
           <t>E07-S04 · Scenario 1 (Full reservation recorded)</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_06</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Verify that requesting exactly the free quantity produces a full reservation and leaves nothing free</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>Equipment Projector-HD has total quantity 10. Six units are reserved for other events overlapping EVT-1003, leaving 4 free. Event EVT-1003 has an equipment request for 4 units</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Technical Support Staff
  2. Open the equipment request for EVT-1003
@@ -8936,52 +9255,52 @@
  4. Re-check availability for the same period</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr">
+      <c r="I168" s="2" t="inlineStr">
         <is>
           <t>Free quantity: 4 · Requested: 4</t>
         </is>
       </c>
-      <c r="J162" s="2" t="inlineStr">
+      <c r="J168" s="2" t="inlineStr">
         <is>
           <t>A reservation of 4 is recorded with status Reserved. Availability for the period shows 0 free. No shortfall notification is sent</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="n">
+    <row r="169">
+      <c r="A169" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
         <is>
           <t>E07-S04 · Scenario 2 (Partial reservation and shortfall) · E08-S03 Scenario 3</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (just above)</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_07</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Verify that requesting one more than the free quantity produces a partial reservation that blocks confirmation</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>Equipment Projector-HD has total quantity 10. Six units are reserved for other events overlapping EVT-1003, leaving 4 free. Event EVT-1003 has an equipment request for 5 units. Event EVT-1003 already has a confirmed venue booking</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Technical Support Staff
  2. Open the equipment request for EVT-1003
@@ -8989,53 +9308,53 @@
  4. Sign in as the assigned Event Coordinator and attempt to confirm the event</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr">
+      <c r="I169" s="2" t="inlineStr">
         <is>
           <t>Free quantity: 4 · Requested: 5 · Reserved: 4 · Outstanding: 1</t>
         </is>
       </c>
-      <c r="J163" s="2" t="inlineStr">
+      <c r="J169" s="2" t="inlineStr">
         <is>
           <t>The reservation is recorded with status Partial. The Coordinator is notified of an outstanding quantity of 1. Confirmation is blocked and the outstanding item is listed against event EVT-1003
 ## E07-S05</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="n">
+    <row r="170">
+      <c r="A170" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
         <is>
           <t>E07-S05 - Scenario 1 (Item marked unavailable)</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>TC_E07S05_01</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Verify that marking an item with no reservations in the period unavailable, with a reason and a period, should exclude it from availability checks for that period</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t>Equipment item "HD Camera" has no reservations between 01/12/2026 and 05/12/2026</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "HD Camera"
@@ -9045,52 +9364,52 @@
   6. Check availability for "HD Camera" on 03/12/2026</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr">
+      <c r="I170" s="2" t="inlineStr">
         <is>
           <t>Period: 01/12/2026-05/12/2026 | Reason: Sensor repair</t>
         </is>
       </c>
-      <c r="J164" s="2" t="inlineStr">
+      <c r="J170" s="2" t="inlineStr">
         <is>
           <t>"HD Camera" shows 0 available units for any date within 01/12/2026-05/12/2026</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="n">
+    <row r="171">
+      <c r="A171" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
         <is>
           <t>E07-S05 - Scenario 2 (Reserved item flags its events)</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>TC_E07S05_02</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Verify that marking an item unavailable while it is reserved for an upcoming event should flag the affected event and notify its Coordinator</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>"HD Camera" is reserved for an upcoming event of "Tech Conference 2026", assigned to coordinator_1@connectsphere.com</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "HD Camera"
@@ -9098,52 +9417,52 @@
   4. Save</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr">
+      <c r="I171" s="2" t="inlineStr">
         <is>
           <t>Affected event: Tech Conference 2026 event with HD Camera reserved</t>
         </is>
       </c>
-      <c r="J165" s="2" t="inlineStr">
+      <c r="J171" s="2" t="inlineStr">
         <is>
           <t>The affected event is flagged, and coordinator_1@connectsphere.com is notified that its reserved "HD Camera" is now unavailable</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="n">
+    <row r="172">
+      <c r="A172" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
         <is>
           <t>E07-S05 (checklist: return item to service)</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>TC_E07S05_03</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Verify that returning an item to service should restore it to availability checks</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>"HD Camera" is currently marked unavailable for 01/12/2026-05/12/2026 with reason "Sensor repair"</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "HD Camera"
@@ -9152,53 +9471,53 @@
   5. Check availability for "HD Camera" on 03/12/2026</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr">
+      <c r="I172" s="2" t="inlineStr">
         <is>
           <t>Item: HD Camera (returning to service)</t>
         </is>
       </c>
-      <c r="J166" s="2" t="inlineStr">
+      <c r="J172" s="2" t="inlineStr">
         <is>
           <t>"HD Camera" now shows as available again for 03/12/2026
 ## E07-S06</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="n">
+    <row r="173">
+      <c r="A173" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
         <is>
           <t>E07-S06 - Scenario 1 (Support request recorded)</t>
         </is>
       </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>TC_E07S06_01</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting a technical support request describing the support needed and the times should notify Technical Support Staff and record it against the event</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" requires on-site technical support</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the event of "Tech Conference 2026"
@@ -9208,104 +9527,104 @@
   6. Check tech_support_1@connectsphere.com's notifications</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr">
+      <c r="I173" s="2" t="inlineStr">
         <is>
           <t>Support description: "1 AV technician for the full event" | Times: 09:00-12:00</t>
         </is>
       </c>
-      <c r="J167" s="2" t="inlineStr">
+      <c r="J173" s="2" t="inlineStr">
         <is>
           <t>The request is recorded against the event, and tech_support_1@connectsphere.com is notified</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="n">
+    <row r="174">
+      <c r="A174" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
         <is>
           <t>E07-S06 - Scenario 2 (Request accepted before venue confirmed)</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>TC_E07S06_02</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting a technical support request before the venue is confirmed should be accepted and reviewed alongside venue identification</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" does not yet have a confirmed venue</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the event of "Tech Conference 2026" (no confirmed venue)
   3. Submit a technical support request describing "1 sound technician" for the event's planned times</t>
         </is>
       </c>
-      <c r="I168" s="2" t="inlineStr">
+      <c r="I174" s="2" t="inlineStr">
         <is>
           <t>the event: no confirmed venue yet</t>
         </is>
       </c>
-      <c r="J168" s="2" t="inlineStr">
+      <c r="J174" s="2" t="inlineStr">
         <is>
           <t>The technical support request is accepted and recorded, without waiting for the venue to be confirmed first</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="n">
+    <row r="175">
+      <c r="A175" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
         <is>
           <t>E07-S06 - Scenario 3 (Event marked as needing none)</t>
         </is>
       </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>TC_E07S06_03</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Verify that marking a event as needing no technical support should create no request and not block confirmation on staff assignment</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>A event of "Charity Run" needs no on-site technical support</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the event of "Charity Run"
@@ -9313,53 +9632,53 @@
   4. Save</t>
         </is>
       </c>
-      <c r="I169" s="2" t="inlineStr">
+      <c r="I175" s="2" t="inlineStr">
         <is>
           <t>Event: Charity Run's event | Technical Support: Not Required</t>
         </is>
       </c>
-      <c r="J169" s="2" t="inlineStr">
+      <c r="J175" s="2" t="inlineStr">
         <is>
           <t>No technical support request is created for the event, and later event confirmation is not blocked waiting for a staff assignment
 ## E07-S07</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="n">
+    <row r="176">
+      <c r="A176" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
         <is>
           <t>E07-S07 - Scenario 1 (Available colleague assigned)</t>
         </is>
       </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_01</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Verify that a colleague with no conflicting assignment during the event's required time period should be successfully assigned</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" (09:00-12:00) has an open technical support request. tech_support_2@connectsphere.com has no assignment overlapping 09:00-12:00 on that date</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the technical support request for the event
@@ -9367,155 +9686,155 @@
   4. Confirm</t>
         </is>
       </c>
-      <c r="I170" s="2" t="inlineStr">
+      <c r="I176" s="2" t="inlineStr">
         <is>
           <t>Assignee: tech_support_2@connectsphere.com | Event time: 09:00-12:00</t>
         </is>
       </c>
-      <c r="J170" s="2" t="inlineStr">
+      <c r="J176" s="2" t="inlineStr">
         <is>
           <t>The assignment succeeds; tech_support_2@connectsphere.com is notified and the assignment appears on their schedule</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="n">
+    <row r="177">
+      <c r="A177" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
         <is>
           <t>E07-S07 (checklist: see assignment on schedule)</t>
         </is>
       </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_02</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Verify that the assignment should be reflected on the assigned staff member's schedule once made</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>tech_support_2@connectsphere.com has just been assigned to the event of "Tech Conference 2026" (09:00-12:00)</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_2@connectsphere.com
   2. Open "My Schedule"</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr">
+      <c r="I177" s="2" t="inlineStr">
         <is>
           <t>Assignment: the event, Tech Conference 2026, 09:00-12:00</t>
         </is>
       </c>
-      <c r="J171" s="2" t="inlineStr">
+      <c r="J177" s="2" t="inlineStr">
         <is>
           <t>The schedule shows the assignment to the event of "Tech Conference 2026" at 09:00-12:00</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="n">
+    <row r="178">
+      <c r="A178" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
         <is>
           <t>E07-S07 - Scenario 2 (Overlapping assignment blocked)</t>
         </is>
       </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_03</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>Verify that assigning a colleague who has an overlapping assignment should be blocked, with the conflicting event identified</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>tech_support_2@connectsphere.com is already assigned to a event of "Charity Run" from 10:00-13:00 on the same date. the event of "Tech Conference 2026" runs 09:00-12:00 on that date and needs a technician assigned</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the technical support request for the event of "Tech Conference 2026"
   3. Attempt to assign tech_support_2@connectsphere.com</t>
         </is>
       </c>
-      <c r="I172" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr">
         <is>
           <t>Existing assignment: Charity Run event, 10:00-13:00 | New attempted assignment: Tech Conference 2026 the event, 09:00-12:00 (overlaps)</t>
         </is>
       </c>
-      <c r="J172" s="2" t="inlineStr">
+      <c r="J178" s="2" t="inlineStr">
         <is>
           <t>The assignment is blocked, and the message identifies the conflicting "Charity Run" event as the reason</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="n">
+    <row r="179">
+      <c r="A179" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
         <is>
           <t>E07-S07 - Scenario 3 (Assignment removed)</t>
         </is>
       </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_04</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Verify that removing an existing assignment from a staff member's schedule should free up that slot</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>tech_support_2@connectsphere.com is assigned to the event of "Tech Conference 2026"</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the assignment for the event
@@ -9524,104 +9843,104 @@
   5. Check tech_support_2@connectsphere.com's schedule</t>
         </is>
       </c>
-      <c r="I173" s="2" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr">
         <is>
           <t>Assignment removed: tech_support_2@connectsphere.com, the event</t>
         </is>
       </c>
-      <c r="J173" s="2" t="inlineStr">
+      <c r="J179" s="2" t="inlineStr">
         <is>
           <t>The assignment no longer appears on tech_support_2@connectsphere.com's schedule, and the slot is free for reassignment</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="n">
+    <row r="180">
+      <c r="A180" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t>E07-S07 - Scenario 4 (Replacement assigned under same check)</t>
         </is>
       </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_05</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>Verify that assigning a replacement colleague after removing an assignment should be subject to the same conflict check used for new assignments</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>The assignment for the event of "Tech Conference 2026" has just been removed from tech_support_2@connectsphere.com. tech_support_3@connectsphere.com already has a conflicting assignment during the event's time</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the now-unassigned technical support request for the event
   3. Attempt to assign tech_support_3@connectsphere.com as a replacement</t>
         </is>
       </c>
-      <c r="I174" s="2" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr">
         <is>
           <t>Replacement candidate: tech_support_3@connectsphere.com (has a conflicting assignment)</t>
         </is>
       </c>
-      <c r="J174" s="2" t="inlineStr">
+      <c r="J180" s="2" t="inlineStr">
         <is>
           <t>The replacement assignment is blocked using the same conflict check as a new assignment, with the conflicting event identified</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="n">
+    <row r="181">
+      <c r="A181" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>E07-S07 (checklist: staff notified when assigned or removed)</t>
         </is>
       </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting (notification consistency)</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_06</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>Verify that the assigned staff member should receive a notification when they are assigned to, or removed from, an event</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>tech_support_2@connectsphere.com is about to be assigned to, and later removed from, the event of "Tech Conference 2026"</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>1. As tech_support_1@connectsphere.com, assign tech_support_2@connectsphere.com to the event
   2. Check tech_support_2@connectsphere.com's notifications
@@ -9629,52 +9948,52 @@
   4. Check tech_support_2@connectsphere.com's notifications again</t>
         </is>
       </c>
-      <c r="I175" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr">
         <is>
           <t>Actions: assign, then remove</t>
         </is>
       </c>
-      <c r="J175" s="2" t="inlineStr">
+      <c r="J181" s="2" t="inlineStr">
         <is>
           <t>tech_support_2@connectsphere.com receives a notification for the assignment, and a separate notification for the removal</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="n">
+    <row r="182">
+      <c r="A182" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>E08-S03 - Scenario 1 (All arrangements complete, event confirmed)</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>TC_E08S03_01</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>Verify that confirming an event where every event has a confirmed venue and full equipment reservation should set its status to Confirmed and notify the Organiser</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has one event with a confirmed venue booking (Riverside Hall) and its full requested equipment reserved, and requires no technical support</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Charity Run"
@@ -9682,260 +10001,260 @@
   4. Check the status and organiser_a@clienta.com's notifications</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr">
         <is>
           <t>Event: Charity Run (venue confirmed, equipment fully reserved, no tech support needed)</t>
         </is>
       </c>
-      <c r="J176" s="2" t="inlineStr">
+      <c r="J182" s="2" t="inlineStr">
         <is>
           <t>The status becomes "Confirmed", and organiser_a@clienta.com is notified with the confirmed details</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="n">
+    <row r="183">
+      <c r="A183" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>E08-S03 - Scenario 2 (Missing venue blocks confirmation)</t>
         </is>
       </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>TC_E08S03_02</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to confirm an event while a event is missing a confirmed venue should be blocked with the outstanding event named</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has the event with a confirmed venue, but the event has no confirmed venue yet</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Tech Conference 2026"
   3. Click "Confirm Event"</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr">
         <is>
           <t>the event: venue confirmed | the event: no venue</t>
         </is>
       </c>
-      <c r="J177" s="2" t="inlineStr">
+      <c r="J183" s="2" t="inlineStr">
         <is>
           <t>Confirmation is blocked; the message lists "the event" as missing a confirmed venue</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="n">
+    <row r="184">
+      <c r="A184" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>E08-S03 - Scenario 3 (Partial equipment blocks confirmation)</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>TC_E08S03_03</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to confirm an event while a event has only a partial equipment reservation should be blocked with the outstanding quantity shown</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has all events with confirmed venues, but the event's "Projector" reservation is partial (2 of 3 requested)</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Tech Conference 2026"
   3. Click "Confirm Event"</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr">
         <is>
           <t>the event: Projector reserved 2 of 3 requested</t>
         </is>
       </c>
-      <c r="J178" s="2" t="inlineStr">
+      <c r="J184" s="2" t="inlineStr">
         <is>
           <t>Confirmation is blocked; the message shows the event's outstanding quantity of 1 "Projector" unit</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="n">
+    <row r="185">
+      <c r="A185" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
         <is>
           <t>E08-S03 - Scenario 5 (Outstanding support assignment blocks confirmation)</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>TC_E08S03_04</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to confirm an event while a event's requested technical support has no staff assigned should be blocked</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>All events of "Tech Conference 2026" have confirmed venues and full equipment, but the event's technical support request has no staff assigned</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Tech Conference 2026"
   3. Click "Confirm Event"</t>
         </is>
       </c>
-      <c r="I179" s="2" t="inlineStr">
+      <c r="I185" s="2" t="inlineStr">
         <is>
           <t>the event: technical support requested, no staff assigned</t>
         </is>
       </c>
-      <c r="J179" s="2" t="inlineStr">
+      <c r="J185" s="2" t="inlineStr">
         <is>
           <t>Confirmation is blocked due to the event's outstanding technical support assignment</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="n">
+    <row r="186">
+      <c r="A186" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>E08-S03 - Scenario 6 (Organiser sees confirmed arrangements)</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>TC_E08S03_05</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>Verify that once an event is confirmed, the Organiser should see the confirmed venue, date, time and arrangements for every event</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has just been confirmed, with venue Riverside Hall, date 15/01/2027, time 09:00-17:00</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the confirmed event "Charity Run"</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr">
+      <c r="I186" s="2" t="inlineStr">
         <is>
           <t>Confirmed venue: Riverside Hall | Date: 15/01/2027 | Time: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J180" s="2" t="inlineStr">
+      <c r="J186" s="2" t="inlineStr">
         <is>
           <t>The Organiser sees the confirmed venue (Riverside Hall), date (15/01/2027), time (09:00-17:00), and full arrangements for the event
 ## E08-S04</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="n">
+    <row r="187">
+      <c r="A187" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C187" s="2" t="inlineStr">
         <is>
           <t>E08-S04 - Scenario 1 (Reverted with a recorded reason)</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>TC_E08S04_01</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>Verify that reverting a Confirmed event to Planning with a recorded reason should update its status and notify the Organiser with the reason</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>Event "Leadership Summit" has status "Confirmed"</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Leadership Summit"
@@ -9944,52 +10263,52 @@
   5. Confirm</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr">
+      <c r="I187" s="2" t="inlineStr">
         <is>
           <t>Reason: "Venue reported a plumbing issue"</t>
         </is>
       </c>
-      <c r="J181" s="2" t="inlineStr">
+      <c r="J187" s="2" t="inlineStr">
         <is>
           <t>The status changes to "Planning", and organiser_a@clienta.com is notified with the reason "Venue reported a plumbing issue"</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="n">
+    <row r="188">
+      <c r="A188" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C188" s="2" t="inlineStr">
         <is>
           <t>E08-S04 - Scenario 2 (Registered Attendees notified)</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>TC_E08S04_02</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>Verify that reverting a Confirmed event with registered Attendees should notify them that arrangements are being revised</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr">
         <is>
           <t>Event "Leadership Summit" has status "Confirmed" with attendee_a@example.com registered</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Leadership Summit"
@@ -9997,413 +10316,413 @@
   4. Check attendee_a@example.com's notifications</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr">
+      <c r="I188" s="2" t="inlineStr">
         <is>
           <t>Registered Attendee: attendee_a@example.com</t>
         </is>
       </c>
-      <c r="J182" s="2" t="inlineStr">
+      <c r="J188" s="2" t="inlineStr">
         <is>
           <t>attendee_a@example.com receives a notification that arrangements for "Leadership Summit" are being revised</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="n">
+    <row r="189">
+      <c r="A189" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C189" s="2" t="inlineStr">
         <is>
           <t>E08-S04 - Scenario 3 (No automatic reversion)</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>TC_E08S04_03</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>Verify that an arrangement breaking on a Confirmed event should not automatically revert its status; the affected arrangement should instead be flagged</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr">
         <is>
           <t>Event "Leadership Summit" has status "Confirmed"; its venue booking has just been flagged due to a broken arrangement, but no one has reverted the event</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Leadership Summit"
   3. Check the event status and the flagged arrangement</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr">
+      <c r="I189" s="2" t="inlineStr">
         <is>
           <t>Flagged arrangement: venue booking</t>
         </is>
       </c>
-      <c r="J183" s="2" t="inlineStr">
+      <c r="J189" s="2" t="inlineStr">
         <is>
           <t>The event status remains "Confirmed"; the affected venue booking is shown flagged, but no automatic status change has occurred</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="n">
+    <row r="190">
+      <c r="A190" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C190" s="2" t="inlineStr">
         <is>
           <t>E08-S04 (checklist: reversion recorded in activity log)</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting (audit logging)</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>TC_E08S04_04</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>Verify that a reversion from Confirmed to Planning should be recorded in the activity log</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr">
         <is>
           <t>Event "Leadership Summit" has just been reverted from "Confirmed" to "Planning" by coordinator_1@connectsphere.com</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t>1. Log in as a System Administrator
   2. Open the Activity Log and search for "Leadership Summit"</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr">
+      <c r="I190" s="2" t="inlineStr">
         <is>
           <t>Event: Leadership Summit</t>
         </is>
       </c>
-      <c r="J184" s="2" t="inlineStr">
+      <c r="J190" s="2" t="inlineStr">
         <is>
           <t>An activity log entry exists recording the reversion, with actor = coordinator_1@connectsphere.com, action = "Reverted to Planning", and a timestamp
 ## E08-S05</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="n">
+    <row r="191">
+      <c r="A191" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
+      <c r="C191" s="2" t="inlineStr">
         <is>
           <t>E08-S05 - Scenario 1 (Auto-completed after the end time)</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_01</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>Verify that a Confirmed event should automatically become Completed once its last event's end time has passed</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has status "Confirmed"; its only event ended at 17:00 on 15/01/2027, which has now passed</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>1. Wait for (or trigger) the system's next scheduled evaluation after 17:00 on 15/01/2027
   2. Open event "Charity Run" and check its status</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr">
+      <c r="I191" s="2" t="inlineStr">
         <is>
           <t>Event end time: 17:00, 15/01/2027 (passed)</t>
         </is>
       </c>
-      <c r="J185" s="2" t="inlineStr">
+      <c r="J191" s="2" t="inlineStr">
         <is>
           <t>The event status has automatically changed to "Completed"</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="n">
+    <row r="192">
+      <c r="A192" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C192" s="2" t="inlineStr">
         <is>
           <t>E08-S05 - Scenario 2 (Marked complete manually)</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_02</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Coordinator should be able to manually mark a Confirmed event complete once its last event has started</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr">
         <is>
           <t>Event "Volunteer Training Day" has status "Confirmed"; its last (only) event started at 09:00 today and is still in progress</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Volunteer Training Day"
   3. Click "Mark Complete"</t>
         </is>
       </c>
-      <c r="I186" s="2" t="inlineStr">
+      <c r="I192" s="2" t="inlineStr">
         <is>
           <t>Event started: 09:00 today</t>
         </is>
       </c>
-      <c r="J186" s="2" t="inlineStr">
+      <c r="J192" s="2" t="inlineStr">
         <is>
           <t>The event status changes to "Completed"</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="n">
+    <row r="193">
+      <c r="A193" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B187" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
+      <c r="C193" s="2" t="inlineStr">
         <is>
           <t>E08-S05 - Scenario 3 (Premature completion blocked)</t>
         </is>
       </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_03</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to mark an event complete before its first event has started should be blocked</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has status "Confirmed"; its first event has not yet started</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Tech Conference 2026"
   3. Attempt to click "Mark Complete"</t>
         </is>
       </c>
-      <c r="I187" s="2" t="inlineStr">
+      <c r="I193" s="2" t="inlineStr">
         <is>
           <t>First event: not yet started</t>
         </is>
       </c>
-      <c r="J187" s="2" t="inlineStr">
+      <c r="J193" s="2" t="inlineStr">
         <is>
           <t>The action is blocked; the event cannot be marked complete before it has started</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="n">
+    <row r="194">
+      <c r="A194" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B188" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
+      <c r="C194" s="2" t="inlineStr">
         <is>
           <t>E08-S05 - Scenario 4 (Cancelled event never auto-completes)</t>
         </is>
       </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_04</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>Verify that a Cancelled event should never auto-complete, even after its original end time passes</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr">
         <is>
           <t>Event "Product Launch Night" has status "Cancelled" (per TC_E10S04_01); its original end time has now passed</t>
         </is>
       </c>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>1. Wait for (or trigger) the system's next scheduled evaluation after "Product Launch Night"'s original end time
   2. Open event "Product Launch Night" and check its status</t>
         </is>
       </c>
-      <c r="I188" s="2" t="inlineStr">
+      <c r="I194" s="2" t="inlineStr">
         <is>
           <t>Original end time: passed</t>
         </is>
       </c>
-      <c r="J188" s="2" t="inlineStr">
+      <c r="J194" s="2" t="inlineStr">
         <is>
           <t>The event status remains "Cancelled"; it has not been auto-completed</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="n">
+    <row r="195">
+      <c r="A195" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B189" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
+      <c r="C195" s="2" t="inlineStr">
         <is>
           <t>E08-S05 (checklist: transition to Completed logged)</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting (audit logging)</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_05</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>Verify that an event's transition to Completed should be recorded in the activity log</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has just transitioned to "Completed" (per TC_E08S05_01)</t>
         </is>
       </c>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>1. Log in as a System Administrator
   2. Open the Activity Log and search for "Charity Run"</t>
         </is>
       </c>
-      <c r="I189" s="2" t="inlineStr">
+      <c r="I195" s="2" t="inlineStr">
         <is>
           <t>Event: Charity Run</t>
         </is>
       </c>
-      <c r="J189" s="2" t="inlineStr">
+      <c r="J195" s="2" t="inlineStr">
         <is>
           <t>An activity log entry exists recording the transition to "Completed", with the time it occurred</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="n">
+    <row r="196">
+      <c r="A196" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="C196" s="2" t="inlineStr">
         <is>
           <t>E08-S05 · Scenario 1 (Auto-completed after the end time)</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_06</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>Verify that an event auto-completes at the exact end time and not before</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2002 is Confirmed and its end time is 2026-11-02 17:00:00 +08:00</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>1. Set the system clock to 2026-11-02 16:59:59 +08:00 and trigger the completion evaluation
  2. Record the event status
@@ -10411,52 +10730,52 @@
  4. Record the event status</t>
         </is>
       </c>
-      <c r="I190" s="2" t="inlineStr">
+      <c r="I196" s="2" t="inlineStr">
         <is>
           <t>Event ends: 2026-11-02 17:00:00 +08:00 · Evaluations at 16:59:59 and 17:00:00</t>
         </is>
       </c>
-      <c r="J190" s="2" t="inlineStr">
+      <c r="J196" s="2" t="inlineStr">
         <is>
           <t>At 16:59:59 the status remains Confirmed. At 17:00:00 the status becomes Completed and the transition is recorded in the activity log</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="n">
+    <row r="197">
+      <c r="A197" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B191" s="2" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
+      <c r="C197" s="2" t="inlineStr">
         <is>
           <t>E09-S01 - Scenario 1 (Place reserved in an open event)</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_01</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting the required registration information for an open event with places remaining should reserve a place and provide a confirmation</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" is Confirmed, registration is open, and 3 of 5 places remain in its event</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Open event "Community Meetup"
@@ -10464,52 +10783,52 @@
   4. Submit registration</t>
         </is>
       </c>
-      <c r="I191" s="2" t="inlineStr">
+      <c r="I197" s="2" t="inlineStr">
         <is>
           <t>Name: Casey Tan | Email: attendee_c@example.com</t>
         </is>
       </c>
-      <c r="J191" s="2" t="inlineStr">
+      <c r="J197" s="2" t="inlineStr">
         <is>
           <t>attendee_c@example.com's place is reserved, and they receive a confirmation containing the event's details (date, time, venue)</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="n">
+    <row r="198">
+      <c r="A198" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B192" s="2" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
+      <c r="C198" s="2" t="inlineStr">
         <is>
           <t>E09-S01 (checklist: choose events to attend in a multi-event event)</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_02</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>Verify that registering for a multi-event event should let the Attendee choose which events to attend, reserving a place in each chosen event</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has the event and the event, both open for registration</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_d@example.com
   2. Open event "Tech Conference 2026"
@@ -10517,104 +10836,104 @@
   4. Submit registration</t>
         </is>
       </c>
-      <c r="I192" s="2" t="inlineStr">
+      <c r="I198" s="2" t="inlineStr">
         <is>
           <t>Selected: the event only</t>
         </is>
       </c>
-      <c r="J192" s="2" t="inlineStr">
+      <c r="J198" s="2" t="inlineStr">
         <is>
           <t>A place is reserved for attendee_d@example.com in the event only; they are not registered for the event</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="n">
+    <row r="199">
+      <c r="A199" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B193" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C193" s="2" t="inlineStr">
+      <c r="C199" s="2" t="inlineStr">
         <is>
           <t>E09-S01 - Scenario 2 (Duplicate registration prevented)</t>
         </is>
       </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_03</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to register again for a event already registered for should be told so, without creating a duplicate</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr">
         <is>
           <t>attendee_c@example.com is already registered for "Community Meetup"'s event</t>
         </is>
       </c>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Open event "Community Meetup"
   3. Attempt to register again</t>
         </is>
       </c>
-      <c r="I193" s="2" t="inlineStr">
+      <c r="I199" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_c@example.com (already registered)</t>
         </is>
       </c>
-      <c r="J193" s="2" t="inlineStr">
+      <c r="J199" s="2" t="inlineStr">
         <is>
           <t>attendee_c@example.com is told they are already registered; no duplicate registration is created</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="n">
+    <row r="200">
+      <c r="A200" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B194" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
+      <c r="C200" s="2" t="inlineStr">
         <is>
           <t>E09-S01 - Scenario 3 (Missing fields identified)</t>
         </is>
       </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_04</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting registration with a required field empty should block registration and identify the missing fields</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" is open for registration</t>
         </is>
       </c>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_e@example.com
   2. Open event "Community Meetup"
@@ -10622,309 +10941,309 @@
   4. Submit registration</t>
         </is>
       </c>
-      <c r="I194" s="2" t="inlineStr">
+      <c r="I200" s="2" t="inlineStr">
         <is>
           <t>Name: filled | Email: (blank)</t>
         </is>
       </c>
-      <c r="J194" s="2" t="inlineStr">
+      <c r="J200" s="2" t="inlineStr">
         <is>
           <t>Registration is blocked, and the Email field is identified as missing</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="n">
+    <row r="201">
+      <c r="A201" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B195" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C195" s="2" t="inlineStr">
+      <c r="C201" s="2" t="inlineStr">
         <is>
           <t>E09-S01 - Scenario 4 (Unconfirmed event refused)</t>
         </is>
       </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_05</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to register for an event that is not Confirmed should be refused</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr">
         <is>
           <t>Event "Draft Networking Event" has status "Planning" (not yet Confirmed)</t>
         </is>
       </c>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Attempt to open the registration form for "Draft Networking Event"</t>
         </is>
       </c>
-      <c r="I195" s="2" t="inlineStr">
+      <c r="I201" s="2" t="inlineStr">
         <is>
           <t>Event status: Planning</t>
         </is>
       </c>
-      <c r="J195" s="2" t="inlineStr">
+      <c r="J201" s="2" t="inlineStr">
         <is>
           <t>Registration is refused, since the event is not yet Confirmed
 ## E09-S02</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="n">
+    <row r="202">
+      <c r="A202" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B196" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C196" s="2" t="inlineStr">
+      <c r="C202" s="2" t="inlineStr">
         <is>
           <t>E09-S02 (checklist: set a registration limit)</t>
         </is>
       </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_01</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Organiser should be able to set a registration limit for a event</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is signed in; event "Community Meetup"'s event has no registration limit set yet</t>
         </is>
       </c>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>1. Open event "Community Meetup"
   2. Set the Registration Limit for its event to 5
   3. Save</t>
         </is>
       </c>
-      <c r="I196" s="2" t="inlineStr">
+      <c r="I202" s="2" t="inlineStr">
         <is>
           <t>Registration Limit: 5</t>
         </is>
       </c>
-      <c r="J196" s="2" t="inlineStr">
+      <c r="J202" s="2" t="inlineStr">
         <is>
           <t>The event's registration limit is saved as 5</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="n">
+    <row r="203">
+      <c r="A203" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B197" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C197" s="2" t="inlineStr">
+      <c r="C203" s="2" t="inlineStr">
         <is>
           <t>E09-S02 - Scenario 1 (Venue capacity enforced)</t>
         </is>
       </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_02</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>Verify that registration should stop once the event reaches the lower of the Organiser's limit and the booked venue's capacity</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s event has an Organiser-set limit of 5 and a booked venue capacity of 8 (the limit is the lower value); 5 Attendees are already registered</t>
         </is>
       </c>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_f@example.com
   2. Attempt to register for "Community Meetup"</t>
         </is>
       </c>
-      <c r="I197" s="2" t="inlineStr">
+      <c r="I203" s="2" t="inlineStr">
         <is>
           <t>Registered so far: 5 (effective limit) | Venue capacity: 8</t>
         </is>
       </c>
-      <c r="J197" s="2" t="inlineStr">
+      <c r="J203" s="2" t="inlineStr">
         <is>
           <t>Registration is refused since the event has reached its effective capacity of 5</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="n">
+    <row r="204">
+      <c r="A204" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B198" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C198" s="2" t="inlineStr">
+      <c r="C204" s="2" t="inlineStr">
         <is>
           <t>E09-S02 - Scenario 2 (Simultaneous final registration)</t>
         </is>
       </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (last place, concurrency)</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_03</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>Verify that when only one place remains, two simultaneous registration attempts should result in exactly one success</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s event has exactly 1 place remaining</t>
         </is>
       </c>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>1. Have attendee_g@example.com and attendee_h@example.com submit registration for the same event at the same moment
   2. Check both outcomes</t>
         </is>
       </c>
-      <c r="I198" s="2" t="inlineStr">
+      <c r="I204" s="2" t="inlineStr">
         <is>
           <t>1 place remaining | 2 simultaneous attempts</t>
         </is>
       </c>
-      <c r="J198" s="2" t="inlineStr">
+      <c r="J204" s="2" t="inlineStr">
         <is>
           <t>Exactly one of the two registrations succeeds; the other is told the event is full</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="n">
+    <row r="205">
+      <c r="A205" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B199" s="2" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr">
+      <c r="C205" s="2" t="inlineStr">
         <is>
           <t>E09-S02 - Scenario 3 (Full event offers the waiting list)</t>
         </is>
       </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_04</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>Verify that opening the registration page for a full event should close registration and offer the waiting list where enabled</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s event is full (5 of 5 places taken); the waiting list is enabled for this event</t>
         </is>
       </c>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_i@example.com
   2. Open the registration page for "Community Meetup"</t>
         </is>
       </c>
-      <c r="I199" s="2" t="inlineStr">
+      <c r="I205" s="2" t="inlineStr">
         <is>
           <t>Event: full | Waiting list: enabled</t>
         </is>
       </c>
-      <c r="J199" s="2" t="inlineStr">
+      <c r="J205" s="2" t="inlineStr">
         <is>
           <t>Registration is shown as closed, and the option to join the waiting list is offered</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="n">
+    <row r="206">
+      <c r="A206" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B200" s="2" t="inlineStr">
+      <c r="B206" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C200" s="2" t="inlineStr">
+      <c r="C206" s="2" t="inlineStr">
         <is>
           <t>E09-S02 · Scenario 4 (VIP added beyond normal registration)</t>
         </is>
       </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (just below venue capacity)</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_06</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>Verify that a VIP can be added manually when normal registration is full but venue capacity is not reached</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with Orchid Hall booked, venue capacity 200. Normal registration has closed at 199 registrations. Coordinator coord_a@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>1. Open event EVT-2001
  2. Select Add attendee manually
@@ -10932,52 +11251,52 @@
  4. Confirm the addition</t>
         </is>
       </c>
-      <c r="I200" s="2" t="inlineStr">
+      <c r="I206" s="2" t="inlineStr">
         <is>
           <t>Venue capacity: 200 · Current registrations: 199 · Added: 1</t>
         </is>
       </c>
-      <c r="J200" s="2" t="inlineStr">
+      <c r="J206" s="2" t="inlineStr">
         <is>
           <t>The registration is created, total registrations reach 200, and the record is marked as a manual addition distinguishable from a normal registration</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="n">
+    <row r="207">
+      <c r="A207" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B201" s="2" t="inlineStr">
+      <c r="B207" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr">
+      <c r="C207" s="2" t="inlineStr">
         <is>
           <t>E09-S02 · Scenario 5 (VIP blocked at venue capacity)</t>
         </is>
       </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at venue capacity)</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_07</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F207" s="2" t="inlineStr">
         <is>
           <t>Verify that a manual VIP addition is blocked once total registrations equal venue capacity</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with Orchid Hall booked, venue capacity 200, and 200 registrations already recorded. Coordinator coord_a@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="H207" s="2" t="inlineStr">
         <is>
           <t>1. Open event EVT-2001
  2. Select Add attendee manually
@@ -10985,310 +11304,310 @@
  4. Confirm the addition</t>
         </is>
       </c>
-      <c r="I201" s="2" t="inlineStr">
+      <c r="I207" s="2" t="inlineStr">
         <is>
           <t>Venue capacity: 200 · Current registrations: 200</t>
         </is>
       </c>
-      <c r="J201" s="2" t="inlineStr">
+      <c r="J207" s="2" t="inlineStr">
         <is>
           <t>The addition is blocked with a message stating the booked venue capacity has been reached. No registration is created
 ## E09-S03</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="n">
+    <row r="208">
+      <c r="A208" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B202" s="2" t="inlineStr">
+      <c r="B208" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C202" s="2" t="inlineStr">
+      <c r="C208" s="2" t="inlineStr">
         <is>
           <t>E09-S03 (checklist: set registration opening/closing dates)</t>
         </is>
       </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="D208" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_01</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F208" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Organiser should be able to set the registration opening and closing dates for an event</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr">
+      <c r="G208" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is signed in; event "Community Meetup" has no registration dates set</t>
         </is>
       </c>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="H208" s="2" t="inlineStr">
         <is>
           <t>1. Open event "Community Meetup"
   2. Set Registration Opens: 01/10/2026, Registration Closes: 01/12/2026
   3. Save</t>
         </is>
       </c>
-      <c r="I202" s="2" t="inlineStr">
+      <c r="I208" s="2" t="inlineStr">
         <is>
           <t>Opens: 01/10/2026 | Closes: 01/12/2026</t>
         </is>
       </c>
-      <c r="J202" s="2" t="inlineStr">
+      <c r="J208" s="2" t="inlineStr">
         <is>
           <t>The registration opening and closing dates are saved as entered</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="n">
+    <row r="209">
+      <c r="A209" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B203" s="2" t="inlineStr">
+      <c r="B209" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C203" s="2" t="inlineStr">
+      <c r="C209" s="2" t="inlineStr">
         <is>
           <t>E09-S03 (checklist: set a withdrawal deadline)</t>
         </is>
       </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="D209" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_02</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F209" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Organiser should be able to set a withdrawal deadline for an event</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is signed in; event "Community Meetup" has no withdrawal deadline set</t>
         </is>
       </c>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="H209" s="2" t="inlineStr">
         <is>
           <t>1. Open event "Community Meetup"
   2. Set Withdrawal Deadline: 10/12/2026
   3. Save</t>
         </is>
       </c>
-      <c r="I203" s="2" t="inlineStr">
+      <c r="I209" s="2" t="inlineStr">
         <is>
           <t>Withdrawal Deadline: 10/12/2026</t>
         </is>
       </c>
-      <c r="J203" s="2" t="inlineStr">
+      <c r="J209" s="2" t="inlineStr">
         <is>
           <t>The withdrawal deadline is saved as 10/12/2026</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="n">
+    <row r="210">
+      <c r="A210" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B204" s="2" t="inlineStr">
+      <c r="B210" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C204" s="2" t="inlineStr">
+      <c r="C210" s="2" t="inlineStr">
         <is>
           <t>E09-S03 - Scenario 1 (Before registration opens)</t>
         </is>
       </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (before)</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_03</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>Verify that an Attendee viewing an event before its registration opening date should see registration as not yet open, with the opening date stated</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr">
+      <c r="G210" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s registration opening date (01/10/2026) has not yet been reached</t>
         </is>
       </c>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="H210" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Open event "Community Meetup"</t>
         </is>
       </c>
-      <c r="I204" s="2" t="inlineStr">
+      <c r="I210" s="2" t="inlineStr">
         <is>
           <t>Opening date: 01/10/2026 (not reached)</t>
         </is>
       </c>
-      <c r="J204" s="2" t="inlineStr">
+      <c r="J210" s="2" t="inlineStr">
         <is>
           <t>Registration is shown as "Not yet open", with the message stating it opens on 01/10/2026</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="n">
+    <row r="211">
+      <c r="A211" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B205" s="2" t="inlineStr">
+      <c r="B211" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C205" s="2" t="inlineStr">
+      <c r="C211" s="2" t="inlineStr">
         <is>
           <t>E09-S03 - Scenario 2 (After registration closes)</t>
         </is>
       </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (after)</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_04</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>Verify that an Attendee trying to register after the registration closing date has passed should be refused</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr">
+      <c r="G211" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s registration closing date (01/12/2026) has passed</t>
         </is>
       </c>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="H211" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Attempt to register for "Community Meetup"</t>
         </is>
       </c>
-      <c r="I205" s="2" t="inlineStr">
+      <c r="I211" s="2" t="inlineStr">
         <is>
           <t>Closing date: 01/12/2026 (passed)</t>
         </is>
       </c>
-      <c r="J205" s="2" t="inlineStr">
+      <c r="J211" s="2" t="inlineStr">
         <is>
           <t>Registration is refused, since the closing date has passed</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="n">
+    <row r="212">
+      <c r="A212" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B206" s="2" t="inlineStr">
+      <c r="B212" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C206" s="2" t="inlineStr">
+      <c r="C212" s="2" t="inlineStr">
         <is>
           <t>E09-S03 - Scenario 3 (Closing date after event start warned)</t>
         </is>
       </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_05</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="F212" s="2" t="inlineStr">
         <is>
           <t>Verify that setting a registration closing date that falls after the event has started should warn the Organiser and ask them to confirm</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr">
+      <c r="G212" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is editing event "Community Meetup", which starts on 15/11/2026</t>
         </is>
       </c>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="H212" s="2" t="inlineStr">
         <is>
           <t>1. Set Registration Closes: 20/11/2026 (after the event's start date)
   2. Click "Save"</t>
         </is>
       </c>
-      <c r="I206" s="2" t="inlineStr">
+      <c r="I212" s="2" t="inlineStr">
         <is>
           <t>Closing date: 20/11/2026 (after event start 15/11/2026)</t>
         </is>
       </c>
-      <c r="J206" s="2" t="inlineStr">
+      <c r="J212" s="2" t="inlineStr">
         <is>
           <t>A warning is shown asking the Organiser to confirm this is intended, before the closing date is saved</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="n">
+    <row r="213">
+      <c r="A213" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B207" s="2" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C207" s="2" t="inlineStr">
+      <c r="C213" s="2" t="inlineStr">
         <is>
           <t>E09-S03 - Scenario 4 (Waiting list enabled)</t>
         </is>
       </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_06</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="F213" s="2" t="inlineStr">
         <is>
           <t>Verify that enabling the waiting list for an event should offer it to Attendees once a event becomes full</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr">
+      <c r="G213" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is about to enable the waiting list for event "Community Meetup"</t>
         </is>
       </c>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="H213" s="2" t="inlineStr">
         <is>
           <t>1. Open event "Community Meetup"
   2. Toggle "Enable Waiting List" on
@@ -11296,363 +11615,363 @@
   4. Fill the event to capacity and attempt a further registration</t>
         </is>
       </c>
-      <c r="I207" s="2" t="inlineStr">
+      <c r="I213" s="2" t="inlineStr">
         <is>
           <t>Waiting List: Enabled</t>
         </is>
       </c>
-      <c r="J207" s="2" t="inlineStr">
+      <c r="J213" s="2" t="inlineStr">
         <is>
           <t>Once the event is full, the further registration attempt is offered the waiting list instead of being simply refused</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="n">
+    <row r="214">
+      <c r="A214" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B208" s="2" t="inlineStr">
+      <c r="B214" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C208" s="2" t="inlineStr">
+      <c r="C214" s="2" t="inlineStr">
         <is>
           <t>E09-S03 · Scenario 1 (Before registration opens)</t>
         </is>
       </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="D214" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E214" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_07</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="F214" s="2" t="inlineStr">
         <is>
           <t>Verify that registration succeeds at the exact opening timestamp</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr">
+      <c r="G214" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with registration opening at 2026-10-01 09:00:00 +08:00. Attendee attendee_a@example.com is signed in. Event EVT-2001 has places remaining</t>
         </is>
       </c>
-      <c r="H208" s="2" t="inlineStr">
+      <c r="H214" s="2" t="inlineStr">
         <is>
           <t>1. Set the system clock to exactly 2026-10-01 09:00:00 +08:00
  2. Open event EVT-2001
  3. Select event EVT-2001 and submit registration</t>
         </is>
       </c>
-      <c r="I208" s="2" t="inlineStr">
+      <c r="I214" s="2" t="inlineStr">
         <is>
           <t>Registration opens: 2026-10-01 09:00:00 +08:00 · Attempt at: 2026-10-01 09:00:00 +08:00</t>
         </is>
       </c>
-      <c r="J208" s="2" t="inlineStr">
+      <c r="J214" s="2" t="inlineStr">
         <is>
           <t>Registration succeeds and a place is reserved. The opening moment is inclusive: registration is open at, not after, the opening timestamp</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2" t="n">
+    <row r="215">
+      <c r="A215" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B209" s="2" t="inlineStr">
+      <c r="B215" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C209" s="2" t="inlineStr">
+      <c r="C215" s="2" t="inlineStr">
         <is>
           <t>E09-S03 · Scenario 2 (After registration closes)</t>
         </is>
       </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="D215" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E215" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_08</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F215" s="2" t="inlineStr">
         <is>
           <t>Verify that registration still succeeds at the exact closing timestamp</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr">
+      <c r="G215" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with registration closing at 2026-10-20 17:00:00 +08:00. Attendee attendee_b@example.com is signed in. Event EVT-2001 has places remaining</t>
         </is>
       </c>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="H215" s="2" t="inlineStr">
         <is>
           <t>1. Set the system clock to exactly 2026-10-20 17:00:00 +08:00
  2. Open event EVT-2001
  3. Select event EVT-2001 and submit registration</t>
         </is>
       </c>
-      <c r="I209" s="2" t="inlineStr">
+      <c r="I215" s="2" t="inlineStr">
         <is>
           <t>Registration closes: 2026-10-20 17:00:00 +08:00 · Attempt at: 2026-10-20 17:00:00 +08:00</t>
         </is>
       </c>
-      <c r="J209" s="2" t="inlineStr">
+      <c r="J215" s="2" t="inlineStr">
         <is>
           <t>Registration succeeds. The acceptance criterion refuses registration once the closing date "has passed", so at the exact closing instant it has not yet passed. One second later the same attempt must be refused
 ## E09-S04</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="2" t="n">
+    <row r="216">
+      <c r="A216" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B210" s="2" t="inlineStr">
+      <c r="B216" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C210" s="2" t="inlineStr">
+      <c r="C216" s="2" t="inlineStr">
         <is>
           <t>E09-S04 - Scenario 1 (Joined a full event's list)</t>
         </is>
       </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="D216" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_01</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="F216" s="2" t="inlineStr">
         <is>
           <t>Verify that joining the waiting list for a full event with the list enabled should add the Attendee and confirm their position</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr">
+      <c r="G216" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s event is full; the waiting list is enabled and currently empty</t>
         </is>
       </c>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="H216" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_i@example.com
   2. Open the registration page for "Community Meetup"
   3. Click "Join Waiting List"</t>
         </is>
       </c>
-      <c r="I210" s="2" t="inlineStr">
+      <c r="I216" s="2" t="inlineStr">
         <is>
           <t>Waiting list: enabled, currently empty</t>
         </is>
       </c>
-      <c r="J210" s="2" t="inlineStr">
+      <c r="J216" s="2" t="inlineStr">
         <is>
           <t>attendee_i@example.com is added to the waiting list and shown their position (e.g. "Position 1")</t>
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="2" t="n">
+    <row r="217">
+      <c r="A217" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B211" s="2" t="inlineStr">
+      <c r="B217" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C211" s="2" t="inlineStr">
+      <c r="C217" s="2" t="inlineStr">
         <is>
           <t>E09-S04 - Scenario 2 (Released place notified to all)</t>
         </is>
       </c>
-      <c r="D211" s="2" t="inlineStr">
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_02</t>
         </is>
       </c>
-      <c r="F211" s="2" t="inlineStr">
+      <c r="F217" s="2" t="inlineStr">
         <is>
           <t>Verify that when a place is released in a event with a waiting list, all waitlisted Attendees should be notified and the place claimed on a first-come, first-served basis</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr">
+      <c r="G217" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s waiting list has attendee_i@example.com (position 1) and attendee_j@example.com (position 2)</t>
         </is>
       </c>
-      <c r="H211" s="2" t="inlineStr">
+      <c r="H217" s="2" t="inlineStr">
         <is>
           <t>1. Have registered Attendee attendee_m@example.com withdraw from "Community Meetup", releasing one place
   2. Check notifications for attendee_i@example.com and attendee_j@example.com
   3. Have attendee_i@example.com claim the released place first</t>
         </is>
       </c>
-      <c r="I211" s="2" t="inlineStr">
+      <c r="I217" s="2" t="inlineStr">
         <is>
           <t>Waiting list: attendee_i@example.com (1st), attendee_j@example.com (2nd)</t>
         </is>
       </c>
-      <c r="J211" s="2" t="inlineStr">
+      <c r="J217" s="2" t="inlineStr">
         <is>
           <t>Both waitlisted Attendees are notified of the released place; attendee_i@example.com successfully claims it since they acted first</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="2" t="n">
+    <row r="218">
+      <c r="A218" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B212" s="2" t="inlineStr">
+      <c r="B218" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C212" s="2" t="inlineStr">
+      <c r="C218" s="2" t="inlineStr">
         <is>
           <t>E09-S04 - Scenario 3 (Claimed place leaves the list)</t>
         </is>
       </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_03</t>
         </is>
       </c>
-      <c r="F212" s="2" t="inlineStr">
+      <c r="F218" s="2" t="inlineStr">
         <is>
           <t>Verify that claiming a released place should remove the Attendee from the waiting list for that event</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr">
+      <c r="G218" s="2" t="inlineStr">
         <is>
           <t>attendee_i@example.com has just claimed a released place in "Community Meetup"'s event</t>
         </is>
       </c>
-      <c r="H212" s="2" t="inlineStr">
+      <c r="H218" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_i@example.com
   2. Check the waiting list for "Community Meetup"'s event</t>
         </is>
       </c>
-      <c r="I212" s="2" t="inlineStr">
+      <c r="I218" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_i@example.com (just claimed a place)</t>
         </is>
       </c>
-      <c r="J212" s="2" t="inlineStr">
+      <c r="J218" s="2" t="inlineStr">
         <is>
           <t>attendee_i@example.com no longer appears on the waiting list for that event, since they are now registered</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="2" t="n">
+    <row r="219">
+      <c r="A219" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B213" s="2" t="inlineStr">
+      <c r="B219" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C213" s="2" t="inlineStr">
+      <c r="C219" s="2" t="inlineStr">
         <is>
           <t>E09-S04 - Scenario 4 (Disabled list offers nothing)</t>
         </is>
       </c>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="D219" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_04</t>
         </is>
       </c>
-      <c r="F213" s="2" t="inlineStr">
+      <c r="F219" s="2" t="inlineStr">
         <is>
           <t>Verify that a full event should not offer a waiting list when the Organiser has disabled it</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr">
+      <c r="G219" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has the waiting list disabled; the event is full</t>
         </is>
       </c>
-      <c r="H213" s="2" t="inlineStr">
+      <c r="H219" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_k@example.com
   2. Open the registration page for the event of "Tech Conference 2026"</t>
         </is>
       </c>
-      <c r="I213" s="2" t="inlineStr">
+      <c r="I219" s="2" t="inlineStr">
         <is>
           <t>Waiting list: disabled | the event: full</t>
         </is>
       </c>
-      <c r="J213" s="2" t="inlineStr">
+      <c r="J219" s="2" t="inlineStr">
         <is>
           <t>No waiting list option is offered; registration is simply shown as closed</t>
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="2" t="n">
+    <row r="220">
+      <c r="A220" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B214" s="2" t="inlineStr">
+      <c r="B220" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C214" s="2" t="inlineStr">
+      <c r="C220" s="2" t="inlineStr">
         <is>
           <t>E09-S04 (checklist: leave the waiting list)</t>
         </is>
       </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_05</t>
         </is>
       </c>
-      <c r="F214" s="2" t="inlineStr">
+      <c r="F220" s="2" t="inlineStr">
         <is>
           <t>Verify that an Attendee should be able to voluntarily leave the waiting list before a place is released</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr">
+      <c r="G220" s="2" t="inlineStr">
         <is>
           <t>attendee_j@example.com is on the waiting list for "Community Meetup"'s event, position 2</t>
         </is>
       </c>
-      <c r="H214" s="2" t="inlineStr">
+      <c r="H220" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_j@example.com
   2. Open the waiting list status for "Community Meetup"
@@ -11660,622 +11979,622 @@
   4. Confirm</t>
         </is>
       </c>
-      <c r="I214" s="2" t="inlineStr">
+      <c r="I220" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_j@example.com</t>
         </is>
       </c>
-      <c r="J214" s="2" t="inlineStr">
+      <c r="J220" s="2" t="inlineStr">
         <is>
           <t>attendee_j@example.com is removed from the waiting list and no longer receives notifications about released places for that event
 ## E09-S05</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="2" t="n">
+    <row r="221">
+      <c r="A221" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B215" s="2" t="inlineStr">
+      <c r="B221" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="C215" s="2" t="inlineStr">
+      <c r="C221" s="2" t="inlineStr">
         <is>
           <t>E09-S05 - Scenario 1 (Registration withdrawn)</t>
         </is>
       </c>
-      <c r="D215" s="2" t="inlineStr">
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>TC_E09S05_01</t>
         </is>
       </c>
-      <c r="F215" s="2" t="inlineStr">
+      <c r="F221" s="2" t="inlineStr">
         <is>
           <t>Verify that withdrawing from a single event before the withdrawal deadline should cancel that registration and release the place, leaving other events unaffected</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr">
+      <c r="G221" s="2" t="inlineStr">
         <is>
           <t>attendee_d@example.com is registered for both the event and the event of "Tech Conference 2026"; the withdrawal deadline has not passed</t>
         </is>
       </c>
-      <c r="H215" s="2" t="inlineStr">
+      <c r="H221" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_d@example.com
   2. Open "My Registrations"
   3. Withdraw from the event only</t>
         </is>
       </c>
-      <c r="I215" s="2" t="inlineStr">
+      <c r="I221" s="2" t="inlineStr">
         <is>
           <t>Withdrawing from: the event only</t>
         </is>
       </c>
-      <c r="J215" s="2" t="inlineStr">
+      <c r="J221" s="2" t="inlineStr">
         <is>
           <t>The the event registration is cancelled and its place becomes available again; attendee_d@example.com remains registered for the event</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2" t="n">
+    <row r="222">
+      <c r="A222" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B216" s="2" t="inlineStr">
+      <c r="B222" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="C216" s="2" t="inlineStr">
+      <c r="C222" s="2" t="inlineStr">
         <is>
           <t>E09-S05 - Scenario 2 (Withdrawal after deadline refused)</t>
         </is>
       </c>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>TC_E09S05_03</t>
         </is>
       </c>
-      <c r="F216" s="2" t="inlineStr">
+      <c r="F222" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to withdraw after the withdrawal deadline has passed should be refused, with a contact provided for assistance</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr">
+      <c r="G222" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s withdrawal deadline (10/12/2026) has passed</t>
         </is>
       </c>
-      <c r="H216" s="2" t="inlineStr">
+      <c r="H222" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Attempt to withdraw from "Community Meetup"</t>
         </is>
       </c>
-      <c r="I216" s="2" t="inlineStr">
+      <c r="I222" s="2" t="inlineStr">
         <is>
           <t>Withdrawal deadline: 10/12/2026 (passed)</t>
         </is>
       </c>
-      <c r="J216" s="2" t="inlineStr">
+      <c r="J222" s="2" t="inlineStr">
         <is>
           <t>Withdrawal is refused with the message "Withdrawal has closed" and a contact is provided for assistance</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="2" t="n">
+    <row r="223">
+      <c r="A223" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B217" s="2" t="inlineStr">
+      <c r="B223" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="C217" s="2" t="inlineStr">
+      <c r="C223" s="2" t="inlineStr">
         <is>
           <t>E09-S05 · Scenario 2 (Withdrawal after deadline refused)</t>
         </is>
       </c>
-      <c r="D217" s="2" t="inlineStr">
+      <c r="D223" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>TC_E09S05_04</t>
         </is>
       </c>
-      <c r="F217" s="2" t="inlineStr">
+      <c r="F223" s="2" t="inlineStr">
         <is>
           <t>Verify that withdrawal succeeds at the exact withdrawal deadline</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr">
+      <c r="G223" s="2" t="inlineStr">
         <is>
           <t>Attendee attendee_a@example.com is registered for event EVT-2001. The withdrawal deadline for event EVT-2001 is 2026-10-25 23:59:59 +08:00</t>
         </is>
       </c>
-      <c r="H217" s="2" t="inlineStr">
+      <c r="H223" s="2" t="inlineStr">
         <is>
           <t>1. Set the system clock to exactly 2026-10-25 23:59:59 +08:00
  2. Sign in as attendee_a@example.com
  3. Open the registration for EVT-2001 and select Withdraw</t>
         </is>
       </c>
-      <c r="I217" s="2" t="inlineStr">
+      <c r="I223" s="2" t="inlineStr">
         <is>
           <t>Withdrawal deadline: 2026-10-25 23:59:59 +08:00 · Attempt at: 2026-10-25 23:59:59 +08:00</t>
         </is>
       </c>
-      <c r="J217" s="2" t="inlineStr">
+      <c r="J223" s="2" t="inlineStr">
         <is>
           <t>The withdrawal succeeds, the registration status becomes Withdrawn and the place is released. Every waitlisted Attendee for EVT-2001 is notified that a place is available
 ## E09-S06</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="2" t="n">
+    <row r="224">
+      <c r="A224" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B218" s="2" t="inlineStr">
+      <c r="B224" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="C218" s="2" t="inlineStr">
+      <c r="C224" s="2" t="inlineStr">
         <is>
           <t>E09-S06 - Scenario 1 (Attendance marked after completion)</t>
         </is>
       </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="D224" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>TC_E09S06_01</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr">
+      <c r="F224" s="2" t="inlineStr">
         <is>
           <t>Verify that marking a registered Attendee as attended for a event after the event is Completed should update their record without changing the registration figure</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr">
+      <c r="G224" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has status "Completed" (per TC_E08S05_01); attendee_a@example.com is registered for its event</t>
         </is>
       </c>
-      <c r="H218" s="2" t="inlineStr">
+      <c r="H224" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the completed event "Charity Run"
   3. Mark attendee_a@example.com as "Attended"</t>
         </is>
       </c>
-      <c r="I218" s="2" t="inlineStr">
+      <c r="I224" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_a@example.com</t>
         </is>
       </c>
-      <c r="J218" s="2" t="inlineStr">
+      <c r="J224" s="2" t="inlineStr">
         <is>
           <t>attendee_a@example.com's record shows "Attended"; the total registration figure for the event remains unchanged</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="2" t="n">
+    <row r="225">
+      <c r="A225" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B219" s="2" t="inlineStr">
+      <c r="B225" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="C219" s="2" t="inlineStr">
+      <c r="C225" s="2" t="inlineStr">
         <is>
           <t>E09-S06 - Scenario 2 (Registered but not attended)</t>
         </is>
       </c>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>TC_E09S06_02</t>
         </is>
       </c>
-      <c r="F219" s="2" t="inlineStr">
+      <c r="F225" s="2" t="inlineStr">
         <is>
           <t>Verify that a registered Attendee who did not attend should be shown as registered but not attended once the event is Completed</t>
         </is>
       </c>
-      <c r="G219" s="2" t="inlineStr">
+      <c r="G225" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has status "Completed"; attendee_b@example.com was registered but has not been marked attended</t>
         </is>
       </c>
-      <c r="H219" s="2" t="inlineStr">
+      <c r="H225" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the completed event "Charity Run"
   3. Check attendee_b@example.com's status</t>
         </is>
       </c>
-      <c r="I219" s="2" t="inlineStr">
+      <c r="I225" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_b@example.com (registered, not marked attended)</t>
         </is>
       </c>
-      <c r="J219" s="2" t="inlineStr">
+      <c r="J225" s="2" t="inlineStr">
         <is>
           <t>attendee_b@example.com is shown as "Registered but not attended"</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="2" t="n">
+    <row r="226">
+      <c r="A226" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B220" s="2" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="C220" s="2" t="inlineStr">
+      <c r="C226" s="2" t="inlineStr">
         <is>
           <t>E09-S06 - Scenario 3 (Recording before completion blocked)</t>
         </is>
       </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>TC_E09S06_03</t>
         </is>
       </c>
-      <c r="F220" s="2" t="inlineStr">
+      <c r="F226" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to record attendance before the event is Completed should be blocked</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr">
+      <c r="G226" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has status "Confirmed" (not yet Completed)</t>
         </is>
       </c>
-      <c r="H220" s="2" t="inlineStr">
+      <c r="H226" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Tech Conference 2026"
   3. Attempt to mark an Attendee as attended</t>
         </is>
       </c>
-      <c r="I220" s="2" t="inlineStr">
+      <c r="I226" s="2" t="inlineStr">
         <is>
           <t>Event status: Confirmed (not Completed)</t>
         </is>
       </c>
-      <c r="J220" s="2" t="inlineStr">
+      <c r="J226" s="2" t="inlineStr">
         <is>
           <t>The action is blocked; attendance cannot be recorded before the event is Completed</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="2" t="n">
+    <row r="227">
+      <c r="A227" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B221" s="2" t="inlineStr">
+      <c r="B227" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="C221" s="2" t="inlineStr">
+      <c r="C227" s="2" t="inlineStr">
         <is>
           <t>E09-S06 (checklist: registration/attendance counts viewable side by side)</t>
         </is>
       </c>
-      <c r="D221" s="2" t="inlineStr">
+      <c r="D227" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E221" s="2" t="inlineStr">
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>TC_E09S06_04</t>
         </is>
       </c>
-      <c r="F221" s="2" t="inlineStr">
+      <c r="F227" s="2" t="inlineStr">
         <is>
           <t>Verify that registration and attendance counts should be viewable side by side for each event</t>
         </is>
       </c>
-      <c r="G221" s="2" t="inlineStr">
+      <c r="G227" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has status "Completed"; its event had 5 registrations and 4 marked attended</t>
         </is>
       </c>
-      <c r="H221" s="2" t="inlineStr">
+      <c r="H227" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the completed event "Charity Run"
   3. View the event's registration and attendance summary</t>
         </is>
       </c>
-      <c r="I221" s="2" t="inlineStr">
+      <c r="I227" s="2" t="inlineStr">
         <is>
           <t>Registered: 5 | Attended: 4</t>
         </is>
       </c>
-      <c r="J221" s="2" t="inlineStr">
+      <c r="J227" s="2" t="inlineStr">
         <is>
           <t>The summary shows "Registered: 5" and "Attended: 4" together, side by side
 ## E09-S07</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="2" t="n">
+    <row r="228">
+      <c r="A228" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B222" s="2" t="inlineStr">
+      <c r="B228" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="C222" s="2" t="inlineStr">
+      <c r="C228" s="2" t="inlineStr">
         <is>
           <t>E09-S07 - Scenario 1 (Registrations grouped by event)</t>
         </is>
       </c>
-      <c r="D222" s="2" t="inlineStr">
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>TC_E09S07_01</t>
         </is>
       </c>
-      <c r="F222" s="2" t="inlineStr">
+      <c r="F228" s="2" t="inlineStr">
         <is>
           <t>Verify that opening the registration list for an event with registered Attendees should show each Attendee's name, email address and contact number</t>
         </is>
       </c>
-      <c r="G222" s="2" t="inlineStr">
+      <c r="G228" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has attendee_a@example.com and attendee_b@example.com registered, each with a name, email address and contact number on file</t>
         </is>
       </c>
-      <c r="H222" s="2" t="inlineStr">
+      <c r="H228" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the registration list for "Tech Conference 2026"</t>
         </is>
       </c>
-      <c r="I222" s="2" t="inlineStr">
+      <c r="I228" s="2" t="inlineStr">
         <is>
           <t>attendee_a@example.com: +65 9123 4567 | attendee_b@example.com: +65 9234 5678</t>
         </is>
       </c>
-      <c r="J222" s="2" t="inlineStr">
+      <c r="J228" s="2" t="inlineStr">
         <is>
           <t>The list shows each Attendee's name, email address and contact number: attendee_a@example.com and attendee_b@example.com both appear with their full contact details</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="2" t="n">
+    <row r="229">
+      <c r="A229" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B223" s="2" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="C223" s="2" t="inlineStr">
+      <c r="C229" s="2" t="inlineStr">
         <is>
           <t>E09-S07 - Scenario 2 (Counts and remaining capacity)</t>
         </is>
       </c>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>TC_E09S07_02</t>
         </is>
       </c>
-      <c r="F223" s="2" t="inlineStr">
+      <c r="F229" s="2" t="inlineStr">
         <is>
           <t>Verify that the registration list should show the registered count and remaining capacity per event</t>
         </is>
       </c>
-      <c r="G223" s="2" t="inlineStr">
+      <c r="G229" s="2" t="inlineStr">
         <is>
           <t>"Tech Conference 2026" the event has 100 registered out of a capacity of 150</t>
         </is>
       </c>
-      <c r="H223" s="2" t="inlineStr">
+      <c r="H229" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the registration list for "Tech Conference 2026"</t>
         </is>
       </c>
-      <c r="I223" s="2" t="inlineStr">
+      <c r="I229" s="2" t="inlineStr">
         <is>
           <t>the event: 100 registered, capacity 150</t>
         </is>
       </c>
-      <c r="J223" s="2" t="inlineStr">
+      <c r="J229" s="2" t="inlineStr">
         <is>
           <t>the event shows "100 registered" and "50 remaining"</t>
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="2" t="n">
+    <row r="230">
+      <c r="A230" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B224" s="2" t="inlineStr">
+      <c r="B230" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="C224" s="2" t="inlineStr">
+      <c r="C230" s="2" t="inlineStr">
         <is>
           <t>E09-S07 - Scenario 3 (Unmanaged event refused)</t>
         </is>
       </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="D230" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="E230" s="2" t="inlineStr">
         <is>
           <t>TC_E09S07_03</t>
         </is>
       </c>
-      <c r="F224" s="2" t="inlineStr">
+      <c r="F230" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to open the registration list for an event that does not belong to the Organiser's client organisation should be refused</t>
         </is>
       </c>
-      <c r="G224" s="2" t="inlineStr">
+      <c r="G230" s="2" t="inlineStr">
         <is>
           <t>organiser_b@clienta.com is linked to Client B; event "Annual Tech Summit" belongs to Client A</t>
         </is>
       </c>
-      <c r="H224" s="2" t="inlineStr">
+      <c r="H230" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_b@clienta.com
   2. Attempt to open the registration list for "Annual Tech Summit"</t>
         </is>
       </c>
-      <c r="I224" s="2" t="inlineStr">
+      <c r="I230" s="2" t="inlineStr">
         <is>
           <t>Acting user: organiser_b@clienta.com | Event: Annual Tech Summit (Client A)</t>
         </is>
       </c>
-      <c r="J224" s="2" t="inlineStr">
+      <c r="J230" s="2" t="inlineStr">
         <is>
           <t>Access is refused, since "Annual Tech Summit" does not belong to organiser_b@clienta.com's client organisation</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="2" t="n">
+    <row r="231">
+      <c r="A231" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B225" s="2" t="inlineStr">
+      <c r="B231" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="C225" s="2" t="inlineStr">
+      <c r="C231" s="2" t="inlineStr">
         <is>
           <t>E09-S07 - Scenario 4 (Waitlist shown separately)</t>
         </is>
       </c>
-      <c r="D225" s="2" t="inlineStr">
+      <c r="D231" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="E231" s="2" t="inlineStr">
         <is>
           <t>TC_E09S07_04</t>
         </is>
       </c>
-      <c r="F225" s="2" t="inlineStr">
+      <c r="F231" s="2" t="inlineStr">
         <is>
           <t>Verify that waitlisted Attendees should be shown separately from registered Attendees on the registration list</t>
         </is>
       </c>
-      <c r="G225" s="2" t="inlineStr">
+      <c r="G231" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s event has 5 registered Attendees and 2 on the waiting list</t>
         </is>
       </c>
-      <c r="H225" s="2" t="inlineStr">
+      <c r="H231" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the registration list for "Community Meetup"</t>
         </is>
       </c>
-      <c r="I225" s="2" t="inlineStr">
+      <c r="I231" s="2" t="inlineStr">
         <is>
           <t>Registered: 5 | Waitlisted: 2</t>
         </is>
       </c>
-      <c r="J225" s="2" t="inlineStr">
+      <c r="J231" s="2" t="inlineStr">
         <is>
           <t>The 5 registered Attendees and the 2 waitlisted Attendees are shown in clearly separate sections/lists</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="2" t="n">
+    <row r="232">
+      <c r="A232" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B226" s="2" t="inlineStr">
+      <c r="B232" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C226" s="2" t="inlineStr">
+      <c r="C232" s="2" t="inlineStr">
         <is>
           <t>E10-S01 - Scenario 1 (Change request recorded)</t>
         </is>
       </c>
-      <c r="D226" s="2" t="inlineStr">
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_01</t>
         </is>
       </c>
-      <c r="F226" s="2" t="inlineStr">
+      <c r="F232" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting a change request on an approved or confirmed event should notify the assigned Coordinator and record the request against the event</t>
         </is>
       </c>
-      <c r="G226" s="2" t="inlineStr">
+      <c r="G232" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" has status "Confirmed"</t>
         </is>
       </c>
-      <c r="H226" s="2" t="inlineStr">
+      <c r="H232" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Community Meetup"
@@ -12284,155 +12603,155 @@
   5. Submit</t>
         </is>
       </c>
-      <c r="I226" s="2" t="inlineStr">
+      <c r="I232" s="2" t="inlineStr">
         <is>
           <t>Change description: "Increase expected attendance to 10"</t>
         </is>
       </c>
-      <c r="J226" s="2" t="inlineStr">
+      <c r="J232" s="2" t="inlineStr">
         <is>
           <t>coordinator_1@connectsphere.com is notified, and the change request is recorded against "Community Meetup"</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="2" t="n">
+    <row r="233">
+      <c r="A233" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B227" s="2" t="inlineStr">
+      <c r="B233" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C227" s="2" t="inlineStr">
+      <c r="C233" s="2" t="inlineStr">
         <is>
           <t>E10-S01 - Scenario 2 (Confirmed details shown alongside)</t>
         </is>
       </c>
-      <c r="D227" s="2" t="inlineStr">
+      <c r="D233" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_02</t>
         </is>
       </c>
-      <c r="F227" s="2" t="inlineStr">
+      <c r="F233" s="2" t="inlineStr">
         <is>
           <t>Verify that viewing an event with a pending change request should still show the currently confirmed details alongside the pending request</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr">
+      <c r="G233" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" has a pending change request; its confirmed details (venue, date, time) remain unchanged</t>
         </is>
       </c>
-      <c r="H227" s="2" t="inlineStr">
+      <c r="H233" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Community Meetup"</t>
         </is>
       </c>
-      <c r="I227" s="2" t="inlineStr">
+      <c r="I233" s="2" t="inlineStr">
         <is>
           <t>Pending request: Increase expected attendance to 10</t>
         </is>
       </c>
-      <c r="J227" s="2" t="inlineStr">
+      <c r="J233" s="2" t="inlineStr">
         <is>
           <t>The page shows both the currently confirmed details and the pending change request together</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="2" t="n">
+    <row r="234">
+      <c r="A234" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B228" s="2" t="inlineStr">
+      <c r="B234" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C228" s="2" t="inlineStr">
+      <c r="C234" s="2" t="inlineStr">
         <is>
           <t>E10-S01 - Scenario 3 (Refused edit offers the form)</t>
         </is>
       </c>
-      <c r="D228" s="2" t="inlineStr">
+      <c r="D234" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="E234" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_03</t>
         </is>
       </c>
-      <c r="F228" s="2" t="inlineStr">
+      <c r="F234" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to directly edit a restricted field after approval should be refused and offered the change request form pre-filled with that field</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr">
+      <c r="G234" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" has status "Confirmed"</t>
         </is>
       </c>
-      <c r="H228" s="2" t="inlineStr">
+      <c r="H234" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Community Meetup"
   3. Attempt to directly edit the Expected Attendance field</t>
         </is>
       </c>
-      <c r="I228" s="2" t="inlineStr">
+      <c r="I234" s="2" t="inlineStr">
         <is>
           <t>Field attempted: Expected Attendance</t>
         </is>
       </c>
-      <c r="J228" s="2" t="inlineStr">
+      <c r="J234" s="2" t="inlineStr">
         <is>
           <t>Direct editing is refused; organiser_a@clienta.com is offered the change request form, pre-filled with the Expected Attendance field</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="2" t="n">
+    <row r="235">
+      <c r="A235" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B229" s="2" t="inlineStr">
+      <c r="B235" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C229" s="2" t="inlineStr">
+      <c r="C235" s="2" t="inlineStr">
         <is>
           <t>E10-S01 - Scenario 4 (Approved change applied)</t>
         </is>
       </c>
-      <c r="D229" s="2" t="inlineStr">
+      <c r="D235" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E229" s="2" t="inlineStr">
+      <c r="E235" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_04</t>
         </is>
       </c>
-      <c r="F229" s="2" t="inlineStr">
+      <c r="F235" s="2" t="inlineStr">
         <is>
           <t>Verify that when the Coordinator approves a change request, the event should be updated and the Organiser notified</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr">
+      <c r="G235" s="2" t="inlineStr">
         <is>
           <t>A change request on "Community Meetup" (increase expected attendance to 10) is pending Coordinator approval</t>
         </is>
       </c>
-      <c r="H229" s="2" t="inlineStr">
+      <c r="H235" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the pending change request
@@ -12440,52 +12759,52 @@
   4. Log in as organiser_a@clienta.com and check the event and notifications</t>
         </is>
       </c>
-      <c r="I229" s="2" t="inlineStr">
+      <c r="I235" s="2" t="inlineStr">
         <is>
           <t>Change: Expected Attendance -&gt; 10</t>
         </is>
       </c>
-      <c r="J229" s="2" t="inlineStr">
+      <c r="J235" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s Expected Attendance is updated to 10, and organiser_a@clienta.com is notified that the change was applied</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="2" t="n">
+    <row r="236">
+      <c r="A236" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B230" s="2" t="inlineStr">
+      <c r="B236" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C230" s="2" t="inlineStr">
+      <c r="C236" s="2" t="inlineStr">
         <is>
           <t>E10-S01 (checklist: notified when Coordinator approves or declines)</t>
         </is>
       </c>
-      <c r="D230" s="2" t="inlineStr">
+      <c r="D236" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E230" s="2" t="inlineStr">
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_05</t>
         </is>
       </c>
-      <c r="F230" s="2" t="inlineStr">
+      <c r="F236" s="2" t="inlineStr">
         <is>
           <t>Verify that when the Coordinator declines a change request, the Organiser should be notified</t>
         </is>
       </c>
-      <c r="G230" s="2" t="inlineStr">
+      <c r="G236" s="2" t="inlineStr">
         <is>
           <t>A change request on "Community Meetup" is pending Coordinator approval</t>
         </is>
       </c>
-      <c r="H230" s="2" t="inlineStr">
+      <c r="H236" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the pending change request
@@ -12494,105 +12813,105 @@
   5. Log in as organiser_a@clienta.com and check notifications</t>
         </is>
       </c>
-      <c r="I230" s="2" t="inlineStr">
+      <c r="I236" s="2" t="inlineStr">
         <is>
           <t>Decision: Declined</t>
         </is>
       </c>
-      <c r="J230" s="2" t="inlineStr">
+      <c r="J236" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is notified that the change request was declined, and the event remains unchanged
 ## E10-S02</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="2" t="n">
+    <row r="237">
+      <c r="A237" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B231" s="2" t="inlineStr">
+      <c r="B237" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C231" s="2" t="inlineStr">
+      <c r="C237" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 1 (Attendance beyond capacity flagged)</t>
         </is>
       </c>
-      <c r="D231" s="2" t="inlineStr">
+      <c r="D237" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E231" s="2" t="inlineStr">
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_01</t>
         </is>
       </c>
-      <c r="F231" s="2" t="inlineStr">
+      <c r="F237" s="2" t="inlineStr">
         <is>
           <t>Verify that increasing a event's expected attendance beyond its confirmed venue's capacity should flag the venue booking for review and notify Venue Staff</t>
         </is>
       </c>
-      <c r="G231" s="2" t="inlineStr">
+      <c r="G237" s="2" t="inlineStr">
         <is>
           <t>A event of "Tech Conference 2026" has a confirmed venue "Riverside Hall" with capacity 200</t>
         </is>
       </c>
-      <c r="H231" s="2" t="inlineStr">
+      <c r="H237" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Increase the event's Expected Attendance to 250
   3. Save</t>
         </is>
       </c>
-      <c r="I231" s="2" t="inlineStr">
+      <c r="I237" s="2" t="inlineStr">
         <is>
           <t>Expected Attendance: 200 -&gt; 250 (venue capacity: 200)</t>
         </is>
       </c>
-      <c r="J231" s="2" t="inlineStr">
+      <c r="J237" s="2" t="inlineStr">
         <is>
           <t>The venue booking for "Riverside Hall" is flagged for review, and venue_staff_1@connectsphere.com is notified</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="2" t="n">
+    <row r="238">
+      <c r="A238" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B232" s="2" t="inlineStr">
+      <c r="B238" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C232" s="2" t="inlineStr">
+      <c r="C238" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 2 (Description-only edit flags nothing)</t>
         </is>
       </c>
-      <c r="D232" s="2" t="inlineStr">
+      <c r="D238" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E232" s="2" t="inlineStr">
+      <c r="E238" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_02</t>
         </is>
       </c>
-      <c r="F232" s="2" t="inlineStr">
+      <c r="F238" s="2" t="inlineStr">
         <is>
           <t>Verify that editing only the event description on an event with confirmed venue and equipment should flag nothing</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr">
+      <c r="G238" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has a confirmed venue and equipment</t>
         </is>
       </c>
-      <c r="H232" s="2" t="inlineStr">
+      <c r="H238" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Edit only the Description field
@@ -12600,208 +12919,208 @@
   4. Check for any flagged arrangements</t>
         </is>
       </c>
-      <c r="I232" s="2" t="inlineStr">
+      <c r="I238" s="2" t="inlineStr">
         <is>
           <t>Field changed: Description only</t>
         </is>
       </c>
-      <c r="J232" s="2" t="inlineStr">
+      <c r="J238" s="2" t="inlineStr">
         <is>
           <t>No arrangements are flagged as a result of this edit</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="2" t="n">
+    <row r="239">
+      <c r="A239" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B233" s="2" t="inlineStr">
+      <c r="B239" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C233" s="2" t="inlineStr">
+      <c r="C239" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 3 (Affected arrangements shown first)</t>
         </is>
       </c>
-      <c r="D233" s="2" t="inlineStr">
+      <c r="D239" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E233" s="2" t="inlineStr">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_03</t>
         </is>
       </c>
-      <c r="F233" s="2" t="inlineStr">
+      <c r="F239" s="2" t="inlineStr">
         <is>
           <t>Verify that saving a change that affects confirmed arrangements should show which arrangements are affected before the change takes effect</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr">
+      <c r="G239" s="2" t="inlineStr">
         <is>
           <t>A pending edit to "Tech Conference 2026" would affect its confirmed venue booking</t>
         </is>
       </c>
-      <c r="H233" s="2" t="inlineStr">
+      <c r="H239" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Make the edit that affects the venue booking
   3. Click "Save"</t>
         </is>
       </c>
-      <c r="I233" s="2" t="inlineStr">
+      <c r="I239" s="2" t="inlineStr">
         <is>
           <t>Edit: affects the confirmed venue booking</t>
         </is>
       </c>
-      <c r="J233" s="2" t="inlineStr">
+      <c r="J239" s="2" t="inlineStr">
         <is>
           <t>Before the change is applied, a confirmation screen lists the affected arrangement (venue booking) for review</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="2" t="n">
+    <row r="240">
+      <c r="A240" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B234" s="2" t="inlineStr">
+      <c r="B240" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C234" s="2" t="inlineStr">
+      <c r="C240" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 4 (Over-subscription warns only)</t>
         </is>
       </c>
-      <c r="D234" s="2" t="inlineStr">
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_04</t>
         </is>
       </c>
-      <c r="F234" s="2" t="inlineStr">
+      <c r="F240" s="2" t="inlineStr">
         <is>
           <t>Verify that a venue change that reduces a event's capacity below its registration count should warn the Coordinator and show the over-subscription without automatically removing or waitlisting anyone</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr">
+      <c r="G240" s="2" t="inlineStr">
         <is>
           <t>A event of "Tech Conference 2026" has 100 registered; a venue change is about to reduce its capacity to 80</t>
         </is>
       </c>
-      <c r="H234" s="2" t="inlineStr">
+      <c r="H240" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Change the event's venue to one with capacity 80
   3. Save</t>
         </is>
       </c>
-      <c r="I234" s="2" t="inlineStr">
+      <c r="I240" s="2" t="inlineStr">
         <is>
           <t>New capacity: 80; Registered: 100</t>
         </is>
       </c>
-      <c r="J234" s="2" t="inlineStr">
+      <c r="J240" s="2" t="inlineStr">
         <is>
           <t>coordinator_1@connectsphere.com is warned and shown the over-subscription (100 vs 80); no Attendee is automatically removed or waitlisted</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="2" t="n">
+    <row r="241">
+      <c r="A241" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B235" s="2" t="inlineStr">
+      <c r="B241" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C235" s="2" t="inlineStr">
+      <c r="C241" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 5 (Date change flags venue and equipment)</t>
         </is>
       </c>
-      <c r="D235" s="2" t="inlineStr">
+      <c r="D241" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_05</t>
         </is>
       </c>
-      <c r="F235" s="2" t="inlineStr">
+      <c r="F241" s="2" t="inlineStr">
         <is>
           <t>Verify that changing a event's date or time should flag its venue booking and equipment reservations as requiring reconfirmation</t>
         </is>
       </c>
-      <c r="G235" s="2" t="inlineStr">
+      <c r="G241" s="2" t="inlineStr">
         <is>
           <t>A event of "Tech Conference 2026" has a confirmed venue and reserved equipment</t>
         </is>
       </c>
-      <c r="H235" s="2" t="inlineStr">
+      <c r="H241" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Change the event's date from 15/11/2026 to 20/11/2026
   3. Save</t>
         </is>
       </c>
-      <c r="I235" s="2" t="inlineStr">
+      <c r="I241" s="2" t="inlineStr">
         <is>
           <t>Date: 15/11/2026 -&gt; 20/11/2026</t>
         </is>
       </c>
-      <c r="J235" s="2" t="inlineStr">
+      <c r="J241" s="2" t="inlineStr">
         <is>
           <t>Both the venue booking and the equipment reservations for this event are flagged as requiring reconfirmation</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="2" t="n">
+    <row r="242">
+      <c r="A242" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B236" s="2" t="inlineStr">
+      <c r="B242" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C236" s="2" t="inlineStr">
+      <c r="C242" s="2" t="inlineStr">
         <is>
           <t>E10-S02 (checklist: Venue Staff and Technical Support Staff both notified)</t>
         </is>
       </c>
-      <c r="D236" s="2" t="inlineStr">
+      <c r="D242" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting (notification consistency)</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="E242" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_06</t>
         </is>
       </c>
-      <c r="F236" s="2" t="inlineStr">
+      <c r="F242" s="2" t="inlineStr">
         <is>
           <t>Verify that when a date or time change flags arrangements for reconfirmation, the assigned Technical Support Staff should also be notified, not just Venue Staff</t>
         </is>
       </c>
-      <c r="G236" s="2" t="inlineStr">
+      <c r="G242" s="2" t="inlineStr">
         <is>
           <t>A event of "Tech Conference 2026" has a confirmed venue, reserved equipment, and tech_support_1@connectsphere.com assigned for on-site support</t>
         </is>
       </c>
-      <c r="H236" s="2" t="inlineStr">
+      <c r="H242" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Change the event's date
@@ -12809,53 +13128,53 @@
   4. Check notifications for both venue_staff_1@connectsphere.com and tech_support_1@connectsphere.com</t>
         </is>
       </c>
-      <c r="I236" s="2" t="inlineStr">
+      <c r="I242" s="2" t="inlineStr">
         <is>
           <t>Changed field: Date</t>
         </is>
       </c>
-      <c r="J236" s="2" t="inlineStr">
+      <c r="J242" s="2" t="inlineStr">
         <is>
           <t>Both venue_staff_1@connectsphere.com and tech_support_1@connectsphere.com receive a notification about the change requiring reconfirmation
 ## E10-S04</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="2" t="n">
+    <row r="243">
+      <c r="A243" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B237" s="2" t="inlineStr">
+      <c r="B243" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="C237" s="2" t="inlineStr">
+      <c r="C243" s="2" t="inlineStr">
         <is>
           <t>E10-S04 - Scenario 1 (Event cancelled, arrangements released)</t>
         </is>
       </c>
-      <c r="D237" s="2" t="inlineStr">
+      <c r="D243" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="E243" s="2" t="inlineStr">
         <is>
           <t>TC_E10S04_01</t>
         </is>
       </c>
-      <c r="F237" s="2" t="inlineStr">
+      <c r="F243" s="2" t="inlineStr">
         <is>
           <t>Verify that cancelling an event and recording a reason should release its venue bookings and equipment reservations, update the venue calendars, and notify affected staff</t>
         </is>
       </c>
-      <c r="G237" s="2" t="inlineStr">
+      <c r="G243" s="2" t="inlineStr">
         <is>
           <t>Event "Product Launch Night" has status "Confirmed" with a confirmed venue "Small Room" and reserved equipment</t>
         </is>
       </c>
-      <c r="H237" s="2" t="inlineStr">
+      <c r="H243" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Product Launch Night"
@@ -12864,156 +13183,156 @@
   5. Confirm</t>
         </is>
       </c>
-      <c r="I237" s="2" t="inlineStr">
+      <c r="I243" s="2" t="inlineStr">
         <is>
           <t>Cancellation reason: "Insufficient sponsor funding"</t>
         </is>
       </c>
-      <c r="J237" s="2" t="inlineStr">
+      <c r="J243" s="2" t="inlineStr">
         <is>
           <t>The status becomes "Cancelled"; "Small Room"'s booking and the reserved equipment are released, the venue calendar is updated, and affected staff are notified</t>
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="2" t="n">
+    <row r="244">
+      <c r="A244" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B238" s="2" t="inlineStr">
+      <c r="B244" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="C238" s="2" t="inlineStr">
+      <c r="C244" s="2" t="inlineStr">
         <is>
           <t>E10-S04 - Scenario 2 (Attendees and waitlist notified)</t>
         </is>
       </c>
-      <c r="D238" s="2" t="inlineStr">
+      <c r="D244" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="E244" s="2" t="inlineStr">
         <is>
           <t>TC_E10S04_03</t>
         </is>
       </c>
-      <c r="F238" s="2" t="inlineStr">
+      <c r="F244" s="2" t="inlineStr">
         <is>
           <t>Verify that cancelling a event should notify all of its registered and waitlisted Attendees</t>
         </is>
       </c>
-      <c r="G238" s="2" t="inlineStr">
+      <c r="G244" s="2" t="inlineStr">
         <is>
           <t>The event of "Tech Conference 2026" being cancelled has attendee_a@example.com registered and attendee_l@example.com waitlisted</t>
         </is>
       </c>
-      <c r="H238" s="2" t="inlineStr">
+      <c r="H244" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Cancel the event
   3. Check notifications for attendee_a@example.com and attendee_l@example.com</t>
         </is>
       </c>
-      <c r="I238" s="2" t="inlineStr">
+      <c r="I244" s="2" t="inlineStr">
         <is>
           <t>Registered: attendee_a@example.com | Waitlisted: attendee_l@example.com</t>
         </is>
       </c>
-      <c r="J238" s="2" t="inlineStr">
+      <c r="J244" s="2" t="inlineStr">
         <is>
           <t>Both attendee_a@example.com and attendee_l@example.com receive a notification of the cancellation</t>
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="2" t="n">
+    <row r="245">
+      <c r="A245" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B239" s="2" t="inlineStr">
+      <c r="B245" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="C239" s="2" t="inlineStr">
+      <c r="C245" s="2" t="inlineStr">
         <is>
           <t>E10-S04 - Scenario 3 (Cancelled event read-only)</t>
         </is>
       </c>
-      <c r="D239" s="2" t="inlineStr">
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
         <is>
           <t>TC_E10S04_04</t>
         </is>
       </c>
-      <c r="F239" s="2" t="inlineStr">
+      <c r="F245" s="2" t="inlineStr">
         <is>
           <t>Verify that a cancelled event should be read-only and show its cancellation reason and date to any viewer</t>
         </is>
       </c>
-      <c r="G239" s="2" t="inlineStr">
+      <c r="G245" s="2" t="inlineStr">
         <is>
           <t>Event "Product Launch Night" was cancelled on 12/09/2026 with reason "Insufficient sponsor funding" (per TC_E10S04_01)</t>
         </is>
       </c>
-      <c r="H239" s="2" t="inlineStr">
+      <c r="H245" s="2" t="inlineStr">
         <is>
           <t>1. Log in as any user with access (e.g. organiser_a@clienta.com)
   2. Open the cancelled event "Product Launch Night"
   3. Attempt to edit any field</t>
         </is>
       </c>
-      <c r="I239" s="2" t="inlineStr">
+      <c r="I245" s="2" t="inlineStr">
         <is>
           <t>Cancellation reason: "Insufficient sponsor funding" | Date: 12/09/2026</t>
         </is>
       </c>
-      <c r="J239" s="2" t="inlineStr">
+      <c r="J245" s="2" t="inlineStr">
         <is>
           <t>The event shows "Cancelled on 12 September 2026 - Insufficient sponsor funding"; all fields are read-only</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="2" t="n">
+    <row r="246">
+      <c r="A246" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B240" s="2" t="inlineStr">
+      <c r="B246" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="C240" s="2" t="inlineStr">
+      <c r="C246" s="2" t="inlineStr">
         <is>
           <t>E10-S04 - Scenario 4 (Organiser cancellation becomes a request)</t>
         </is>
       </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>TC_E10S04_05</t>
         </is>
       </c>
-      <c r="F240" s="2" t="inlineStr">
+      <c r="F246" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Organiser attempting to cancel directly should have the action recorded as a cancellation request for the Coordinator to action</t>
         </is>
       </c>
-      <c r="G240" s="2" t="inlineStr">
+      <c r="G246" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" has status "Confirmed", assigned to coordinator_1@connectsphere.com</t>
         </is>
       </c>
-      <c r="H240" s="2" t="inlineStr">
+      <c r="H246" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Community Meetup"
@@ -13021,308 +13340,517 @@
   4. Enter a reason and submit</t>
         </is>
       </c>
-      <c r="I240" s="2" t="inlineStr">
+      <c r="I246" s="2" t="inlineStr">
         <is>
           <t>Reason: "No longer needed"</t>
         </is>
       </c>
-      <c r="J240" s="2" t="inlineStr">
-        <is>
-          <t>The event is NOT immediately cancelled; instead, a cancellation request is recorded and coordinator_1@connectsphere.com is notified to action it</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="J246" s="2" t="inlineStr">
+        <is>
+          <t>The event is NOT immediately cancelled; instead, a cancellation request is recorded and coordinator_1@connectsphere.com is notified to action it
+## E10-S05</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>E10-S05</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>E10-S05 — Scenario 1 (Lost venue flags the event); assumes O-24</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>TC_E10S05_01</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>Verify that when a booked venue is marked unavailable the Coordinator's event should be flagged with the booking shown as Conflicting while status and other arrangements stay unchanged</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>Event "Charity Run" is Confirmed with a Confirmed booking at "Riverside Hall" on 15/01/2027 10:00-12:00, a reserved projector and an assigned technical staff member; coordinator_1@connectsphere.com owns it</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>1. As venue_staff_1@connectsphere.com, mark "Riverside Hall" unavailable 15/01/2027 00:00 to 16/01/2027 00:00, category "Renovation" (E05-S06)
+  2. Sign in as coordinator_1@connectsphere.com and open the inbox
+  3. Open event "Charity Run"</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>Event status before: Confirmed | Equipment: 1 projector reserved | Technical staff: 1 assigned</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="inlineStr">
+        <is>
+          <t>coordinator_1 has a notification about the lost venue; the event page shows a "needs alternative arrangements" flag with reason "Renovation", the venue booking marked Conflicting, status still Confirmed, and the projector reservation and staff assignment unchanged</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>E10-S05</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>E10-S05 — Scenario 2 (Flagged event offers a replacement search)</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>TC_E10S05_02</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>Verify that a flagged event should show the reason, period and affected booking, preserve the original event information, and offer a venue search for the same event</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>As TC_E10S05_01 after step 1; coordinator_1@connectsphere.com is signed in</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>1. Open event "Charity Run"
+  2. Read the flag panel
+  3. Click "Find a replacement venue"</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>Original: Riverside Hall, 15/01/2027 10:00-12:00, 120 attendees, Theatre layout, wheelchair access required</t>
+        </is>
+      </c>
+      <c r="J248" s="2" t="inlineStr">
+        <is>
+          <t>The panel shows reason "Renovation", period 15/01/2027, and the Conflicting Riverside Hall booking; the event's dates, attendance, layout and accessibility requirements are unchanged; the search opens pre-filled with those requirements for the same event (E06-S01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>E10-S05</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>E10-S05 — Scenario 3 (Replacement requested without losing the original)</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>TC_E10S05_03</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>Verify that requesting a replacement venue should create a second booking request on the same event without cancelling the Conflicting booking, which the Coordinator cancels explicitly afterwards</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>As TC_E10S05_02; venue "Harbour Suite" is Free on 15/01/2027 and meets the requirements</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>1. From the replacement search, request "Harbour Suite" for 15/01/2027 10:00-12:00 (E06-S03)
+  2. Open event "Charity Run" and read its venue bookings
+  3. As venue_staff_1@connectsphere.com, approve the Harbour Suite request (E06-S04)
+  4. As coordinator_1, cancel the Conflicting Riverside Hall booking</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>Replacement: Harbour Suite 15/01/2027 10:00-12:00</t>
+        </is>
+      </c>
+      <c r="J249" s="2" t="inlineStr">
+        <is>
+          <t>After step 1 the event shows two bookings: Riverside Hall (Conflicting) and Harbour Suite (Pending); after step 3 Harbour Suite is Confirmed and Riverside Hall is still Conflicting, not auto-cancelled; after step 4 only Harbour Suite remains and the event is still Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>E10-S05</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>E10-S05 — Scenario 4 (Organiser and Attendees told on the actual change); assumes O-25</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>3 - Cross-cutting (notification consistency)</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>TC_E10S05_04</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>Verify that the Organiser and registered Attendees should be notified of the venue change only when the replacement is confirmed, not when the original venue is lost</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>As TC_E10S05_03 with the Organiser organiser_1@connectsphere.com and two registered Attendees; notification relay enabled against the intercepted provider</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>1. After the venue is marked unavailable (TC_E10S05_01 step 1), check the Organiser's and Attendees' inboxes and the intercepted emails
+  2. After the Harbour Suite request is approved (TC_E10S05_03 step 3), check them again</t>
+        </is>
+      </c>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>Recipients at step 2: organiser_1, attendee_1, attendee_2</t>
+        </is>
+      </c>
+      <c r="J250" s="2" t="inlineStr">
+        <is>
+          <t>At step 1 none of the Organiser or Attendees has a notification about the venue; at step 2 each has exactly one notification naming the new venue "Harbour Suite" via the existing venue-change routing (E11-S01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B241" s="2" t="inlineStr">
+      <c r="B251" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C241" s="2" t="inlineStr">
+      <c r="C251" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 1 (Status change notified)</t>
         </is>
       </c>
-      <c r="D241" s="2" t="inlineStr">
+      <c r="D251" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E241" s="2" t="inlineStr">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_01</t>
         </is>
       </c>
-      <c r="F241" s="2" t="inlineStr">
+      <c r="F251" s="2" t="inlineStr">
         <is>
           <t>Verify that a user linked to an event should be notified when its status changes or a booking decision is made, with details of what/when/which event</t>
         </is>
       </c>
-      <c r="G241" s="2" t="inlineStr">
+      <c r="G251" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is linked to event "Annual Tech Summit", currently "Under Review"</t>
         </is>
       </c>
-      <c r="H241" s="2" t="inlineStr">
+      <c r="H251" s="2" t="inlineStr">
         <is>
           <t>1. As coordinator_1@connectsphere.com, approve request "Annual Tech Summit" (status -&gt; Approved)
   2. Log in as organiser_a@clienta.com and open notifications</t>
         </is>
       </c>
-      <c r="I241" s="2" t="inlineStr">
+      <c r="I251" s="2" t="inlineStr">
         <is>
           <t>Event: Annual Tech Summit | Change: Under Review -&gt; Approved</t>
         </is>
       </c>
-      <c r="J241" s="2" t="inlineStr">
+      <c r="J251" s="2" t="inlineStr">
         <is>
           <t>A notification is received stating the status changed to "Approved", the time of the change, and that it concerns "Annual Tech Summit"</t>
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="2" t="n">
+    <row r="252">
+      <c r="A252" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B242" s="2" t="inlineStr">
+      <c r="B252" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C242" s="2" t="inlineStr">
+      <c r="C252" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 2 (All affected parties notified)</t>
         </is>
       </c>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="D252" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E242" s="2" t="inlineStr">
+      <c r="E252" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_02</t>
         </is>
       </c>
-      <c r="F242" s="2" t="inlineStr">
+      <c r="F252" s="2" t="inlineStr">
         <is>
           <t>Verify that effective date, time or venue changes follow the approved recipient matrix</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr">
+      <c r="G252" s="2" t="inlineStr">
         <is>
           <t>Event "Annual Tech Summit" the event has organiser_a@clienta.com, venue_staff_1@connectsphere.com, and tech_support_1@connectsphere.com assigned, and attendee_a@example.com registered; attendee_b@example.com is waitlisted and coordinator_1@connectsphere.com is the assigned Coordinator</t>
         </is>
       </c>
-      <c r="H242" s="2" t="inlineStr">
+      <c r="H252" s="2" t="inlineStr">
         <is>
           <t>1. As coordinator_1@connectsphere.com, change the event's venue
   2. Check notifications for organiser_a@clienta.com, venue_staff_1@connectsphere.com, tech_support_1@connectsphere.com, and attendee_a@example.com</t>
         </is>
       </c>
-      <c r="I242" s="2" t="inlineStr">
+      <c r="I252" s="2" t="inlineStr">
         <is>
           <t>Changed field: Venue</t>
         </is>
       </c>
-      <c r="J242" s="2" t="inlineStr">
+      <c r="J252" s="2" t="inlineStr">
         <is>
           <t>The Organiser, assigned Venue Staff, assigned Technical Support Staff, registered Attendee and waitlisted Attendee receive a notification. The acting Coordinator receives no self-notification. If another authorized actor or a system operation makes the change, the assigned Coordinator is included. Venue-move tests include responsible staff for both the old and new venues. Backend resolver fixtures are not evidence that the venue-assignment workflow is implemented.</t>
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="2" t="n">
+    <row r="253">
+      <c r="A253" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B243" s="2" t="inlineStr">
+      <c r="B253" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C243" s="2" t="inlineStr">
+      <c r="C253" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 3 (Unaffected users not notified)</t>
         </is>
       </c>
-      <c r="D243" s="2" t="inlineStr">
+      <c r="D253" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E243" s="2" t="inlineStr">
+      <c r="E253" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_03</t>
         </is>
       </c>
-      <c r="F243" s="2" t="inlineStr">
+      <c r="F253" s="2" t="inlineStr">
         <is>
           <t>Verify that a user whose responsibilities are unaffected by a change should not be notified</t>
         </is>
       </c>
-      <c r="G243" s="2" t="inlineStr">
+      <c r="G253" s="2" t="inlineStr">
         <is>
           <t>Event "Annual Tech Summit" the event's Description field is about to be edited; venue_staff_1@connectsphere.com has no responsibility tied to the Description field</t>
         </is>
       </c>
-      <c r="H243" s="2" t="inlineStr">
+      <c r="H253" s="2" t="inlineStr">
         <is>
           <t>1. As organiser_a@clienta.com, edit the Description field only
   2. Check venue_staff_1@connectsphere.com's notifications</t>
         </is>
       </c>
-      <c r="I243" s="2" t="inlineStr">
+      <c r="I253" s="2" t="inlineStr">
         <is>
           <t>Changed field: Description only</t>
         </is>
       </c>
-      <c r="J243" s="2" t="inlineStr">
+      <c r="J253" s="2" t="inlineStr">
         <is>
           <t>venue_staff_1@connectsphere.com receives no notification, since the Description change does not affect their responsibilities</t>
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="2" t="n">
+    <row r="254">
+      <c r="A254" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B244" s="2" t="inlineStr">
+      <c r="B254" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C244" s="2" t="inlineStr">
+      <c r="C254" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 4 (Delivered in-app and by email)</t>
         </is>
       </c>
-      <c r="D244" s="2" t="inlineStr">
+      <c r="D254" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E244" s="2" t="inlineStr">
+      <c r="E254" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_05</t>
         </is>
       </c>
-      <c r="F244" s="2" t="inlineStr">
+      <c r="F254" s="2" t="inlineStr">
         <is>
           <t>Verify that a generated notification should appear in the system and also be sent to the user's registered email address</t>
         </is>
       </c>
-      <c r="G244" s="2" t="inlineStr">
+      <c r="G254" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com's registered email is organiser_a@clienta.com; a notification-triggering status change is about to occur on their event</t>
         </is>
       </c>
-      <c r="H244" s="2" t="inlineStr">
+      <c r="H254" s="2" t="inlineStr">
         <is>
           <t>1. Trigger a status change on organiser_a@clienta.com's event
   2. Log in as organiser_a@clienta.com and check the in-app notification list
   3. Check the inbox for organiser_a@clienta.com</t>
         </is>
       </c>
-      <c r="I244" s="2" t="inlineStr">
+      <c r="I254" s="2" t="inlineStr">
         <is>
           <t>Registered email: organiser_a@clienta.com</t>
         </is>
       </c>
-      <c r="J244" s="2" t="inlineStr">
+      <c r="J254" s="2" t="inlineStr">
         <is>
           <t>The notification appears in the in-app notification list, and an equivalent email is also delivered to organiser_a@clienta.com's inbox</t>
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="2" t="n">
+    <row r="255">
+      <c r="A255" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B245" s="2" t="inlineStr">
+      <c r="B255" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C245" s="2" t="inlineStr">
+      <c r="C255" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 5 (Unread notifications distinguished)</t>
         </is>
       </c>
-      <c r="D245" s="2" t="inlineStr">
+      <c r="D255" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E245" s="2" t="inlineStr">
+      <c r="E255" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_06</t>
         </is>
       </c>
-      <c r="F245" s="2" t="inlineStr">
+      <c r="F255" s="2" t="inlineStr">
         <is>
           <t>Verify that opening the notification list with several unread notifications should show them newest first with unread ones distinguished</t>
         </is>
       </c>
-      <c r="G245" s="2" t="inlineStr">
+      <c r="G255" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com has 3 notifications on 09/09/2026: 08:00 (read), 10:00 (unread), 14:00 (unread)</t>
         </is>
       </c>
-      <c r="H245" s="2" t="inlineStr">
+      <c r="H255" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the notification list</t>
         </is>
       </c>
-      <c r="I245" s="2" t="inlineStr">
+      <c r="I255" s="2" t="inlineStr">
         <is>
           <t>Notifications: 08:00 (read), 10:00 (unread), 14:00 (unread)</t>
         </is>
       </c>
-      <c r="J245" s="2" t="inlineStr">
+      <c r="J255" s="2" t="inlineStr">
         <is>
           <t>Notifications are listed newest first (14:00, then 10:00, then 08:00), with the 14:00 and 10:00 entries visually marked as unread and 08:00 shown as read</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="2" t="n">
+    <row r="256">
+      <c r="A256" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B246" s="2" t="inlineStr">
+      <c r="B256" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C246" s="2" t="inlineStr">
+      <c r="C256" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 6 (Marked as read)</t>
         </is>
       </c>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="D256" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="E256" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_07</t>
         </is>
       </c>
-      <c r="F246" s="2" t="inlineStr">
+      <c r="F256" s="2" t="inlineStr">
         <is>
           <t>Verify that opening an unread notification should mark it as read</t>
         </is>
       </c>
-      <c r="G246" s="2" t="inlineStr">
+      <c r="G256" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com has an unread notification from 10:00 on 09/09/2026</t>
         </is>
       </c>
-      <c r="H246" s="2" t="inlineStr">
+      <c r="H256" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the notification list
@@ -13330,52 +13858,52 @@
   4. Return to the notification list</t>
         </is>
       </c>
-      <c r="I246" s="2" t="inlineStr">
+      <c r="I256" s="2" t="inlineStr">
         <is>
           <t>Notification: 10:00 on 09/09/2026 (initially unread)</t>
         </is>
       </c>
-      <c r="J246" s="2" t="inlineStr">
+      <c r="J256" s="2" t="inlineStr">
         <is>
           <t>The 10:00 notification is now shown as read (no longer marked unread) in the list</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="2" t="n">
+    <row r="257">
+      <c r="A257" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B247" s="2" t="inlineStr">
+      <c r="B257" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C247" s="2" t="inlineStr">
+      <c r="C257" s="2" t="inlineStr">
         <is>
           <t>E11-S01 · Scenario 5 (Delivered in-app and by email) · ADR-006</t>
         </is>
       </c>
-      <c r="D247" s="2" t="inlineStr">
+      <c r="D257" s="2" t="inlineStr">
         <is>
           <t>4 - Negative (third-party unavailable)</t>
         </is>
       </c>
-      <c r="E247" s="2" t="inlineStr">
+      <c r="E257" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_08</t>
         </is>
       </c>
-      <c r="F247" s="2" t="inlineStr">
+      <c r="F257" s="2" t="inlineStr">
         <is>
           <t>Verify that an unreachable email provider does not affect the business change or the in-app notification</t>
         </is>
       </c>
-      <c r="G247" s="2" t="inlineStr">
+      <c r="G257" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2003 has an assigned Coordinator coord_a@connectsphere.com. The email provider endpoint is configured to an unreachable host so every SMTP attempt fails</t>
         </is>
       </c>
-      <c r="H247" s="2" t="inlineStr">
+      <c r="H257" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Venue Staff and approve the pending venue booking for EVT-2003
  2. Confirm the booking status has changed
@@ -13383,52 +13911,52 @@
  4. Inspect the delivery records for that notification</t>
         </is>
       </c>
-      <c r="I247" s="2" t="inlineStr">
+      <c r="I257" s="2" t="inlineStr">
         <is>
           <t>SMTP host: unreachable · Notification: venue booking approved</t>
         </is>
       </c>
-      <c r="J247" s="2" t="inlineStr">
+      <c r="J257" s="2" t="inlineStr">
         <is>
           <t>The booking is Confirmed and the change persists. The in-app notification appears for the Coordinator. The email delivery row is marked failed with a recorded reason. The business transaction is not rolled back by the email failure</t>
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="2" t="n">
+    <row r="258">
+      <c r="A258" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B248" s="2" t="inlineStr">
+      <c r="B258" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C248" s="2" t="inlineStr">
+      <c r="C258" s="2" t="inlineStr">
         <is>
           <t>E11-S01 · Scenario 1 (Status change notified) · ADR-006 outbox guarantee</t>
         </is>
       </c>
-      <c r="D248" s="2" t="inlineStr">
+      <c r="D258" s="2" t="inlineStr">
         <is>
           <t>4 - Negative (transaction rollback)</t>
         </is>
       </c>
-      <c r="E248" s="2" t="inlineStr">
+      <c r="E258" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_09</t>
         </is>
       </c>
-      <c r="F248" s="2" t="inlineStr">
+      <c r="F258" s="2" t="inlineStr">
         <is>
           <t>Verify that a rolled-back business transaction publishes no notification</t>
         </is>
       </c>
-      <c r="G248" s="2" t="inlineStr">
+      <c r="G258" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2004 is at status Under Review. A fault is injected so that the approval transaction fails after the notification delivery rows are written but before commit</t>
         </is>
       </c>
-      <c r="H248" s="2" t="inlineStr">
+      <c r="H258" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as the assigned Event Coordinator
  2. Approve EVT-2004, triggering the injected failure
@@ -13436,610 +13964,610 @@
  4. Inspect the job queue and the Organiser's notification list</t>
         </is>
       </c>
-      <c r="I248" s="2" t="inlineStr">
+      <c r="I258" s="2" t="inlineStr">
         <is>
           <t>Event: EVT-2004 · Injected failure point: after delivery rows written, before commit</t>
         </is>
       </c>
-      <c r="J248" s="2" t="inlineStr">
+      <c r="J258" s="2" t="inlineStr">
         <is>
           <t>The event remains at Under Review. No delivery row is persisted, nothing is published to the queue, and the Organiser receives no in-app notification and no email. Only committed deliveries are ever published</t>
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="2" t="n">
+    <row r="259">
+      <c r="A259" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B249" s="2" t="inlineStr">
+      <c r="B259" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C249" s="2" t="inlineStr">
+      <c r="C259" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
         </is>
       </c>
-      <c r="D249" s="2" t="inlineStr">
+      <c r="D259" s="2" t="inlineStr">
         <is>
           <t>3 - Integration / regression</t>
         </is>
       </c>
-      <c r="E249" s="2" t="inlineStr">
+      <c r="E259" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_10</t>
         </is>
       </c>
-      <c r="F249" s="2" t="inlineStr">
+      <c r="F259" s="2" t="inlineStr">
         <is>
           <t>Apply the approved role/change recipient matrix</t>
         </is>
       </c>
-      <c r="G249" s="2" t="inlineStr">
+      <c r="G259" s="2" t="inlineStr">
         <is>
           <t>The event has active links to all six recipient groups and a public snapshot.</t>
         </is>
       </c>
-      <c r="H249" s="2" t="inlineStr">
+      <c r="H259" s="2" t="inlineStr">
         <is>
           <t>1. Trigger each internal status, booking, equipment, public status, arrangement, place-release and description-only change through the selector.</t>
         </is>
       </c>
-      <c r="I249" s="2" t="inlineStr">
+      <c r="I259" s="2" t="inlineStr">
         <is>
           <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
         </is>
       </c>
-      <c r="J249" s="2" t="inlineStr">
+      <c r="J259" s="2" t="inlineStr">
         <is>
           <t>Recipient sets match the E11-S01 matrix; internal decisions do not reach Attendees; initial Planning differs from Confirmed-to-Planning.</t>
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="2" t="n">
+    <row r="260">
+      <c r="A260" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B250" s="2" t="inlineStr">
+      <c r="B260" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C250" s="2" t="inlineStr">
+      <c r="C260" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
         </is>
       </c>
-      <c r="D250" s="2" t="inlineStr">
+      <c r="D260" s="2" t="inlineStr">
         <is>
           <t>3 - Integration / regression</t>
         </is>
       </c>
-      <c r="E250" s="2" t="inlineStr">
+      <c r="E260" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_11</t>
         </is>
       </c>
-      <c r="F250" s="2" t="inlineStr">
+      <c r="F260" s="2" t="inlineStr">
         <is>
           <t>Suppress self-notifications and duplicate recipient links</t>
         </is>
       </c>
-      <c r="G250" s="2" t="inlineStr">
+      <c r="G260" s="2" t="inlineStr">
         <is>
           <t>A user is both the actor and a candidate recipient; duplicated staff links exist.</t>
         </is>
       </c>
-      <c r="H250" s="2" t="inlineStr">
+      <c r="H260" s="2" t="inlineStr">
         <is>
           <t>1. Select recipients for an arrangement change and an actor-made booking decision.</t>
         </is>
       </c>
-      <c r="I250" s="2" t="inlineStr">
+      <c r="I260" s="2" t="inlineStr">
         <is>
           <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
         </is>
       </c>
-      <c r="J250" s="2" t="inlineStr">
+      <c r="J260" s="2" t="inlineStr">
         <is>
           <t>The actor receives no routine self-notification; every remaining user appears once; system changes have no excluded actor.</t>
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="2" t="n">
+    <row r="261">
+      <c r="A261" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B251" s="2" t="inlineStr">
+      <c r="B261" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C251" s="2" t="inlineStr">
+      <c r="C261" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
         </is>
       </c>
-      <c r="D251" s="2" t="inlineStr">
+      <c r="D261" s="2" t="inlineStr">
         <is>
           <t>3 - Integration / regression</t>
         </is>
       </c>
-      <c r="E251" s="2" t="inlineStr">
+      <c r="E261" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_12</t>
         </is>
       </c>
-      <c r="F251" s="2" t="inlineStr">
+      <c r="F261" s="2" t="inlineStr">
         <is>
           <t>Preserve before/after recipients during cancellation and venue moves</t>
         </is>
       </c>
-      <c r="G251" s="2" t="inlineStr">
+      <c r="G261" s="2" t="inlineStr">
         <is>
           <t>An event has active bookings, assigned staff, registered and waitlisted Attendees.</t>
         </is>
       </c>
-      <c r="H251" s="2" t="inlineStr">
+      <c r="H261" s="2" t="inlineStr">
         <is>
           <t>1. Capture its audience, release links during cancellation or replace the venue, then call the hook with both snapshots.</t>
         </is>
       </c>
-      <c r="I251" s="2" t="inlineStr">
+      <c r="I261" s="2" t="inlineStr">
         <is>
           <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
         </is>
       </c>
-      <c r="J251" s="2" t="inlineStr">
+      <c r="J261" s="2" t="inlineStr">
         <is>
           <t>Cancellation notifies the pre-release audience. Venue moves include responsible staff at both venues. These are hook-contract tests until the owning workflows integrate.</t>
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="2" t="n">
+    <row r="262">
+      <c r="A262" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B252" s="2" t="inlineStr">
+      <c r="B262" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C252" s="2" t="inlineStr">
+      <c r="C262" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
         </is>
       </c>
-      <c r="D252" s="2" t="inlineStr">
+      <c r="D262" s="2" t="inlineStr">
         <is>
           <t>3 - Integration / regression</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="E262" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_13</t>
         </is>
       </c>
-      <c r="F252" s="2" t="inlineStr">
+      <c r="F262" s="2" t="inlineStr">
         <is>
           <t>Expose missing Venue Staff assignments without an unsafe fallback</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr">
+      <c r="G262" s="2" t="inlineStr">
         <is>
           <t>No explicit venue assignment adapter is available; a booking has a decided_by actor and unrelated Venue Staff accounts exist.</t>
         </is>
       </c>
-      <c r="H252" s="2" t="inlineStr">
+      <c r="H262" s="2" t="inlineStr">
         <is>
           <t>1. Capture the audience and select booking-request recipients.</t>
         </is>
       </c>
-      <c r="I252" s="2" t="inlineStr">
+      <c r="I262" s="2" t="inlineStr">
         <is>
           <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
         </is>
       </c>
-      <c r="J252" s="2" t="inlineStr">
+      <c r="J262" s="2" t="inlineStr">
         <is>
           <t>Venue Staff recipients are unresolved, the venue IDs are reported, and neither decided_by nor all Venue Staff is substituted.</t>
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="2" t="n">
+    <row r="263">
+      <c r="A263" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B253" s="2" t="inlineStr">
+      <c r="B263" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C253" s="2" t="inlineStr">
+      <c r="C263" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
         </is>
       </c>
-      <c r="D253" s="2" t="inlineStr">
+      <c r="D263" s="2" t="inlineStr">
         <is>
           <t>3 - Integration / regression</t>
         </is>
       </c>
-      <c r="E253" s="2" t="inlineStr">
+      <c r="E263" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_14</t>
         </is>
       </c>
-      <c r="F253" s="2" t="inlineStr">
+      <c r="F263" s="2" t="inlineStr">
         <is>
           <t>Protect attendee notification content and membership boundaries</t>
         </is>
       </c>
-      <c r="G253" s="2" t="inlineStr">
+      <c r="G263" s="2" t="inlineStr">
         <is>
           <t>The internal event title differs from its publication; registered, waitlisted, withdrawn, inactive and unrelated users exist.</t>
         </is>
       </c>
-      <c r="H253" s="2" t="inlineStr">
+      <c r="H263" s="2" t="inlineStr">
         <is>
           <t>1. Apply an effective date change; inspect notification messages and retained email payloads. Also select recipients for an unpublished event.</t>
         </is>
       </c>
-      <c r="I253" s="2" t="inlineStr">
+      <c r="I263" s="2" t="inlineStr">
         <is>
           <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
         </is>
       </c>
-      <c r="J253" s="2" t="inlineStr">
+      <c r="J263" s="2" t="inlineStr">
         <is>
           <t>Only eligible linked active users are selected. Attendees receive the published event name and fixed public change description; no internal title/reason/comment leaks. Unpublished events produce no attendee notice.</t>
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="2" t="n">
+    <row r="264">
+      <c r="A264" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B254" s="2" t="inlineStr">
+      <c r="B264" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C254" s="2" t="inlineStr">
+      <c r="C264" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
         </is>
       </c>
-      <c r="D254" s="2" t="inlineStr">
+      <c r="D264" s="2" t="inlineStr">
         <is>
           <t>3 - Integration / regression</t>
         </is>
       </c>
-      <c r="E254" s="2" t="inlineStr">
+      <c r="E264" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_15</t>
         </is>
       </c>
-      <c r="F254" s="2" t="inlineStr">
+      <c r="F264" s="2" t="inlineStr">
         <is>
           <t>Deduplicate concurrent notification-hook retries</t>
         </is>
       </c>
-      <c r="G254" s="2" t="inlineStr">
+      <c r="G264" s="2" t="inlineStr">
         <is>
           <t>Two transactions use the same event, stable change ID and recipient snapshot.</t>
         </is>
       </c>
-      <c r="H254" s="2" t="inlineStr">
+      <c r="H264" s="2" t="inlineStr">
         <is>
           <t>1. Call the notification hook concurrently and commit both attempts.</t>
         </is>
       </c>
-      <c r="I254" s="2" t="inlineStr">
+      <c r="I264" s="2" t="inlineStr">
         <is>
           <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
         </is>
       </c>
-      <c r="J254" s="2" t="inlineStr">
+      <c r="J264" s="2" t="inlineStr">
         <is>
           <t>Exactly one in-app row and one email-delivery row exist per recipient for the logical change. A new change ID identifies a different business change.</t>
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" s="2" t="n">
+    <row r="265">
+      <c r="A265" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B255" s="2" t="inlineStr">
+      <c r="B265" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C255" s="2" t="inlineStr">
+      <c r="C265" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
         </is>
       </c>
-      <c r="D255" s="2" t="inlineStr">
+      <c r="D265" s="2" t="inlineStr">
         <is>
           <t>3 - Integration / regression</t>
         </is>
       </c>
-      <c r="E255" s="2" t="inlineStr">
+      <c r="E265" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_16</t>
         </is>
       </c>
-      <c r="F255" s="2" t="inlineStr">
+      <c r="F265" s="2" t="inlineStr">
         <is>
           <t>Keep uncommitted notifications invisible and roll back all writes</t>
         </is>
       </c>
-      <c r="G255" s="2" t="inlineStr">
+      <c r="G265" s="2" t="inlineStr">
         <is>
           <t>A business transaction has inserted notifications and prepared email delivery rows but has not committed.</t>
         </is>
       </c>
-      <c r="H255" s="2" t="inlineStr">
+      <c r="H265" s="2" t="inlineStr">
         <is>
           <t>1. Read from another connection, then force the business transaction to roll back.</t>
         </is>
       </c>
-      <c r="I255" s="2" t="inlineStr">
+      <c r="I265" s="2" t="inlineStr">
         <is>
           <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
         </is>
       </c>
-      <c r="J255" s="2" t="inlineStr">
+      <c r="J265" s="2" t="inlineStr">
         <is>
           <t>The other connection cannot observe the uncommitted messages. After rollback no notification or email-delivery row remains.</t>
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" s="2" t="n">
+    <row r="266">
+      <c r="A266" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B256" s="2" t="inlineStr">
+      <c r="B266" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C256" s="2" t="inlineStr">
+      <c r="C266" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 1 (Status change recorded)</t>
         </is>
       </c>
-      <c r="D256" s="2" t="inlineStr">
+      <c r="D266" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E256" s="2" t="inlineStr">
+      <c r="E266" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_01</t>
         </is>
       </c>
-      <c r="F256" s="2" t="inlineStr">
+      <c r="F266" s="2" t="inlineStr">
         <is>
           <t>Verify that an event status change should be recorded with the actor, action, affected event, and time</t>
         </is>
       </c>
-      <c r="G256" s="2" t="inlineStr">
+      <c r="G266" s="2" t="inlineStr">
         <is>
           <t>Request "Annual Tech Summit" has status "Under Review"</t>
         </is>
       </c>
-      <c r="H256" s="2" t="inlineStr">
+      <c r="H266" s="2" t="inlineStr">
         <is>
           <t>1. As coordinator_1@connectsphere.com, approve the request (status -&gt; Approved)
   2. Log in as a System Administrator
   3. Open the Activity Log and locate the entry</t>
         </is>
       </c>
-      <c r="I256" s="2" t="inlineStr">
+      <c r="I266" s="2" t="inlineStr">
         <is>
           <t>Event: Annual Tech Summit | Action: Approve</t>
         </is>
       </c>
-      <c r="J256" s="2" t="inlineStr">
+      <c r="J266" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded with actor = coordinator_1@connectsphere.com, action = "Status changed to Approved", event = Annual Tech Summit, and a timestamp</t>
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="2" t="n">
+    <row r="267">
+      <c r="A267" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B257" s="2" t="inlineStr">
+      <c r="B267" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C257" s="2" t="inlineStr">
+      <c r="C267" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 2 (Access denial recorded)</t>
         </is>
       </c>
-      <c r="D257" s="2" t="inlineStr">
+      <c r="D267" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E257" s="2" t="inlineStr">
+      <c r="E267" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_02</t>
         </is>
       </c>
-      <c r="F257" s="2" t="inlineStr">
+      <c r="F267" s="2" t="inlineStr">
         <is>
           <t>Verify that a denied access attempt should be recorded with the user, target, and time</t>
         </is>
       </c>
-      <c r="G257" s="2" t="inlineStr">
+      <c r="G267" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is linked to Client A; event EVT-B01 belongs to Client B</t>
         </is>
       </c>
-      <c r="H257" s="2" t="inlineStr">
+      <c r="H267" s="2" t="inlineStr">
         <is>
           <t>1. As organiser_a@clienta.com, attempt to access EVT-B01 directly
   2. Log in as a System Administrator
   3. Check the Activity Log</t>
         </is>
       </c>
-      <c r="I257" s="2" t="inlineStr">
+      <c r="I267" s="2" t="inlineStr">
         <is>
           <t>User: organiser_a@clienta.com | Target: EVT-B01</t>
         </is>
       </c>
-      <c r="J257" s="2" t="inlineStr">
+      <c r="J267" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded with user = organiser_a@clienta.com, target = EVT-B01, action = "Access Denied", and a timestamp</t>
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" s="2" t="n">
+    <row r="268">
+      <c r="A268" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B258" s="2" t="inlineStr">
+      <c r="B268" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C258" s="2" t="inlineStr">
+      <c r="C268" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 3 (Booking decision recorded)</t>
         </is>
       </c>
-      <c r="D258" s="2" t="inlineStr">
+      <c r="D268" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E258" s="2" t="inlineStr">
+      <c r="E268" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_03</t>
         </is>
       </c>
-      <c r="F258" s="2" t="inlineStr">
+      <c r="F268" s="2" t="inlineStr">
         <is>
           <t>Verify that an approved venue booking should be recorded with the actor, action, affected records, and time</t>
         </is>
       </c>
-      <c r="G258" s="2" t="inlineStr">
+      <c r="G268" s="2" t="inlineStr">
         <is>
           <t>A booking request for Venue Z is pending</t>
         </is>
       </c>
-      <c r="H258" s="2" t="inlineStr">
+      <c r="H268" s="2" t="inlineStr">
         <is>
           <t>1. As Venue Staff, approve the booking request
   2. Log in as a System Administrator
   3. Check the Activity Log</t>
         </is>
       </c>
-      <c r="I258" s="2" t="inlineStr">
+      <c r="I268" s="2" t="inlineStr">
         <is>
           <t>Venue: Venue Z | Action: Approve Booking</t>
         </is>
       </c>
-      <c r="J258" s="2" t="inlineStr">
+      <c r="J268" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded with the actor, action ("Booking Approved"), the affected booking/event, and a timestamp</t>
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="2" t="n">
+    <row r="269">
+      <c r="A269" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B259" s="2" t="inlineStr">
+      <c r="B269" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C259" s="2" t="inlineStr">
+      <c r="C269" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 4 (Deactivation recorded)</t>
         </is>
       </c>
-      <c r="D259" s="2" t="inlineStr">
+      <c r="D269" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E259" s="2" t="inlineStr">
+      <c r="E269" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_04</t>
         </is>
       </c>
-      <c r="F259" s="2" t="inlineStr">
+      <c r="F269" s="2" t="inlineStr">
         <is>
           <t>Verify that an account deactivation should be recorded in the activity log</t>
         </is>
       </c>
-      <c r="G259" s="2" t="inlineStr">
+      <c r="G269" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is signed in</t>
         </is>
       </c>
-      <c r="H259" s="2" t="inlineStr">
+      <c r="H269" s="2" t="inlineStr">
         <is>
           <t>1. Deactivate the account
   2. Log in as a System Administrator
   3. Check the Activity Log</t>
         </is>
       </c>
-      <c r="I259" s="2" t="inlineStr">
+      <c r="I269" s="2" t="inlineStr">
         <is>
           <t>Account: organiser_a@clienta.com</t>
         </is>
       </c>
-      <c r="J259" s="2" t="inlineStr">
+      <c r="J269" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded showing the account deactivation with actor and timestamp</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="2" t="n">
+    <row r="270">
+      <c r="A270" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B260" s="2" t="inlineStr">
+      <c r="B270" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C260" s="2" t="inlineStr">
+      <c r="C270" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 5 (Log entries immutable)</t>
         </is>
       </c>
-      <c r="D260" s="2" t="inlineStr">
+      <c r="D270" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E260" s="2" t="inlineStr">
+      <c r="E270" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_05</t>
         </is>
       </c>
-      <c r="F260" s="2" t="inlineStr">
+      <c r="F270" s="2" t="inlineStr">
         <is>
           <t>Verify that any attempt to edit or delete an activity log entry should be refused</t>
         </is>
       </c>
-      <c r="G260" s="2" t="inlineStr">
+      <c r="G270" s="2" t="inlineStr">
         <is>
           <t>A log entry exists: Event = Annual Tech Summit, Action = "Status changed to Approved", Actor = coordinator_1@connectsphere.com (created in TC_E14S02_01)</t>
         </is>
       </c>
-      <c r="H260" s="2" t="inlineStr">
+      <c r="H270" s="2" t="inlineStr">
         <is>
           <t>1. Log in as a System Administrator
   2. Open the Activity Log and locate the entry for Event = Annual Tech Summit, Action = "Status changed to Approved"
@@ -14048,272 +14576,272 @@
   5. If no UI path exists for either action, attempt the same edit and delete via a direct API call to the log entry's ID</t>
         </is>
       </c>
-      <c r="I260" s="2" t="inlineStr">
+      <c r="I270" s="2" t="inlineStr">
         <is>
           <t>Target log entry: Event = Annual Tech Summit, Action = "Status changed to Approved" | Attempted edit: Action -&gt; "Status changed to Rejected"</t>
         </is>
       </c>
-      <c r="J260" s="2" t="inlineStr">
+      <c r="J270" s="2" t="inlineStr">
         <is>
           <t>Both the edit and delete attempts are refused; no UI control exists to modify or remove a log entry, and the direct API call returns an authorization/forbidden error with the entry left unchanged</t>
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" s="2" t="n">
+    <row r="271">
+      <c r="A271" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B261" s="2" t="inlineStr">
+      <c r="B271" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C261" s="2" t="inlineStr">
+      <c r="C271" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 3 (Booking decision recorded)</t>
         </is>
       </c>
-      <c r="D261" s="2" t="inlineStr">
+      <c r="D271" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E261" s="2" t="inlineStr">
+      <c r="E271" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_06</t>
         </is>
       </c>
-      <c r="F261" s="2" t="inlineStr">
+      <c r="F271" s="2" t="inlineStr">
         <is>
           <t>Verify that a rejected venue booking should be recorded with the actor, action, affected records, and time</t>
         </is>
       </c>
-      <c r="G261" s="2" t="inlineStr">
+      <c r="G271" s="2" t="inlineStr">
         <is>
           <t>A booking request for Venue Z is pending</t>
         </is>
       </c>
-      <c r="H261" s="2" t="inlineStr">
+      <c r="H271" s="2" t="inlineStr">
         <is>
           <t>1. As Venue Staff, reject the booking request with reason "Venue unavailable for maintenance"
   2. Log in as a System Administrator
   3. Check the Activity Log</t>
         </is>
       </c>
-      <c r="I261" s="2" t="inlineStr">
+      <c r="I271" s="2" t="inlineStr">
         <is>
           <t>Venue: Venue Z | Action: Reject Booking | Reason: Venue unavailable for maintenance</t>
         </is>
       </c>
-      <c r="J261" s="2" t="inlineStr">
+      <c r="J271" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded with the actor, action ("Booking Rejected"), the affected booking/event, and a timestamp</t>
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" s="2" t="n">
+    <row r="272">
+      <c r="A272" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B262" s="2" t="inlineStr">
+      <c r="B272" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C262" s="2" t="inlineStr">
+      <c r="C272" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 3 (Booking decision recorded)</t>
         </is>
       </c>
-      <c r="D262" s="2" t="inlineStr">
+      <c r="D272" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E262" s="2" t="inlineStr">
+      <c r="E272" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_07</t>
         </is>
       </c>
-      <c r="F262" s="2" t="inlineStr">
+      <c r="F272" s="2" t="inlineStr">
         <is>
           <t>Verify that a released venue booking should be recorded with the actor, action, affected records, and time</t>
         </is>
       </c>
-      <c r="G262" s="2" t="inlineStr">
+      <c r="G272" s="2" t="inlineStr">
         <is>
           <t>Venue Z has a confirmed booking for event "Annual Tech Summit"</t>
         </is>
       </c>
-      <c r="H262" s="2" t="inlineStr">
+      <c r="H272" s="2" t="inlineStr">
         <is>
           <t>1. As Venue Staff or Coordinator, release the confirmed booking for Venue Z (e.g. due to event cancellation)
   2. Log in as a System Administrator
   3. Check the Activity Log</t>
         </is>
       </c>
-      <c r="I262" s="2" t="inlineStr">
+      <c r="I272" s="2" t="inlineStr">
         <is>
           <t>Venue: Venue Z | Action: Release Booking | Event: Annual Tech Summit</t>
         </is>
       </c>
-      <c r="J262" s="2" t="inlineStr">
+      <c r="J272" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded with the actor, action ("Booking Released"), the affected booking/event, and a timestamp</t>
         </is>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" s="2" t="n">
+    <row r="273">
+      <c r="A273" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B263" s="2" t="inlineStr">
+      <c r="B273" s="2" t="inlineStr">
         <is>
           <t>Definition of Done</t>
         </is>
       </c>
-      <c r="C263" s="2" t="inlineStr">
+      <c r="C273" s="2" t="inlineStr">
         <is>
           <t>Definition of Done · BDR T-51 · Week 1 §8a</t>
         </is>
       </c>
-      <c r="D263" s="2" t="inlineStr">
+      <c r="D273" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting</t>
         </is>
       </c>
-      <c r="E263" s="2" t="inlineStr">
+      <c r="E273" s="2" t="inlineStr">
         <is>
           <t>TC_PERF_01</t>
         </is>
       </c>
-      <c r="F263" s="2" t="inlineStr">
+      <c r="F273" s="2" t="inlineStr">
         <is>
           <t>Verify a venue search returns within the 3-second target on a realistic catalogue</t>
         </is>
       </c>
-      <c r="G263" s="2" t="inlineStr">
+      <c r="G273" s="2" t="inlineStr">
         <is>
           <t>The venue catalogue holds 50 venues with layouts, accessibility features and facilities. 200 confirmed bookings exist across the next 90 days. Coordinator coord_a@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H263" s="2" t="inlineStr">
+      <c r="H273" s="2" t="inlineStr">
         <is>
           <t>1. Open the venue search
  2. Enter date 2026-12-01, time 09:00–11:00, expected attendance 120, layout Theatre, accessibility Step-free access
  3. Start a timer on submit and stop it when results render</t>
         </is>
       </c>
-      <c r="I263" s="2" t="inlineStr">
+      <c r="I273" s="2" t="inlineStr">
         <is>
           <t>50 venues · 200 bookings · elapsed time measured client-side</t>
         </is>
       </c>
-      <c r="J263" s="2" t="inlineStr">
+      <c r="J273" s="2" t="inlineStr">
         <is>
           <t>Results render in under 3 seconds. Record the measured time; if it exceeds 3 seconds the story does not meet the Definition of Done</t>
         </is>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" s="2" t="n">
+    <row r="274">
+      <c r="A274" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B264" s="2" t="inlineStr">
+      <c r="B274" s="2" t="inlineStr">
         <is>
           <t>Definition of Done</t>
         </is>
       </c>
-      <c r="C264" s="2" t="inlineStr">
+      <c r="C274" s="2" t="inlineStr">
         <is>
           <t>Definition of Done · BDR T-51 · Week 1 §8a</t>
         </is>
       </c>
-      <c r="D264" s="2" t="inlineStr">
+      <c r="D274" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting</t>
         </is>
       </c>
-      <c r="E264" s="2" t="inlineStr">
+      <c r="E274" s="2" t="inlineStr">
         <is>
           <t>TC_PERF_02</t>
         </is>
       </c>
-      <c r="F264" s="2" t="inlineStr">
+      <c r="F274" s="2" t="inlineStr">
         <is>
           <t>Verify the venue availability calendar loads within the 3-second target for a busy month</t>
         </is>
       </c>
-      <c r="G264" s="2" t="inlineStr">
+      <c r="G274" s="2" t="inlineStr">
         <is>
           <t>Orchid Hall has 40 confirmed bookings, 5 tentative holds and 3 maintenance blocks within 2026-12-01 to 2026-12-31</t>
         </is>
       </c>
-      <c r="H264" s="2" t="inlineStr">
+      <c r="H274" s="2" t="inlineStr">
         <is>
           <t>1. Open Orchid Hall in the venue catalogue
  2. Select the calendar for December 2026
  3. Start a timer on selection and stop it when all states have rendered</t>
         </is>
       </c>
-      <c r="I264" s="2" t="inlineStr">
+      <c r="I274" s="2" t="inlineStr">
         <is>
           <t>48 calendar entries in one month · elapsed time measured client-side</t>
         </is>
       </c>
-      <c r="J264" s="2" t="inlineStr">
+      <c r="J274" s="2" t="inlineStr">
         <is>
           <t>The calendar renders all Free, Tentative, Confirmed and Blocked states in under 3 seconds</t>
         </is>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" s="2" t="n">
+    <row r="275">
+      <c r="A275" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B265" s="2" t="inlineStr">
+      <c r="B275" s="2" t="inlineStr">
         <is>
           <t>Definition of Done</t>
         </is>
       </c>
-      <c r="C265" s="2" t="inlineStr">
+      <c r="C275" s="2" t="inlineStr">
         <is>
           <t>Definition of Done · BDR T-51 · Week 1 §8a</t>
         </is>
       </c>
-      <c r="D265" s="2" t="inlineStr">
+      <c r="D275" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting</t>
         </is>
       </c>
-      <c r="E265" s="2" t="inlineStr">
+      <c r="E275" s="2" t="inlineStr">
         <is>
           <t>TC_PERF_03</t>
         </is>
       </c>
-      <c r="F265" s="2" t="inlineStr">
+      <c r="F275" s="2" t="inlineStr">
         <is>
           <t>Verify a registration submission completes within the 3-second target near capacity</t>
         </is>
       </c>
-      <c r="G265" s="2" t="inlineStr">
+      <c r="G275" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with Orchid Hall booked, venue capacity 200, and 198 registrations recorded. Attendee attendee_b@example.com is signed in</t>
         </is>
       </c>
-      <c r="H265" s="2" t="inlineStr">
+      <c r="H275" s="2" t="inlineStr">
         <is>
           <t>1. Open event EVT-2001
  2. Submit a registration
  3. Start a timer on submit and stop it when confirmation renders</t>
         </is>
       </c>
-      <c r="I265" s="2" t="inlineStr">
+      <c r="I275" s="2" t="inlineStr">
         <is>
           <t>198 existing registrations · capacity 200 · elapsed time measured client-side</t>
         </is>
       </c>
-      <c r="J265" s="2" t="inlineStr">
+      <c r="J275" s="2" t="inlineStr">
         <is>
           <t>The registration is created and confirmation renders in under 3 seconds, including the capacity check against the booked venue</t>
         </is>

--- a/docs/testing/PROJECT TEST CASES CAA 031026.xlsx
+++ b/docs/testing/PROJECT TEST CASES CAA 031026.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J265"/>
+  <dimension ref="A1:J272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7410,8 +7410,7 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>Submission is blocked; the message identifies "Charity Run" and its buffered window 09:30-12:45; no Pending request is created
-## E06-S04</t>
+          <t>Submission is blocked; the message identifies "Charity Run" and its buffered window 09:30-12:45; no Pending request is created</t>
         </is>
       </c>
     </row>
@@ -7421,35 +7420,141 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
+          <t>E06-S03</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>E06-S03 — Scenario 3 (Several venue bookings for one event); Scenario 3a (Each booking carries its own purpose and headcount); assumes O-27</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>TC_E06S03_07</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Verify that a Coordinator should be able to hold several venue bookings for one event, each with its own purpose, headcount and status</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>coordinator_1@connectsphere.com is signed in; event "Tech Summit" is Approved for 15/01/2027 09:00-18:00 with expected attendance 500; venues "Grand Auditorium" (capacity 600), "Seminar Room A" (capacity 60) and "Seminar Room B" (capacity 60) are Free that day</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>1. Open "Tech Summit" and request "Grand Auditorium" for 09:00-18:00, purpose "Main programme", headcount 500
+  2. Request "Seminar Room A" for 14:00-16:00, purpose "Breakout A", headcount 50
+  3. Request "Seminar Room B" for 14:00-16:00, purpose "Breakout B", headcount 50
+  4. Open the event's venue bookings list</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>Three requests on one event; Seminar Rooms would fail a 500-attendee capacity check but pass on their own headcount of 50</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>All three requests are created as Pending and listed on the event with their purpose, period, headcount and status; the Seminar Room requests are not flagged as undersized because suitability used the booking headcount of 50; the event moved to Planning on the first request</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>E06-S03</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>E06-S03 — Scenario 3 (Several venue bookings for one event); Scenario 3b (Bookings may cover different windows inside the event); assumes O-29</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>4 - Negative (business rule)</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>TC_E06S03_08</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Verify that withdrawing one of several venue bookings should leave the others untouched and that a booking outside the event's period should be refused</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>As TC_E06S03_07 after step 3; coordinator_1@connectsphere.com is signed in</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>1. Withdraw the "Seminar Room B" request
+  2. Read the event's venue bookings list
+  3. Request "Seminar Room B" again for 15/01/2027 18:30-20:00 (after the event ends at 18:00)</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>Event period 09:00-18:00 | Out-of-window request 18:30-20:00</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>After step 1 "Grand Auditorium" and "Seminar Room A" are still Pending and unchanged; the event stays in Planning; step 3 is refused with a message that the booking must fall within the event's 09:00-18:00
+## E06-S04</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>E06-S04</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
         <is>
           <t>E06-S04 - Scenario 1 (Request approved and confirmed)</t>
         </is>
       </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>TC_E06S04_01</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Verify that approving a pending request for a venue that is free for the period should confirm the booking, update the calendar, and notify the Coordinator</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>Booking request for "Riverside Hall" (event "Charity Run") is Pending; the venue is free for the requested period</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>1. Log in as venue_staff_1@connectsphere.com
   2. Open the pending request for "Riverside Hall" / "Charity Run"
@@ -7457,52 +7562,52 @@
   4. Check "Riverside Hall"'s calendar and coordinator_1@connectsphere.com's notifications</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr">
         <is>
           <t>Request: Riverside Hall for Charity Run</t>
         </is>
       </c>
-      <c r="J134" s="2" t="inlineStr">
+      <c r="J136" s="2" t="inlineStr">
         <is>
           <t>The booking becomes "Confirmed"; the calendar shows the period as Confirmed; coordinator_1@connectsphere.com is notified of the approval</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="n">
+    <row r="137">
+      <c r="A137" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>E06-S04</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
         <is>
           <t>E06-S04 - Scenario 2 (Rejected with reason and alternative)</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>TC_E06S04_02</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Verify that rejecting a request with a recorded reason and a suggested alternative venue should notify the Coordinator with both, allowing them to amend without restarting the search</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>Booking request for "Small Room" (event "Product Expo 2026") is Pending</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>1. Log in as venue_staff_1@connectsphere.com
   2. Open the pending request for "Small Room"
@@ -7512,52 +7617,52 @@
   6. Log in as the assigned Coordinator and check the notification and request</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr">
+      <c r="I137" s="2" t="inlineStr">
         <is>
           <t>Rejection reason: "Capacity too small for expected attendance" | Suggested alternative: Riverside Hall</t>
         </is>
       </c>
-      <c r="J135" s="2" t="inlineStr">
+      <c r="J137" s="2" t="inlineStr">
         <is>
           <t>The Coordinator is notified with both the reason and the suggested alternative, and can amend the existing request directly to "Riverside Hall" without starting a new search</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
+    <row r="138">
+      <c r="A138" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>E06-S04</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
         <is>
           <t>E06-S04 - Scenario 3 (Rejection without reason blocked)</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>TC_E06S04_03</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to reject a request without recording a reason should be blocked</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>Booking request for "Riverside Hall" (event "Charity Run") is Pending</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>1. Log in as venue_staff_1@connectsphere.com
   2. Open the pending request
@@ -7566,156 +7671,156 @@
   5. Click "Confirm"</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr">
         <is>
           <t>Rejection reason: (blank)</t>
         </is>
       </c>
-      <c r="J136" s="2" t="inlineStr">
+      <c r="J138" s="2" t="inlineStr">
         <is>
           <t>The rejection is blocked with a message that a reason is required; the request remains Pending</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
+    <row r="139">
+      <c r="A139" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>E06-S04</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
         <is>
           <t>E06-S04 — Scenario 4 (Approval checks the buffered window)</t>
         </is>
       </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>4 - Negative (business rule)</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>TC_E06S04_04</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Verify that approving a request whose buffered window overlaps another confirmed booking's buffered window should be blocked even when the advertised times do not overlap</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>Venue "Riverside Hall" has Setup time 30 and Turnaround time 45; "Charity Run" is Confirmed 15/01/2027 10:00-12:00; a Pending request for "Alumni Dinner" 15/01/2027 12:30-14:00 was created before the buffers were set; venue_staff_1@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>1. Open the pending request for "Alumni Dinner"
   2. Click "Approve"</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr">
         <is>
           <t>Charity Run buffered: 09:30-12:45 | Alumni Dinner buffered: 12:00-14:45</t>
         </is>
       </c>
-      <c r="J137" s="2" t="inlineStr">
+      <c r="J139" s="2" t="inlineStr">
         <is>
           <t>Approval is blocked; "Charity Run" is identified as the conflicting booking with its buffered window; the request stays Pending
 ## E06-S05</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
+    <row r="140">
+      <c r="A140" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>E06-S05</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
         <is>
           <t>E06-S05 · Scenario 2 (Slot already held or booked)</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>4 - Negative (business rule)</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>TC_E06S05_01</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Verify that a second tentative hold on the same venue and period is refused</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>Orchid Hall has an active tentative hold for 2026-12-01 09:00 to 11:00 against event EVT-1005. Coordinator coord_b@connectsphere.com is planning event EVT-1006</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as coord_b@connectsphere.com
  2. Open the venue calendar for Orchid Hall on 2026-12-01
  3. Attempt to place a tentative hold for 09:00–11:00 against EVT-1006</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr">
         <is>
           <t>Existing hold: EVT-1005, 09:00–11:00 · Requested: EVT-1006, same period</t>
         </is>
       </c>
-      <c r="J138" s="2" t="inlineStr">
+      <c r="J140" s="2" t="inlineStr">
         <is>
           <t>The hold is refused and the existing hold against EVT-1005 is identified. The calendar continues to show the period as Tentative for one event only</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
+    <row r="141">
+      <c r="A141" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>E06-S05</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
         <is>
           <t>E06-S05 — Scenario 5 (Hold occupies the buffered window)</t>
         </is>
       </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>TC_E06S05_02</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Verify that a tentative hold should occupy the venue's buffered window so that an overlapping hold or request is refused</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>Venue "Riverside Hall" has Setup time 30 and Turnaround time 45 and is Free on 15/01/2027; coordinator_1@connectsphere.com and coordinator_2@connectsphere.com each have an Approved event</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>1. As coordinator_1, place a tentative hold on "Riverside Hall" for 15/01/2027 10:00-12:00
   2. Open the availability calendar for 15/01/2027
@@ -7723,363 +7828,415 @@
   4. As coordinator_2, attempt a booking request for "Riverside Hall" for 15/01/2027 13:15-14:00</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr">
+      <c r="I141" s="2" t="inlineStr">
         <is>
           <t>Hold: 10:00-12:00 (buffered 09:30-12:45) | Attempt A: 12:30-13:30 | Attempt B: 13:15-14:00 (buffered 12:45-14:45)</t>
         </is>
       </c>
-      <c r="J139" s="2" t="inlineStr">
+      <c r="J141" s="2" t="inlineStr">
         <is>
           <t>The calendar shows Tentative from 09:30 to 12:45 with the buffer portions marked; Attempt A is refused naming coordinator_1's hold; Attempt B is accepted because its own buffered window starts at exactly 12:45, when the hold's ends
 ## E06-S06</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="n">
+    <row r="142">
+      <c r="A142" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
         <is>
           <t>E06-S06 - Scenario 1 (Overlapping approval blocked)</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_01</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to approve a request that overlaps an existing confirmed booking for the same venue should be blocked with the conflicting booking identified</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>"Riverside Hall" has a confirmed booking for "Charity Run" on 15/01/2027, 09:00-17:00. A second pending request for "Riverside Hall" on 15/01/2027, 14:00-18:00 exists for event "Product Expo 2026"</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>1. Log in as venue_staff_1@connectsphere.com
   2. Open the pending request for "Product Expo 2026"
   3. Attempt to click "Approve"</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr">
+      <c r="I142" s="2" t="inlineStr">
         <is>
           <t>Existing confirmed booking: Charity Run, 15/01/2027 09:00-17:00 | Conflicting request: Product Expo 2026, 15/01/2027 14:00-18:00</t>
         </is>
       </c>
-      <c r="J140" s="2" t="inlineStr">
+      <c r="J142" s="2" t="inlineStr">
         <is>
           <t>Approval is blocked, and the message identifies the existing confirmed "Charity Run" booking as the conflict</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="n">
+    <row r="143">
+      <c r="A143" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
         <is>
           <t>E06-S06 - Scenario 2 (Competing request flagged)</t>
         </is>
       </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_02</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Verify that approving one of two pending requests for the same venue and overlapping times should flag the other as conflicting</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>Two pending requests exist for "Riverside Hall" on 20/01/2027, both 09:00-12:00: Request A ("Tech Conference 2026") and Request B ("Product Expo 2026")</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>1. Log in as venue_staff_1@connectsphere.com
   2. Approve Request A ("Tech Conference 2026")
   3. Open Request B ("Product Expo 2026")</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr">
         <is>
           <t>Request A: Tech Conference 2026 (approved) | Request B: Product Expo 2026 (same venue, overlapping time)</t>
         </is>
       </c>
-      <c r="J141" s="2" t="inlineStr">
+      <c r="J143" s="2" t="inlineStr">
         <is>
           <t>Request B is now flagged as conflicting and cannot be approved until the conflict is resolved</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="n">
+    <row r="144">
+      <c r="A144" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
         <is>
           <t>E06-S06 - Scenario 3 (Simultaneous approval fails safely)</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_03</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Verify that if another Venue Staff member approves a conflicting request moments earlier, a simultaneous approval attempt should fail safely and inform the user the venue has just been taken</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>Two pending requests exist for "Riverside Hall" on 25/01/2027, overlapping times. venue_staff_2@connectsphere.com approves one of them a moment before venue_staff_1@connectsphere.com processes the other</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>1. As venue_staff_2@connectsphere.com, approve Request A for "Riverside Hall" on 25/01/2027
   2. Immediately as venue_staff_1@connectsphere.com, attempt to approve the conflicting Request B for the same venue and overlapping time</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr">
         <is>
           <t>Request A approved by venue_staff_2@connectsphere.com just before venue_staff_1@connectsphere.com's attempt on Request B</t>
         </is>
       </c>
-      <c r="J142" s="2" t="inlineStr">
+      <c r="J144" s="2" t="inlineStr">
         <is>
           <t>venue_staff_1@connectsphere.com's approval attempt fails safely, with a message stating the venue has just been taken by another approval</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="n">
+    <row r="145">
+      <c r="A145" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
         <is>
           <t>E06-S06 · Scenario 1 (Overlapping approval blocked)</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (adjacent, must not conflict)</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_04</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Verify that a booking beginning exactly when another ends is not treated as a conflict</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>Venue Orchid Hall has a confirmed booking for 2026-11-10 09:00:00 to 2026-11-10 11:00:00. A pending request exists for the same venue for 2026-11-10 11:00:00 to 2026-11-10 13:00:00</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Venue Staff
  2. Open the pending request for 11:00–13:00
  3. Approve it</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr">
+      <c r="I145" s="2" t="inlineStr">
         <is>
           <t>Existing: 09:00–11:00 · Requested: 11:00–13:00 · Shared boundary: 11:00</t>
         </is>
       </c>
-      <c r="J143" s="2" t="inlineStr">
+      <c r="J145" s="2" t="inlineStr">
         <is>
           <t>The approval succeeds and both bookings show as Confirmed on the venue calendar. Ranges are half-open, so touching at the boundary is not an overlap</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="n">
+    <row r="146">
+      <c r="A146" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
         <is>
           <t>E06-S06 · Scenario 1 (Overlapping approval blocked)</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (one minute of overlap, must conflict)</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_05</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Verify that a booking overlapping an existing one by a single minute is blocked</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>Venue Orchid Hall has a confirmed booking for 2026-11-10 09:00:00 to 2026-11-10 11:00:00. A pending request exists for the same venue for 2026-11-10 10:59:00 to 2026-11-10 13:00:00</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Venue Staff
  2. Open the pending request for 10:59–13:00
  3. Attempt to approve it</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr">
+      <c r="I146" s="2" t="inlineStr">
         <is>
           <t>Existing: 09:00–11:00 · Requested: 10:59–13:00 · Overlap: 1 minute</t>
         </is>
       </c>
-      <c r="J144" s="2" t="inlineStr">
+      <c r="J146" s="2" t="inlineStr">
         <is>
           <t>Approval is blocked and the conflicting 09:00–11:00 booking is identified. The venue never holds two confirmed bookings over the same period</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="n">
+    <row r="147">
+      <c r="A147" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
         <is>
           <t>E06-S06 — Scenario 4 (Buffered windows are what must not overlap)</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>3 - Integration / regression</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_06</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Verify that two approvals whose advertised times do not overlap but whose buffered windows do should let at most one succeed when processed at the same moment</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>Venue "Riverside Hall" has Setup time 30 and Turnaround time 45; two Pending requests exist on it for 15/01/2027: "Charity Run" 10:00-12:00 and "Alumni Dinner" 12:30-14:00; two Venue Staff accounts are signed in; TEST_DATABASE_URL points at the disposable test schema</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>1. Trigger approval of both requests concurrently (integration test issues both approvals in parallel transactions)
   2. Read back both bookings and the venue calendar</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr">
         <is>
           <t>Charity Run buffered: 09:30-12:45 | Alumni Dinner buffered: 12:00-14:45 (advertised times do not overlap; buffered windows overlap 12:00-12:45)</t>
         </is>
       </c>
-      <c r="J145" s="2" t="inlineStr">
+      <c r="J147" s="2" t="inlineStr">
         <is>
           <t>Exactly one booking is Confirmed; the other approval fails with the conflict identified and its request remains Pending; the database exclusion constraint rejected the second write on the buffered range (ADR-003), so TC_E06S06_04 (adjacent, must not conflict) and TC_E06S06_05 (one minute of overlap) continue to hold on buffered windows</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="n">
+    <row r="148">
+      <c r="A148" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>E06-S06</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>E06-S06 — Scenario 5 (Conflicts are per venue, not per event)</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>3 - Integration / regression</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>TC_E06S06_07</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Verify that approving two requests from the same event on two different venues over the same period should confirm both</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>Event "Tech Summit" has Pending requests on "Seminar Room A" and "Seminar Room B" for 15/01/2027 14:00-16:00 (TC_E06S03_07); venue_staff_1@connectsphere.com is signed in</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>1. Approve the "Seminar Room A" request
+  2. Approve the "Seminar Room B" request
+  3. Open the availability calendar for both venues on 15/01/2027</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>Same event, same period, two venues</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>Both bookings become Confirmed; neither approval is blocked; each venue's calendar shows its own Confirmed period; TC_E06S06_01 to TC_E06S06_06 (conflicts on one venue) continue to hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>E07-S01 - Scenario 1 (Item added and reservable)</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>TC_E07S01_01</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Verify that saving a new equipment item with its full details should make it available for reservation</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>tech_support_1@connectsphere.com is signed in; equipment item "Wireless Microphone" does not yet exist</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to "Add Equipment"
   2. Enter Type: "Wireless Microphone", Description: "Handheld, UHF", Quantity: 10, Location: "Main Storage", Operational Status: "Working"
@@ -8087,52 +8244,52 @@
   4. Log in as an Event Coordinator and check equipment availability for "Wireless Microphone"</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr">
         <is>
           <t>Item: Wireless Microphone | Quantity: 10 | Location: Main Storage | Status: Working</t>
         </is>
       </c>
-      <c r="J146" s="2" t="inlineStr">
+      <c r="J149" s="2" t="inlineStr">
         <is>
           <t>The item is saved and appears as available for reservation, with 10 units free</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="n">
+    <row r="150">
+      <c r="A150" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t>E07-S01 - Scenario 2 (Quantity drop flags reservations)</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>TC_E07S01_02</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Verify that reducing an item's quantity below the amount already reserved for upcoming events should flag the affected reservations and notify the relevant Coordinators</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>"Wireless Microphone" (quantity 10) has 6 units reserved for an upcoming event of "Tech Conference 2026", assigned to coordinator_1@connectsphere.com</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "Wireless Microphone"
@@ -8140,52 +8297,52 @@
   4. Save</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr">
         <is>
           <t>Quantity: 10 -&gt; 4 | Existing reservation: 6 units</t>
         </is>
       </c>
-      <c r="J147" s="2" t="inlineStr">
+      <c r="J150" s="2" t="inlineStr">
         <is>
           <t>The 6-unit reservation is flagged for review since it now exceeds total stock, and coordinator_1@connectsphere.com is notified</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="n">
+    <row r="151">
+      <c r="A151" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
         <is>
           <t>E07-S01 - Scenario 3 (Item retired)</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>TC_E07S01_03</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Verify that retiring an item with no future reservations should remove it from availability checks while retaining its past reservations</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>Equipment item "Old Projector" has no future reservations; it has 2 past (completed) reservations on record</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "Old Projector"
@@ -8194,52 +8351,52 @@
   5. Check availability for "Old Projector" as an Event Coordinator</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr">
         <is>
           <t>Item: Old Projector (no future reservations)</t>
         </is>
       </c>
-      <c r="J148" s="2" t="inlineStr">
+      <c r="J151" s="2" t="inlineStr">
         <is>
           <t>"Old Projector" no longer appears in availability checks; its 2 past reservations remain retained and viewable in historical records</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="n">
+    <row r="152">
+      <c r="A152" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t>E07-S01 (checklist: update equipment attributes)</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>TC_E07S01_04</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Verify that updating an existing equipment item's attributes should save the changes</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>Equipment item "Wireless Microphone" exists with Location: "Main Storage"</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "Wireless Microphone"
@@ -8247,53 +8404,53 @@
   4. Click "Save"</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr">
         <is>
           <t>Location: Main Storage -&gt; Annex Storage</t>
         </is>
       </c>
-      <c r="J149" s="2" t="inlineStr">
+      <c r="J152" s="2" t="inlineStr">
         <is>
           <t>The updated Location value is saved and shown when the item record is reopened
 ## E07-S02</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="n">
+    <row r="153">
+      <c r="A153" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
         <is>
           <t>E07-S02 - Scenario 1 (Equipment recorded against an event)</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>TC_E07S02_01</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Verify that adding equipment items with quantities to a event of an approved event should save the request and notify Technical Support Staff</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" is Approved; the event has no equipment requested yet</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the event of "Tech Conference 2026"
@@ -8302,52 +8459,52 @@
   5. Check tech_support_1@connectsphere.com's notifications</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr">
         <is>
           <t>the event equipment: Wireless Microphone x2, Projector x1</t>
         </is>
       </c>
-      <c r="J150" s="2" t="inlineStr">
+      <c r="J153" s="2" t="inlineStr">
         <is>
           <t>The equipment request is saved against the event, and tech_support_1@connectsphere.com is notified</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="n">
+    <row r="154">
+      <c r="A154" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
         <is>
           <t>E07-S02 - Scenario 2 (Request exceeds total stock)</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>TC_E07S02_02</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Verify that requesting more of an item than ConnectSphere owns in total should warn that the request cannot be met from existing stock</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>"Wireless Microphone" has a total stock of 10 units</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open a event of "Tech Conference 2026"
@@ -8355,52 +8512,52 @@
   4. Save</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr">
         <is>
           <t>Requested quantity: 15 | Total stock: 10</t>
         </is>
       </c>
-      <c r="J151" s="2" t="inlineStr">
+      <c r="J154" s="2" t="inlineStr">
         <is>
           <t>A warning is shown that the request (15 units) cannot be met from existing stock (10 units)</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="n">
+    <row r="155">
+      <c r="A155" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
         <is>
           <t>E07-S02 - Scenario 3 (Events independent of each other)</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>TC_E07S02_03</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Verify that recording equipment for one event should leave a different event's equipment unaffected</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>Coordinator coordinator_1@connectsphere.com manages two separate events, "Tech Conference 2026" and "Charity Run", neither with equipment requested yet</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open "Tech Conference 2026" and add "Projector" x 1
@@ -8408,52 +8565,52 @@
   4. Open "Charity Run" and check its equipment list</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr">
         <is>
           <t>"Tech Conference 2026": Projector x1 added | "Charity Run": unchanged</t>
         </is>
       </c>
-      <c r="J152" s="2" t="inlineStr">
+      <c r="J155" s="2" t="inlineStr">
         <is>
           <t>"Tech Conference 2026" shows "Projector x1"; "Charity Run"'s equipment list remains empty, unaffected by the other event's request</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="n">
+    <row r="156">
+      <c r="A156" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
         <is>
           <t>E07-S02 (checklist: amend or remove equipment request before reservation)</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>TC_E07S02_04</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Verify that amending or removing an equipment request before it is reserved should update or clear the request accordingly</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" has an unreserved equipment request: "Wireless Microphone" x 2</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the event's equipment request
@@ -8462,208 +8619,208 @@
   5. Save</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr">
         <is>
           <t>Quantity change: 2 -&gt; 3, then removed entirely</t>
         </is>
       </c>
-      <c r="J153" s="2" t="inlineStr">
+      <c r="J156" s="2" t="inlineStr">
         <is>
           <t>After step 3, the request shows "Wireless Microphone x3"; after step 5, the request no longer includes "Wireless Microphone"
 ## E07-S03</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="n">
+    <row r="157">
+      <c r="A157" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
         <is>
           <t>E07-S03 - Scenario 1 (Reserved and faulty stock excluded)</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>TC_E07S03_01</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Verify that checking availability for a period with other reservations should exclude those reservations and any damaged or under-maintenance items from the free quantity</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>"Wireless Microphone" has total stock 10; 3 units are reserved for another event on 15/11/2026, 09:00-12:00; 2 units are marked damaged</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Check availability for "Wireless Microphone" on 15/11/2026, 09:00-12:00</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr">
         <is>
           <t>Total stock: 10 | Reserved: 3 | Damaged: 2</t>
         </is>
       </c>
-      <c r="J154" s="2" t="inlineStr">
+      <c r="J157" s="2" t="inlineStr">
         <is>
           <t>The free quantity shown is 5 (10 minus 3 reserved minus 2 damaged)</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="n">
+    <row r="158">
+      <c r="A158" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
         <is>
           <t>E07-S03 - Scenario 2 (Location does not affect availability)</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>TC_E07S03_02</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Verify that an item free for the requested date and time but located at another venue should still be shown as available, with no transport allowance applied</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>"Projector" is free for 15/11/2026, 09:00-12:00, but is currently located at "Grand Ballroom" rather than the requested venue</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Check availability for "Projector" on 15/11/2026, 09:00-12:00 for a event at "Riverside Hall"</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr">
         <is>
           <t>Item location: Grand Ballroom | Requested venue: Riverside Hall</t>
         </is>
       </c>
-      <c r="J155" s="2" t="inlineStr">
+      <c r="J158" s="2" t="inlineStr">
         <is>
           <t>"Projector" is shown as available with its full free quantity; no transport time or allowance is added to the availability check</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="n">
+    <row r="159">
+      <c r="A159" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
         <is>
           <t>E07-S03 - Scenario 3 (Non-overlapping events share an item)</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>TC_E07S03_03</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Verify that two events requiring the same item at non-overlapping times on the same day should both show it as free</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>"Tech Conference 2026" the event (09:00-12:00) and the event (14:00-17:00) both require "Wireless Microphone", with no other reservations that day</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Check availability for "Wireless Microphone" during the event's time (09:00-12:00)
   3. Check availability for "Wireless Microphone" during the event's time (14:00-17:00)</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr">
         <is>
           <t>the event: 09:00-12:00 | the event: 14:00-17:00 (same day, non-overlapping)</t>
         </is>
       </c>
-      <c r="J156" s="2" t="inlineStr">
+      <c r="J159" s="2" t="inlineStr">
         <is>
           <t>"Wireless Microphone" shows its full free quantity for both the event's and the event's time windows
 ## E07-S04</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="n">
+    <row r="160">
+      <c r="A160" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
         <is>
           <t>E07-S04 - Scenario 1 (Full reservation recorded)</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_01</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Verify that reserving the requested quantity when sufficient equipment is free should record the reservation and notify the Event Coordinator</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" requested "Wireless Microphone" x 2; 5 units are free for that period</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the equipment request for the event
@@ -8672,52 +8829,52 @@
   5. Check coordinator_1@connectsphere.com's notifications</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr">
         <is>
           <t>Reserved: Wireless Microphone x2 (5 free)</t>
         </is>
       </c>
-      <c r="J157" s="2" t="inlineStr">
+      <c r="J160" s="2" t="inlineStr">
         <is>
           <t>The reservation is recorded against the event, and coordinator_1@connectsphere.com receives a confirmation showing the event's date/time, item, and quantity</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="n">
+    <row r="161">
+      <c r="A161" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
         <is>
           <t>E07-S04 - Scenario 2 (Partial reservation and shortfall)</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_02</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Verify that recording a partial reservation when only part of the requested quantity is free should notify the Coordinator of the shortfall</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" requested "Projector" x 3; only 2 units are free for that period</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the equipment request for the event
@@ -8725,103 +8882,103 @@
   4. Confirm</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr">
         <is>
           <t>Requested: 3 | Reserved (partial): 2 | Shortfall: 1</t>
         </is>
       </c>
-      <c r="J158" s="2" t="inlineStr">
+      <c r="J161" s="2" t="inlineStr">
         <is>
           <t>coordinator_1@connectsphere.com is notified of the shortfall, showing 2 reserved and 1 outstanding unit of "Projector"</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="n">
+    <row r="162">
+      <c r="A162" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
         <is>
           <t>E07-S04 - Scenario 3 (Fully committed item shows nothing free)</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_03</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Verify that once an item becomes fully committed, a subsequent availability check for that period should show no free quantity</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>"Portable Stage" (total stock 2) has both units fully reserved for the period 20/11/2026, 09:00-17:00</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Check availability for "Portable Stage" on 20/11/2026, 09:00-17:00</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr">
         <is>
           <t>Portable Stage: 2 total, 2 reserved</t>
         </is>
       </c>
-      <c r="J159" s="2" t="inlineStr">
+      <c r="J162" s="2" t="inlineStr">
         <is>
           <t>The availability check shows 0 free units of "Portable Stage" for that period</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="n">
+    <row r="163">
+      <c r="A163" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
         <is>
           <t>E07-S04 - Scenario 4 (Reservation released)</t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_04</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Verify that releasing a reservation when a event is cancelled or the equipment is no longer required should return the quantity to the available pool</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" has a reservation of "Wireless Microphone" x 2</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the reservation for the event
@@ -8830,52 +8987,52 @@
   5. Check availability for "Wireless Microphone" for that period</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr">
         <is>
           <t>Released reservation: Wireless Microphone x2</t>
         </is>
       </c>
-      <c r="J160" s="2" t="inlineStr">
+      <c r="J163" s="2" t="inlineStr">
         <is>
           <t>The 2 units are returned to the available pool, increasing the free quantity for that period by 2</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="n">
+    <row r="164">
+      <c r="A164" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
         <is>
           <t>E07-S04 · Scenario 1 (Full reservation recorded)</t>
         </is>
       </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (just below)</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_05</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Verify that requesting one fewer than the free quantity produces a full reservation and leaves the remainder free</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>Equipment Projector-HD has total quantity 10. Six units are reserved for other events overlapping EVT-1003, leaving 4 free. Event EVT-1003 has an equipment request for 3 units</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Technical Support Staff
  2. Open the equipment request for EVT-1003
@@ -8883,52 +9040,52 @@
  4. Re-check availability for the same period</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr">
         <is>
           <t>Free quantity: 4 · Requested: 3</t>
         </is>
       </c>
-      <c r="J161" s="2" t="inlineStr">
+      <c r="J164" s="2" t="inlineStr">
         <is>
           <t>A reservation of 3 is recorded with status Reserved, not Partial. Availability for the period now shows 1 free. Confirmation of the event is not blocked by this reservation</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="n">
+    <row r="165">
+      <c r="A165" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
         <is>
           <t>E07-S04 · Scenario 1 (Full reservation recorded)</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_06</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Verify that requesting exactly the free quantity produces a full reservation and leaves nothing free</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>Equipment Projector-HD has total quantity 10. Six units are reserved for other events overlapping EVT-1003, leaving 4 free. Event EVT-1003 has an equipment request for 4 units</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Technical Support Staff
  2. Open the equipment request for EVT-1003
@@ -8936,52 +9093,52 @@
  4. Re-check availability for the same period</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr">
+      <c r="I165" s="2" t="inlineStr">
         <is>
           <t>Free quantity: 4 · Requested: 4</t>
         </is>
       </c>
-      <c r="J162" s="2" t="inlineStr">
+      <c r="J165" s="2" t="inlineStr">
         <is>
           <t>A reservation of 4 is recorded with status Reserved. Availability for the period shows 0 free. No shortfall notification is sent</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="n">
+    <row r="166">
+      <c r="A166" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
         <is>
           <t>E07-S04 · Scenario 2 (Partial reservation and shortfall) · E08-S03 Scenario 3</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (just above)</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_07</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Verify that requesting one more than the free quantity produces a partial reservation that blocks confirmation</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>Equipment Projector-HD has total quantity 10. Six units are reserved for other events overlapping EVT-1003, leaving 4 free. Event EVT-1003 has an equipment request for 5 units. Event EVT-1003 already has a confirmed venue booking</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Technical Support Staff
  2. Open the equipment request for EVT-1003
@@ -8989,53 +9146,53 @@
  4. Sign in as the assigned Event Coordinator and attempt to confirm the event</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr">
+      <c r="I166" s="2" t="inlineStr">
         <is>
           <t>Free quantity: 4 · Requested: 5 · Reserved: 4 · Outstanding: 1</t>
         </is>
       </c>
-      <c r="J163" s="2" t="inlineStr">
+      <c r="J166" s="2" t="inlineStr">
         <is>
           <t>The reservation is recorded with status Partial. The Coordinator is notified of an outstanding quantity of 1. Confirmation is blocked and the outstanding item is listed against event EVT-1003
 ## E07-S05</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="n">
+    <row r="167">
+      <c r="A167" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
         <is>
           <t>E07-S05 - Scenario 1 (Item marked unavailable)</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>TC_E07S05_01</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Verify that marking an item with no reservations in the period unavailable, with a reason and a period, should exclude it from availability checks for that period</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>Equipment item "HD Camera" has no reservations between 01/12/2026 and 05/12/2026</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "HD Camera"
@@ -9045,52 +9202,52 @@
   6. Check availability for "HD Camera" on 03/12/2026</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr">
+      <c r="I167" s="2" t="inlineStr">
         <is>
           <t>Period: 01/12/2026-05/12/2026 | Reason: Sensor repair</t>
         </is>
       </c>
-      <c r="J164" s="2" t="inlineStr">
+      <c r="J167" s="2" t="inlineStr">
         <is>
           <t>"HD Camera" shows 0 available units for any date within 01/12/2026-05/12/2026</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="n">
+    <row r="168">
+      <c r="A168" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
         <is>
           <t>E07-S05 - Scenario 2 (Reserved item flags its events)</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>TC_E07S05_02</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Verify that marking an item unavailable while it is reserved for an upcoming event should flag the affected event and notify its Coordinator</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>"HD Camera" is reserved for an upcoming event of "Tech Conference 2026", assigned to coordinator_1@connectsphere.com</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "HD Camera"
@@ -9098,52 +9255,52 @@
   4. Save</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr">
+      <c r="I168" s="2" t="inlineStr">
         <is>
           <t>Affected event: Tech Conference 2026 event with HD Camera reserved</t>
         </is>
       </c>
-      <c r="J165" s="2" t="inlineStr">
+      <c r="J168" s="2" t="inlineStr">
         <is>
           <t>The affected event is flagged, and coordinator_1@connectsphere.com is notified that its reserved "HD Camera" is now unavailable</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="n">
+    <row r="169">
+      <c r="A169" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
         <is>
           <t>E07-S05 (checklist: return item to service)</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>TC_E07S05_03</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Verify that returning an item to service should restore it to availability checks</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>"HD Camera" is currently marked unavailable for 01/12/2026-05/12/2026 with reason "Sensor repair"</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "HD Camera"
@@ -9152,53 +9309,53 @@
   5. Check availability for "HD Camera" on 03/12/2026</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr">
+      <c r="I169" s="2" t="inlineStr">
         <is>
           <t>Item: HD Camera (returning to service)</t>
         </is>
       </c>
-      <c r="J166" s="2" t="inlineStr">
+      <c r="J169" s="2" t="inlineStr">
         <is>
           <t>"HD Camera" now shows as available again for 03/12/2026
 ## E07-S06</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="n">
+    <row r="170">
+      <c r="A170" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
         <is>
           <t>E07-S06 - Scenario 1 (Support request recorded)</t>
         </is>
       </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>TC_E07S06_01</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting a technical support request describing the support needed and the times should notify Technical Support Staff and record it against the event</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" requires on-site technical support</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the event of "Tech Conference 2026"
@@ -9208,104 +9365,104 @@
   6. Check tech_support_1@connectsphere.com's notifications</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr">
+      <c r="I170" s="2" t="inlineStr">
         <is>
           <t>Support description: "1 AV technician for the full event" | Times: 09:00-12:00</t>
         </is>
       </c>
-      <c r="J167" s="2" t="inlineStr">
+      <c r="J170" s="2" t="inlineStr">
         <is>
           <t>The request is recorded against the event, and tech_support_1@connectsphere.com is notified</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="n">
+    <row r="171">
+      <c r="A171" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
         <is>
           <t>E07-S06 - Scenario 2 (Request accepted before venue confirmed)</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>TC_E07S06_02</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting a technical support request before the venue is confirmed should be accepted and reviewed alongside venue identification</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" does not yet have a confirmed venue</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the event of "Tech Conference 2026" (no confirmed venue)
   3. Submit a technical support request describing "1 sound technician" for the event's planned times</t>
         </is>
       </c>
-      <c r="I168" s="2" t="inlineStr">
+      <c r="I171" s="2" t="inlineStr">
         <is>
           <t>the event: no confirmed venue yet</t>
         </is>
       </c>
-      <c r="J168" s="2" t="inlineStr">
+      <c r="J171" s="2" t="inlineStr">
         <is>
           <t>The technical support request is accepted and recorded, without waiting for the venue to be confirmed first</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="n">
+    <row r="172">
+      <c r="A172" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
         <is>
           <t>E07-S06 - Scenario 3 (Event marked as needing none)</t>
         </is>
       </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>TC_E07S06_03</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Verify that marking a event as needing no technical support should create no request and not block confirmation on staff assignment</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>A event of "Charity Run" needs no on-site technical support</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the event of "Charity Run"
@@ -9313,53 +9470,53 @@
   4. Save</t>
         </is>
       </c>
-      <c r="I169" s="2" t="inlineStr">
+      <c r="I172" s="2" t="inlineStr">
         <is>
           <t>Event: Charity Run's event | Technical Support: Not Required</t>
         </is>
       </c>
-      <c r="J169" s="2" t="inlineStr">
+      <c r="J172" s="2" t="inlineStr">
         <is>
           <t>No technical support request is created for the event, and later event confirmation is not blocked waiting for a staff assignment
 ## E07-S07</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="n">
+    <row r="173">
+      <c r="A173" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
         <is>
           <t>E07-S07 - Scenario 1 (Available colleague assigned)</t>
         </is>
       </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_01</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Verify that a colleague with no conflicting assignment during the event's required time period should be successfully assigned</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" (09:00-12:00) has an open technical support request. tech_support_2@connectsphere.com has no assignment overlapping 09:00-12:00 on that date</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the technical support request for the event
@@ -9367,155 +9524,155 @@
   4. Confirm</t>
         </is>
       </c>
-      <c r="I170" s="2" t="inlineStr">
+      <c r="I173" s="2" t="inlineStr">
         <is>
           <t>Assignee: tech_support_2@connectsphere.com | Event time: 09:00-12:00</t>
         </is>
       </c>
-      <c r="J170" s="2" t="inlineStr">
+      <c r="J173" s="2" t="inlineStr">
         <is>
           <t>The assignment succeeds; tech_support_2@connectsphere.com is notified and the assignment appears on their schedule</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="n">
+    <row r="174">
+      <c r="A174" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
         <is>
           <t>E07-S07 (checklist: see assignment on schedule)</t>
         </is>
       </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_02</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Verify that the assignment should be reflected on the assigned staff member's schedule once made</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t>tech_support_2@connectsphere.com has just been assigned to the event of "Tech Conference 2026" (09:00-12:00)</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_2@connectsphere.com
   2. Open "My Schedule"</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr">
+      <c r="I174" s="2" t="inlineStr">
         <is>
           <t>Assignment: the event, Tech Conference 2026, 09:00-12:00</t>
         </is>
       </c>
-      <c r="J171" s="2" t="inlineStr">
+      <c r="J174" s="2" t="inlineStr">
         <is>
           <t>The schedule shows the assignment to the event of "Tech Conference 2026" at 09:00-12:00</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="n">
+    <row r="175">
+      <c r="A175" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
         <is>
           <t>E07-S07 - Scenario 2 (Overlapping assignment blocked)</t>
         </is>
       </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_03</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Verify that assigning a colleague who has an overlapping assignment should be blocked, with the conflicting event identified</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>tech_support_2@connectsphere.com is already assigned to a event of "Charity Run" from 10:00-13:00 on the same date. the event of "Tech Conference 2026" runs 09:00-12:00 on that date and needs a technician assigned</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the technical support request for the event of "Tech Conference 2026"
   3. Attempt to assign tech_support_2@connectsphere.com</t>
         </is>
       </c>
-      <c r="I172" s="2" t="inlineStr">
+      <c r="I175" s="2" t="inlineStr">
         <is>
           <t>Existing assignment: Charity Run event, 10:00-13:00 | New attempted assignment: Tech Conference 2026 the event, 09:00-12:00 (overlaps)</t>
         </is>
       </c>
-      <c r="J172" s="2" t="inlineStr">
+      <c r="J175" s="2" t="inlineStr">
         <is>
           <t>The assignment is blocked, and the message identifies the conflicting "Charity Run" event as the reason</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="n">
+    <row r="176">
+      <c r="A176" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
         <is>
           <t>E07-S07 - Scenario 3 (Assignment removed)</t>
         </is>
       </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_04</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Verify that removing an existing assignment from a staff member's schedule should free up that slot</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t>tech_support_2@connectsphere.com is assigned to the event of "Tech Conference 2026"</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the assignment for the event
@@ -9524,104 +9681,104 @@
   5. Check tech_support_2@connectsphere.com's schedule</t>
         </is>
       </c>
-      <c r="I173" s="2" t="inlineStr">
+      <c r="I176" s="2" t="inlineStr">
         <is>
           <t>Assignment removed: tech_support_2@connectsphere.com, the event</t>
         </is>
       </c>
-      <c r="J173" s="2" t="inlineStr">
+      <c r="J176" s="2" t="inlineStr">
         <is>
           <t>The assignment no longer appears on tech_support_2@connectsphere.com's schedule, and the slot is free for reassignment</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="n">
+    <row r="177">
+      <c r="A177" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
         <is>
           <t>E07-S07 - Scenario 4 (Replacement assigned under same check)</t>
         </is>
       </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_05</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Verify that assigning a replacement colleague after removing an assignment should be subject to the same conflict check used for new assignments</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>The assignment for the event of "Tech Conference 2026" has just been removed from tech_support_2@connectsphere.com. tech_support_3@connectsphere.com already has a conflicting assignment during the event's time</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the now-unassigned technical support request for the event
   3. Attempt to assign tech_support_3@connectsphere.com as a replacement</t>
         </is>
       </c>
-      <c r="I174" s="2" t="inlineStr">
+      <c r="I177" s="2" t="inlineStr">
         <is>
           <t>Replacement candidate: tech_support_3@connectsphere.com (has a conflicting assignment)</t>
         </is>
       </c>
-      <c r="J174" s="2" t="inlineStr">
+      <c r="J177" s="2" t="inlineStr">
         <is>
           <t>The replacement assignment is blocked using the same conflict check as a new assignment, with the conflicting event identified</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="n">
+    <row r="178">
+      <c r="A178" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
         <is>
           <t>E07-S07 (checklist: staff notified when assigned or removed)</t>
         </is>
       </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting (notification consistency)</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_06</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>Verify that the assigned staff member should receive a notification when they are assigned to, or removed from, an event</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>tech_support_2@connectsphere.com is about to be assigned to, and later removed from, the event of "Tech Conference 2026"</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>1. As tech_support_1@connectsphere.com, assign tech_support_2@connectsphere.com to the event
   2. Check tech_support_2@connectsphere.com's notifications
@@ -9629,52 +9786,52 @@
   4. Check tech_support_2@connectsphere.com's notifications again</t>
         </is>
       </c>
-      <c r="I175" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr">
         <is>
           <t>Actions: assign, then remove</t>
         </is>
       </c>
-      <c r="J175" s="2" t="inlineStr">
+      <c r="J178" s="2" t="inlineStr">
         <is>
           <t>tech_support_2@connectsphere.com receives a notification for the assignment, and a separate notification for the removal</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="n">
+    <row r="179">
+      <c r="A179" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
         <is>
           <t>E08-S03 - Scenario 1 (All arrangements complete, event confirmed)</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>TC_E08S03_01</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Verify that confirming an event where every event has a confirmed venue and full equipment reservation should set its status to Confirmed and notify the Organiser</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has one event with a confirmed venue booking (Riverside Hall) and its full requested equipment reserved, and requires no technical support</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Charity Run"
@@ -9682,260 +9839,362 @@
   4. Check the status and organiser_a@clienta.com's notifications</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr">
         <is>
           <t>Event: Charity Run (venue confirmed, equipment fully reserved, no tech support needed)</t>
         </is>
       </c>
-      <c r="J176" s="2" t="inlineStr">
+      <c r="J179" s="2" t="inlineStr">
         <is>
           <t>The status becomes "Confirmed", and organiser_a@clienta.com is notified with the confirmed details</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="n">
+    <row r="180">
+      <c r="A180" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t>E08-S03 - Scenario 2 (Missing venue blocks confirmation)</t>
         </is>
       </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>TC_E08S03_02</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to confirm an event while a event is missing a confirmed venue should be blocked with the outstanding event named</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has the event with a confirmed venue, but the event has no confirmed venue yet</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Tech Conference 2026"
   3. Click "Confirm Event"</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr">
         <is>
           <t>the event: venue confirmed | the event: no venue</t>
         </is>
       </c>
-      <c r="J177" s="2" t="inlineStr">
+      <c r="J180" s="2" t="inlineStr">
         <is>
           <t>Confirmation is blocked; the message lists "the event" as missing a confirmed venue</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="n">
+    <row r="181">
+      <c r="A181" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>E08-S03 - Scenario 3 (Partial equipment blocks confirmation)</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>TC_E08S03_03</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to confirm an event while a event has only a partial equipment reservation should be blocked with the outstanding quantity shown</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has all events with confirmed venues, but the event's "Projector" reservation is partial (2 of 3 requested)</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Tech Conference 2026"
   3. Click "Confirm Event"</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr">
         <is>
           <t>the event: Projector reserved 2 of 3 requested</t>
         </is>
       </c>
-      <c r="J178" s="2" t="inlineStr">
+      <c r="J181" s="2" t="inlineStr">
         <is>
           <t>Confirmation is blocked; the message shows the event's outstanding quantity of 1 "Projector" unit</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="n">
+    <row r="182">
+      <c r="A182" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>E08-S03 - Scenario 5 (Outstanding support assignment blocks confirmation)</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>TC_E08S03_04</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to confirm an event while a event's requested technical support has no staff assigned should be blocked</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>All events of "Tech Conference 2026" have confirmed venues and full equipment, but the event's technical support request has no staff assigned</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Tech Conference 2026"
   3. Click "Confirm Event"</t>
         </is>
       </c>
-      <c r="I179" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr">
         <is>
           <t>the event: technical support requested, no staff assigned</t>
         </is>
       </c>
-      <c r="J179" s="2" t="inlineStr">
+      <c r="J182" s="2" t="inlineStr">
         <is>
           <t>Confirmation is blocked due to the event's outstanding technical support assignment</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="n">
+    <row r="183">
+      <c r="A183" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>E08-S03 - Scenario 6 (Organiser sees confirmed arrangements)</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>TC_E08S03_05</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>Verify that once an event is confirmed, the Organiser should see the confirmed venue, date, time and arrangements for every event</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has just been confirmed, with venue Riverside Hall, date 15/01/2027, time 09:00-17:00</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the confirmed event "Charity Run"</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr">
         <is>
           <t>Confirmed venue: Riverside Hall | Date: 15/01/2027 | Time: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J180" s="2" t="inlineStr">
-        <is>
-          <t>The Organiser sees the confirmed venue (Riverside Hall), date (15/01/2027), time (09:00-17:00), and full arrangements for the event
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>The Organiser sees the confirmed venue (Riverside Hall), date (15/01/2027), time (09:00-17:00), and full arrangements for the event</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>E08-S03</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>E08-S03 — Scenario 2 (Missing venue blocks confirmation); assumes O-28</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>4 - Negative (business rule)</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>TC_E08S03_06</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Verify that confirming an event with several venue bookings should be blocked while any booking is still Pending or Conflicting, listing each outstanding booking by venue</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>Event "Tech Summit" has "Grand Auditorium" Confirmed, "Seminar Room A" Confirmed and "Seminar Room B" Pending; equipment fully reserved; technical support assigned; coordinator_1@connectsphere.com is signed in</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>1. Open "Tech Summit" and click "Confirm event"</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>Two Confirmed bookings, one Pending</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>Confirmation is blocked; the outstanding-items list names "Seminar Room B" (Pending) and nothing else; the event stays in Planning</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>E08-S03</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>E08-S03 — Scenario 1 (All arrangements complete, event confirmed); Scenario 6 (Organiser sees confirmed arrangements); assumes O-28</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>TC_E08S03_07</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>Verify that an event should be confirmable once every venue booking is Confirmed or withdrawn and the Organiser should see every confirmed venue</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>As TC_E08S03_06; organiser_1@connectsphere.com owns the event</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>1. As venue_staff_1, approve the "Seminar Room B" request
+  2. As coordinator_1, click "Confirm event"
+  3. As organiser_1, open "Tech Summit"</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>Three Confirmed bookings: Grand Auditorium 09:00-18:00 Main programme; Seminar Room A and B 14:00-16:00 Breakout A/B</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>The event becomes Confirmed and organiser_1 is notified; the Organiser's view lists all three venues with their purpose and period
 ## E08-S04</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="n">
+    <row r="186">
+      <c r="A186" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>E08-S04 - Scenario 1 (Reverted with a recorded reason)</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>TC_E08S04_01</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>Verify that reverting a Confirmed event to Planning with a recorded reason should update its status and notify the Organiser with the reason</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>Event "Leadership Summit" has status "Confirmed"</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Leadership Summit"
@@ -9944,52 +10203,52 @@
   5. Confirm</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr">
+      <c r="I186" s="2" t="inlineStr">
         <is>
           <t>Reason: "Venue reported a plumbing issue"</t>
         </is>
       </c>
-      <c r="J181" s="2" t="inlineStr">
+      <c r="J186" s="2" t="inlineStr">
         <is>
           <t>The status changes to "Planning", and organiser_a@clienta.com is notified with the reason "Venue reported a plumbing issue"</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="n">
+    <row r="187">
+      <c r="A187" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C187" s="2" t="inlineStr">
         <is>
           <t>E08-S04 - Scenario 2 (Registered Attendees notified)</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>TC_E08S04_02</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>Verify that reverting a Confirmed event with registered Attendees should notify them that arrangements are being revised</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>Event "Leadership Summit" has status "Confirmed" with attendee_a@example.com registered</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Leadership Summit"
@@ -9997,413 +10256,413 @@
   4. Check attendee_a@example.com's notifications</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr">
+      <c r="I187" s="2" t="inlineStr">
         <is>
           <t>Registered Attendee: attendee_a@example.com</t>
         </is>
       </c>
-      <c r="J182" s="2" t="inlineStr">
+      <c r="J187" s="2" t="inlineStr">
         <is>
           <t>attendee_a@example.com receives a notification that arrangements for "Leadership Summit" are being revised</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="n">
+    <row r="188">
+      <c r="A188" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C188" s="2" t="inlineStr">
         <is>
           <t>E08-S04 - Scenario 3 (No automatic reversion)</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>TC_E08S04_03</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>Verify that an arrangement breaking on a Confirmed event should not automatically revert its status; the affected arrangement should instead be flagged</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr">
         <is>
           <t>Event "Leadership Summit" has status "Confirmed"; its venue booking has just been flagged due to a broken arrangement, but no one has reverted the event</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Leadership Summit"
   3. Check the event status and the flagged arrangement</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr">
+      <c r="I188" s="2" t="inlineStr">
         <is>
           <t>Flagged arrangement: venue booking</t>
         </is>
       </c>
-      <c r="J183" s="2" t="inlineStr">
+      <c r="J188" s="2" t="inlineStr">
         <is>
           <t>The event status remains "Confirmed"; the affected venue booking is shown flagged, but no automatic status change has occurred</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="n">
+    <row r="189">
+      <c r="A189" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C189" s="2" t="inlineStr">
         <is>
           <t>E08-S04 (checklist: reversion recorded in activity log)</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting (audit logging)</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>TC_E08S04_04</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>Verify that a reversion from Confirmed to Planning should be recorded in the activity log</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr">
         <is>
           <t>Event "Leadership Summit" has just been reverted from "Confirmed" to "Planning" by coordinator_1@connectsphere.com</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>1. Log in as a System Administrator
   2. Open the Activity Log and search for "Leadership Summit"</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr">
+      <c r="I189" s="2" t="inlineStr">
         <is>
           <t>Event: Leadership Summit</t>
         </is>
       </c>
-      <c r="J184" s="2" t="inlineStr">
+      <c r="J189" s="2" t="inlineStr">
         <is>
           <t>An activity log entry exists recording the reversion, with actor = coordinator_1@connectsphere.com, action = "Reverted to Planning", and a timestamp
 ## E08-S05</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="n">
+    <row r="190">
+      <c r="A190" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
+      <c r="C190" s="2" t="inlineStr">
         <is>
           <t>E08-S05 - Scenario 1 (Auto-completed after the end time)</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_01</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>Verify that a Confirmed event should automatically become Completed once its last event's end time has passed</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has status "Confirmed"; its only event ended at 17:00 on 15/01/2027, which has now passed</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t>1. Wait for (or trigger) the system's next scheduled evaluation after 17:00 on 15/01/2027
   2. Open event "Charity Run" and check its status</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr">
+      <c r="I190" s="2" t="inlineStr">
         <is>
           <t>Event end time: 17:00, 15/01/2027 (passed)</t>
         </is>
       </c>
-      <c r="J185" s="2" t="inlineStr">
+      <c r="J190" s="2" t="inlineStr">
         <is>
           <t>The event status has automatically changed to "Completed"</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="n">
+    <row r="191">
+      <c r="A191" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C191" s="2" t="inlineStr">
         <is>
           <t>E08-S05 - Scenario 2 (Marked complete manually)</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_02</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Coordinator should be able to manually mark a Confirmed event complete once its last event has started</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr">
         <is>
           <t>Event "Volunteer Training Day" has status "Confirmed"; its last (only) event started at 09:00 today and is still in progress</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Volunteer Training Day"
   3. Click "Mark Complete"</t>
         </is>
       </c>
-      <c r="I186" s="2" t="inlineStr">
+      <c r="I191" s="2" t="inlineStr">
         <is>
           <t>Event started: 09:00 today</t>
         </is>
       </c>
-      <c r="J186" s="2" t="inlineStr">
+      <c r="J191" s="2" t="inlineStr">
         <is>
           <t>The event status changes to "Completed"</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="n">
+    <row r="192">
+      <c r="A192" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B187" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
+      <c r="C192" s="2" t="inlineStr">
         <is>
           <t>E08-S05 - Scenario 3 (Premature completion blocked)</t>
         </is>
       </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_03</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to mark an event complete before its first event has started should be blocked</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has status "Confirmed"; its first event has not yet started</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Tech Conference 2026"
   3. Attempt to click "Mark Complete"</t>
         </is>
       </c>
-      <c r="I187" s="2" t="inlineStr">
+      <c r="I192" s="2" t="inlineStr">
         <is>
           <t>First event: not yet started</t>
         </is>
       </c>
-      <c r="J187" s="2" t="inlineStr">
+      <c r="J192" s="2" t="inlineStr">
         <is>
           <t>The action is blocked; the event cannot be marked complete before it has started</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="n">
+    <row r="193">
+      <c r="A193" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B188" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
+      <c r="C193" s="2" t="inlineStr">
         <is>
           <t>E08-S05 - Scenario 4 (Cancelled event never auto-completes)</t>
         </is>
       </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_04</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>Verify that a Cancelled event should never auto-complete, even after its original end time passes</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr">
         <is>
           <t>Event "Product Launch Night" has status "Cancelled" (per TC_E10S04_01); its original end time has now passed</t>
         </is>
       </c>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>1. Wait for (or trigger) the system's next scheduled evaluation after "Product Launch Night"'s original end time
   2. Open event "Product Launch Night" and check its status</t>
         </is>
       </c>
-      <c r="I188" s="2" t="inlineStr">
+      <c r="I193" s="2" t="inlineStr">
         <is>
           <t>Original end time: passed</t>
         </is>
       </c>
-      <c r="J188" s="2" t="inlineStr">
+      <c r="J193" s="2" t="inlineStr">
         <is>
           <t>The event status remains "Cancelled"; it has not been auto-completed</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="n">
+    <row r="194">
+      <c r="A194" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B189" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
+      <c r="C194" s="2" t="inlineStr">
         <is>
           <t>E08-S05 (checklist: transition to Completed logged)</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting (audit logging)</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_05</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>Verify that an event's transition to Completed should be recorded in the activity log</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has just transitioned to "Completed" (per TC_E08S05_01)</t>
         </is>
       </c>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>1. Log in as a System Administrator
   2. Open the Activity Log and search for "Charity Run"</t>
         </is>
       </c>
-      <c r="I189" s="2" t="inlineStr">
+      <c r="I194" s="2" t="inlineStr">
         <is>
           <t>Event: Charity Run</t>
         </is>
       </c>
-      <c r="J189" s="2" t="inlineStr">
+      <c r="J194" s="2" t="inlineStr">
         <is>
           <t>An activity log entry exists recording the transition to "Completed", with the time it occurred</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="n">
+    <row r="195">
+      <c r="A195" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="C195" s="2" t="inlineStr">
         <is>
           <t>E08-S05 · Scenario 1 (Auto-completed after the end time)</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_06</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>Verify that an event auto-completes at the exact end time and not before</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2002 is Confirmed and its end time is 2026-11-02 17:00:00 +08:00</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>1. Set the system clock to 2026-11-02 16:59:59 +08:00 and trigger the completion evaluation
  2. Record the event status
@@ -10411,52 +10670,52 @@
  4. Record the event status</t>
         </is>
       </c>
-      <c r="I190" s="2" t="inlineStr">
+      <c r="I195" s="2" t="inlineStr">
         <is>
           <t>Event ends: 2026-11-02 17:00:00 +08:00 · Evaluations at 16:59:59 and 17:00:00</t>
         </is>
       </c>
-      <c r="J190" s="2" t="inlineStr">
+      <c r="J195" s="2" t="inlineStr">
         <is>
           <t>At 16:59:59 the status remains Confirmed. At 17:00:00 the status becomes Completed and the transition is recorded in the activity log</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="n">
+    <row r="196">
+      <c r="A196" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B191" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
+      <c r="C196" s="2" t="inlineStr">
         <is>
           <t>E09-S01 - Scenario 1 (Place reserved in an open event)</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_01</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting the required registration information for an open event with places remaining should reserve a place and provide a confirmation</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" is Confirmed, registration is open, and 3 of 5 places remain in its event</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Open event "Community Meetup"
@@ -10464,52 +10723,52 @@
   4. Submit registration</t>
         </is>
       </c>
-      <c r="I191" s="2" t="inlineStr">
+      <c r="I196" s="2" t="inlineStr">
         <is>
           <t>Name: Casey Tan | Email: attendee_c@example.com</t>
         </is>
       </c>
-      <c r="J191" s="2" t="inlineStr">
+      <c r="J196" s="2" t="inlineStr">
         <is>
           <t>attendee_c@example.com's place is reserved, and they receive a confirmation containing the event's details (date, time, venue)</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="n">
+    <row r="197">
+      <c r="A197" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B192" s="2" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
+      <c r="C197" s="2" t="inlineStr">
         <is>
           <t>E09-S01 (checklist: choose events to attend in a multi-event event)</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_02</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>Verify that registering for a multi-event event should let the Attendee choose which events to attend, reserving a place in each chosen event</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has the event and the event, both open for registration</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_d@example.com
   2. Open event "Tech Conference 2026"
@@ -10517,104 +10776,104 @@
   4. Submit registration</t>
         </is>
       </c>
-      <c r="I192" s="2" t="inlineStr">
+      <c r="I197" s="2" t="inlineStr">
         <is>
           <t>Selected: the event only</t>
         </is>
       </c>
-      <c r="J192" s="2" t="inlineStr">
+      <c r="J197" s="2" t="inlineStr">
         <is>
           <t>A place is reserved for attendee_d@example.com in the event only; they are not registered for the event</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="n">
+    <row r="198">
+      <c r="A198" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B193" s="2" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C193" s="2" t="inlineStr">
+      <c r="C198" s="2" t="inlineStr">
         <is>
           <t>E09-S01 - Scenario 2 (Duplicate registration prevented)</t>
         </is>
       </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_03</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to register again for a event already registered for should be told so, without creating a duplicate</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr">
         <is>
           <t>attendee_c@example.com is already registered for "Community Meetup"'s event</t>
         </is>
       </c>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Open event "Community Meetup"
   3. Attempt to register again</t>
         </is>
       </c>
-      <c r="I193" s="2" t="inlineStr">
+      <c r="I198" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_c@example.com (already registered)</t>
         </is>
       </c>
-      <c r="J193" s="2" t="inlineStr">
+      <c r="J198" s="2" t="inlineStr">
         <is>
           <t>attendee_c@example.com is told they are already registered; no duplicate registration is created</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="n">
+    <row r="199">
+      <c r="A199" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B194" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
+      <c r="C199" s="2" t="inlineStr">
         <is>
           <t>E09-S01 - Scenario 3 (Missing fields identified)</t>
         </is>
       </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_04</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting registration with a required field empty should block registration and identify the missing fields</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" is open for registration</t>
         </is>
       </c>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_e@example.com
   2. Open event "Community Meetup"
@@ -10622,309 +10881,361 @@
   4. Submit registration</t>
         </is>
       </c>
-      <c r="I194" s="2" t="inlineStr">
+      <c r="I199" s="2" t="inlineStr">
         <is>
           <t>Name: filled | Email: (blank)</t>
         </is>
       </c>
-      <c r="J194" s="2" t="inlineStr">
+      <c r="J199" s="2" t="inlineStr">
         <is>
           <t>Registration is blocked, and the Email field is identified as missing</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="n">
+    <row r="200">
+      <c r="A200" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B195" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C195" s="2" t="inlineStr">
+      <c r="C200" s="2" t="inlineStr">
         <is>
           <t>E09-S01 - Scenario 4 (Unconfirmed event refused)</t>
         </is>
       </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_05</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to register for an event that is not Confirmed should be refused</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr">
         <is>
           <t>Event "Draft Networking Event" has status "Planning" (not yet Confirmed)</t>
         </is>
       </c>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Attempt to open the registration form for "Draft Networking Event"</t>
         </is>
       </c>
-      <c r="I195" s="2" t="inlineStr">
+      <c r="I200" s="2" t="inlineStr">
         <is>
           <t>Event status: Planning</t>
         </is>
       </c>
-      <c r="J195" s="2" t="inlineStr">
-        <is>
-          <t>Registration is refused, since the event is not yet Confirmed
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t>Registration is refused, since the event is not yet Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>E09-S01</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>E09-S01 — Scenario 5 (One venue shown for a multi-venue event); assumes O-30</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>TC_E09S01_06</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>Verify that an Attendee viewing a multi-venue event should see only the primary venue</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>Event "Tech Summit" is Confirmed with three Confirmed venue bookings and "Grand Auditorium" marked primary; registration is open; attendee_1@connectsphere.com is signed in</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>1. Open "Tech Summit" from the attendee event list
+  2. Read the venue shown
+  3. Register</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>Primary: Grand Auditorium | Others: Seminar Room A, Seminar Room B</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>The event page shows "Grand Auditorium" as the venue; Seminar Rooms A and B are not offered as separate registration options; registration succeeds once as in TC_E09S01_01
 ## E09-S02</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="n">
+    <row r="202">
+      <c r="A202" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B196" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C196" s="2" t="inlineStr">
+      <c r="C202" s="2" t="inlineStr">
         <is>
           <t>E09-S02 (checklist: set a registration limit)</t>
         </is>
       </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_01</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Organiser should be able to set a registration limit for a event</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is signed in; event "Community Meetup"'s event has no registration limit set yet</t>
         </is>
       </c>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>1. Open event "Community Meetup"
   2. Set the Registration Limit for its event to 5
   3. Save</t>
         </is>
       </c>
-      <c r="I196" s="2" t="inlineStr">
+      <c r="I202" s="2" t="inlineStr">
         <is>
           <t>Registration Limit: 5</t>
         </is>
       </c>
-      <c r="J196" s="2" t="inlineStr">
+      <c r="J202" s="2" t="inlineStr">
         <is>
           <t>The event's registration limit is saved as 5</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="n">
+    <row r="203">
+      <c r="A203" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B197" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C197" s="2" t="inlineStr">
+      <c r="C203" s="2" t="inlineStr">
         <is>
           <t>E09-S02 - Scenario 1 (Venue capacity enforced)</t>
         </is>
       </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_02</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>Verify that registration should stop once the event reaches the lower of the Organiser's limit and the booked venue's capacity</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s event has an Organiser-set limit of 5 and a booked venue capacity of 8 (the limit is the lower value); 5 Attendees are already registered</t>
         </is>
       </c>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_f@example.com
   2. Attempt to register for "Community Meetup"</t>
         </is>
       </c>
-      <c r="I197" s="2" t="inlineStr">
+      <c r="I203" s="2" t="inlineStr">
         <is>
           <t>Registered so far: 5 (effective limit) | Venue capacity: 8</t>
         </is>
       </c>
-      <c r="J197" s="2" t="inlineStr">
+      <c r="J203" s="2" t="inlineStr">
         <is>
           <t>Registration is refused since the event has reached its effective capacity of 5</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="n">
+    <row r="204">
+      <c r="A204" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B198" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C198" s="2" t="inlineStr">
+      <c r="C204" s="2" t="inlineStr">
         <is>
           <t>E09-S02 - Scenario 2 (Simultaneous final registration)</t>
         </is>
       </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (last place, concurrency)</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_03</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>Verify that when only one place remains, two simultaneous registration attempts should result in exactly one success</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s event has exactly 1 place remaining</t>
         </is>
       </c>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>1. Have attendee_g@example.com and attendee_h@example.com submit registration for the same event at the same moment
   2. Check both outcomes</t>
         </is>
       </c>
-      <c r="I198" s="2" t="inlineStr">
+      <c r="I204" s="2" t="inlineStr">
         <is>
           <t>1 place remaining | 2 simultaneous attempts</t>
         </is>
       </c>
-      <c r="J198" s="2" t="inlineStr">
+      <c r="J204" s="2" t="inlineStr">
         <is>
           <t>Exactly one of the two registrations succeeds; the other is told the event is full</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="n">
+    <row r="205">
+      <c r="A205" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B199" s="2" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr">
+      <c r="C205" s="2" t="inlineStr">
         <is>
           <t>E09-S02 - Scenario 3 (Full event offers the waiting list)</t>
         </is>
       </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_04</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>Verify that opening the registration page for a full event should close registration and offer the waiting list where enabled</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s event is full (5 of 5 places taken); the waiting list is enabled for this event</t>
         </is>
       </c>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_i@example.com
   2. Open the registration page for "Community Meetup"</t>
         </is>
       </c>
-      <c r="I199" s="2" t="inlineStr">
+      <c r="I205" s="2" t="inlineStr">
         <is>
           <t>Event: full | Waiting list: enabled</t>
         </is>
       </c>
-      <c r="J199" s="2" t="inlineStr">
+      <c r="J205" s="2" t="inlineStr">
         <is>
           <t>Registration is shown as closed, and the option to join the waiting list is offered</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="n">
+    <row r="206">
+      <c r="A206" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B200" s="2" t="inlineStr">
+      <c r="B206" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C200" s="2" t="inlineStr">
+      <c r="C206" s="2" t="inlineStr">
         <is>
           <t>E09-S02 · Scenario 4 (VIP added beyond normal registration)</t>
         </is>
       </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (just below venue capacity)</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_06</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>Verify that a VIP can be added manually when normal registration is full but venue capacity is not reached</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with Orchid Hall booked, venue capacity 200. Normal registration has closed at 199 registrations. Coordinator coord_a@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>1. Open event EVT-2001
  2. Select Add attendee manually
@@ -10932,52 +11243,52 @@
  4. Confirm the addition</t>
         </is>
       </c>
-      <c r="I200" s="2" t="inlineStr">
+      <c r="I206" s="2" t="inlineStr">
         <is>
           <t>Venue capacity: 200 · Current registrations: 199 · Added: 1</t>
         </is>
       </c>
-      <c r="J200" s="2" t="inlineStr">
+      <c r="J206" s="2" t="inlineStr">
         <is>
           <t>The registration is created, total registrations reach 200, and the record is marked as a manual addition distinguishable from a normal registration</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="n">
+    <row r="207">
+      <c r="A207" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B201" s="2" t="inlineStr">
+      <c r="B207" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr">
+      <c r="C207" s="2" t="inlineStr">
         <is>
           <t>E09-S02 · Scenario 5 (VIP blocked at venue capacity)</t>
         </is>
       </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at venue capacity)</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_07</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F207" s="2" t="inlineStr">
         <is>
           <t>Verify that a manual VIP addition is blocked once total registrations equal venue capacity</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with Orchid Hall booked, venue capacity 200, and 200 registrations already recorded. Coordinator coord_a@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="H207" s="2" t="inlineStr">
         <is>
           <t>1. Open event EVT-2001
  2. Select Add attendee manually
@@ -10985,310 +11296,310 @@
  4. Confirm the addition</t>
         </is>
       </c>
-      <c r="I201" s="2" t="inlineStr">
+      <c r="I207" s="2" t="inlineStr">
         <is>
           <t>Venue capacity: 200 · Current registrations: 200</t>
         </is>
       </c>
-      <c r="J201" s="2" t="inlineStr">
+      <c r="J207" s="2" t="inlineStr">
         <is>
           <t>The addition is blocked with a message stating the booked venue capacity has been reached. No registration is created
 ## E09-S03</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="n">
+    <row r="208">
+      <c r="A208" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B202" s="2" t="inlineStr">
+      <c r="B208" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C202" s="2" t="inlineStr">
+      <c r="C208" s="2" t="inlineStr">
         <is>
           <t>E09-S03 (checklist: set registration opening/closing dates)</t>
         </is>
       </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="D208" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_01</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F208" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Organiser should be able to set the registration opening and closing dates for an event</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr">
+      <c r="G208" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is signed in; event "Community Meetup" has no registration dates set</t>
         </is>
       </c>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="H208" s="2" t="inlineStr">
         <is>
           <t>1. Open event "Community Meetup"
   2. Set Registration Opens: 01/10/2026, Registration Closes: 01/12/2026
   3. Save</t>
         </is>
       </c>
-      <c r="I202" s="2" t="inlineStr">
+      <c r="I208" s="2" t="inlineStr">
         <is>
           <t>Opens: 01/10/2026 | Closes: 01/12/2026</t>
         </is>
       </c>
-      <c r="J202" s="2" t="inlineStr">
+      <c r="J208" s="2" t="inlineStr">
         <is>
           <t>The registration opening and closing dates are saved as entered</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="n">
+    <row r="209">
+      <c r="A209" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B203" s="2" t="inlineStr">
+      <c r="B209" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C203" s="2" t="inlineStr">
+      <c r="C209" s="2" t="inlineStr">
         <is>
           <t>E09-S03 (checklist: set a withdrawal deadline)</t>
         </is>
       </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="D209" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_02</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F209" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Organiser should be able to set a withdrawal deadline for an event</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is signed in; event "Community Meetup" has no withdrawal deadline set</t>
         </is>
       </c>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="H209" s="2" t="inlineStr">
         <is>
           <t>1. Open event "Community Meetup"
   2. Set Withdrawal Deadline: 10/12/2026
   3. Save</t>
         </is>
       </c>
-      <c r="I203" s="2" t="inlineStr">
+      <c r="I209" s="2" t="inlineStr">
         <is>
           <t>Withdrawal Deadline: 10/12/2026</t>
         </is>
       </c>
-      <c r="J203" s="2" t="inlineStr">
+      <c r="J209" s="2" t="inlineStr">
         <is>
           <t>The withdrawal deadline is saved as 10/12/2026</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="n">
+    <row r="210">
+      <c r="A210" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B204" s="2" t="inlineStr">
+      <c r="B210" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C204" s="2" t="inlineStr">
+      <c r="C210" s="2" t="inlineStr">
         <is>
           <t>E09-S03 - Scenario 1 (Before registration opens)</t>
         </is>
       </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (before)</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_03</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>Verify that an Attendee viewing an event before its registration opening date should see registration as not yet open, with the opening date stated</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr">
+      <c r="G210" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s registration opening date (01/10/2026) has not yet been reached</t>
         </is>
       </c>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="H210" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Open event "Community Meetup"</t>
         </is>
       </c>
-      <c r="I204" s="2" t="inlineStr">
+      <c r="I210" s="2" t="inlineStr">
         <is>
           <t>Opening date: 01/10/2026 (not reached)</t>
         </is>
       </c>
-      <c r="J204" s="2" t="inlineStr">
+      <c r="J210" s="2" t="inlineStr">
         <is>
           <t>Registration is shown as "Not yet open", with the message stating it opens on 01/10/2026</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="n">
+    <row r="211">
+      <c r="A211" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B205" s="2" t="inlineStr">
+      <c r="B211" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C205" s="2" t="inlineStr">
+      <c r="C211" s="2" t="inlineStr">
         <is>
           <t>E09-S03 - Scenario 2 (After registration closes)</t>
         </is>
       </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (after)</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_04</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>Verify that an Attendee trying to register after the registration closing date has passed should be refused</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr">
+      <c r="G211" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s registration closing date (01/12/2026) has passed</t>
         </is>
       </c>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="H211" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Attempt to register for "Community Meetup"</t>
         </is>
       </c>
-      <c r="I205" s="2" t="inlineStr">
+      <c r="I211" s="2" t="inlineStr">
         <is>
           <t>Closing date: 01/12/2026 (passed)</t>
         </is>
       </c>
-      <c r="J205" s="2" t="inlineStr">
+      <c r="J211" s="2" t="inlineStr">
         <is>
           <t>Registration is refused, since the closing date has passed</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="n">
+    <row r="212">
+      <c r="A212" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B206" s="2" t="inlineStr">
+      <c r="B212" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C206" s="2" t="inlineStr">
+      <c r="C212" s="2" t="inlineStr">
         <is>
           <t>E09-S03 - Scenario 3 (Closing date after event start warned)</t>
         </is>
       </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_05</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="F212" s="2" t="inlineStr">
         <is>
           <t>Verify that setting a registration closing date that falls after the event has started should warn the Organiser and ask them to confirm</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr">
+      <c r="G212" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is editing event "Community Meetup", which starts on 15/11/2026</t>
         </is>
       </c>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="H212" s="2" t="inlineStr">
         <is>
           <t>1. Set Registration Closes: 20/11/2026 (after the event's start date)
   2. Click "Save"</t>
         </is>
       </c>
-      <c r="I206" s="2" t="inlineStr">
+      <c r="I212" s="2" t="inlineStr">
         <is>
           <t>Closing date: 20/11/2026 (after event start 15/11/2026)</t>
         </is>
       </c>
-      <c r="J206" s="2" t="inlineStr">
+      <c r="J212" s="2" t="inlineStr">
         <is>
           <t>A warning is shown asking the Organiser to confirm this is intended, before the closing date is saved</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="n">
+    <row r="213">
+      <c r="A213" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B207" s="2" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C207" s="2" t="inlineStr">
+      <c r="C213" s="2" t="inlineStr">
         <is>
           <t>E09-S03 - Scenario 4 (Waiting list enabled)</t>
         </is>
       </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_06</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="F213" s="2" t="inlineStr">
         <is>
           <t>Verify that enabling the waiting list for an event should offer it to Attendees once a event becomes full</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr">
+      <c r="G213" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is about to enable the waiting list for event "Community Meetup"</t>
         </is>
       </c>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="H213" s="2" t="inlineStr">
         <is>
           <t>1. Open event "Community Meetup"
   2. Toggle "Enable Waiting List" on
@@ -11296,363 +11607,363 @@
   4. Fill the event to capacity and attempt a further registration</t>
         </is>
       </c>
-      <c r="I207" s="2" t="inlineStr">
+      <c r="I213" s="2" t="inlineStr">
         <is>
           <t>Waiting List: Enabled</t>
         </is>
       </c>
-      <c r="J207" s="2" t="inlineStr">
+      <c r="J213" s="2" t="inlineStr">
         <is>
           <t>Once the event is full, the further registration attempt is offered the waiting list instead of being simply refused</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="n">
+    <row r="214">
+      <c r="A214" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B208" s="2" t="inlineStr">
+      <c r="B214" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C208" s="2" t="inlineStr">
+      <c r="C214" s="2" t="inlineStr">
         <is>
           <t>E09-S03 · Scenario 1 (Before registration opens)</t>
         </is>
       </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="D214" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E214" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_07</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="F214" s="2" t="inlineStr">
         <is>
           <t>Verify that registration succeeds at the exact opening timestamp</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr">
+      <c r="G214" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with registration opening at 2026-10-01 09:00:00 +08:00. Attendee attendee_a@example.com is signed in. Event EVT-2001 has places remaining</t>
         </is>
       </c>
-      <c r="H208" s="2" t="inlineStr">
+      <c r="H214" s="2" t="inlineStr">
         <is>
           <t>1. Set the system clock to exactly 2026-10-01 09:00:00 +08:00
  2. Open event EVT-2001
  3. Select event EVT-2001 and submit registration</t>
         </is>
       </c>
-      <c r="I208" s="2" t="inlineStr">
+      <c r="I214" s="2" t="inlineStr">
         <is>
           <t>Registration opens: 2026-10-01 09:00:00 +08:00 · Attempt at: 2026-10-01 09:00:00 +08:00</t>
         </is>
       </c>
-      <c r="J208" s="2" t="inlineStr">
+      <c r="J214" s="2" t="inlineStr">
         <is>
           <t>Registration succeeds and a place is reserved. The opening moment is inclusive: registration is open at, not after, the opening timestamp</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2" t="n">
+    <row r="215">
+      <c r="A215" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B209" s="2" t="inlineStr">
+      <c r="B215" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C209" s="2" t="inlineStr">
+      <c r="C215" s="2" t="inlineStr">
         <is>
           <t>E09-S03 · Scenario 2 (After registration closes)</t>
         </is>
       </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="D215" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E215" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_08</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F215" s="2" t="inlineStr">
         <is>
           <t>Verify that registration still succeeds at the exact closing timestamp</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr">
+      <c r="G215" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with registration closing at 2026-10-20 17:00:00 +08:00. Attendee attendee_b@example.com is signed in. Event EVT-2001 has places remaining</t>
         </is>
       </c>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="H215" s="2" t="inlineStr">
         <is>
           <t>1. Set the system clock to exactly 2026-10-20 17:00:00 +08:00
  2. Open event EVT-2001
  3. Select event EVT-2001 and submit registration</t>
         </is>
       </c>
-      <c r="I209" s="2" t="inlineStr">
+      <c r="I215" s="2" t="inlineStr">
         <is>
           <t>Registration closes: 2026-10-20 17:00:00 +08:00 · Attempt at: 2026-10-20 17:00:00 +08:00</t>
         </is>
       </c>
-      <c r="J209" s="2" t="inlineStr">
+      <c r="J215" s="2" t="inlineStr">
         <is>
           <t>Registration succeeds. The acceptance criterion refuses registration once the closing date "has passed", so at the exact closing instant it has not yet passed. One second later the same attempt must be refused
 ## E09-S04</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="2" t="n">
+    <row r="216">
+      <c r="A216" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B210" s="2" t="inlineStr">
+      <c r="B216" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C210" s="2" t="inlineStr">
+      <c r="C216" s="2" t="inlineStr">
         <is>
           <t>E09-S04 - Scenario 1 (Joined a full event's list)</t>
         </is>
       </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="D216" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_01</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="F216" s="2" t="inlineStr">
         <is>
           <t>Verify that joining the waiting list for a full event with the list enabled should add the Attendee and confirm their position</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr">
+      <c r="G216" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s event is full; the waiting list is enabled and currently empty</t>
         </is>
       </c>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="H216" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_i@example.com
   2. Open the registration page for "Community Meetup"
   3. Click "Join Waiting List"</t>
         </is>
       </c>
-      <c r="I210" s="2" t="inlineStr">
+      <c r="I216" s="2" t="inlineStr">
         <is>
           <t>Waiting list: enabled, currently empty</t>
         </is>
       </c>
-      <c r="J210" s="2" t="inlineStr">
+      <c r="J216" s="2" t="inlineStr">
         <is>
           <t>attendee_i@example.com is added to the waiting list and shown their position (e.g. "Position 1")</t>
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="2" t="n">
+    <row r="217">
+      <c r="A217" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B211" s="2" t="inlineStr">
+      <c r="B217" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C211" s="2" t="inlineStr">
+      <c r="C217" s="2" t="inlineStr">
         <is>
           <t>E09-S04 - Scenario 2 (Released place notified to all)</t>
         </is>
       </c>
-      <c r="D211" s="2" t="inlineStr">
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_02</t>
         </is>
       </c>
-      <c r="F211" s="2" t="inlineStr">
+      <c r="F217" s="2" t="inlineStr">
         <is>
           <t>Verify that when a place is released in a event with a waiting list, all waitlisted Attendees should be notified and the place claimed on a first-come, first-served basis</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr">
+      <c r="G217" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s waiting list has attendee_i@example.com (position 1) and attendee_j@example.com (position 2)</t>
         </is>
       </c>
-      <c r="H211" s="2" t="inlineStr">
+      <c r="H217" s="2" t="inlineStr">
         <is>
           <t>1. Have registered Attendee attendee_m@example.com withdraw from "Community Meetup", releasing one place
   2. Check notifications for attendee_i@example.com and attendee_j@example.com
   3. Have attendee_i@example.com claim the released place first</t>
         </is>
       </c>
-      <c r="I211" s="2" t="inlineStr">
+      <c r="I217" s="2" t="inlineStr">
         <is>
           <t>Waiting list: attendee_i@example.com (1st), attendee_j@example.com (2nd)</t>
         </is>
       </c>
-      <c r="J211" s="2" t="inlineStr">
+      <c r="J217" s="2" t="inlineStr">
         <is>
           <t>Both waitlisted Attendees are notified of the released place; attendee_i@example.com successfully claims it since they acted first</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="2" t="n">
+    <row r="218">
+      <c r="A218" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B212" s="2" t="inlineStr">
+      <c r="B218" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C212" s="2" t="inlineStr">
+      <c r="C218" s="2" t="inlineStr">
         <is>
           <t>E09-S04 - Scenario 3 (Claimed place leaves the list)</t>
         </is>
       </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_03</t>
         </is>
       </c>
-      <c r="F212" s="2" t="inlineStr">
+      <c r="F218" s="2" t="inlineStr">
         <is>
           <t>Verify that claiming a released place should remove the Attendee from the waiting list for that event</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr">
+      <c r="G218" s="2" t="inlineStr">
         <is>
           <t>attendee_i@example.com has just claimed a released place in "Community Meetup"'s event</t>
         </is>
       </c>
-      <c r="H212" s="2" t="inlineStr">
+      <c r="H218" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_i@example.com
   2. Check the waiting list for "Community Meetup"'s event</t>
         </is>
       </c>
-      <c r="I212" s="2" t="inlineStr">
+      <c r="I218" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_i@example.com (just claimed a place)</t>
         </is>
       </c>
-      <c r="J212" s="2" t="inlineStr">
+      <c r="J218" s="2" t="inlineStr">
         <is>
           <t>attendee_i@example.com no longer appears on the waiting list for that event, since they are now registered</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="2" t="n">
+    <row r="219">
+      <c r="A219" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B213" s="2" t="inlineStr">
+      <c r="B219" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C213" s="2" t="inlineStr">
+      <c r="C219" s="2" t="inlineStr">
         <is>
           <t>E09-S04 - Scenario 4 (Disabled list offers nothing)</t>
         </is>
       </c>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="D219" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_04</t>
         </is>
       </c>
-      <c r="F213" s="2" t="inlineStr">
+      <c r="F219" s="2" t="inlineStr">
         <is>
           <t>Verify that a full event should not offer a waiting list when the Organiser has disabled it</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr">
+      <c r="G219" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has the waiting list disabled; the event is full</t>
         </is>
       </c>
-      <c r="H213" s="2" t="inlineStr">
+      <c r="H219" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_k@example.com
   2. Open the registration page for the event of "Tech Conference 2026"</t>
         </is>
       </c>
-      <c r="I213" s="2" t="inlineStr">
+      <c r="I219" s="2" t="inlineStr">
         <is>
           <t>Waiting list: disabled | the event: full</t>
         </is>
       </c>
-      <c r="J213" s="2" t="inlineStr">
+      <c r="J219" s="2" t="inlineStr">
         <is>
           <t>No waiting list option is offered; registration is simply shown as closed</t>
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="2" t="n">
+    <row r="220">
+      <c r="A220" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B214" s="2" t="inlineStr">
+      <c r="B220" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C214" s="2" t="inlineStr">
+      <c r="C220" s="2" t="inlineStr">
         <is>
           <t>E09-S04 (checklist: leave the waiting list)</t>
         </is>
       </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_05</t>
         </is>
       </c>
-      <c r="F214" s="2" t="inlineStr">
+      <c r="F220" s="2" t="inlineStr">
         <is>
           <t>Verify that an Attendee should be able to voluntarily leave the waiting list before a place is released</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr">
+      <c r="G220" s="2" t="inlineStr">
         <is>
           <t>attendee_j@example.com is on the waiting list for "Community Meetup"'s event, position 2</t>
         </is>
       </c>
-      <c r="H214" s="2" t="inlineStr">
+      <c r="H220" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_j@example.com
   2. Open the waiting list status for "Community Meetup"
@@ -11660,622 +11971,622 @@
   4. Confirm</t>
         </is>
       </c>
-      <c r="I214" s="2" t="inlineStr">
+      <c r="I220" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_j@example.com</t>
         </is>
       </c>
-      <c r="J214" s="2" t="inlineStr">
+      <c r="J220" s="2" t="inlineStr">
         <is>
           <t>attendee_j@example.com is removed from the waiting list and no longer receives notifications about released places for that event
 ## E09-S05</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="2" t="n">
+    <row r="221">
+      <c r="A221" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B215" s="2" t="inlineStr">
+      <c r="B221" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="C215" s="2" t="inlineStr">
+      <c r="C221" s="2" t="inlineStr">
         <is>
           <t>E09-S05 - Scenario 1 (Registration withdrawn)</t>
         </is>
       </c>
-      <c r="D215" s="2" t="inlineStr">
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>TC_E09S05_01</t>
         </is>
       </c>
-      <c r="F215" s="2" t="inlineStr">
+      <c r="F221" s="2" t="inlineStr">
         <is>
           <t>Verify that withdrawing from a single event before the withdrawal deadline should cancel that registration and release the place, leaving other events unaffected</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr">
+      <c r="G221" s="2" t="inlineStr">
         <is>
           <t>attendee_d@example.com is registered for both the event and the event of "Tech Conference 2026"; the withdrawal deadline has not passed</t>
         </is>
       </c>
-      <c r="H215" s="2" t="inlineStr">
+      <c r="H221" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_d@example.com
   2. Open "My Registrations"
   3. Withdraw from the event only</t>
         </is>
       </c>
-      <c r="I215" s="2" t="inlineStr">
+      <c r="I221" s="2" t="inlineStr">
         <is>
           <t>Withdrawing from: the event only</t>
         </is>
       </c>
-      <c r="J215" s="2" t="inlineStr">
+      <c r="J221" s="2" t="inlineStr">
         <is>
           <t>The the event registration is cancelled and its place becomes available again; attendee_d@example.com remains registered for the event</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2" t="n">
+    <row r="222">
+      <c r="A222" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B216" s="2" t="inlineStr">
+      <c r="B222" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="C216" s="2" t="inlineStr">
+      <c r="C222" s="2" t="inlineStr">
         <is>
           <t>E09-S05 - Scenario 2 (Withdrawal after deadline refused)</t>
         </is>
       </c>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>TC_E09S05_03</t>
         </is>
       </c>
-      <c r="F216" s="2" t="inlineStr">
+      <c r="F222" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to withdraw after the withdrawal deadline has passed should be refused, with a contact provided for assistance</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr">
+      <c r="G222" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s withdrawal deadline (10/12/2026) has passed</t>
         </is>
       </c>
-      <c r="H216" s="2" t="inlineStr">
+      <c r="H222" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Attempt to withdraw from "Community Meetup"</t>
         </is>
       </c>
-      <c r="I216" s="2" t="inlineStr">
+      <c r="I222" s="2" t="inlineStr">
         <is>
           <t>Withdrawal deadline: 10/12/2026 (passed)</t>
         </is>
       </c>
-      <c r="J216" s="2" t="inlineStr">
+      <c r="J222" s="2" t="inlineStr">
         <is>
           <t>Withdrawal is refused with the message "Withdrawal has closed" and a contact is provided for assistance</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="2" t="n">
+    <row r="223">
+      <c r="A223" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B217" s="2" t="inlineStr">
+      <c r="B223" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="C217" s="2" t="inlineStr">
+      <c r="C223" s="2" t="inlineStr">
         <is>
           <t>E09-S05 · Scenario 2 (Withdrawal after deadline refused)</t>
         </is>
       </c>
-      <c r="D217" s="2" t="inlineStr">
+      <c r="D223" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>TC_E09S05_04</t>
         </is>
       </c>
-      <c r="F217" s="2" t="inlineStr">
+      <c r="F223" s="2" t="inlineStr">
         <is>
           <t>Verify that withdrawal succeeds at the exact withdrawal deadline</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr">
+      <c r="G223" s="2" t="inlineStr">
         <is>
           <t>Attendee attendee_a@example.com is registered for event EVT-2001. The withdrawal deadline for event EVT-2001 is 2026-10-25 23:59:59 +08:00</t>
         </is>
       </c>
-      <c r="H217" s="2" t="inlineStr">
+      <c r="H223" s="2" t="inlineStr">
         <is>
           <t>1. Set the system clock to exactly 2026-10-25 23:59:59 +08:00
  2. Sign in as attendee_a@example.com
  3. Open the registration for EVT-2001 and select Withdraw</t>
         </is>
       </c>
-      <c r="I217" s="2" t="inlineStr">
+      <c r="I223" s="2" t="inlineStr">
         <is>
           <t>Withdrawal deadline: 2026-10-25 23:59:59 +08:00 · Attempt at: 2026-10-25 23:59:59 +08:00</t>
         </is>
       </c>
-      <c r="J217" s="2" t="inlineStr">
+      <c r="J223" s="2" t="inlineStr">
         <is>
           <t>The withdrawal succeeds, the registration status becomes Withdrawn and the place is released. Every waitlisted Attendee for EVT-2001 is notified that a place is available
 ## E09-S06</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="2" t="n">
+    <row r="224">
+      <c r="A224" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B218" s="2" t="inlineStr">
+      <c r="B224" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="C218" s="2" t="inlineStr">
+      <c r="C224" s="2" t="inlineStr">
         <is>
           <t>E09-S06 - Scenario 1 (Attendance marked after completion)</t>
         </is>
       </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="D224" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>TC_E09S06_01</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr">
+      <c r="F224" s="2" t="inlineStr">
         <is>
           <t>Verify that marking a registered Attendee as attended for a event after the event is Completed should update their record without changing the registration figure</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr">
+      <c r="G224" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has status "Completed" (per TC_E08S05_01); attendee_a@example.com is registered for its event</t>
         </is>
       </c>
-      <c r="H218" s="2" t="inlineStr">
+      <c r="H224" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the completed event "Charity Run"
   3. Mark attendee_a@example.com as "Attended"</t>
         </is>
       </c>
-      <c r="I218" s="2" t="inlineStr">
+      <c r="I224" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_a@example.com</t>
         </is>
       </c>
-      <c r="J218" s="2" t="inlineStr">
+      <c r="J224" s="2" t="inlineStr">
         <is>
           <t>attendee_a@example.com's record shows "Attended"; the total registration figure for the event remains unchanged</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="2" t="n">
+    <row r="225">
+      <c r="A225" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B219" s="2" t="inlineStr">
+      <c r="B225" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="C219" s="2" t="inlineStr">
+      <c r="C225" s="2" t="inlineStr">
         <is>
           <t>E09-S06 - Scenario 2 (Registered but not attended)</t>
         </is>
       </c>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>TC_E09S06_02</t>
         </is>
       </c>
-      <c r="F219" s="2" t="inlineStr">
+      <c r="F225" s="2" t="inlineStr">
         <is>
           <t>Verify that a registered Attendee who did not attend should be shown as registered but not attended once the event is Completed</t>
         </is>
       </c>
-      <c r="G219" s="2" t="inlineStr">
+      <c r="G225" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has status "Completed"; attendee_b@example.com was registered but has not been marked attended</t>
         </is>
       </c>
-      <c r="H219" s="2" t="inlineStr">
+      <c r="H225" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the completed event "Charity Run"
   3. Check attendee_b@example.com's status</t>
         </is>
       </c>
-      <c r="I219" s="2" t="inlineStr">
+      <c r="I225" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_b@example.com (registered, not marked attended)</t>
         </is>
       </c>
-      <c r="J219" s="2" t="inlineStr">
+      <c r="J225" s="2" t="inlineStr">
         <is>
           <t>attendee_b@example.com is shown as "Registered but not attended"</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="2" t="n">
+    <row r="226">
+      <c r="A226" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B220" s="2" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="C220" s="2" t="inlineStr">
+      <c r="C226" s="2" t="inlineStr">
         <is>
           <t>E09-S06 - Scenario 3 (Recording before completion blocked)</t>
         </is>
       </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>TC_E09S06_03</t>
         </is>
       </c>
-      <c r="F220" s="2" t="inlineStr">
+      <c r="F226" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to record attendance before the event is Completed should be blocked</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr">
+      <c r="G226" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has status "Confirmed" (not yet Completed)</t>
         </is>
       </c>
-      <c r="H220" s="2" t="inlineStr">
+      <c r="H226" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Tech Conference 2026"
   3. Attempt to mark an Attendee as attended</t>
         </is>
       </c>
-      <c r="I220" s="2" t="inlineStr">
+      <c r="I226" s="2" t="inlineStr">
         <is>
           <t>Event status: Confirmed (not Completed)</t>
         </is>
       </c>
-      <c r="J220" s="2" t="inlineStr">
+      <c r="J226" s="2" t="inlineStr">
         <is>
           <t>The action is blocked; attendance cannot be recorded before the event is Completed</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="2" t="n">
+    <row r="227">
+      <c r="A227" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B221" s="2" t="inlineStr">
+      <c r="B227" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="C221" s="2" t="inlineStr">
+      <c r="C227" s="2" t="inlineStr">
         <is>
           <t>E09-S06 (checklist: registration/attendance counts viewable side by side)</t>
         </is>
       </c>
-      <c r="D221" s="2" t="inlineStr">
+      <c r="D227" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E221" s="2" t="inlineStr">
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>TC_E09S06_04</t>
         </is>
       </c>
-      <c r="F221" s="2" t="inlineStr">
+      <c r="F227" s="2" t="inlineStr">
         <is>
           <t>Verify that registration and attendance counts should be viewable side by side for each event</t>
         </is>
       </c>
-      <c r="G221" s="2" t="inlineStr">
+      <c r="G227" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has status "Completed"; its event had 5 registrations and 4 marked attended</t>
         </is>
       </c>
-      <c r="H221" s="2" t="inlineStr">
+      <c r="H227" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the completed event "Charity Run"
   3. View the event's registration and attendance summary</t>
         </is>
       </c>
-      <c r="I221" s="2" t="inlineStr">
+      <c r="I227" s="2" t="inlineStr">
         <is>
           <t>Registered: 5 | Attended: 4</t>
         </is>
       </c>
-      <c r="J221" s="2" t="inlineStr">
+      <c r="J227" s="2" t="inlineStr">
         <is>
           <t>The summary shows "Registered: 5" and "Attended: 4" together, side by side
 ## E09-S07</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="2" t="n">
+    <row r="228">
+      <c r="A228" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B222" s="2" t="inlineStr">
+      <c r="B228" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="C222" s="2" t="inlineStr">
+      <c r="C228" s="2" t="inlineStr">
         <is>
           <t>E09-S07 - Scenario 1 (Registrations grouped by event)</t>
         </is>
       </c>
-      <c r="D222" s="2" t="inlineStr">
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>TC_E09S07_01</t>
         </is>
       </c>
-      <c r="F222" s="2" t="inlineStr">
+      <c r="F228" s="2" t="inlineStr">
         <is>
           <t>Verify that opening the registration list for an event with registered Attendees should show each Attendee's name, email address and contact number</t>
         </is>
       </c>
-      <c r="G222" s="2" t="inlineStr">
+      <c r="G228" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has attendee_a@example.com and attendee_b@example.com registered, each with a name, email address and contact number on file</t>
         </is>
       </c>
-      <c r="H222" s="2" t="inlineStr">
+      <c r="H228" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the registration list for "Tech Conference 2026"</t>
         </is>
       </c>
-      <c r="I222" s="2" t="inlineStr">
+      <c r="I228" s="2" t="inlineStr">
         <is>
           <t>attendee_a@example.com: +65 9123 4567 | attendee_b@example.com: +65 9234 5678</t>
         </is>
       </c>
-      <c r="J222" s="2" t="inlineStr">
+      <c r="J228" s="2" t="inlineStr">
         <is>
           <t>The list shows each Attendee's name, email address and contact number: attendee_a@example.com and attendee_b@example.com both appear with their full contact details</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="2" t="n">
+    <row r="229">
+      <c r="A229" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B223" s="2" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="C223" s="2" t="inlineStr">
+      <c r="C229" s="2" t="inlineStr">
         <is>
           <t>E09-S07 - Scenario 2 (Counts and remaining capacity)</t>
         </is>
       </c>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>TC_E09S07_02</t>
         </is>
       </c>
-      <c r="F223" s="2" t="inlineStr">
+      <c r="F229" s="2" t="inlineStr">
         <is>
           <t>Verify that the registration list should show the registered count and remaining capacity per event</t>
         </is>
       </c>
-      <c r="G223" s="2" t="inlineStr">
+      <c r="G229" s="2" t="inlineStr">
         <is>
           <t>"Tech Conference 2026" the event has 100 registered out of a capacity of 150</t>
         </is>
       </c>
-      <c r="H223" s="2" t="inlineStr">
+      <c r="H229" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the registration list for "Tech Conference 2026"</t>
         </is>
       </c>
-      <c r="I223" s="2" t="inlineStr">
+      <c r="I229" s="2" t="inlineStr">
         <is>
           <t>the event: 100 registered, capacity 150</t>
         </is>
       </c>
-      <c r="J223" s="2" t="inlineStr">
+      <c r="J229" s="2" t="inlineStr">
         <is>
           <t>the event shows "100 registered" and "50 remaining"</t>
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="2" t="n">
+    <row r="230">
+      <c r="A230" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B224" s="2" t="inlineStr">
+      <c r="B230" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="C224" s="2" t="inlineStr">
+      <c r="C230" s="2" t="inlineStr">
         <is>
           <t>E09-S07 - Scenario 3 (Unmanaged event refused)</t>
         </is>
       </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="D230" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="E230" s="2" t="inlineStr">
         <is>
           <t>TC_E09S07_03</t>
         </is>
       </c>
-      <c r="F224" s="2" t="inlineStr">
+      <c r="F230" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to open the registration list for an event that does not belong to the Organiser's client organisation should be refused</t>
         </is>
       </c>
-      <c r="G224" s="2" t="inlineStr">
+      <c r="G230" s="2" t="inlineStr">
         <is>
           <t>organiser_b@clienta.com is linked to Client B; event "Annual Tech Summit" belongs to Client A</t>
         </is>
       </c>
-      <c r="H224" s="2" t="inlineStr">
+      <c r="H230" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_b@clienta.com
   2. Attempt to open the registration list for "Annual Tech Summit"</t>
         </is>
       </c>
-      <c r="I224" s="2" t="inlineStr">
+      <c r="I230" s="2" t="inlineStr">
         <is>
           <t>Acting user: organiser_b@clienta.com | Event: Annual Tech Summit (Client A)</t>
         </is>
       </c>
-      <c r="J224" s="2" t="inlineStr">
+      <c r="J230" s="2" t="inlineStr">
         <is>
           <t>Access is refused, since "Annual Tech Summit" does not belong to organiser_b@clienta.com's client organisation</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="2" t="n">
+    <row r="231">
+      <c r="A231" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B225" s="2" t="inlineStr">
+      <c r="B231" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="C225" s="2" t="inlineStr">
+      <c r="C231" s="2" t="inlineStr">
         <is>
           <t>E09-S07 - Scenario 4 (Waitlist shown separately)</t>
         </is>
       </c>
-      <c r="D225" s="2" t="inlineStr">
+      <c r="D231" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="E231" s="2" t="inlineStr">
         <is>
           <t>TC_E09S07_04</t>
         </is>
       </c>
-      <c r="F225" s="2" t="inlineStr">
+      <c r="F231" s="2" t="inlineStr">
         <is>
           <t>Verify that waitlisted Attendees should be shown separately from registered Attendees on the registration list</t>
         </is>
       </c>
-      <c r="G225" s="2" t="inlineStr">
+      <c r="G231" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s event has 5 registered Attendees and 2 on the waiting list</t>
         </is>
       </c>
-      <c r="H225" s="2" t="inlineStr">
+      <c r="H231" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the registration list for "Community Meetup"</t>
         </is>
       </c>
-      <c r="I225" s="2" t="inlineStr">
+      <c r="I231" s="2" t="inlineStr">
         <is>
           <t>Registered: 5 | Waitlisted: 2</t>
         </is>
       </c>
-      <c r="J225" s="2" t="inlineStr">
+      <c r="J231" s="2" t="inlineStr">
         <is>
           <t>The 5 registered Attendees and the 2 waitlisted Attendees are shown in clearly separate sections/lists</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="2" t="n">
+    <row r="232">
+      <c r="A232" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B226" s="2" t="inlineStr">
+      <c r="B232" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C226" s="2" t="inlineStr">
+      <c r="C232" s="2" t="inlineStr">
         <is>
           <t>E10-S01 - Scenario 1 (Change request recorded)</t>
         </is>
       </c>
-      <c r="D226" s="2" t="inlineStr">
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_01</t>
         </is>
       </c>
-      <c r="F226" s="2" t="inlineStr">
+      <c r="F232" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting a change request on an approved or confirmed event should notify the assigned Coordinator and record the request against the event</t>
         </is>
       </c>
-      <c r="G226" s="2" t="inlineStr">
+      <c r="G232" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" has status "Confirmed"</t>
         </is>
       </c>
-      <c r="H226" s="2" t="inlineStr">
+      <c r="H232" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Community Meetup"
@@ -12284,155 +12595,155 @@
   5. Submit</t>
         </is>
       </c>
-      <c r="I226" s="2" t="inlineStr">
+      <c r="I232" s="2" t="inlineStr">
         <is>
           <t>Change description: "Increase expected attendance to 10"</t>
         </is>
       </c>
-      <c r="J226" s="2" t="inlineStr">
+      <c r="J232" s="2" t="inlineStr">
         <is>
           <t>coordinator_1@connectsphere.com is notified, and the change request is recorded against "Community Meetup"</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="2" t="n">
+    <row r="233">
+      <c r="A233" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B227" s="2" t="inlineStr">
+      <c r="B233" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C227" s="2" t="inlineStr">
+      <c r="C233" s="2" t="inlineStr">
         <is>
           <t>E10-S01 - Scenario 2 (Confirmed details shown alongside)</t>
         </is>
       </c>
-      <c r="D227" s="2" t="inlineStr">
+      <c r="D233" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_02</t>
         </is>
       </c>
-      <c r="F227" s="2" t="inlineStr">
+      <c r="F233" s="2" t="inlineStr">
         <is>
           <t>Verify that viewing an event with a pending change request should still show the currently confirmed details alongside the pending request</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr">
+      <c r="G233" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" has a pending change request; its confirmed details (venue, date, time) remain unchanged</t>
         </is>
       </c>
-      <c r="H227" s="2" t="inlineStr">
+      <c r="H233" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Community Meetup"</t>
         </is>
       </c>
-      <c r="I227" s="2" t="inlineStr">
+      <c r="I233" s="2" t="inlineStr">
         <is>
           <t>Pending request: Increase expected attendance to 10</t>
         </is>
       </c>
-      <c r="J227" s="2" t="inlineStr">
+      <c r="J233" s="2" t="inlineStr">
         <is>
           <t>The page shows both the currently confirmed details and the pending change request together</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="2" t="n">
+    <row r="234">
+      <c r="A234" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B228" s="2" t="inlineStr">
+      <c r="B234" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C228" s="2" t="inlineStr">
+      <c r="C234" s="2" t="inlineStr">
         <is>
           <t>E10-S01 - Scenario 3 (Refused edit offers the form)</t>
         </is>
       </c>
-      <c r="D228" s="2" t="inlineStr">
+      <c r="D234" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="E234" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_03</t>
         </is>
       </c>
-      <c r="F228" s="2" t="inlineStr">
+      <c r="F234" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to directly edit a restricted field after approval should be refused and offered the change request form pre-filled with that field</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr">
+      <c r="G234" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" has status "Confirmed"</t>
         </is>
       </c>
-      <c r="H228" s="2" t="inlineStr">
+      <c r="H234" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Community Meetup"
   3. Attempt to directly edit the Expected Attendance field</t>
         </is>
       </c>
-      <c r="I228" s="2" t="inlineStr">
+      <c r="I234" s="2" t="inlineStr">
         <is>
           <t>Field attempted: Expected Attendance</t>
         </is>
       </c>
-      <c r="J228" s="2" t="inlineStr">
+      <c r="J234" s="2" t="inlineStr">
         <is>
           <t>Direct editing is refused; organiser_a@clienta.com is offered the change request form, pre-filled with the Expected Attendance field</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="2" t="n">
+    <row r="235">
+      <c r="A235" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B229" s="2" t="inlineStr">
+      <c r="B235" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C229" s="2" t="inlineStr">
+      <c r="C235" s="2" t="inlineStr">
         <is>
           <t>E10-S01 - Scenario 4 (Approved change applied)</t>
         </is>
       </c>
-      <c r="D229" s="2" t="inlineStr">
+      <c r="D235" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E229" s="2" t="inlineStr">
+      <c r="E235" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_04</t>
         </is>
       </c>
-      <c r="F229" s="2" t="inlineStr">
+      <c r="F235" s="2" t="inlineStr">
         <is>
           <t>Verify that when the Coordinator approves a change request, the event should be updated and the Organiser notified</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr">
+      <c r="G235" s="2" t="inlineStr">
         <is>
           <t>A change request on "Community Meetup" (increase expected attendance to 10) is pending Coordinator approval</t>
         </is>
       </c>
-      <c r="H229" s="2" t="inlineStr">
+      <c r="H235" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the pending change request
@@ -12440,52 +12751,52 @@
   4. Log in as organiser_a@clienta.com and check the event and notifications</t>
         </is>
       </c>
-      <c r="I229" s="2" t="inlineStr">
+      <c r="I235" s="2" t="inlineStr">
         <is>
           <t>Change: Expected Attendance -&gt; 10</t>
         </is>
       </c>
-      <c r="J229" s="2" t="inlineStr">
+      <c r="J235" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s Expected Attendance is updated to 10, and organiser_a@clienta.com is notified that the change was applied</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="2" t="n">
+    <row r="236">
+      <c r="A236" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B230" s="2" t="inlineStr">
+      <c r="B236" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C230" s="2" t="inlineStr">
+      <c r="C236" s="2" t="inlineStr">
         <is>
           <t>E10-S01 (checklist: notified when Coordinator approves or declines)</t>
         </is>
       </c>
-      <c r="D230" s="2" t="inlineStr">
+      <c r="D236" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E230" s="2" t="inlineStr">
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_05</t>
         </is>
       </c>
-      <c r="F230" s="2" t="inlineStr">
+      <c r="F236" s="2" t="inlineStr">
         <is>
           <t>Verify that when the Coordinator declines a change request, the Organiser should be notified</t>
         </is>
       </c>
-      <c r="G230" s="2" t="inlineStr">
+      <c r="G236" s="2" t="inlineStr">
         <is>
           <t>A change request on "Community Meetup" is pending Coordinator approval</t>
         </is>
       </c>
-      <c r="H230" s="2" t="inlineStr">
+      <c r="H236" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the pending change request
@@ -12494,105 +12805,105 @@
   5. Log in as organiser_a@clienta.com and check notifications</t>
         </is>
       </c>
-      <c r="I230" s="2" t="inlineStr">
+      <c r="I236" s="2" t="inlineStr">
         <is>
           <t>Decision: Declined</t>
         </is>
       </c>
-      <c r="J230" s="2" t="inlineStr">
+      <c r="J236" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is notified that the change request was declined, and the event remains unchanged
 ## E10-S02</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="2" t="n">
+    <row r="237">
+      <c r="A237" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B231" s="2" t="inlineStr">
+      <c r="B237" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C231" s="2" t="inlineStr">
+      <c r="C237" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 1 (Attendance beyond capacity flagged)</t>
         </is>
       </c>
-      <c r="D231" s="2" t="inlineStr">
+      <c r="D237" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E231" s="2" t="inlineStr">
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_01</t>
         </is>
       </c>
-      <c r="F231" s="2" t="inlineStr">
+      <c r="F237" s="2" t="inlineStr">
         <is>
           <t>Verify that increasing a event's expected attendance beyond its confirmed venue's capacity should flag the venue booking for review and notify Venue Staff</t>
         </is>
       </c>
-      <c r="G231" s="2" t="inlineStr">
+      <c r="G237" s="2" t="inlineStr">
         <is>
           <t>A event of "Tech Conference 2026" has a confirmed venue "Riverside Hall" with capacity 200</t>
         </is>
       </c>
-      <c r="H231" s="2" t="inlineStr">
+      <c r="H237" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Increase the event's Expected Attendance to 250
   3. Save</t>
         </is>
       </c>
-      <c r="I231" s="2" t="inlineStr">
+      <c r="I237" s="2" t="inlineStr">
         <is>
           <t>Expected Attendance: 200 -&gt; 250 (venue capacity: 200)</t>
         </is>
       </c>
-      <c r="J231" s="2" t="inlineStr">
+      <c r="J237" s="2" t="inlineStr">
         <is>
           <t>The venue booking for "Riverside Hall" is flagged for review, and venue_staff_1@connectsphere.com is notified</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="2" t="n">
+    <row r="238">
+      <c r="A238" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B232" s="2" t="inlineStr">
+      <c r="B238" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C232" s="2" t="inlineStr">
+      <c r="C238" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 2 (Description-only edit flags nothing)</t>
         </is>
       </c>
-      <c r="D232" s="2" t="inlineStr">
+      <c r="D238" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E232" s="2" t="inlineStr">
+      <c r="E238" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_02</t>
         </is>
       </c>
-      <c r="F232" s="2" t="inlineStr">
+      <c r="F238" s="2" t="inlineStr">
         <is>
           <t>Verify that editing only the event description on an event with confirmed venue and equipment should flag nothing</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr">
+      <c r="G238" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has a confirmed venue and equipment</t>
         </is>
       </c>
-      <c r="H232" s="2" t="inlineStr">
+      <c r="H238" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Edit only the Description field
@@ -12600,208 +12911,208 @@
   4. Check for any flagged arrangements</t>
         </is>
       </c>
-      <c r="I232" s="2" t="inlineStr">
+      <c r="I238" s="2" t="inlineStr">
         <is>
           <t>Field changed: Description only</t>
         </is>
       </c>
-      <c r="J232" s="2" t="inlineStr">
+      <c r="J238" s="2" t="inlineStr">
         <is>
           <t>No arrangements are flagged as a result of this edit</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="2" t="n">
+    <row r="239">
+      <c r="A239" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B233" s="2" t="inlineStr">
+      <c r="B239" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C233" s="2" t="inlineStr">
+      <c r="C239" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 3 (Affected arrangements shown first)</t>
         </is>
       </c>
-      <c r="D233" s="2" t="inlineStr">
+      <c r="D239" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E233" s="2" t="inlineStr">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_03</t>
         </is>
       </c>
-      <c r="F233" s="2" t="inlineStr">
+      <c r="F239" s="2" t="inlineStr">
         <is>
           <t>Verify that saving a change that affects confirmed arrangements should show which arrangements are affected before the change takes effect</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr">
+      <c r="G239" s="2" t="inlineStr">
         <is>
           <t>A pending edit to "Tech Conference 2026" would affect its confirmed venue booking</t>
         </is>
       </c>
-      <c r="H233" s="2" t="inlineStr">
+      <c r="H239" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Make the edit that affects the venue booking
   3. Click "Save"</t>
         </is>
       </c>
-      <c r="I233" s="2" t="inlineStr">
+      <c r="I239" s="2" t="inlineStr">
         <is>
           <t>Edit: affects the confirmed venue booking</t>
         </is>
       </c>
-      <c r="J233" s="2" t="inlineStr">
+      <c r="J239" s="2" t="inlineStr">
         <is>
           <t>Before the change is applied, a confirmation screen lists the affected arrangement (venue booking) for review</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="2" t="n">
+    <row r="240">
+      <c r="A240" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B234" s="2" t="inlineStr">
+      <c r="B240" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C234" s="2" t="inlineStr">
+      <c r="C240" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 4 (Over-subscription warns only)</t>
         </is>
       </c>
-      <c r="D234" s="2" t="inlineStr">
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_04</t>
         </is>
       </c>
-      <c r="F234" s="2" t="inlineStr">
+      <c r="F240" s="2" t="inlineStr">
         <is>
           <t>Verify that a venue change that reduces a event's capacity below its registration count should warn the Coordinator and show the over-subscription without automatically removing or waitlisting anyone</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr">
+      <c r="G240" s="2" t="inlineStr">
         <is>
           <t>A event of "Tech Conference 2026" has 100 registered; a venue change is about to reduce its capacity to 80</t>
         </is>
       </c>
-      <c r="H234" s="2" t="inlineStr">
+      <c r="H240" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Change the event's venue to one with capacity 80
   3. Save</t>
         </is>
       </c>
-      <c r="I234" s="2" t="inlineStr">
+      <c r="I240" s="2" t="inlineStr">
         <is>
           <t>New capacity: 80; Registered: 100</t>
         </is>
       </c>
-      <c r="J234" s="2" t="inlineStr">
+      <c r="J240" s="2" t="inlineStr">
         <is>
           <t>coordinator_1@connectsphere.com is warned and shown the over-subscription (100 vs 80); no Attendee is automatically removed or waitlisted</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="2" t="n">
+    <row r="241">
+      <c r="A241" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B235" s="2" t="inlineStr">
+      <c r="B241" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C235" s="2" t="inlineStr">
+      <c r="C241" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 5 (Date change flags venue and equipment)</t>
         </is>
       </c>
-      <c r="D235" s="2" t="inlineStr">
+      <c r="D241" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_05</t>
         </is>
       </c>
-      <c r="F235" s="2" t="inlineStr">
+      <c r="F241" s="2" t="inlineStr">
         <is>
           <t>Verify that changing a event's date or time should flag its venue booking and equipment reservations as requiring reconfirmation</t>
         </is>
       </c>
-      <c r="G235" s="2" t="inlineStr">
+      <c r="G241" s="2" t="inlineStr">
         <is>
           <t>A event of "Tech Conference 2026" has a confirmed venue and reserved equipment</t>
         </is>
       </c>
-      <c r="H235" s="2" t="inlineStr">
+      <c r="H241" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Change the event's date from 15/11/2026 to 20/11/2026
   3. Save</t>
         </is>
       </c>
-      <c r="I235" s="2" t="inlineStr">
+      <c r="I241" s="2" t="inlineStr">
         <is>
           <t>Date: 15/11/2026 -&gt; 20/11/2026</t>
         </is>
       </c>
-      <c r="J235" s="2" t="inlineStr">
+      <c r="J241" s="2" t="inlineStr">
         <is>
           <t>Both the venue booking and the equipment reservations for this event are flagged as requiring reconfirmation</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="2" t="n">
+    <row r="242">
+      <c r="A242" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B236" s="2" t="inlineStr">
+      <c r="B242" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C236" s="2" t="inlineStr">
+      <c r="C242" s="2" t="inlineStr">
         <is>
           <t>E10-S02 (checklist: Venue Staff and Technical Support Staff both notified)</t>
         </is>
       </c>
-      <c r="D236" s="2" t="inlineStr">
+      <c r="D242" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting (notification consistency)</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="E242" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_06</t>
         </is>
       </c>
-      <c r="F236" s="2" t="inlineStr">
+      <c r="F242" s="2" t="inlineStr">
         <is>
           <t>Verify that when a date or time change flags arrangements for reconfirmation, the assigned Technical Support Staff should also be notified, not just Venue Staff</t>
         </is>
       </c>
-      <c r="G236" s="2" t="inlineStr">
+      <c r="G242" s="2" t="inlineStr">
         <is>
           <t>A event of "Tech Conference 2026" has a confirmed venue, reserved equipment, and tech_support_1@connectsphere.com assigned for on-site support</t>
         </is>
       </c>
-      <c r="H236" s="2" t="inlineStr">
+      <c r="H242" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Change the event's date
@@ -12809,53 +13120,106 @@
   4. Check notifications for both venue_staff_1@connectsphere.com and tech_support_1@connectsphere.com</t>
         </is>
       </c>
-      <c r="I236" s="2" t="inlineStr">
+      <c r="I242" s="2" t="inlineStr">
         <is>
           <t>Changed field: Date</t>
         </is>
       </c>
-      <c r="J236" s="2" t="inlineStr">
-        <is>
-          <t>Both venue_staff_1@connectsphere.com and tech_support_1@connectsphere.com receive a notification about the change requiring reconfirmation
+      <c r="J242" s="2" t="inlineStr">
+        <is>
+          <t>Both venue_staff_1@connectsphere.com and tech_support_1@connectsphere.com receive a notification about the change requiring reconfirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>E10-S02</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>E10-S02 — Scenario 1 (Attendance beyond capacity flagged); assumes O-27</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>5 - Boundary (exactly at)</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>TC_E10S02_07</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>Verify that increasing expected attendance on a multi-venue event should flag only the venue bookings whose governing headcount now exceeds capacity</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>Event "Tech Summit" is Confirmed with "Grand Auditorium" (capacity 600, booking headcount not set) and "Seminar Room A" (capacity 60, booking headcount 50); expected attendance is 500; coordinator_1@connectsphere.com is signed in</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>1. Change expected attendance to 600 and save
+  2. Read the arrangement flags
+  3. Change expected attendance to 601 and save
+  4. Read the arrangement flags</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>Auditorium governed by event attendance (600 = exactly at capacity, 601 = above); Seminar Room A governed by its own headcount 50</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="inlineStr">
+        <is>
+          <t>After step 1 no booking is flagged; after step 3 only "Grand Auditorium" is flagged for review and "Seminar Room A" is not, because its booking headcount of 50 is unchanged
 ## E10-S04</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="2" t="n">
+    <row r="244">
+      <c r="A244" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B237" s="2" t="inlineStr">
+      <c r="B244" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="C237" s="2" t="inlineStr">
+      <c r="C244" s="2" t="inlineStr">
         <is>
           <t>E10-S04 - Scenario 1 (Event cancelled, arrangements released)</t>
         </is>
       </c>
-      <c r="D237" s="2" t="inlineStr">
+      <c r="D244" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="E244" s="2" t="inlineStr">
         <is>
           <t>TC_E10S04_01</t>
         </is>
       </c>
-      <c r="F237" s="2" t="inlineStr">
+      <c r="F244" s="2" t="inlineStr">
         <is>
           <t>Verify that cancelling an event and recording a reason should release its venue bookings and equipment reservations, update the venue calendars, and notify affected staff</t>
         </is>
       </c>
-      <c r="G237" s="2" t="inlineStr">
+      <c r="G244" s="2" t="inlineStr">
         <is>
           <t>Event "Product Launch Night" has status "Confirmed" with a confirmed venue "Small Room" and reserved equipment</t>
         </is>
       </c>
-      <c r="H237" s="2" t="inlineStr">
+      <c r="H244" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Product Launch Night"
@@ -12864,156 +13228,156 @@
   5. Confirm</t>
         </is>
       </c>
-      <c r="I237" s="2" t="inlineStr">
+      <c r="I244" s="2" t="inlineStr">
         <is>
           <t>Cancellation reason: "Insufficient sponsor funding"</t>
         </is>
       </c>
-      <c r="J237" s="2" t="inlineStr">
+      <c r="J244" s="2" t="inlineStr">
         <is>
           <t>The status becomes "Cancelled"; "Small Room"'s booking and the reserved equipment are released, the venue calendar is updated, and affected staff are notified</t>
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="2" t="n">
+    <row r="245">
+      <c r="A245" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B238" s="2" t="inlineStr">
+      <c r="B245" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="C238" s="2" t="inlineStr">
+      <c r="C245" s="2" t="inlineStr">
         <is>
           <t>E10-S04 - Scenario 2 (Attendees and waitlist notified)</t>
         </is>
       </c>
-      <c r="D238" s="2" t="inlineStr">
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
         <is>
           <t>TC_E10S04_03</t>
         </is>
       </c>
-      <c r="F238" s="2" t="inlineStr">
+      <c r="F245" s="2" t="inlineStr">
         <is>
           <t>Verify that cancelling a event should notify all of its registered and waitlisted Attendees</t>
         </is>
       </c>
-      <c r="G238" s="2" t="inlineStr">
+      <c r="G245" s="2" t="inlineStr">
         <is>
           <t>The event of "Tech Conference 2026" being cancelled has attendee_a@example.com registered and attendee_l@example.com waitlisted</t>
         </is>
       </c>
-      <c r="H238" s="2" t="inlineStr">
+      <c r="H245" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Cancel the event
   3. Check notifications for attendee_a@example.com and attendee_l@example.com</t>
         </is>
       </c>
-      <c r="I238" s="2" t="inlineStr">
+      <c r="I245" s="2" t="inlineStr">
         <is>
           <t>Registered: attendee_a@example.com | Waitlisted: attendee_l@example.com</t>
         </is>
       </c>
-      <c r="J238" s="2" t="inlineStr">
+      <c r="J245" s="2" t="inlineStr">
         <is>
           <t>Both attendee_a@example.com and attendee_l@example.com receive a notification of the cancellation</t>
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="2" t="n">
+    <row r="246">
+      <c r="A246" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B239" s="2" t="inlineStr">
+      <c r="B246" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="C239" s="2" t="inlineStr">
+      <c r="C246" s="2" t="inlineStr">
         <is>
           <t>E10-S04 - Scenario 3 (Cancelled event read-only)</t>
         </is>
       </c>
-      <c r="D239" s="2" t="inlineStr">
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>TC_E10S04_04</t>
         </is>
       </c>
-      <c r="F239" s="2" t="inlineStr">
+      <c r="F246" s="2" t="inlineStr">
         <is>
           <t>Verify that a cancelled event should be read-only and show its cancellation reason and date to any viewer</t>
         </is>
       </c>
-      <c r="G239" s="2" t="inlineStr">
+      <c r="G246" s="2" t="inlineStr">
         <is>
           <t>Event "Product Launch Night" was cancelled on 12/09/2026 with reason "Insufficient sponsor funding" (per TC_E10S04_01)</t>
         </is>
       </c>
-      <c r="H239" s="2" t="inlineStr">
+      <c r="H246" s="2" t="inlineStr">
         <is>
           <t>1. Log in as any user with access (e.g. organiser_a@clienta.com)
   2. Open the cancelled event "Product Launch Night"
   3. Attempt to edit any field</t>
         </is>
       </c>
-      <c r="I239" s="2" t="inlineStr">
+      <c r="I246" s="2" t="inlineStr">
         <is>
           <t>Cancellation reason: "Insufficient sponsor funding" | Date: 12/09/2026</t>
         </is>
       </c>
-      <c r="J239" s="2" t="inlineStr">
+      <c r="J246" s="2" t="inlineStr">
         <is>
           <t>The event shows "Cancelled on 12 September 2026 - Insufficient sponsor funding"; all fields are read-only</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="2" t="n">
+    <row r="247">
+      <c r="A247" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B240" s="2" t="inlineStr">
+      <c r="B247" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="C240" s="2" t="inlineStr">
+      <c r="C247" s="2" t="inlineStr">
         <is>
           <t>E10-S04 - Scenario 4 (Organiser cancellation becomes a request)</t>
         </is>
       </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="D247" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>TC_E10S04_05</t>
         </is>
       </c>
-      <c r="F240" s="2" t="inlineStr">
+      <c r="F247" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Organiser attempting to cancel directly should have the action recorded as a cancellation request for the Coordinator to action</t>
         </is>
       </c>
-      <c r="G240" s="2" t="inlineStr">
+      <c r="G247" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" has status "Confirmed", assigned to coordinator_1@connectsphere.com</t>
         </is>
       </c>
-      <c r="H240" s="2" t="inlineStr">
+      <c r="H247" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Community Meetup"
@@ -13021,308 +13385,308 @@
   4. Enter a reason and submit</t>
         </is>
       </c>
-      <c r="I240" s="2" t="inlineStr">
+      <c r="I247" s="2" t="inlineStr">
         <is>
           <t>Reason: "No longer needed"</t>
         </is>
       </c>
-      <c r="J240" s="2" t="inlineStr">
+      <c r="J247" s="2" t="inlineStr">
         <is>
           <t>The event is NOT immediately cancelled; instead, a cancellation request is recorded and coordinator_1@connectsphere.com is notified to action it</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="2" t="n">
+    <row r="248">
+      <c r="A248" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B241" s="2" t="inlineStr">
+      <c r="B248" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C241" s="2" t="inlineStr">
+      <c r="C248" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 1 (Status change notified)</t>
         </is>
       </c>
-      <c r="D241" s="2" t="inlineStr">
+      <c r="D248" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E241" s="2" t="inlineStr">
+      <c r="E248" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_01</t>
         </is>
       </c>
-      <c r="F241" s="2" t="inlineStr">
+      <c r="F248" s="2" t="inlineStr">
         <is>
           <t>Verify that a user linked to an event should be notified when its status changes or a booking decision is made, with details of what/when/which event</t>
         </is>
       </c>
-      <c r="G241" s="2" t="inlineStr">
+      <c r="G248" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is linked to event "Annual Tech Summit", currently "Under Review"</t>
         </is>
       </c>
-      <c r="H241" s="2" t="inlineStr">
+      <c r="H248" s="2" t="inlineStr">
         <is>
           <t>1. As coordinator_1@connectsphere.com, approve request "Annual Tech Summit" (status -&gt; Approved)
   2. Log in as organiser_a@clienta.com and open notifications</t>
         </is>
       </c>
-      <c r="I241" s="2" t="inlineStr">
+      <c r="I248" s="2" t="inlineStr">
         <is>
           <t>Event: Annual Tech Summit | Change: Under Review -&gt; Approved</t>
         </is>
       </c>
-      <c r="J241" s="2" t="inlineStr">
+      <c r="J248" s="2" t="inlineStr">
         <is>
           <t>A notification is received stating the status changed to "Approved", the time of the change, and that it concerns "Annual Tech Summit"</t>
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="2" t="n">
+    <row r="249">
+      <c r="A249" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B242" s="2" t="inlineStr">
+      <c r="B249" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C242" s="2" t="inlineStr">
+      <c r="C249" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 2 (All affected parties notified)</t>
         </is>
       </c>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E242" s="2" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_02</t>
         </is>
       </c>
-      <c r="F242" s="2" t="inlineStr">
+      <c r="F249" s="2" t="inlineStr">
         <is>
           <t>Verify that effective date, time or venue changes follow the approved recipient matrix</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr">
+      <c r="G249" s="2" t="inlineStr">
         <is>
           <t>Event "Annual Tech Summit" the event has organiser_a@clienta.com, venue_staff_1@connectsphere.com, and tech_support_1@connectsphere.com assigned, and attendee_a@example.com registered; attendee_b@example.com is waitlisted and coordinator_1@connectsphere.com is the assigned Coordinator</t>
         </is>
       </c>
-      <c r="H242" s="2" t="inlineStr">
+      <c r="H249" s="2" t="inlineStr">
         <is>
           <t>1. As coordinator_1@connectsphere.com, change the event's venue
   2. Check notifications for organiser_a@clienta.com, venue_staff_1@connectsphere.com, tech_support_1@connectsphere.com, and attendee_a@example.com</t>
         </is>
       </c>
-      <c r="I242" s="2" t="inlineStr">
+      <c r="I249" s="2" t="inlineStr">
         <is>
           <t>Changed field: Venue</t>
         </is>
       </c>
-      <c r="J242" s="2" t="inlineStr">
+      <c r="J249" s="2" t="inlineStr">
         <is>
           <t>The Organiser, assigned Venue Staff, assigned Technical Support Staff, registered Attendee and waitlisted Attendee receive a notification. The acting Coordinator receives no self-notification. If another authorized actor or a system operation makes the change, the assigned Coordinator is included. Venue-move tests include responsible staff for both the old and new venues. Backend resolver fixtures are not evidence that the venue-assignment workflow is implemented.</t>
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="2" t="n">
+    <row r="250">
+      <c r="A250" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B243" s="2" t="inlineStr">
+      <c r="B250" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C243" s="2" t="inlineStr">
+      <c r="C250" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 3 (Unaffected users not notified)</t>
         </is>
       </c>
-      <c r="D243" s="2" t="inlineStr">
+      <c r="D250" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E243" s="2" t="inlineStr">
+      <c r="E250" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_03</t>
         </is>
       </c>
-      <c r="F243" s="2" t="inlineStr">
+      <c r="F250" s="2" t="inlineStr">
         <is>
           <t>Verify that a user whose responsibilities are unaffected by a change should not be notified</t>
         </is>
       </c>
-      <c r="G243" s="2" t="inlineStr">
+      <c r="G250" s="2" t="inlineStr">
         <is>
           <t>Event "Annual Tech Summit" the event's Description field is about to be edited; venue_staff_1@connectsphere.com has no responsibility tied to the Description field</t>
         </is>
       </c>
-      <c r="H243" s="2" t="inlineStr">
+      <c r="H250" s="2" t="inlineStr">
         <is>
           <t>1. As organiser_a@clienta.com, edit the Description field only
   2. Check venue_staff_1@connectsphere.com's notifications</t>
         </is>
       </c>
-      <c r="I243" s="2" t="inlineStr">
+      <c r="I250" s="2" t="inlineStr">
         <is>
           <t>Changed field: Description only</t>
         </is>
       </c>
-      <c r="J243" s="2" t="inlineStr">
+      <c r="J250" s="2" t="inlineStr">
         <is>
           <t>venue_staff_1@connectsphere.com receives no notification, since the Description change does not affect their responsibilities</t>
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="2" t="n">
+    <row r="251">
+      <c r="A251" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B244" s="2" t="inlineStr">
+      <c r="B251" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C244" s="2" t="inlineStr">
+      <c r="C251" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 4 (Delivered in-app and by email)</t>
         </is>
       </c>
-      <c r="D244" s="2" t="inlineStr">
+      <c r="D251" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E244" s="2" t="inlineStr">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_05</t>
         </is>
       </c>
-      <c r="F244" s="2" t="inlineStr">
+      <c r="F251" s="2" t="inlineStr">
         <is>
           <t>Verify that a generated notification should appear in the system and also be sent to the user's registered email address</t>
         </is>
       </c>
-      <c r="G244" s="2" t="inlineStr">
+      <c r="G251" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com's registered email is organiser_a@clienta.com; a notification-triggering status change is about to occur on their event</t>
         </is>
       </c>
-      <c r="H244" s="2" t="inlineStr">
+      <c r="H251" s="2" t="inlineStr">
         <is>
           <t>1. Trigger a status change on organiser_a@clienta.com's event
   2. Log in as organiser_a@clienta.com and check the in-app notification list
   3. Check the inbox for organiser_a@clienta.com</t>
         </is>
       </c>
-      <c r="I244" s="2" t="inlineStr">
+      <c r="I251" s="2" t="inlineStr">
         <is>
           <t>Registered email: organiser_a@clienta.com</t>
         </is>
       </c>
-      <c r="J244" s="2" t="inlineStr">
+      <c r="J251" s="2" t="inlineStr">
         <is>
           <t>The notification appears in the in-app notification list, and an equivalent email is also delivered to organiser_a@clienta.com's inbox</t>
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="2" t="n">
+    <row r="252">
+      <c r="A252" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B245" s="2" t="inlineStr">
+      <c r="B252" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C245" s="2" t="inlineStr">
+      <c r="C252" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 5 (Unread notifications distinguished)</t>
         </is>
       </c>
-      <c r="D245" s="2" t="inlineStr">
+      <c r="D252" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E245" s="2" t="inlineStr">
+      <c r="E252" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_06</t>
         </is>
       </c>
-      <c r="F245" s="2" t="inlineStr">
+      <c r="F252" s="2" t="inlineStr">
         <is>
           <t>Verify that opening the notification list with several unread notifications should show them newest first with unread ones distinguished</t>
         </is>
       </c>
-      <c r="G245" s="2" t="inlineStr">
+      <c r="G252" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com has 3 notifications on 09/09/2026: 08:00 (read), 10:00 (unread), 14:00 (unread)</t>
         </is>
       </c>
-      <c r="H245" s="2" t="inlineStr">
+      <c r="H252" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the notification list</t>
         </is>
       </c>
-      <c r="I245" s="2" t="inlineStr">
+      <c r="I252" s="2" t="inlineStr">
         <is>
           <t>Notifications: 08:00 (read), 10:00 (unread), 14:00 (unread)</t>
         </is>
       </c>
-      <c r="J245" s="2" t="inlineStr">
+      <c r="J252" s="2" t="inlineStr">
         <is>
           <t>Notifications are listed newest first (14:00, then 10:00, then 08:00), with the 14:00 and 10:00 entries visually marked as unread and 08:00 shown as read</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="2" t="n">
+    <row r="253">
+      <c r="A253" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B246" s="2" t="inlineStr">
+      <c r="B253" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C246" s="2" t="inlineStr">
+      <c r="C253" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 6 (Marked as read)</t>
         </is>
       </c>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="D253" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="E253" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_07</t>
         </is>
       </c>
-      <c r="F246" s="2" t="inlineStr">
+      <c r="F253" s="2" t="inlineStr">
         <is>
           <t>Verify that opening an unread notification should mark it as read</t>
         </is>
       </c>
-      <c r="G246" s="2" t="inlineStr">
+      <c r="G253" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com has an unread notification from 10:00 on 09/09/2026</t>
         </is>
       </c>
-      <c r="H246" s="2" t="inlineStr">
+      <c r="H253" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the notification list
@@ -13330,52 +13694,52 @@
   4. Return to the notification list</t>
         </is>
       </c>
-      <c r="I246" s="2" t="inlineStr">
+      <c r="I253" s="2" t="inlineStr">
         <is>
           <t>Notification: 10:00 on 09/09/2026 (initially unread)</t>
         </is>
       </c>
-      <c r="J246" s="2" t="inlineStr">
+      <c r="J253" s="2" t="inlineStr">
         <is>
           <t>The 10:00 notification is now shown as read (no longer marked unread) in the list</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="2" t="n">
+    <row r="254">
+      <c r="A254" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B247" s="2" t="inlineStr">
+      <c r="B254" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C247" s="2" t="inlineStr">
+      <c r="C254" s="2" t="inlineStr">
         <is>
           <t>E11-S01 · Scenario 5 (Delivered in-app and by email) · ADR-006</t>
         </is>
       </c>
-      <c r="D247" s="2" t="inlineStr">
+      <c r="D254" s="2" t="inlineStr">
         <is>
           <t>4 - Negative (third-party unavailable)</t>
         </is>
       </c>
-      <c r="E247" s="2" t="inlineStr">
+      <c r="E254" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_08</t>
         </is>
       </c>
-      <c r="F247" s="2" t="inlineStr">
+      <c r="F254" s="2" t="inlineStr">
         <is>
           <t>Verify that an unreachable email provider does not affect the business change or the in-app notification</t>
         </is>
       </c>
-      <c r="G247" s="2" t="inlineStr">
+      <c r="G254" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2003 has an assigned Coordinator coord_a@connectsphere.com. The email provider endpoint is configured to an unreachable host so every SMTP attempt fails</t>
         </is>
       </c>
-      <c r="H247" s="2" t="inlineStr">
+      <c r="H254" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Venue Staff and approve the pending venue booking for EVT-2003
  2. Confirm the booking status has changed
@@ -13383,52 +13747,52 @@
  4. Inspect the delivery records for that notification</t>
         </is>
       </c>
-      <c r="I247" s="2" t="inlineStr">
+      <c r="I254" s="2" t="inlineStr">
         <is>
           <t>SMTP host: unreachable · Notification: venue booking approved</t>
         </is>
       </c>
-      <c r="J247" s="2" t="inlineStr">
+      <c r="J254" s="2" t="inlineStr">
         <is>
           <t>The booking is Confirmed and the change persists. The in-app notification appears for the Coordinator. The email delivery row is marked failed with a recorded reason. The business transaction is not rolled back by the email failure</t>
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="2" t="n">
+    <row r="255">
+      <c r="A255" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B248" s="2" t="inlineStr">
+      <c r="B255" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C248" s="2" t="inlineStr">
+      <c r="C255" s="2" t="inlineStr">
         <is>
           <t>E11-S01 · Scenario 1 (Status change notified) · ADR-006 outbox guarantee</t>
         </is>
       </c>
-      <c r="D248" s="2" t="inlineStr">
+      <c r="D255" s="2" t="inlineStr">
         <is>
           <t>4 - Negative (transaction rollback)</t>
         </is>
       </c>
-      <c r="E248" s="2" t="inlineStr">
+      <c r="E255" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_09</t>
         </is>
       </c>
-      <c r="F248" s="2" t="inlineStr">
+      <c r="F255" s="2" t="inlineStr">
         <is>
           <t>Verify that a rolled-back business transaction publishes no notification</t>
         </is>
       </c>
-      <c r="G248" s="2" t="inlineStr">
+      <c r="G255" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2004 is at status Under Review. A fault is injected so that the approval transaction fails after the notification delivery rows are written but before commit</t>
         </is>
       </c>
-      <c r="H248" s="2" t="inlineStr">
+      <c r="H255" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as the assigned Event Coordinator
  2. Approve EVT-2004, triggering the injected failure
@@ -13436,610 +13800,610 @@
  4. Inspect the job queue and the Organiser's notification list</t>
         </is>
       </c>
-      <c r="I248" s="2" t="inlineStr">
+      <c r="I255" s="2" t="inlineStr">
         <is>
           <t>Event: EVT-2004 · Injected failure point: after delivery rows written, before commit</t>
         </is>
       </c>
-      <c r="J248" s="2" t="inlineStr">
+      <c r="J255" s="2" t="inlineStr">
         <is>
           <t>The event remains at Under Review. No delivery row is persisted, nothing is published to the queue, and the Organiser receives no in-app notification and no email. Only committed deliveries are ever published</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B249" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01</t>
-        </is>
-      </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
-        </is>
-      </c>
-      <c r="D249" s="2" t="inlineStr">
-        <is>
-          <t>3 - Integration / regression</t>
-        </is>
-      </c>
-      <c r="E249" s="2" t="inlineStr">
-        <is>
-          <t>TC_E11S01_10</t>
-        </is>
-      </c>
-      <c r="F249" s="2" t="inlineStr">
-        <is>
-          <t>Apply the approved role/change recipient matrix</t>
-        </is>
-      </c>
-      <c r="G249" s="2" t="inlineStr">
-        <is>
-          <t>The event has active links to all six recipient groups and a public snapshot.</t>
-        </is>
-      </c>
-      <c r="H249" s="2" t="inlineStr">
-        <is>
-          <t>1. Trigger each internal status, booking, equipment, public status, arrangement, place-release and description-only change through the selector.</t>
-        </is>
-      </c>
-      <c r="I249" s="2" t="inlineStr">
-        <is>
-          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
-        </is>
-      </c>
-      <c r="J249" s="2" t="inlineStr">
-        <is>
-          <t>Recipient sets match the E11-S01 matrix; internal decisions do not reach Attendees; initial Planning differs from Confirmed-to-Planning.</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B250" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01</t>
-        </is>
-      </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
-        </is>
-      </c>
-      <c r="D250" s="2" t="inlineStr">
-        <is>
-          <t>3 - Integration / regression</t>
-        </is>
-      </c>
-      <c r="E250" s="2" t="inlineStr">
-        <is>
-          <t>TC_E11S01_11</t>
-        </is>
-      </c>
-      <c r="F250" s="2" t="inlineStr">
-        <is>
-          <t>Suppress self-notifications and duplicate recipient links</t>
-        </is>
-      </c>
-      <c r="G250" s="2" t="inlineStr">
-        <is>
-          <t>A user is both the actor and a candidate recipient; duplicated staff links exist.</t>
-        </is>
-      </c>
-      <c r="H250" s="2" t="inlineStr">
-        <is>
-          <t>1. Select recipients for an arrangement change and an actor-made booking decision.</t>
-        </is>
-      </c>
-      <c r="I250" s="2" t="inlineStr">
-        <is>
-          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
-        </is>
-      </c>
-      <c r="J250" s="2" t="inlineStr">
-        <is>
-          <t>The actor receives no routine self-notification; every remaining user appears once; system changes have no excluded actor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B251" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
-        </is>
-      </c>
-      <c r="D251" s="2" t="inlineStr">
-        <is>
-          <t>3 - Integration / regression</t>
-        </is>
-      </c>
-      <c r="E251" s="2" t="inlineStr">
-        <is>
-          <t>TC_E11S01_12</t>
-        </is>
-      </c>
-      <c r="F251" s="2" t="inlineStr">
-        <is>
-          <t>Preserve before/after recipients during cancellation and venue moves</t>
-        </is>
-      </c>
-      <c r="G251" s="2" t="inlineStr">
-        <is>
-          <t>An event has active bookings, assigned staff, registered and waitlisted Attendees.</t>
-        </is>
-      </c>
-      <c r="H251" s="2" t="inlineStr">
-        <is>
-          <t>1. Capture its audience, release links during cancellation or replace the venue, then call the hook with both snapshots.</t>
-        </is>
-      </c>
-      <c r="I251" s="2" t="inlineStr">
-        <is>
-          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
-        </is>
-      </c>
-      <c r="J251" s="2" t="inlineStr">
-        <is>
-          <t>Cancellation notifies the pre-release audience. Venue moves include responsible staff at both venues. These are hook-contract tests until the owning workflows integrate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B252" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01</t>
-        </is>
-      </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
-        </is>
-      </c>
-      <c r="D252" s="2" t="inlineStr">
-        <is>
-          <t>3 - Integration / regression</t>
-        </is>
-      </c>
-      <c r="E252" s="2" t="inlineStr">
-        <is>
-          <t>TC_E11S01_13</t>
-        </is>
-      </c>
-      <c r="F252" s="2" t="inlineStr">
-        <is>
-          <t>Expose missing Venue Staff assignments without an unsafe fallback</t>
-        </is>
-      </c>
-      <c r="G252" s="2" t="inlineStr">
-        <is>
-          <t>No explicit venue assignment adapter is available; a booking has a decided_by actor and unrelated Venue Staff accounts exist.</t>
-        </is>
-      </c>
-      <c r="H252" s="2" t="inlineStr">
-        <is>
-          <t>1. Capture the audience and select booking-request recipients.</t>
-        </is>
-      </c>
-      <c r="I252" s="2" t="inlineStr">
-        <is>
-          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
-        </is>
-      </c>
-      <c r="J252" s="2" t="inlineStr">
-        <is>
-          <t>Venue Staff recipients are unresolved, the venue IDs are reported, and neither decided_by nor all Venue Staff is substituted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B253" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01</t>
-        </is>
-      </c>
-      <c r="C253" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
-        </is>
-      </c>
-      <c r="D253" s="2" t="inlineStr">
-        <is>
-          <t>3 - Integration / regression</t>
-        </is>
-      </c>
-      <c r="E253" s="2" t="inlineStr">
-        <is>
-          <t>TC_E11S01_14</t>
-        </is>
-      </c>
-      <c r="F253" s="2" t="inlineStr">
-        <is>
-          <t>Protect attendee notification content and membership boundaries</t>
-        </is>
-      </c>
-      <c r="G253" s="2" t="inlineStr">
-        <is>
-          <t>The internal event title differs from its publication; registered, waitlisted, withdrawn, inactive and unrelated users exist.</t>
-        </is>
-      </c>
-      <c r="H253" s="2" t="inlineStr">
-        <is>
-          <t>1. Apply an effective date change; inspect notification messages and retained email payloads. Also select recipients for an unpublished event.</t>
-        </is>
-      </c>
-      <c r="I253" s="2" t="inlineStr">
-        <is>
-          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
-        </is>
-      </c>
-      <c r="J253" s="2" t="inlineStr">
-        <is>
-          <t>Only eligible linked active users are selected. Attendees receive the published event name and fixed public change description; no internal title/reason/comment leaks. Unpublished events produce no attendee notice.</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B254" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01</t>
-        </is>
-      </c>
-      <c r="C254" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
-        </is>
-      </c>
-      <c r="D254" s="2" t="inlineStr">
-        <is>
-          <t>3 - Integration / regression</t>
-        </is>
-      </c>
-      <c r="E254" s="2" t="inlineStr">
-        <is>
-          <t>TC_E11S01_15</t>
-        </is>
-      </c>
-      <c r="F254" s="2" t="inlineStr">
-        <is>
-          <t>Deduplicate concurrent notification-hook retries</t>
-        </is>
-      </c>
-      <c r="G254" s="2" t="inlineStr">
-        <is>
-          <t>Two transactions use the same event, stable change ID and recipient snapshot.</t>
-        </is>
-      </c>
-      <c r="H254" s="2" t="inlineStr">
-        <is>
-          <t>1. Call the notification hook concurrently and commit both attempts.</t>
-        </is>
-      </c>
-      <c r="I254" s="2" t="inlineStr">
-        <is>
-          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
-        </is>
-      </c>
-      <c r="J254" s="2" t="inlineStr">
-        <is>
-          <t>Exactly one in-app row and one email-delivery row exist per recipient for the logical change. A new change ID identifies a different business change.</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B255" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01</t>
-        </is>
-      </c>
-      <c r="C255" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
-        </is>
-      </c>
-      <c r="D255" s="2" t="inlineStr">
-        <is>
-          <t>3 - Integration / regression</t>
-        </is>
-      </c>
-      <c r="E255" s="2" t="inlineStr">
-        <is>
-          <t>TC_E11S01_16</t>
-        </is>
-      </c>
-      <c r="F255" s="2" t="inlineStr">
-        <is>
-          <t>Keep uncommitted notifications invisible and roll back all writes</t>
-        </is>
-      </c>
-      <c r="G255" s="2" t="inlineStr">
-        <is>
-          <t>A business transaction has inserted notifications and prepared email delivery rows but has not committed.</t>
-        </is>
-      </c>
-      <c r="H255" s="2" t="inlineStr">
-        <is>
-          <t>1. Read from another connection, then force the business transaction to roll back.</t>
-        </is>
-      </c>
-      <c r="I255" s="2" t="inlineStr">
-        <is>
-          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
-        </is>
-      </c>
-      <c r="J255" s="2" t="inlineStr">
-        <is>
-          <t>The other connection cannot observe the uncommitted messages. After rollback no notification or email-delivery row remains.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>3 - Integration / regression</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>TC_E11S01_10</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>Apply the approved role/change recipient matrix</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>The event has active links to all six recipient groups and a public snapshot.</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>1. Trigger each internal status, booking, equipment, public status, arrangement, place-release and description-only change through the selector.</t>
+        </is>
+      </c>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
+        </is>
+      </c>
+      <c r="J256" s="2" t="inlineStr">
+        <is>
+          <t>Recipient sets match the E11-S01 matrix; internal decisions do not reach Attendees; initial Planning differs from Confirmed-to-Planning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>3 - Integration / regression</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>TC_E11S01_11</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>Suppress self-notifications and duplicate recipient links</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>A user is both the actor and a candidate recipient; duplicated staff links exist.</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>1. Select recipients for an arrangement change and an actor-made booking decision.</t>
+        </is>
+      </c>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
+        </is>
+      </c>
+      <c r="J257" s="2" t="inlineStr">
+        <is>
+          <t>The actor receives no routine self-notification; every remaining user appears once; system changes have no excluded actor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>3 - Integration / regression</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>TC_E11S01_12</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>Preserve before/after recipients during cancellation and venue moves</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>An event has active bookings, assigned staff, registered and waitlisted Attendees.</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>1. Capture its audience, release links during cancellation or replace the venue, then call the hook with both snapshots.</t>
+        </is>
+      </c>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
+        </is>
+      </c>
+      <c r="J258" s="2" t="inlineStr">
+        <is>
+          <t>Cancellation notifies the pre-release audience. Venue moves include responsible staff at both venues. These are hook-contract tests until the owning workflows integrate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>3 - Integration / regression</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>TC_E11S01_13</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>Expose missing Venue Staff assignments without an unsafe fallback</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>No explicit venue assignment adapter is available; a booking has a decided_by actor and unrelated Venue Staff accounts exist.</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>1. Capture the audience and select booking-request recipients.</t>
+        </is>
+      </c>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
+        </is>
+      </c>
+      <c r="J259" s="2" t="inlineStr">
+        <is>
+          <t>Venue Staff recipients are unresolved, the venue IDs are reported, and neither decided_by nor all Venue Staff is substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>3 - Integration / regression</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>TC_E11S01_14</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>Protect attendee notification content and membership boundaries</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>The internal event title differs from its publication; registered, waitlisted, withdrawn, inactive and unrelated users exist.</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>1. Apply an effective date change; inspect notification messages and retained email payloads. Also select recipients for an unpublished event.</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
+        </is>
+      </c>
+      <c r="J260" s="2" t="inlineStr">
+        <is>
+          <t>Only eligible linked active users are selected. Attendees receive the published event name and fixed public change description; no internal title/reason/comment leaks. Unpublished events produce no attendee notice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>3 - Integration / regression</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>TC_E11S01_15</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>Deduplicate concurrent notification-hook retries</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>Two transactions use the same event, stable change ID and recipient snapshot.</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>1. Call the notification hook concurrently and commit both attempts.</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
+        </is>
+      </c>
+      <c r="J261" s="2" t="inlineStr">
+        <is>
+          <t>Exactly one in-app row and one email-delivery row exist per recipient for the logical change. A new change ID identifies a different business change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>3 - Integration / regression</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>TC_E11S01_16</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>Keep uncommitted notifications invisible and roll back all writes</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>A business transaction has inserted notifications and prepared email delivery rows but has not committed.</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>1. Read from another connection, then force the business transaction to roll back.</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="inlineStr">
+        <is>
+          <t>The other connection cannot observe the uncommitted messages. After rollback no notification or email-delivery row remains.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B256" s="2" t="inlineStr">
+      <c r="B263" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C256" s="2" t="inlineStr">
+      <c r="C263" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 1 (Status change recorded)</t>
         </is>
       </c>
-      <c r="D256" s="2" t="inlineStr">
+      <c r="D263" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E256" s="2" t="inlineStr">
+      <c r="E263" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_01</t>
         </is>
       </c>
-      <c r="F256" s="2" t="inlineStr">
+      <c r="F263" s="2" t="inlineStr">
         <is>
           <t>Verify that an event status change should be recorded with the actor, action, affected event, and time</t>
         </is>
       </c>
-      <c r="G256" s="2" t="inlineStr">
+      <c r="G263" s="2" t="inlineStr">
         <is>
           <t>Request "Annual Tech Summit" has status "Under Review"</t>
         </is>
       </c>
-      <c r="H256" s="2" t="inlineStr">
+      <c r="H263" s="2" t="inlineStr">
         <is>
           <t>1. As coordinator_1@connectsphere.com, approve the request (status -&gt; Approved)
   2. Log in as a System Administrator
   3. Open the Activity Log and locate the entry</t>
         </is>
       </c>
-      <c r="I256" s="2" t="inlineStr">
+      <c r="I263" s="2" t="inlineStr">
         <is>
           <t>Event: Annual Tech Summit | Action: Approve</t>
         </is>
       </c>
-      <c r="J256" s="2" t="inlineStr">
+      <c r="J263" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded with actor = coordinator_1@connectsphere.com, action = "Status changed to Approved", event = Annual Tech Summit, and a timestamp</t>
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="2" t="n">
+    <row r="264">
+      <c r="A264" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B257" s="2" t="inlineStr">
+      <c r="B264" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C257" s="2" t="inlineStr">
+      <c r="C264" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 2 (Access denial recorded)</t>
         </is>
       </c>
-      <c r="D257" s="2" t="inlineStr">
+      <c r="D264" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E257" s="2" t="inlineStr">
+      <c r="E264" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_02</t>
         </is>
       </c>
-      <c r="F257" s="2" t="inlineStr">
+      <c r="F264" s="2" t="inlineStr">
         <is>
           <t>Verify that a denied access attempt should be recorded with the user, target, and time</t>
         </is>
       </c>
-      <c r="G257" s="2" t="inlineStr">
+      <c r="G264" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is linked to Client A; event EVT-B01 belongs to Client B</t>
         </is>
       </c>
-      <c r="H257" s="2" t="inlineStr">
+      <c r="H264" s="2" t="inlineStr">
         <is>
           <t>1. As organiser_a@clienta.com, attempt to access EVT-B01 directly
   2. Log in as a System Administrator
   3. Check the Activity Log</t>
         </is>
       </c>
-      <c r="I257" s="2" t="inlineStr">
+      <c r="I264" s="2" t="inlineStr">
         <is>
           <t>User: organiser_a@clienta.com | Target: EVT-B01</t>
         </is>
       </c>
-      <c r="J257" s="2" t="inlineStr">
+      <c r="J264" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded with user = organiser_a@clienta.com, target = EVT-B01, action = "Access Denied", and a timestamp</t>
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" s="2" t="n">
+    <row r="265">
+      <c r="A265" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B258" s="2" t="inlineStr">
+      <c r="B265" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C258" s="2" t="inlineStr">
+      <c r="C265" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 3 (Booking decision recorded)</t>
         </is>
       </c>
-      <c r="D258" s="2" t="inlineStr">
+      <c r="D265" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E258" s="2" t="inlineStr">
+      <c r="E265" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_03</t>
         </is>
       </c>
-      <c r="F258" s="2" t="inlineStr">
+      <c r="F265" s="2" t="inlineStr">
         <is>
           <t>Verify that an approved venue booking should be recorded with the actor, action, affected records, and time</t>
         </is>
       </c>
-      <c r="G258" s="2" t="inlineStr">
+      <c r="G265" s="2" t="inlineStr">
         <is>
           <t>A booking request for Venue Z is pending</t>
         </is>
       </c>
-      <c r="H258" s="2" t="inlineStr">
+      <c r="H265" s="2" t="inlineStr">
         <is>
           <t>1. As Venue Staff, approve the booking request
   2. Log in as a System Administrator
   3. Check the Activity Log</t>
         </is>
       </c>
-      <c r="I258" s="2" t="inlineStr">
+      <c r="I265" s="2" t="inlineStr">
         <is>
           <t>Venue: Venue Z | Action: Approve Booking</t>
         </is>
       </c>
-      <c r="J258" s="2" t="inlineStr">
+      <c r="J265" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded with the actor, action ("Booking Approved"), the affected booking/event, and a timestamp</t>
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="2" t="n">
+    <row r="266">
+      <c r="A266" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B259" s="2" t="inlineStr">
+      <c r="B266" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C259" s="2" t="inlineStr">
+      <c r="C266" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 4 (Deactivation recorded)</t>
         </is>
       </c>
-      <c r="D259" s="2" t="inlineStr">
+      <c r="D266" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E259" s="2" t="inlineStr">
+      <c r="E266" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_04</t>
         </is>
       </c>
-      <c r="F259" s="2" t="inlineStr">
+      <c r="F266" s="2" t="inlineStr">
         <is>
           <t>Verify that an account deactivation should be recorded in the activity log</t>
         </is>
       </c>
-      <c r="G259" s="2" t="inlineStr">
+      <c r="G266" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is signed in</t>
         </is>
       </c>
-      <c r="H259" s="2" t="inlineStr">
+      <c r="H266" s="2" t="inlineStr">
         <is>
           <t>1. Deactivate the account
   2. Log in as a System Administrator
   3. Check the Activity Log</t>
         </is>
       </c>
-      <c r="I259" s="2" t="inlineStr">
+      <c r="I266" s="2" t="inlineStr">
         <is>
           <t>Account: organiser_a@clienta.com</t>
         </is>
       </c>
-      <c r="J259" s="2" t="inlineStr">
+      <c r="J266" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded showing the account deactivation with actor and timestamp</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="2" t="n">
+    <row r="267">
+      <c r="A267" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B260" s="2" t="inlineStr">
+      <c r="B267" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C260" s="2" t="inlineStr">
+      <c r="C267" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 5 (Log entries immutable)</t>
         </is>
       </c>
-      <c r="D260" s="2" t="inlineStr">
+      <c r="D267" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E260" s="2" t="inlineStr">
+      <c r="E267" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_05</t>
         </is>
       </c>
-      <c r="F260" s="2" t="inlineStr">
+      <c r="F267" s="2" t="inlineStr">
         <is>
           <t>Verify that any attempt to edit or delete an activity log entry should be refused</t>
         </is>
       </c>
-      <c r="G260" s="2" t="inlineStr">
+      <c r="G267" s="2" t="inlineStr">
         <is>
           <t>A log entry exists: Event = Annual Tech Summit, Action = "Status changed to Approved", Actor = coordinator_1@connectsphere.com (created in TC_E14S02_01)</t>
         </is>
       </c>
-      <c r="H260" s="2" t="inlineStr">
+      <c r="H267" s="2" t="inlineStr">
         <is>
           <t>1. Log in as a System Administrator
   2. Open the Activity Log and locate the entry for Event = Annual Tech Summit, Action = "Status changed to Approved"
@@ -14048,272 +14412,272 @@
   5. If no UI path exists for either action, attempt the same edit and delete via a direct API call to the log entry's ID</t>
         </is>
       </c>
-      <c r="I260" s="2" t="inlineStr">
+      <c r="I267" s="2" t="inlineStr">
         <is>
           <t>Target log entry: Event = Annual Tech Summit, Action = "Status changed to Approved" | Attempted edit: Action -&gt; "Status changed to Rejected"</t>
         </is>
       </c>
-      <c r="J260" s="2" t="inlineStr">
+      <c r="J267" s="2" t="inlineStr">
         <is>
           <t>Both the edit and delete attempts are refused; no UI control exists to modify or remove a log entry, and the direct API call returns an authorization/forbidden error with the entry left unchanged</t>
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" s="2" t="n">
+    <row r="268">
+      <c r="A268" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B261" s="2" t="inlineStr">
+      <c r="B268" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C261" s="2" t="inlineStr">
+      <c r="C268" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 3 (Booking decision recorded)</t>
         </is>
       </c>
-      <c r="D261" s="2" t="inlineStr">
+      <c r="D268" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E261" s="2" t="inlineStr">
+      <c r="E268" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_06</t>
         </is>
       </c>
-      <c r="F261" s="2" t="inlineStr">
+      <c r="F268" s="2" t="inlineStr">
         <is>
           <t>Verify that a rejected venue booking should be recorded with the actor, action, affected records, and time</t>
         </is>
       </c>
-      <c r="G261" s="2" t="inlineStr">
+      <c r="G268" s="2" t="inlineStr">
         <is>
           <t>A booking request for Venue Z is pending</t>
         </is>
       </c>
-      <c r="H261" s="2" t="inlineStr">
+      <c r="H268" s="2" t="inlineStr">
         <is>
           <t>1. As Venue Staff, reject the booking request with reason "Venue unavailable for maintenance"
   2. Log in as a System Administrator
   3. Check the Activity Log</t>
         </is>
       </c>
-      <c r="I261" s="2" t="inlineStr">
+      <c r="I268" s="2" t="inlineStr">
         <is>
           <t>Venue: Venue Z | Action: Reject Booking | Reason: Venue unavailable for maintenance</t>
         </is>
       </c>
-      <c r="J261" s="2" t="inlineStr">
+      <c r="J268" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded with the actor, action ("Booking Rejected"), the affected booking/event, and a timestamp</t>
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" s="2" t="n">
+    <row r="269">
+      <c r="A269" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B262" s="2" t="inlineStr">
+      <c r="B269" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C262" s="2" t="inlineStr">
+      <c r="C269" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 3 (Booking decision recorded)</t>
         </is>
       </c>
-      <c r="D262" s="2" t="inlineStr">
+      <c r="D269" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E262" s="2" t="inlineStr">
+      <c r="E269" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_07</t>
         </is>
       </c>
-      <c r="F262" s="2" t="inlineStr">
+      <c r="F269" s="2" t="inlineStr">
         <is>
           <t>Verify that a released venue booking should be recorded with the actor, action, affected records, and time</t>
         </is>
       </c>
-      <c r="G262" s="2" t="inlineStr">
+      <c r="G269" s="2" t="inlineStr">
         <is>
           <t>Venue Z has a confirmed booking for event "Annual Tech Summit"</t>
         </is>
       </c>
-      <c r="H262" s="2" t="inlineStr">
+      <c r="H269" s="2" t="inlineStr">
         <is>
           <t>1. As Venue Staff or Coordinator, release the confirmed booking for Venue Z (e.g. due to event cancellation)
   2. Log in as a System Administrator
   3. Check the Activity Log</t>
         </is>
       </c>
-      <c r="I262" s="2" t="inlineStr">
+      <c r="I269" s="2" t="inlineStr">
         <is>
           <t>Venue: Venue Z | Action: Release Booking | Event: Annual Tech Summit</t>
         </is>
       </c>
-      <c r="J262" s="2" t="inlineStr">
+      <c r="J269" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded with the actor, action ("Booking Released"), the affected booking/event, and a timestamp</t>
         </is>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" s="2" t="n">
+    <row r="270">
+      <c r="A270" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B263" s="2" t="inlineStr">
+      <c r="B270" s="2" t="inlineStr">
         <is>
           <t>Definition of Done</t>
         </is>
       </c>
-      <c r="C263" s="2" t="inlineStr">
+      <c r="C270" s="2" t="inlineStr">
         <is>
           <t>Definition of Done · BDR T-51 · Week 1 §8a</t>
         </is>
       </c>
-      <c r="D263" s="2" t="inlineStr">
+      <c r="D270" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting</t>
         </is>
       </c>
-      <c r="E263" s="2" t="inlineStr">
+      <c r="E270" s="2" t="inlineStr">
         <is>
           <t>TC_PERF_01</t>
         </is>
       </c>
-      <c r="F263" s="2" t="inlineStr">
+      <c r="F270" s="2" t="inlineStr">
         <is>
           <t>Verify a venue search returns within the 3-second target on a realistic catalogue</t>
         </is>
       </c>
-      <c r="G263" s="2" t="inlineStr">
+      <c r="G270" s="2" t="inlineStr">
         <is>
           <t>The venue catalogue holds 50 venues with layouts, accessibility features and facilities. 200 confirmed bookings exist across the next 90 days. Coordinator coord_a@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H263" s="2" t="inlineStr">
+      <c r="H270" s="2" t="inlineStr">
         <is>
           <t>1. Open the venue search
  2. Enter date 2026-12-01, time 09:00–11:00, expected attendance 120, layout Theatre, accessibility Step-free access
  3. Start a timer on submit and stop it when results render</t>
         </is>
       </c>
-      <c r="I263" s="2" t="inlineStr">
+      <c r="I270" s="2" t="inlineStr">
         <is>
           <t>50 venues · 200 bookings · elapsed time measured client-side</t>
         </is>
       </c>
-      <c r="J263" s="2" t="inlineStr">
+      <c r="J270" s="2" t="inlineStr">
         <is>
           <t>Results render in under 3 seconds. Record the measured time; if it exceeds 3 seconds the story does not meet the Definition of Done</t>
         </is>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" s="2" t="n">
+    <row r="271">
+      <c r="A271" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B264" s="2" t="inlineStr">
+      <c r="B271" s="2" t="inlineStr">
         <is>
           <t>Definition of Done</t>
         </is>
       </c>
-      <c r="C264" s="2" t="inlineStr">
+      <c r="C271" s="2" t="inlineStr">
         <is>
           <t>Definition of Done · BDR T-51 · Week 1 §8a</t>
         </is>
       </c>
-      <c r="D264" s="2" t="inlineStr">
+      <c r="D271" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting</t>
         </is>
       </c>
-      <c r="E264" s="2" t="inlineStr">
+      <c r="E271" s="2" t="inlineStr">
         <is>
           <t>TC_PERF_02</t>
         </is>
       </c>
-      <c r="F264" s="2" t="inlineStr">
+      <c r="F271" s="2" t="inlineStr">
         <is>
           <t>Verify the venue availability calendar loads within the 3-second target for a busy month</t>
         </is>
       </c>
-      <c r="G264" s="2" t="inlineStr">
+      <c r="G271" s="2" t="inlineStr">
         <is>
           <t>Orchid Hall has 40 confirmed bookings, 5 tentative holds and 3 maintenance blocks within 2026-12-01 to 2026-12-31</t>
         </is>
       </c>
-      <c r="H264" s="2" t="inlineStr">
+      <c r="H271" s="2" t="inlineStr">
         <is>
           <t>1. Open Orchid Hall in the venue catalogue
  2. Select the calendar for December 2026
  3. Start a timer on selection and stop it when all states have rendered</t>
         </is>
       </c>
-      <c r="I264" s="2" t="inlineStr">
+      <c r="I271" s="2" t="inlineStr">
         <is>
           <t>48 calendar entries in one month · elapsed time measured client-side</t>
         </is>
       </c>
-      <c r="J264" s="2" t="inlineStr">
+      <c r="J271" s="2" t="inlineStr">
         <is>
           <t>The calendar renders all Free, Tentative, Confirmed and Blocked states in under 3 seconds</t>
         </is>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" s="2" t="n">
+    <row r="272">
+      <c r="A272" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B265" s="2" t="inlineStr">
+      <c r="B272" s="2" t="inlineStr">
         <is>
           <t>Definition of Done</t>
         </is>
       </c>
-      <c r="C265" s="2" t="inlineStr">
+      <c r="C272" s="2" t="inlineStr">
         <is>
           <t>Definition of Done · BDR T-51 · Week 1 §8a</t>
         </is>
       </c>
-      <c r="D265" s="2" t="inlineStr">
+      <c r="D272" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting</t>
         </is>
       </c>
-      <c r="E265" s="2" t="inlineStr">
+      <c r="E272" s="2" t="inlineStr">
         <is>
           <t>TC_PERF_03</t>
         </is>
       </c>
-      <c r="F265" s="2" t="inlineStr">
+      <c r="F272" s="2" t="inlineStr">
         <is>
           <t>Verify a registration submission completes within the 3-second target near capacity</t>
         </is>
       </c>
-      <c r="G265" s="2" t="inlineStr">
+      <c r="G272" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with Orchid Hall booked, venue capacity 200, and 198 registrations recorded. Attendee attendee_b@example.com is signed in</t>
         </is>
       </c>
-      <c r="H265" s="2" t="inlineStr">
+      <c r="H272" s="2" t="inlineStr">
         <is>
           <t>1. Open event EVT-2001
  2. Submit a registration
  3. Start a timer on submit and stop it when confirmation renders</t>
         </is>
       </c>
-      <c r="I265" s="2" t="inlineStr">
+      <c r="I272" s="2" t="inlineStr">
         <is>
           <t>198 existing registrations · capacity 200 · elapsed time measured client-side</t>
         </is>
       </c>
-      <c r="J265" s="2" t="inlineStr">
+      <c r="J272" s="2" t="inlineStr">
         <is>
           <t>The registration is created and confirmation renders in under 3 seconds, including the capacity check against the booked venue</t>
         </is>

--- a/docs/testing/PROJECT TEST CASES CAA 031026.xlsx
+++ b/docs/testing/PROJECT TEST CASES CAA 031026.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J272"/>
+  <dimension ref="A1:J277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7835,8 +7835,7 @@
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>The calendar shows Tentative from 09:30 to 12:45 with the buffer portions marked; Attempt A is refused naming coordinator_1's hold; Attempt B is accepted because its own buffered window starts at exactly 12:45, when the hold's ends
-## E06-S06</t>
+          <t>The calendar shows Tentative from 09:30 to 12:45 with the buffer portions marked; Attempt A is refused naming coordinator_1's hold; Attempt B is accepted because its own buffered window starts at exactly 12:45, when the hold's ends</t>
         </is>
       </c>
     </row>
@@ -7846,397 +7845,658 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
+          <t>E06-S05</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>E06-S05 — Scenario 1 (Tentative hold placed); assumes O-31</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>TC_E06S05_03</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Verify that a new tentative hold should carry an expiry 48 hours after creation that Venue Staff can change</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Venue "Riverside Hall" is Free on 15/01/2027; coordinator_1@connectsphere.com has an Approved event; the clock reads 03/01/2027 10:00</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>1. As coordinator_1, place a tentative hold on "Riverside Hall" for 15/01/2027 10:00-12:00
+  2. Read the hold's expiry on the event
+  3. As venue_staff_1@connectsphere.com, open the hold and set the expiry to 06/01/2027 10:00</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Created 03/01/2027 10:00 | Default expiry 05/01/2027 10:00 | Changed to 06/01/2027 10:00</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>After step 1 the hold shows expiry 05/01/2027 10:00; after step 3 it shows 06/01/2027 10:00 and the activity log records the change by venue_staff_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>E06-S05</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>E06-S05 — Scenario 3 (Hold becomes a booking request); assumes O-32</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>TC_E06S05_04</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Verify that submitting a booking request for a held venue should complete the hold so that it no longer expires</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>As TC_E06S05_03 after step 1</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>1. As coordinator_1, submit a booking request for "Riverside Hall" 15/01/2027 10:00-12:00 from the hold
+  2. Advance the clock past 05/01/2027 10:00 and run the expiry job
+  3. Read the booking and the calendar</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>Hold converted before its expiry</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>The request is Pending, the hold shows no expiry, and after the job runs the booking is still Pending and the calendar still shows the period as Tentative; nothing expired</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>E06-S05</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>E06-S05 — Scenario 6 (Hold expires and frees the venue); Scenario 9 (Expiry exactly at the boundary)</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>5 - Boundary (exactly at)</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>TC_E06S05_05</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Verify that an unconverted hold should become Expired when its expiry passes, freeing the venue and never counting as a booking</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>coordinator_1 holds "Riverside Hall" for 15/01/2027 10:00-12:00 with expiry 05/01/2027 10:00:00 and has not requested it; coordinator_2 has an Approved event "Alumni Dinner"</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>1. Set the clock to 05/01/2027 09:59:59 and run the expiry job; read the hold and the calendar
+  2. Set the clock to 05/01/2027 10:00:00 and run the expiry job; read the hold and the calendar
+  3. As coordinator_2, place a tentative hold on "Riverside Hall" for 15/01/2027 10:00-12:00
+  4. As coordinator_1, attempt to confirm the event (E08-S03) using only the expired hold as its venue</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Expiry 05/01/2027 10:00:00 | Job at 09:59:59 then 10:00:00</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>After step 1 the hold is still Tentative and the calendar shows Tentative; after step 2 the hold is Expired and the calendar shows Free; step 3 succeeds; step 4 is blocked with "no Confirmed venue booking", the expired hold not being counted</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>E06-S05</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>E06-S05 — Scenario 7 (Coordinator told before and at expiry); assumes O-33</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>3 - Cross-cutting (notification consistency)</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>TC_E06S05_06</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Verify that the Coordinator should receive a reminder 24 hours before a hold expires and a notice when it expires</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>As TC_E06S05_05 before step 1; notification relay enabled against the intercepted email provider</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>1. Set the clock to 04/01/2027 10:00 and run the expiry job; open coordinator_1's inbox and the intercepted emails
+  2. Set the clock to 05/01/2027 10:00 and run the expiry job; open them again
+  3. Run the expiry job a third time</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>Reminder at expiry minus 24h | Notice at expiry</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>After step 1 exactly one in-app notification and one email name "Riverside Hall", the event and the expiry time; after step 2 exactly one further notification and email say the hold has expired and the venue is free; step 3 produces nothing more</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>E06-S05</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>E06-S05 — Scenario 8 (Venue Staff may extend a hold); assumes O-34</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>4 - Negative (business rule)</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>TC_E06S05_07</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Verify that Venue Staff should be able to extend an unexpired hold but not an expired one</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>coordinator_1 holds "Riverside Hall" with expiry 05/01/2027 10:00; a second hold on "Harbour Suite" expired at 04/01/2027 10:00; venue_staff_1@connectsphere.com is signed in on 04/01/2027 12:00</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Riverside Hall hold and set expiry to 07/01/2027 10:00; save
+  2. Open the Harbour Suite hold and attempt to set expiry to 07/01/2027 10:00</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>One live hold, one expired hold</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>Step 1 succeeds, the activity log records the extension by venue_staff_1, and the reminder is rescheduled to 06/01/2027 10:00; step 2 is refused with a message that an expired hold cannot be extended and must be placed again
+## E06-S06</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
         <is>
           <t>E06-S06 - Scenario 1 (Overlapping approval blocked)</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_01</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to approve a request that overlaps an existing confirmed booking for the same venue should be blocked with the conflicting booking identified</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>"Riverside Hall" has a confirmed booking for "Charity Run" on 15/01/2027, 09:00-17:00. A second pending request for "Riverside Hall" on 15/01/2027, 14:00-18:00 exists for event "Product Expo 2026"</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>1. Log in as venue_staff_1@connectsphere.com
   2. Open the pending request for "Product Expo 2026"
   3. Attempt to click "Approve"</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr">
         <is>
           <t>Existing confirmed booking: Charity Run, 15/01/2027 09:00-17:00 | Conflicting request: Product Expo 2026, 15/01/2027 14:00-18:00</t>
         </is>
       </c>
-      <c r="J142" s="2" t="inlineStr">
+      <c r="J147" s="2" t="inlineStr">
         <is>
           <t>Approval is blocked, and the message identifies the existing confirmed "Charity Run" booking as the conflict</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="n">
+    <row r="148">
+      <c r="A148" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
         <is>
           <t>E06-S06 - Scenario 2 (Competing request flagged)</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_02</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Verify that approving one of two pending requests for the same venue and overlapping times should flag the other as conflicting</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>Two pending requests exist for "Riverside Hall" on 20/01/2027, both 09:00-12:00: Request A ("Tech Conference 2026") and Request B ("Product Expo 2026")</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>1. Log in as venue_staff_1@connectsphere.com
   2. Approve Request A ("Tech Conference 2026")
   3. Open Request B ("Product Expo 2026")</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr">
         <is>
           <t>Request A: Tech Conference 2026 (approved) | Request B: Product Expo 2026 (same venue, overlapping time)</t>
         </is>
       </c>
-      <c r="J143" s="2" t="inlineStr">
+      <c r="J148" s="2" t="inlineStr">
         <is>
           <t>Request B is now flagged as conflicting and cannot be approved until the conflict is resolved</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="n">
+    <row r="149">
+      <c r="A149" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>E06-S06 - Scenario 3 (Simultaneous approval fails safely)</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_03</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Verify that if another Venue Staff member approves a conflicting request moments earlier, a simultaneous approval attempt should fail safely and inform the user the venue has just been taken</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>Two pending requests exist for "Riverside Hall" on 25/01/2027, overlapping times. venue_staff_2@connectsphere.com approves one of them a moment before venue_staff_1@connectsphere.com processes the other</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>1. As venue_staff_2@connectsphere.com, approve Request A for "Riverside Hall" on 25/01/2027
   2. Immediately as venue_staff_1@connectsphere.com, attempt to approve the conflicting Request B for the same venue and overlapping time</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr">
         <is>
           <t>Request A approved by venue_staff_2@connectsphere.com just before venue_staff_1@connectsphere.com's attempt on Request B</t>
         </is>
       </c>
-      <c r="J144" s="2" t="inlineStr">
+      <c r="J149" s="2" t="inlineStr">
         <is>
           <t>venue_staff_1@connectsphere.com's approval attempt fails safely, with a message stating the venue has just been taken by another approval</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="n">
+    <row r="150">
+      <c r="A150" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t>E06-S06 · Scenario 1 (Overlapping approval blocked)</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (adjacent, must not conflict)</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_04</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Verify that a booking beginning exactly when another ends is not treated as a conflict</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>Venue Orchid Hall has a confirmed booking for 2026-11-10 09:00:00 to 2026-11-10 11:00:00. A pending request exists for the same venue for 2026-11-10 11:00:00 to 2026-11-10 13:00:00</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Venue Staff
  2. Open the pending request for 11:00–13:00
  3. Approve it</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr">
         <is>
           <t>Existing: 09:00–11:00 · Requested: 11:00–13:00 · Shared boundary: 11:00</t>
         </is>
       </c>
-      <c r="J145" s="2" t="inlineStr">
+      <c r="J150" s="2" t="inlineStr">
         <is>
           <t>The approval succeeds and both bookings show as Confirmed on the venue calendar. Ranges are half-open, so touching at the boundary is not an overlap</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="n">
+    <row r="151">
+      <c r="A151" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
         <is>
           <t>E06-S06 · Scenario 1 (Overlapping approval blocked)</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (one minute of overlap, must conflict)</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_05</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Verify that a booking overlapping an existing one by a single minute is blocked</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>Venue Orchid Hall has a confirmed booking for 2026-11-10 09:00:00 to 2026-11-10 11:00:00. A pending request exists for the same venue for 2026-11-10 10:59:00 to 2026-11-10 13:00:00</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Venue Staff
  2. Open the pending request for 10:59–13:00
  3. Attempt to approve it</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr">
         <is>
           <t>Existing: 09:00–11:00 · Requested: 10:59–13:00 · Overlap: 1 minute</t>
         </is>
       </c>
-      <c r="J146" s="2" t="inlineStr">
+      <c r="J151" s="2" t="inlineStr">
         <is>
           <t>Approval is blocked and the conflicting 09:00–11:00 booking is identified. The venue never holds two confirmed bookings over the same period</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="n">
+    <row r="152">
+      <c r="A152" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t>E06-S06 — Scenario 4 (Buffered windows are what must not overlap)</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>3 - Integration / regression</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_06</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Verify that two approvals whose advertised times do not overlap but whose buffered windows do should let at most one succeed when processed at the same moment</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>Venue "Riverside Hall" has Setup time 30 and Turnaround time 45; two Pending requests exist on it for 15/01/2027: "Charity Run" 10:00-12:00 and "Alumni Dinner" 12:30-14:00; two Venue Staff accounts are signed in; TEST_DATABASE_URL points at the disposable test schema</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>1. Trigger approval of both requests concurrently (integration test issues both approvals in parallel transactions)
   2. Read back both bookings and the venue calendar</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr">
         <is>
           <t>Charity Run buffered: 09:30-12:45 | Alumni Dinner buffered: 12:00-14:45 (advertised times do not overlap; buffered windows overlap 12:00-12:45)</t>
         </is>
       </c>
-      <c r="J147" s="2" t="inlineStr">
+      <c r="J152" s="2" t="inlineStr">
         <is>
           <t>Exactly one booking is Confirmed; the other approval fails with the conflict identified and its request remains Pending; the database exclusion constraint rejected the second write on the buffered range (ADR-003), so TC_E06S06_04 (adjacent, must not conflict) and TC_E06S06_05 (one minute of overlap) continue to hold on buffered windows</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="n">
+    <row r="153">
+      <c r="A153" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
         <is>
           <t>E06-S06 — Scenario 5 (Conflicts are per venue, not per event)</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>3 - Integration / regression</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>TC_E06S06_07</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Verify that approving two requests from the same event on two different venues over the same period should confirm both</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Summit" has Pending requests on "Seminar Room A" and "Seminar Room B" for 15/01/2027 14:00-16:00 (TC_E06S03_07); venue_staff_1@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>1. Approve the "Seminar Room A" request
   2. Approve the "Seminar Room B" request
   3. Open the availability calendar for both venues on 15/01/2027</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr">
         <is>
           <t>Same event, same period, two venues</t>
         </is>
       </c>
-      <c r="J148" s="2" t="inlineStr">
+      <c r="J153" s="2" t="inlineStr">
         <is>
           <t>Both bookings become Confirmed; neither approval is blocked; each venue's calendar shows its own Confirmed period; TC_E06S06_01 to TC_E06S06_06 (conflicts on one venue) continue to hold</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="n">
+    <row r="154">
+      <c r="A154" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
         <is>
           <t>E07-S01 - Scenario 1 (Item added and reservable)</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>TC_E07S01_01</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Verify that saving a new equipment item with its full details should make it available for reservation</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>tech_support_1@connectsphere.com is signed in; equipment item "Wireless Microphone" does not yet exist</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to "Add Equipment"
   2. Enter Type: "Wireless Microphone", Description: "Handheld, UHF", Quantity: 10, Location: "Main Storage", Operational Status: "Working"
@@ -8244,52 +8504,52 @@
   4. Log in as an Event Coordinator and check equipment availability for "Wireless Microphone"</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr">
         <is>
           <t>Item: Wireless Microphone | Quantity: 10 | Location: Main Storage | Status: Working</t>
         </is>
       </c>
-      <c r="J149" s="2" t="inlineStr">
+      <c r="J154" s="2" t="inlineStr">
         <is>
           <t>The item is saved and appears as available for reservation, with 10 units free</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="n">
+    <row r="155">
+      <c r="A155" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
         <is>
           <t>E07-S01 - Scenario 2 (Quantity drop flags reservations)</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>TC_E07S01_02</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Verify that reducing an item's quantity below the amount already reserved for upcoming events should flag the affected reservations and notify the relevant Coordinators</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>"Wireless Microphone" (quantity 10) has 6 units reserved for an upcoming event of "Tech Conference 2026", assigned to coordinator_1@connectsphere.com</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "Wireless Microphone"
@@ -8297,52 +8557,52 @@
   4. Save</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr">
         <is>
           <t>Quantity: 10 -&gt; 4 | Existing reservation: 6 units</t>
         </is>
       </c>
-      <c r="J150" s="2" t="inlineStr">
+      <c r="J155" s="2" t="inlineStr">
         <is>
           <t>The 6-unit reservation is flagged for review since it now exceeds total stock, and coordinator_1@connectsphere.com is notified</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="n">
+    <row r="156">
+      <c r="A156" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
         <is>
           <t>E07-S01 - Scenario 3 (Item retired)</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>TC_E07S01_03</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Verify that retiring an item with no future reservations should remove it from availability checks while retaining its past reservations</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>Equipment item "Old Projector" has no future reservations; it has 2 past (completed) reservations on record</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "Old Projector"
@@ -8351,52 +8611,52 @@
   5. Check availability for "Old Projector" as an Event Coordinator</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr">
         <is>
           <t>Item: Old Projector (no future reservations)</t>
         </is>
       </c>
-      <c r="J151" s="2" t="inlineStr">
+      <c r="J156" s="2" t="inlineStr">
         <is>
           <t>"Old Projector" no longer appears in availability checks; its 2 past reservations remain retained and viewable in historical records</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="n">
+    <row r="157">
+      <c r="A157" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
         <is>
           <t>E07-S01 (checklist: update equipment attributes)</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>TC_E07S01_04</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Verify that updating an existing equipment item's attributes should save the changes</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>Equipment item "Wireless Microphone" exists with Location: "Main Storage"</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "Wireless Microphone"
@@ -8404,53 +8664,53 @@
   4. Click "Save"</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr">
         <is>
           <t>Location: Main Storage -&gt; Annex Storage</t>
         </is>
       </c>
-      <c r="J152" s="2" t="inlineStr">
+      <c r="J157" s="2" t="inlineStr">
         <is>
           <t>The updated Location value is saved and shown when the item record is reopened
 ## E07-S02</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="n">
+    <row r="158">
+      <c r="A158" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
         <is>
           <t>E07-S02 - Scenario 1 (Equipment recorded against an event)</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>TC_E07S02_01</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Verify that adding equipment items with quantities to a event of an approved event should save the request and notify Technical Support Staff</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" is Approved; the event has no equipment requested yet</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the event of "Tech Conference 2026"
@@ -8459,52 +8719,52 @@
   5. Check tech_support_1@connectsphere.com's notifications</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr">
         <is>
           <t>the event equipment: Wireless Microphone x2, Projector x1</t>
         </is>
       </c>
-      <c r="J153" s="2" t="inlineStr">
+      <c r="J158" s="2" t="inlineStr">
         <is>
           <t>The equipment request is saved against the event, and tech_support_1@connectsphere.com is notified</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="n">
+    <row r="159">
+      <c r="A159" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
         <is>
           <t>E07-S02 - Scenario 2 (Request exceeds total stock)</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>TC_E07S02_02</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Verify that requesting more of an item than ConnectSphere owns in total should warn that the request cannot be met from existing stock</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>"Wireless Microphone" has a total stock of 10 units</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open a event of "Tech Conference 2026"
@@ -8512,52 +8772,52 @@
   4. Save</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr">
         <is>
           <t>Requested quantity: 15 | Total stock: 10</t>
         </is>
       </c>
-      <c r="J154" s="2" t="inlineStr">
+      <c r="J159" s="2" t="inlineStr">
         <is>
           <t>A warning is shown that the request (15 units) cannot be met from existing stock (10 units)</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="n">
+    <row r="160">
+      <c r="A160" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
         <is>
           <t>E07-S02 - Scenario 3 (Events independent of each other)</t>
         </is>
       </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>TC_E07S02_03</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Verify that recording equipment for one event should leave a different event's equipment unaffected</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>Coordinator coordinator_1@connectsphere.com manages two separate events, "Tech Conference 2026" and "Charity Run", neither with equipment requested yet</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open "Tech Conference 2026" and add "Projector" x 1
@@ -8565,52 +8825,52 @@
   4. Open "Charity Run" and check its equipment list</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr">
         <is>
           <t>"Tech Conference 2026": Projector x1 added | "Charity Run": unchanged</t>
         </is>
       </c>
-      <c r="J155" s="2" t="inlineStr">
+      <c r="J160" s="2" t="inlineStr">
         <is>
           <t>"Tech Conference 2026" shows "Projector x1"; "Charity Run"'s equipment list remains empty, unaffected by the other event's request</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="n">
+    <row r="161">
+      <c r="A161" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
         <is>
           <t>E07-S02 (checklist: amend or remove equipment request before reservation)</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>TC_E07S02_04</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Verify that amending or removing an equipment request before it is reserved should update or clear the request accordingly</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" has an unreserved equipment request: "Wireless Microphone" x 2</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the event's equipment request
@@ -8619,208 +8879,208 @@
   5. Save</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr">
         <is>
           <t>Quantity change: 2 -&gt; 3, then removed entirely</t>
         </is>
       </c>
-      <c r="J156" s="2" t="inlineStr">
+      <c r="J161" s="2" t="inlineStr">
         <is>
           <t>After step 3, the request shows "Wireless Microphone x3"; after step 5, the request no longer includes "Wireless Microphone"
 ## E07-S03</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="n">
+    <row r="162">
+      <c r="A162" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
         <is>
           <t>E07-S03 - Scenario 1 (Reserved and faulty stock excluded)</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>TC_E07S03_01</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Verify that checking availability for a period with other reservations should exclude those reservations and any damaged or under-maintenance items from the free quantity</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>"Wireless Microphone" has total stock 10; 3 units are reserved for another event on 15/11/2026, 09:00-12:00; 2 units are marked damaged</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Check availability for "Wireless Microphone" on 15/11/2026, 09:00-12:00</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr">
         <is>
           <t>Total stock: 10 | Reserved: 3 | Damaged: 2</t>
         </is>
       </c>
-      <c r="J157" s="2" t="inlineStr">
+      <c r="J162" s="2" t="inlineStr">
         <is>
           <t>The free quantity shown is 5 (10 minus 3 reserved minus 2 damaged)</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="n">
+    <row r="163">
+      <c r="A163" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
         <is>
           <t>E07-S03 - Scenario 2 (Location does not affect availability)</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>TC_E07S03_02</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Verify that an item free for the requested date and time but located at another venue should still be shown as available, with no transport allowance applied</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>"Projector" is free for 15/11/2026, 09:00-12:00, but is currently located at "Grand Ballroom" rather than the requested venue</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Check availability for "Projector" on 15/11/2026, 09:00-12:00 for a event at "Riverside Hall"</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr">
         <is>
           <t>Item location: Grand Ballroom | Requested venue: Riverside Hall</t>
         </is>
       </c>
-      <c r="J158" s="2" t="inlineStr">
+      <c r="J163" s="2" t="inlineStr">
         <is>
           <t>"Projector" is shown as available with its full free quantity; no transport time or allowance is added to the availability check</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="n">
+    <row r="164">
+      <c r="A164" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
         <is>
           <t>E07-S03 - Scenario 3 (Non-overlapping events share an item)</t>
         </is>
       </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>TC_E07S03_03</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Verify that two events requiring the same item at non-overlapping times on the same day should both show it as free</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>"Tech Conference 2026" the event (09:00-12:00) and the event (14:00-17:00) both require "Wireless Microphone", with no other reservations that day</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Check availability for "Wireless Microphone" during the event's time (09:00-12:00)
   3. Check availability for "Wireless Microphone" during the event's time (14:00-17:00)</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr">
         <is>
           <t>the event: 09:00-12:00 | the event: 14:00-17:00 (same day, non-overlapping)</t>
         </is>
       </c>
-      <c r="J159" s="2" t="inlineStr">
+      <c r="J164" s="2" t="inlineStr">
         <is>
           <t>"Wireless Microphone" shows its full free quantity for both the event's and the event's time windows
 ## E07-S04</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="n">
+    <row r="165">
+      <c r="A165" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
         <is>
           <t>E07-S04 - Scenario 1 (Full reservation recorded)</t>
         </is>
       </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_01</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Verify that reserving the requested quantity when sufficient equipment is free should record the reservation and notify the Event Coordinator</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" requested "Wireless Microphone" x 2; 5 units are free for that period</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the equipment request for the event
@@ -8829,52 +9089,52 @@
   5. Check coordinator_1@connectsphere.com's notifications</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr">
+      <c r="I165" s="2" t="inlineStr">
         <is>
           <t>Reserved: Wireless Microphone x2 (5 free)</t>
         </is>
       </c>
-      <c r="J160" s="2" t="inlineStr">
+      <c r="J165" s="2" t="inlineStr">
         <is>
           <t>The reservation is recorded against the event, and coordinator_1@connectsphere.com receives a confirmation showing the event's date/time, item, and quantity</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="n">
+    <row r="166">
+      <c r="A166" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
         <is>
           <t>E07-S04 - Scenario 2 (Partial reservation and shortfall)</t>
         </is>
       </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_02</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Verify that recording a partial reservation when only part of the requested quantity is free should notify the Coordinator of the shortfall</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" requested "Projector" x 3; only 2 units are free for that period</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the equipment request for the event
@@ -8882,103 +9142,103 @@
   4. Confirm</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr">
+      <c r="I166" s="2" t="inlineStr">
         <is>
           <t>Requested: 3 | Reserved (partial): 2 | Shortfall: 1</t>
         </is>
       </c>
-      <c r="J161" s="2" t="inlineStr">
+      <c r="J166" s="2" t="inlineStr">
         <is>
           <t>coordinator_1@connectsphere.com is notified of the shortfall, showing 2 reserved and 1 outstanding unit of "Projector"</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="n">
+    <row r="167">
+      <c r="A167" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
         <is>
           <t>E07-S04 - Scenario 3 (Fully committed item shows nothing free)</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_03</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Verify that once an item becomes fully committed, a subsequent availability check for that period should show no free quantity</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>"Portable Stage" (total stock 2) has both units fully reserved for the period 20/11/2026, 09:00-17:00</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Check availability for "Portable Stage" on 20/11/2026, 09:00-17:00</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr">
+      <c r="I167" s="2" t="inlineStr">
         <is>
           <t>Portable Stage: 2 total, 2 reserved</t>
         </is>
       </c>
-      <c r="J162" s="2" t="inlineStr">
+      <c r="J167" s="2" t="inlineStr">
         <is>
           <t>The availability check shows 0 free units of "Portable Stage" for that period</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="n">
+    <row r="168">
+      <c r="A168" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
         <is>
           <t>E07-S04 - Scenario 4 (Reservation released)</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_04</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Verify that releasing a reservation when a event is cancelled or the equipment is no longer required should return the quantity to the available pool</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" has a reservation of "Wireless Microphone" x 2</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the reservation for the event
@@ -8987,52 +9247,52 @@
   5. Check availability for "Wireless Microphone" for that period</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr">
+      <c r="I168" s="2" t="inlineStr">
         <is>
           <t>Released reservation: Wireless Microphone x2</t>
         </is>
       </c>
-      <c r="J163" s="2" t="inlineStr">
+      <c r="J168" s="2" t="inlineStr">
         <is>
           <t>The 2 units are returned to the available pool, increasing the free quantity for that period by 2</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="n">
+    <row r="169">
+      <c r="A169" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
         <is>
           <t>E07-S04 · Scenario 1 (Full reservation recorded)</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (just below)</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_05</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Verify that requesting one fewer than the free quantity produces a full reservation and leaves the remainder free</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>Equipment Projector-HD has total quantity 10. Six units are reserved for other events overlapping EVT-1003, leaving 4 free. Event EVT-1003 has an equipment request for 3 units</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Technical Support Staff
  2. Open the equipment request for EVT-1003
@@ -9040,52 +9300,52 @@
  4. Re-check availability for the same period</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr">
+      <c r="I169" s="2" t="inlineStr">
         <is>
           <t>Free quantity: 4 · Requested: 3</t>
         </is>
       </c>
-      <c r="J164" s="2" t="inlineStr">
+      <c r="J169" s="2" t="inlineStr">
         <is>
           <t>A reservation of 3 is recorded with status Reserved, not Partial. Availability for the period now shows 1 free. Confirmation of the event is not blocked by this reservation</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="n">
+    <row r="170">
+      <c r="A170" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
         <is>
           <t>E07-S04 · Scenario 1 (Full reservation recorded)</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_06</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Verify that requesting exactly the free quantity produces a full reservation and leaves nothing free</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t>Equipment Projector-HD has total quantity 10. Six units are reserved for other events overlapping EVT-1003, leaving 4 free. Event EVT-1003 has an equipment request for 4 units</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Technical Support Staff
  2. Open the equipment request for EVT-1003
@@ -9093,52 +9353,52 @@
  4. Re-check availability for the same period</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr">
+      <c r="I170" s="2" t="inlineStr">
         <is>
           <t>Free quantity: 4 · Requested: 4</t>
         </is>
       </c>
-      <c r="J165" s="2" t="inlineStr">
+      <c r="J170" s="2" t="inlineStr">
         <is>
           <t>A reservation of 4 is recorded with status Reserved. Availability for the period shows 0 free. No shortfall notification is sent</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="n">
+    <row r="171">
+      <c r="A171" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
         <is>
           <t>E07-S04 · Scenario 2 (Partial reservation and shortfall) · E08-S03 Scenario 3</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (just above)</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>TC_E07S04_07</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Verify that requesting one more than the free quantity produces a partial reservation that blocks confirmation</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>Equipment Projector-HD has total quantity 10. Six units are reserved for other events overlapping EVT-1003, leaving 4 free. Event EVT-1003 has an equipment request for 5 units. Event EVT-1003 already has a confirmed venue booking</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Technical Support Staff
  2. Open the equipment request for EVT-1003
@@ -9146,53 +9406,53 @@
  4. Sign in as the assigned Event Coordinator and attempt to confirm the event</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr">
+      <c r="I171" s="2" t="inlineStr">
         <is>
           <t>Free quantity: 4 · Requested: 5 · Reserved: 4 · Outstanding: 1</t>
         </is>
       </c>
-      <c r="J166" s="2" t="inlineStr">
+      <c r="J171" s="2" t="inlineStr">
         <is>
           <t>The reservation is recorded with status Partial. The Coordinator is notified of an outstanding quantity of 1. Confirmation is blocked and the outstanding item is listed against event EVT-1003
 ## E07-S05</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="n">
+    <row r="172">
+      <c r="A172" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
         <is>
           <t>E07-S05 - Scenario 1 (Item marked unavailable)</t>
         </is>
       </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>TC_E07S05_01</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Verify that marking an item with no reservations in the period unavailable, with a reason and a period, should exclude it from availability checks for that period</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>Equipment item "HD Camera" has no reservations between 01/12/2026 and 05/12/2026</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "HD Camera"
@@ -9202,52 +9462,52 @@
   6. Check availability for "HD Camera" on 03/12/2026</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr">
+      <c r="I172" s="2" t="inlineStr">
         <is>
           <t>Period: 01/12/2026-05/12/2026 | Reason: Sensor repair</t>
         </is>
       </c>
-      <c r="J167" s="2" t="inlineStr">
+      <c r="J172" s="2" t="inlineStr">
         <is>
           <t>"HD Camera" shows 0 available units for any date within 01/12/2026-05/12/2026</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="n">
+    <row r="173">
+      <c r="A173" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
         <is>
           <t>E07-S05 - Scenario 2 (Reserved item flags its events)</t>
         </is>
       </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>TC_E07S05_02</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Verify that marking an item unavailable while it is reserved for an upcoming event should flag the affected event and notify its Coordinator</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>"HD Camera" is reserved for an upcoming event of "Tech Conference 2026", assigned to coordinator_1@connectsphere.com</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "HD Camera"
@@ -9255,52 +9515,52 @@
   4. Save</t>
         </is>
       </c>
-      <c r="I168" s="2" t="inlineStr">
+      <c r="I173" s="2" t="inlineStr">
         <is>
           <t>Affected event: Tech Conference 2026 event with HD Camera reserved</t>
         </is>
       </c>
-      <c r="J168" s="2" t="inlineStr">
+      <c r="J173" s="2" t="inlineStr">
         <is>
           <t>The affected event is flagged, and coordinator_1@connectsphere.com is notified that its reserved "HD Camera" is now unavailable</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="n">
+    <row r="174">
+      <c r="A174" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
         <is>
           <t>E07-S05 (checklist: return item to service)</t>
         </is>
       </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>TC_E07S05_03</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Verify that returning an item to service should restore it to availability checks</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t>"HD Camera" is currently marked unavailable for 01/12/2026-05/12/2026 with reason "Sensor repair"</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open equipment item "HD Camera"
@@ -9309,53 +9569,53 @@
   5. Check availability for "HD Camera" on 03/12/2026</t>
         </is>
       </c>
-      <c r="I169" s="2" t="inlineStr">
+      <c r="I174" s="2" t="inlineStr">
         <is>
           <t>Item: HD Camera (returning to service)</t>
         </is>
       </c>
-      <c r="J169" s="2" t="inlineStr">
+      <c r="J174" s="2" t="inlineStr">
         <is>
           <t>"HD Camera" now shows as available again for 03/12/2026
 ## E07-S06</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="n">
+    <row r="175">
+      <c r="A175" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
         <is>
           <t>E07-S06 - Scenario 1 (Support request recorded)</t>
         </is>
       </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>TC_E07S06_01</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting a technical support request describing the support needed and the times should notify Technical Support Staff and record it against the event</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" requires on-site technical support</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the event of "Tech Conference 2026"
@@ -9365,104 +9625,104 @@
   6. Check tech_support_1@connectsphere.com's notifications</t>
         </is>
       </c>
-      <c r="I170" s="2" t="inlineStr">
+      <c r="I175" s="2" t="inlineStr">
         <is>
           <t>Support description: "1 AV technician for the full event" | Times: 09:00-12:00</t>
         </is>
       </c>
-      <c r="J170" s="2" t="inlineStr">
+      <c r="J175" s="2" t="inlineStr">
         <is>
           <t>The request is recorded against the event, and tech_support_1@connectsphere.com is notified</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="n">
+    <row r="176">
+      <c r="A176" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
         <is>
           <t>E07-S06 - Scenario 2 (Request accepted before venue confirmed)</t>
         </is>
       </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>TC_E07S06_02</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting a technical support request before the venue is confirmed should be accepted and reviewed alongside venue identification</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" does not yet have a confirmed venue</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the event of "Tech Conference 2026" (no confirmed venue)
   3. Submit a technical support request describing "1 sound technician" for the event's planned times</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr">
+      <c r="I176" s="2" t="inlineStr">
         <is>
           <t>the event: no confirmed venue yet</t>
         </is>
       </c>
-      <c r="J171" s="2" t="inlineStr">
+      <c r="J176" s="2" t="inlineStr">
         <is>
           <t>The technical support request is accepted and recorded, without waiting for the venue to be confirmed first</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="n">
+    <row r="177">
+      <c r="A177" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
         <is>
           <t>E07-S06 - Scenario 3 (Event marked as needing none)</t>
         </is>
       </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>TC_E07S06_03</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Verify that marking a event as needing no technical support should create no request and not block confirmation on staff assignment</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>A event of "Charity Run" needs no on-site technical support</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the event of "Charity Run"
@@ -9470,53 +9730,53 @@
   4. Save</t>
         </is>
       </c>
-      <c r="I172" s="2" t="inlineStr">
+      <c r="I177" s="2" t="inlineStr">
         <is>
           <t>Event: Charity Run's event | Technical Support: Not Required</t>
         </is>
       </c>
-      <c r="J172" s="2" t="inlineStr">
+      <c r="J177" s="2" t="inlineStr">
         <is>
           <t>No technical support request is created for the event, and later event confirmation is not blocked waiting for a staff assignment
 ## E07-S07</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="n">
+    <row r="178">
+      <c r="A178" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
         <is>
           <t>E07-S07 - Scenario 1 (Available colleague assigned)</t>
         </is>
       </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_01</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>Verify that a colleague with no conflicting assignment during the event's required time period should be successfully assigned</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>the event of "Tech Conference 2026" (09:00-12:00) has an open technical support request. tech_support_2@connectsphere.com has no assignment overlapping 09:00-12:00 on that date</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the technical support request for the event
@@ -9524,155 +9784,155 @@
   4. Confirm</t>
         </is>
       </c>
-      <c r="I173" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr">
         <is>
           <t>Assignee: tech_support_2@connectsphere.com | Event time: 09:00-12:00</t>
         </is>
       </c>
-      <c r="J173" s="2" t="inlineStr">
+      <c r="J178" s="2" t="inlineStr">
         <is>
           <t>The assignment succeeds; tech_support_2@connectsphere.com is notified and the assignment appears on their schedule</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="n">
+    <row r="179">
+      <c r="A179" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
         <is>
           <t>E07-S07 (checklist: see assignment on schedule)</t>
         </is>
       </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_02</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Verify that the assignment should be reflected on the assigned staff member's schedule once made</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>tech_support_2@connectsphere.com has just been assigned to the event of "Tech Conference 2026" (09:00-12:00)</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_2@connectsphere.com
   2. Open "My Schedule"</t>
         </is>
       </c>
-      <c r="I174" s="2" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr">
         <is>
           <t>Assignment: the event, Tech Conference 2026, 09:00-12:00</t>
         </is>
       </c>
-      <c r="J174" s="2" t="inlineStr">
+      <c r="J179" s="2" t="inlineStr">
         <is>
           <t>The schedule shows the assignment to the event of "Tech Conference 2026" at 09:00-12:00</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="n">
+    <row r="180">
+      <c r="A180" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t>E07-S07 - Scenario 2 (Overlapping assignment blocked)</t>
         </is>
       </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_03</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>Verify that assigning a colleague who has an overlapping assignment should be blocked, with the conflicting event identified</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>tech_support_2@connectsphere.com is already assigned to a event of "Charity Run" from 10:00-13:00 on the same date. the event of "Tech Conference 2026" runs 09:00-12:00 on that date and needs a technician assigned</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the technical support request for the event of "Tech Conference 2026"
   3. Attempt to assign tech_support_2@connectsphere.com</t>
         </is>
       </c>
-      <c r="I175" s="2" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr">
         <is>
           <t>Existing assignment: Charity Run event, 10:00-13:00 | New attempted assignment: Tech Conference 2026 the event, 09:00-12:00 (overlaps)</t>
         </is>
       </c>
-      <c r="J175" s="2" t="inlineStr">
+      <c r="J180" s="2" t="inlineStr">
         <is>
           <t>The assignment is blocked, and the message identifies the conflicting "Charity Run" event as the reason</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="n">
+    <row r="181">
+      <c r="A181" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>E07-S07 - Scenario 3 (Assignment removed)</t>
         </is>
       </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_04</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>Verify that removing an existing assignment from a staff member's schedule should free up that slot</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>tech_support_2@connectsphere.com is assigned to the event of "Tech Conference 2026"</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the assignment for the event
@@ -9681,104 +9941,104 @@
   5. Check tech_support_2@connectsphere.com's schedule</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr">
         <is>
           <t>Assignment removed: tech_support_2@connectsphere.com, the event</t>
         </is>
       </c>
-      <c r="J176" s="2" t="inlineStr">
+      <c r="J181" s="2" t="inlineStr">
         <is>
           <t>The assignment no longer appears on tech_support_2@connectsphere.com's schedule, and the slot is free for reassignment</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="n">
+    <row r="182">
+      <c r="A182" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>E07-S07 - Scenario 4 (Replacement assigned under same check)</t>
         </is>
       </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_05</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>Verify that assigning a replacement colleague after removing an assignment should be subject to the same conflict check used for new assignments</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>The assignment for the event of "Tech Conference 2026" has just been removed from tech_support_2@connectsphere.com. tech_support_3@connectsphere.com already has a conflicting assignment during the event's time</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>1. Log in as tech_support_1@connectsphere.com
   2. Open the now-unassigned technical support request for the event
   3. Attempt to assign tech_support_3@connectsphere.com as a replacement</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr">
         <is>
           <t>Replacement candidate: tech_support_3@connectsphere.com (has a conflicting assignment)</t>
         </is>
       </c>
-      <c r="J177" s="2" t="inlineStr">
+      <c r="J182" s="2" t="inlineStr">
         <is>
           <t>The replacement assignment is blocked using the same conflict check as a new assignment, with the conflicting event identified</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="n">
+    <row r="183">
+      <c r="A183" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>E07-S07 (checklist: staff notified when assigned or removed)</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting (notification consistency)</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>TC_E07S07_06</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>Verify that the assigned staff member should receive a notification when they are assigned to, or removed from, an event</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>tech_support_2@connectsphere.com is about to be assigned to, and later removed from, the event of "Tech Conference 2026"</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>1. As tech_support_1@connectsphere.com, assign tech_support_2@connectsphere.com to the event
   2. Check tech_support_2@connectsphere.com's notifications
@@ -9786,52 +10046,52 @@
   4. Check tech_support_2@connectsphere.com's notifications again</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr">
         <is>
           <t>Actions: assign, then remove</t>
         </is>
       </c>
-      <c r="J178" s="2" t="inlineStr">
+      <c r="J183" s="2" t="inlineStr">
         <is>
           <t>tech_support_2@connectsphere.com receives a notification for the assignment, and a separate notification for the removal</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="n">
+    <row r="184">
+      <c r="A184" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>E08-S03 - Scenario 1 (All arrangements complete, event confirmed)</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>TC_E08S03_01</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>Verify that confirming an event where every event has a confirmed venue and full equipment reservation should set its status to Confirmed and notify the Organiser</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has one event with a confirmed venue booking (Riverside Hall) and its full requested equipment reserved, and requires no technical support</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Charity Run"
@@ -9839,362 +10099,362 @@
   4. Check the status and organiser_a@clienta.com's notifications</t>
         </is>
       </c>
-      <c r="I179" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr">
         <is>
           <t>Event: Charity Run (venue confirmed, equipment fully reserved, no tech support needed)</t>
         </is>
       </c>
-      <c r="J179" s="2" t="inlineStr">
+      <c r="J184" s="2" t="inlineStr">
         <is>
           <t>The status becomes "Confirmed", and organiser_a@clienta.com is notified with the confirmed details</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="n">
+    <row r="185">
+      <c r="A185" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
         <is>
           <t>E08-S03 - Scenario 2 (Missing venue blocks confirmation)</t>
         </is>
       </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>TC_E08S03_02</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to confirm an event while a event is missing a confirmed venue should be blocked with the outstanding event named</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has the event with a confirmed venue, but the event has no confirmed venue yet</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Tech Conference 2026"
   3. Click "Confirm Event"</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr">
+      <c r="I185" s="2" t="inlineStr">
         <is>
           <t>the event: venue confirmed | the event: no venue</t>
         </is>
       </c>
-      <c r="J180" s="2" t="inlineStr">
+      <c r="J185" s="2" t="inlineStr">
         <is>
           <t>Confirmation is blocked; the message lists "the event" as missing a confirmed venue</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="n">
+    <row r="186">
+      <c r="A186" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>E08-S03 - Scenario 3 (Partial equipment blocks confirmation)</t>
         </is>
       </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>TC_E08S03_03</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to confirm an event while a event has only a partial equipment reservation should be blocked with the outstanding quantity shown</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has all events with confirmed venues, but the event's "Projector" reservation is partial (2 of 3 requested)</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Tech Conference 2026"
   3. Click "Confirm Event"</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr">
+      <c r="I186" s="2" t="inlineStr">
         <is>
           <t>the event: Projector reserved 2 of 3 requested</t>
         </is>
       </c>
-      <c r="J181" s="2" t="inlineStr">
+      <c r="J186" s="2" t="inlineStr">
         <is>
           <t>Confirmation is blocked; the message shows the event's outstanding quantity of 1 "Projector" unit</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="n">
+    <row r="187">
+      <c r="A187" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
+      <c r="C187" s="2" t="inlineStr">
         <is>
           <t>E08-S03 - Scenario 5 (Outstanding support assignment blocks confirmation)</t>
         </is>
       </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>TC_E08S03_04</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to confirm an event while a event's requested technical support has no staff assigned should be blocked</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>All events of "Tech Conference 2026" have confirmed venues and full equipment, but the event's technical support request has no staff assigned</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Tech Conference 2026"
   3. Click "Confirm Event"</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr">
+      <c r="I187" s="2" t="inlineStr">
         <is>
           <t>the event: technical support requested, no staff assigned</t>
         </is>
       </c>
-      <c r="J182" s="2" t="inlineStr">
+      <c r="J187" s="2" t="inlineStr">
         <is>
           <t>Confirmation is blocked due to the event's outstanding technical support assignment</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="n">
+    <row r="188">
+      <c r="A188" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
+      <c r="C188" s="2" t="inlineStr">
         <is>
           <t>E08-S03 - Scenario 6 (Organiser sees confirmed arrangements)</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>TC_E08S03_05</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>Verify that once an event is confirmed, the Organiser should see the confirmed venue, date, time and arrangements for every event</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has just been confirmed, with venue Riverside Hall, date 15/01/2027, time 09:00-17:00</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the confirmed event "Charity Run"</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr">
+      <c r="I188" s="2" t="inlineStr">
         <is>
           <t>Confirmed venue: Riverside Hall | Date: 15/01/2027 | Time: 09:00-17:00</t>
         </is>
       </c>
-      <c r="J183" s="2" t="inlineStr">
+      <c r="J188" s="2" t="inlineStr">
         <is>
           <t>The Organiser sees the confirmed venue (Riverside Hall), date (15/01/2027), time (09:00-17:00), and full arrangements for the event</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="n">
+    <row r="189">
+      <c r="A189" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
+      <c r="C189" s="2" t="inlineStr">
         <is>
           <t>E08-S03 — Scenario 2 (Missing venue blocks confirmation); assumes O-28</t>
         </is>
       </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>4 - Negative (business rule)</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>TC_E08S03_06</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>Verify that confirming an event with several venue bookings should be blocked while any booking is still Pending or Conflicting, listing each outstanding booking by venue</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Summit" has "Grand Auditorium" Confirmed, "Seminar Room A" Confirmed and "Seminar Room B" Pending; equipment fully reserved; technical support assigned; coordinator_1@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>1. Open "Tech Summit" and click "Confirm event"</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr">
+      <c r="I189" s="2" t="inlineStr">
         <is>
           <t>Two Confirmed bookings, one Pending</t>
         </is>
       </c>
-      <c r="J184" s="2" t="inlineStr">
+      <c r="J189" s="2" t="inlineStr">
         <is>
           <t>Confirmation is blocked; the outstanding-items list names "Seminar Room B" (Pending) and nothing else; the event stays in Planning</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="n">
+    <row r="190">
+      <c r="A190" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
+      <c r="C190" s="2" t="inlineStr">
         <is>
           <t>E08-S03 — Scenario 1 (All arrangements complete, event confirmed); Scenario 6 (Organiser sees confirmed arrangements); assumes O-28</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>TC_E08S03_07</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>Verify that an event should be confirmable once every venue booking is Confirmed or withdrawn and the Organiser should see every confirmed venue</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr">
         <is>
           <t>As TC_E08S03_06; organiser_1@connectsphere.com owns the event</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t>1. As venue_staff_1, approve the "Seminar Room B" request
   2. As coordinator_1, click "Confirm event"
   3. As organiser_1, open "Tech Summit"</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr">
+      <c r="I190" s="2" t="inlineStr">
         <is>
           <t>Three Confirmed bookings: Grand Auditorium 09:00-18:00 Main programme; Seminar Room A and B 14:00-16:00 Breakout A/B</t>
         </is>
       </c>
-      <c r="J185" s="2" t="inlineStr">
+      <c r="J190" s="2" t="inlineStr">
         <is>
           <t>The event becomes Confirmed and organiser_1 is notified; the Organiser's view lists all three venues with their purpose and period
 ## E08-S04</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="n">
+    <row r="191">
+      <c r="A191" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
+      <c r="C191" s="2" t="inlineStr">
         <is>
           <t>E08-S04 - Scenario 1 (Reverted with a recorded reason)</t>
         </is>
       </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>TC_E08S04_01</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>Verify that reverting a Confirmed event to Planning with a recorded reason should update its status and notify the Organiser with the reason</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr">
         <is>
           <t>Event "Leadership Summit" has status "Confirmed"</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Leadership Summit"
@@ -10203,52 +10463,52 @@
   5. Confirm</t>
         </is>
       </c>
-      <c r="I186" s="2" t="inlineStr">
+      <c r="I191" s="2" t="inlineStr">
         <is>
           <t>Reason: "Venue reported a plumbing issue"</t>
         </is>
       </c>
-      <c r="J186" s="2" t="inlineStr">
+      <c r="J191" s="2" t="inlineStr">
         <is>
           <t>The status changes to "Planning", and organiser_a@clienta.com is notified with the reason "Venue reported a plumbing issue"</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="n">
+    <row r="192">
+      <c r="A192" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B187" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
+      <c r="C192" s="2" t="inlineStr">
         <is>
           <t>E08-S04 - Scenario 2 (Registered Attendees notified)</t>
         </is>
       </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>TC_E08S04_02</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>Verify that reverting a Confirmed event with registered Attendees should notify them that arrangements are being revised</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr">
         <is>
           <t>Event "Leadership Summit" has status "Confirmed" with attendee_a@example.com registered</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Leadership Summit"
@@ -10256,413 +10516,413 @@
   4. Check attendee_a@example.com's notifications</t>
         </is>
       </c>
-      <c r="I187" s="2" t="inlineStr">
+      <c r="I192" s="2" t="inlineStr">
         <is>
           <t>Registered Attendee: attendee_a@example.com</t>
         </is>
       </c>
-      <c r="J187" s="2" t="inlineStr">
+      <c r="J192" s="2" t="inlineStr">
         <is>
           <t>attendee_a@example.com receives a notification that arrangements for "Leadership Summit" are being revised</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="n">
+    <row r="193">
+      <c r="A193" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B188" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
+      <c r="C193" s="2" t="inlineStr">
         <is>
           <t>E08-S04 - Scenario 3 (No automatic reversion)</t>
         </is>
       </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>TC_E08S04_03</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>Verify that an arrangement breaking on a Confirmed event should not automatically revert its status; the affected arrangement should instead be flagged</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr">
         <is>
           <t>Event "Leadership Summit" has status "Confirmed"; its venue booking has just been flagged due to a broken arrangement, but no one has reverted the event</t>
         </is>
       </c>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Leadership Summit"
   3. Check the event status and the flagged arrangement</t>
         </is>
       </c>
-      <c r="I188" s="2" t="inlineStr">
+      <c r="I193" s="2" t="inlineStr">
         <is>
           <t>Flagged arrangement: venue booking</t>
         </is>
       </c>
-      <c r="J188" s="2" t="inlineStr">
+      <c r="J193" s="2" t="inlineStr">
         <is>
           <t>The event status remains "Confirmed"; the affected venue booking is shown flagged, but no automatic status change has occurred</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="n">
+    <row r="194">
+      <c r="A194" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B189" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
+      <c r="C194" s="2" t="inlineStr">
         <is>
           <t>E08-S04 (checklist: reversion recorded in activity log)</t>
         </is>
       </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting (audit logging)</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>TC_E08S04_04</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>Verify that a reversion from Confirmed to Planning should be recorded in the activity log</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr">
         <is>
           <t>Event "Leadership Summit" has just been reverted from "Confirmed" to "Planning" by coordinator_1@connectsphere.com</t>
         </is>
       </c>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>1. Log in as a System Administrator
   2. Open the Activity Log and search for "Leadership Summit"</t>
         </is>
       </c>
-      <c r="I189" s="2" t="inlineStr">
+      <c r="I194" s="2" t="inlineStr">
         <is>
           <t>Event: Leadership Summit</t>
         </is>
       </c>
-      <c r="J189" s="2" t="inlineStr">
+      <c r="J194" s="2" t="inlineStr">
         <is>
           <t>An activity log entry exists recording the reversion, with actor = coordinator_1@connectsphere.com, action = "Reverted to Planning", and a timestamp
 ## E08-S05</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="n">
+    <row r="195">
+      <c r="A195" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="C195" s="2" t="inlineStr">
         <is>
           <t>E08-S05 - Scenario 1 (Auto-completed after the end time)</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_01</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>Verify that a Confirmed event should automatically become Completed once its last event's end time has passed</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has status "Confirmed"; its only event ended at 17:00 on 15/01/2027, which has now passed</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>1. Wait for (or trigger) the system's next scheduled evaluation after 17:00 on 15/01/2027
   2. Open event "Charity Run" and check its status</t>
         </is>
       </c>
-      <c r="I190" s="2" t="inlineStr">
+      <c r="I195" s="2" t="inlineStr">
         <is>
           <t>Event end time: 17:00, 15/01/2027 (passed)</t>
         </is>
       </c>
-      <c r="J190" s="2" t="inlineStr">
+      <c r="J195" s="2" t="inlineStr">
         <is>
           <t>The event status has automatically changed to "Completed"</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="n">
+    <row r="196">
+      <c r="A196" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B191" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
+      <c r="C196" s="2" t="inlineStr">
         <is>
           <t>E08-S05 - Scenario 2 (Marked complete manually)</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_02</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Coordinator should be able to manually mark a Confirmed event complete once its last event has started</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr">
         <is>
           <t>Event "Volunteer Training Day" has status "Confirmed"; its last (only) event started at 09:00 today and is still in progress</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Volunteer Training Day"
   3. Click "Mark Complete"</t>
         </is>
       </c>
-      <c r="I191" s="2" t="inlineStr">
+      <c r="I196" s="2" t="inlineStr">
         <is>
           <t>Event started: 09:00 today</t>
         </is>
       </c>
-      <c r="J191" s="2" t="inlineStr">
+      <c r="J196" s="2" t="inlineStr">
         <is>
           <t>The event status changes to "Completed"</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="n">
+    <row r="197">
+      <c r="A197" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B192" s="2" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
+      <c r="C197" s="2" t="inlineStr">
         <is>
           <t>E08-S05 - Scenario 3 (Premature completion blocked)</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_03</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to mark an event complete before its first event has started should be blocked</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has status "Confirmed"; its first event has not yet started</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Tech Conference 2026"
   3. Attempt to click "Mark Complete"</t>
         </is>
       </c>
-      <c r="I192" s="2" t="inlineStr">
+      <c r="I197" s="2" t="inlineStr">
         <is>
           <t>First event: not yet started</t>
         </is>
       </c>
-      <c r="J192" s="2" t="inlineStr">
+      <c r="J197" s="2" t="inlineStr">
         <is>
           <t>The action is blocked; the event cannot be marked complete before it has started</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="n">
+    <row r="198">
+      <c r="A198" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B193" s="2" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C193" s="2" t="inlineStr">
+      <c r="C198" s="2" t="inlineStr">
         <is>
           <t>E08-S05 - Scenario 4 (Cancelled event never auto-completes)</t>
         </is>
       </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_04</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>Verify that a Cancelled event should never auto-complete, even after its original end time passes</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr">
         <is>
           <t>Event "Product Launch Night" has status "Cancelled" (per TC_E10S04_01); its original end time has now passed</t>
         </is>
       </c>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>1. Wait for (or trigger) the system's next scheduled evaluation after "Product Launch Night"'s original end time
   2. Open event "Product Launch Night" and check its status</t>
         </is>
       </c>
-      <c r="I193" s="2" t="inlineStr">
+      <c r="I198" s="2" t="inlineStr">
         <is>
           <t>Original end time: passed</t>
         </is>
       </c>
-      <c r="J193" s="2" t="inlineStr">
+      <c r="J198" s="2" t="inlineStr">
         <is>
           <t>The event status remains "Cancelled"; it has not been auto-completed</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="n">
+    <row r="199">
+      <c r="A199" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B194" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
+      <c r="C199" s="2" t="inlineStr">
         <is>
           <t>E08-S05 (checklist: transition to Completed logged)</t>
         </is>
       </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting (audit logging)</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_05</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>Verify that an event's transition to Completed should be recorded in the activity log</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has just transitioned to "Completed" (per TC_E08S05_01)</t>
         </is>
       </c>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>1. Log in as a System Administrator
   2. Open the Activity Log and search for "Charity Run"</t>
         </is>
       </c>
-      <c r="I194" s="2" t="inlineStr">
+      <c r="I199" s="2" t="inlineStr">
         <is>
           <t>Event: Charity Run</t>
         </is>
       </c>
-      <c r="J194" s="2" t="inlineStr">
+      <c r="J199" s="2" t="inlineStr">
         <is>
           <t>An activity log entry exists recording the transition to "Completed", with the time it occurred</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="n">
+    <row r="200">
+      <c r="A200" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B195" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C195" s="2" t="inlineStr">
+      <c r="C200" s="2" t="inlineStr">
         <is>
           <t>E08-S05 · Scenario 1 (Auto-completed after the end time)</t>
         </is>
       </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_06</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>Verify that an event auto-completes at the exact end time and not before</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2002 is Confirmed and its end time is 2026-11-02 17:00:00 +08:00</t>
         </is>
       </c>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>1. Set the system clock to 2026-11-02 16:59:59 +08:00 and trigger the completion evaluation
  2. Record the event status
@@ -10670,52 +10930,52 @@
  4. Record the event status</t>
         </is>
       </c>
-      <c r="I195" s="2" t="inlineStr">
+      <c r="I200" s="2" t="inlineStr">
         <is>
           <t>Event ends: 2026-11-02 17:00:00 +08:00 · Evaluations at 16:59:59 and 17:00:00</t>
         </is>
       </c>
-      <c r="J195" s="2" t="inlineStr">
+      <c r="J200" s="2" t="inlineStr">
         <is>
           <t>At 16:59:59 the status remains Confirmed. At 17:00:00 the status becomes Completed and the transition is recorded in the activity log</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="n">
+    <row r="201">
+      <c r="A201" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B196" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C196" s="2" t="inlineStr">
+      <c r="C201" s="2" t="inlineStr">
         <is>
           <t>E09-S01 - Scenario 1 (Place reserved in an open event)</t>
         </is>
       </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_01</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting the required registration information for an open event with places remaining should reserve a place and provide a confirmation</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" is Confirmed, registration is open, and 3 of 5 places remain in its event</t>
         </is>
       </c>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Open event "Community Meetup"
@@ -10723,52 +10983,52 @@
   4. Submit registration</t>
         </is>
       </c>
-      <c r="I196" s="2" t="inlineStr">
+      <c r="I201" s="2" t="inlineStr">
         <is>
           <t>Name: Casey Tan | Email: attendee_c@example.com</t>
         </is>
       </c>
-      <c r="J196" s="2" t="inlineStr">
+      <c r="J201" s="2" t="inlineStr">
         <is>
           <t>attendee_c@example.com's place is reserved, and they receive a confirmation containing the event's details (date, time, venue)</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="n">
+    <row r="202">
+      <c r="A202" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B197" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C197" s="2" t="inlineStr">
+      <c r="C202" s="2" t="inlineStr">
         <is>
           <t>E09-S01 (checklist: choose events to attend in a multi-event event)</t>
         </is>
       </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_02</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>Verify that registering for a multi-event event should let the Attendee choose which events to attend, reserving a place in each chosen event</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has the event and the event, both open for registration</t>
         </is>
       </c>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_d@example.com
   2. Open event "Tech Conference 2026"
@@ -10776,104 +11036,104 @@
   4. Submit registration</t>
         </is>
       </c>
-      <c r="I197" s="2" t="inlineStr">
+      <c r="I202" s="2" t="inlineStr">
         <is>
           <t>Selected: the event only</t>
         </is>
       </c>
-      <c r="J197" s="2" t="inlineStr">
+      <c r="J202" s="2" t="inlineStr">
         <is>
           <t>A place is reserved for attendee_d@example.com in the event only; they are not registered for the event</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="n">
+    <row r="203">
+      <c r="A203" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B198" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C198" s="2" t="inlineStr">
+      <c r="C203" s="2" t="inlineStr">
         <is>
           <t>E09-S01 - Scenario 2 (Duplicate registration prevented)</t>
         </is>
       </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_03</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to register again for a event already registered for should be told so, without creating a duplicate</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr">
         <is>
           <t>attendee_c@example.com is already registered for "Community Meetup"'s event</t>
         </is>
       </c>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Open event "Community Meetup"
   3. Attempt to register again</t>
         </is>
       </c>
-      <c r="I198" s="2" t="inlineStr">
+      <c r="I203" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_c@example.com (already registered)</t>
         </is>
       </c>
-      <c r="J198" s="2" t="inlineStr">
+      <c r="J203" s="2" t="inlineStr">
         <is>
           <t>attendee_c@example.com is told they are already registered; no duplicate registration is created</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="n">
+    <row r="204">
+      <c r="A204" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B199" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr">
+      <c r="C204" s="2" t="inlineStr">
         <is>
           <t>E09-S01 - Scenario 3 (Missing fields identified)</t>
         </is>
       </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_04</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting registration with a required field empty should block registration and identify the missing fields</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" is open for registration</t>
         </is>
       </c>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_e@example.com
   2. Open event "Community Meetup"
@@ -10881,361 +11141,361 @@
   4. Submit registration</t>
         </is>
       </c>
-      <c r="I199" s="2" t="inlineStr">
+      <c r="I204" s="2" t="inlineStr">
         <is>
           <t>Name: filled | Email: (blank)</t>
         </is>
       </c>
-      <c r="J199" s="2" t="inlineStr">
+      <c r="J204" s="2" t="inlineStr">
         <is>
           <t>Registration is blocked, and the Email field is identified as missing</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="n">
+    <row r="205">
+      <c r="A205" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B200" s="2" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C200" s="2" t="inlineStr">
+      <c r="C205" s="2" t="inlineStr">
         <is>
           <t>E09-S01 - Scenario 4 (Unconfirmed event refused)</t>
         </is>
       </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_05</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to register for an event that is not Confirmed should be refused</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr">
         <is>
           <t>Event "Draft Networking Event" has status "Planning" (not yet Confirmed)</t>
         </is>
       </c>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Attempt to open the registration form for "Draft Networking Event"</t>
         </is>
       </c>
-      <c r="I200" s="2" t="inlineStr">
+      <c r="I205" s="2" t="inlineStr">
         <is>
           <t>Event status: Planning</t>
         </is>
       </c>
-      <c r="J200" s="2" t="inlineStr">
+      <c r="J205" s="2" t="inlineStr">
         <is>
           <t>Registration is refused, since the event is not yet Confirmed</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="n">
+    <row r="206">
+      <c r="A206" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B201" s="2" t="inlineStr">
+      <c r="B206" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr">
+      <c r="C206" s="2" t="inlineStr">
         <is>
           <t>E09-S01 — Scenario 5 (One venue shown for a multi-venue event); assumes O-30</t>
         </is>
       </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_06</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>Verify that an Attendee viewing a multi-venue event should see only the primary venue</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Summit" is Confirmed with three Confirmed venue bookings and "Grand Auditorium" marked primary; registration is open; attendee_1@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>1. Open "Tech Summit" from the attendee event list
   2. Read the venue shown
   3. Register</t>
         </is>
       </c>
-      <c r="I201" s="2" t="inlineStr">
+      <c r="I206" s="2" t="inlineStr">
         <is>
           <t>Primary: Grand Auditorium | Others: Seminar Room A, Seminar Room B</t>
         </is>
       </c>
-      <c r="J201" s="2" t="inlineStr">
+      <c r="J206" s="2" t="inlineStr">
         <is>
           <t>The event page shows "Grand Auditorium" as the venue; Seminar Rooms A and B are not offered as separate registration options; registration succeeds once as in TC_E09S01_01
 ## E09-S02</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="n">
+    <row r="207">
+      <c r="A207" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B202" s="2" t="inlineStr">
+      <c r="B207" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C202" s="2" t="inlineStr">
+      <c r="C207" s="2" t="inlineStr">
         <is>
           <t>E09-S02 (checklist: set a registration limit)</t>
         </is>
       </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_01</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F207" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Organiser should be able to set a registration limit for a event</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is signed in; event "Community Meetup"'s event has no registration limit set yet</t>
         </is>
       </c>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="H207" s="2" t="inlineStr">
         <is>
           <t>1. Open event "Community Meetup"
   2. Set the Registration Limit for its event to 5
   3. Save</t>
         </is>
       </c>
-      <c r="I202" s="2" t="inlineStr">
+      <c r="I207" s="2" t="inlineStr">
         <is>
           <t>Registration Limit: 5</t>
         </is>
       </c>
-      <c r="J202" s="2" t="inlineStr">
+      <c r="J207" s="2" t="inlineStr">
         <is>
           <t>The event's registration limit is saved as 5</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="n">
+    <row r="208">
+      <c r="A208" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B203" s="2" t="inlineStr">
+      <c r="B208" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C203" s="2" t="inlineStr">
+      <c r="C208" s="2" t="inlineStr">
         <is>
           <t>E09-S02 - Scenario 1 (Venue capacity enforced)</t>
         </is>
       </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="D208" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_02</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F208" s="2" t="inlineStr">
         <is>
           <t>Verify that registration should stop once the event reaches the lower of the Organiser's limit and the booked venue's capacity</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr">
+      <c r="G208" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s event has an Organiser-set limit of 5 and a booked venue capacity of 8 (the limit is the lower value); 5 Attendees are already registered</t>
         </is>
       </c>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="H208" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_f@example.com
   2. Attempt to register for "Community Meetup"</t>
         </is>
       </c>
-      <c r="I203" s="2" t="inlineStr">
+      <c r="I208" s="2" t="inlineStr">
         <is>
           <t>Registered so far: 5 (effective limit) | Venue capacity: 8</t>
         </is>
       </c>
-      <c r="J203" s="2" t="inlineStr">
+      <c r="J208" s="2" t="inlineStr">
         <is>
           <t>Registration is refused since the event has reached its effective capacity of 5</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="n">
+    <row r="209">
+      <c r="A209" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B204" s="2" t="inlineStr">
+      <c r="B209" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C204" s="2" t="inlineStr">
+      <c r="C209" s="2" t="inlineStr">
         <is>
           <t>E09-S02 - Scenario 2 (Simultaneous final registration)</t>
         </is>
       </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="D209" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (last place, concurrency)</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_03</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F209" s="2" t="inlineStr">
         <is>
           <t>Verify that when only one place remains, two simultaneous registration attempts should result in exactly one success</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s event has exactly 1 place remaining</t>
         </is>
       </c>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="H209" s="2" t="inlineStr">
         <is>
           <t>1. Have attendee_g@example.com and attendee_h@example.com submit registration for the same event at the same moment
   2. Check both outcomes</t>
         </is>
       </c>
-      <c r="I204" s="2" t="inlineStr">
+      <c r="I209" s="2" t="inlineStr">
         <is>
           <t>1 place remaining | 2 simultaneous attempts</t>
         </is>
       </c>
-      <c r="J204" s="2" t="inlineStr">
+      <c r="J209" s="2" t="inlineStr">
         <is>
           <t>Exactly one of the two registrations succeeds; the other is told the event is full</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="n">
+    <row r="210">
+      <c r="A210" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B205" s="2" t="inlineStr">
+      <c r="B210" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C205" s="2" t="inlineStr">
+      <c r="C210" s="2" t="inlineStr">
         <is>
           <t>E09-S02 - Scenario 3 (Full event offers the waiting list)</t>
         </is>
       </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_04</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>Verify that opening the registration page for a full event should close registration and offer the waiting list where enabled</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr">
+      <c r="G210" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s event is full (5 of 5 places taken); the waiting list is enabled for this event</t>
         </is>
       </c>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="H210" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_i@example.com
   2. Open the registration page for "Community Meetup"</t>
         </is>
       </c>
-      <c r="I205" s="2" t="inlineStr">
+      <c r="I210" s="2" t="inlineStr">
         <is>
           <t>Event: full | Waiting list: enabled</t>
         </is>
       </c>
-      <c r="J205" s="2" t="inlineStr">
+      <c r="J210" s="2" t="inlineStr">
         <is>
           <t>Registration is shown as closed, and the option to join the waiting list is offered</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="n">
+    <row r="211">
+      <c r="A211" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B206" s="2" t="inlineStr">
+      <c r="B211" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C206" s="2" t="inlineStr">
+      <c r="C211" s="2" t="inlineStr">
         <is>
           <t>E09-S02 · Scenario 4 (VIP added beyond normal registration)</t>
         </is>
       </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (just below venue capacity)</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_06</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>Verify that a VIP can be added manually when normal registration is full but venue capacity is not reached</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr">
+      <c r="G211" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with Orchid Hall booked, venue capacity 200. Normal registration has closed at 199 registrations. Coordinator coord_a@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="H211" s="2" t="inlineStr">
         <is>
           <t>1. Open event EVT-2001
  2. Select Add attendee manually
@@ -11243,52 +11503,52 @@
  4. Confirm the addition</t>
         </is>
       </c>
-      <c r="I206" s="2" t="inlineStr">
+      <c r="I211" s="2" t="inlineStr">
         <is>
           <t>Venue capacity: 200 · Current registrations: 199 · Added: 1</t>
         </is>
       </c>
-      <c r="J206" s="2" t="inlineStr">
+      <c r="J211" s="2" t="inlineStr">
         <is>
           <t>The registration is created, total registrations reach 200, and the record is marked as a manual addition distinguishable from a normal registration</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="n">
+    <row r="212">
+      <c r="A212" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B207" s="2" t="inlineStr">
+      <c r="B212" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C207" s="2" t="inlineStr">
+      <c r="C212" s="2" t="inlineStr">
         <is>
           <t>E09-S02 · Scenario 5 (VIP blocked at venue capacity)</t>
         </is>
       </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at venue capacity)</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_07</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="F212" s="2" t="inlineStr">
         <is>
           <t>Verify that a manual VIP addition is blocked once total registrations equal venue capacity</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr">
+      <c r="G212" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with Orchid Hall booked, venue capacity 200, and 200 registrations already recorded. Coordinator coord_a@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="H212" s="2" t="inlineStr">
         <is>
           <t>1. Open event EVT-2001
  2. Select Add attendee manually
@@ -11296,310 +11556,310 @@
  4. Confirm the addition</t>
         </is>
       </c>
-      <c r="I207" s="2" t="inlineStr">
+      <c r="I212" s="2" t="inlineStr">
         <is>
           <t>Venue capacity: 200 · Current registrations: 200</t>
         </is>
       </c>
-      <c r="J207" s="2" t="inlineStr">
+      <c r="J212" s="2" t="inlineStr">
         <is>
           <t>The addition is blocked with a message stating the booked venue capacity has been reached. No registration is created
 ## E09-S03</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="n">
+    <row r="213">
+      <c r="A213" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B208" s="2" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C208" s="2" t="inlineStr">
+      <c r="C213" s="2" t="inlineStr">
         <is>
           <t>E09-S03 (checklist: set registration opening/closing dates)</t>
         </is>
       </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_01</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="F213" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Organiser should be able to set the registration opening and closing dates for an event</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr">
+      <c r="G213" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is signed in; event "Community Meetup" has no registration dates set</t>
         </is>
       </c>
-      <c r="H208" s="2" t="inlineStr">
+      <c r="H213" s="2" t="inlineStr">
         <is>
           <t>1. Open event "Community Meetup"
   2. Set Registration Opens: 01/10/2026, Registration Closes: 01/12/2026
   3. Save</t>
         </is>
       </c>
-      <c r="I208" s="2" t="inlineStr">
+      <c r="I213" s="2" t="inlineStr">
         <is>
           <t>Opens: 01/10/2026 | Closes: 01/12/2026</t>
         </is>
       </c>
-      <c r="J208" s="2" t="inlineStr">
+      <c r="J213" s="2" t="inlineStr">
         <is>
           <t>The registration opening and closing dates are saved as entered</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2" t="n">
+    <row r="214">
+      <c r="A214" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B209" s="2" t="inlineStr">
+      <c r="B214" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C209" s="2" t="inlineStr">
+      <c r="C214" s="2" t="inlineStr">
         <is>
           <t>E09-S03 (checklist: set a withdrawal deadline)</t>
         </is>
       </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="D214" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E214" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_02</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F214" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Organiser should be able to set a withdrawal deadline for an event</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr">
+      <c r="G214" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is signed in; event "Community Meetup" has no withdrawal deadline set</t>
         </is>
       </c>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="H214" s="2" t="inlineStr">
         <is>
           <t>1. Open event "Community Meetup"
   2. Set Withdrawal Deadline: 10/12/2026
   3. Save</t>
         </is>
       </c>
-      <c r="I209" s="2" t="inlineStr">
+      <c r="I214" s="2" t="inlineStr">
         <is>
           <t>Withdrawal Deadline: 10/12/2026</t>
         </is>
       </c>
-      <c r="J209" s="2" t="inlineStr">
+      <c r="J214" s="2" t="inlineStr">
         <is>
           <t>The withdrawal deadline is saved as 10/12/2026</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="2" t="n">
+    <row r="215">
+      <c r="A215" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B210" s="2" t="inlineStr">
+      <c r="B215" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C210" s="2" t="inlineStr">
+      <c r="C215" s="2" t="inlineStr">
         <is>
           <t>E09-S03 - Scenario 1 (Before registration opens)</t>
         </is>
       </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="D215" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (before)</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E215" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_03</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="F215" s="2" t="inlineStr">
         <is>
           <t>Verify that an Attendee viewing an event before its registration opening date should see registration as not yet open, with the opening date stated</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr">
+      <c r="G215" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s registration opening date (01/10/2026) has not yet been reached</t>
         </is>
       </c>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="H215" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Open event "Community Meetup"</t>
         </is>
       </c>
-      <c r="I210" s="2" t="inlineStr">
+      <c r="I215" s="2" t="inlineStr">
         <is>
           <t>Opening date: 01/10/2026 (not reached)</t>
         </is>
       </c>
-      <c r="J210" s="2" t="inlineStr">
+      <c r="J215" s="2" t="inlineStr">
         <is>
           <t>Registration is shown as "Not yet open", with the message stating it opens on 01/10/2026</t>
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="2" t="n">
+    <row r="216">
+      <c r="A216" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B211" s="2" t="inlineStr">
+      <c r="B216" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C211" s="2" t="inlineStr">
+      <c r="C216" s="2" t="inlineStr">
         <is>
           <t>E09-S03 - Scenario 2 (After registration closes)</t>
         </is>
       </c>
-      <c r="D211" s="2" t="inlineStr">
+      <c r="D216" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (after)</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_04</t>
         </is>
       </c>
-      <c r="F211" s="2" t="inlineStr">
+      <c r="F216" s="2" t="inlineStr">
         <is>
           <t>Verify that an Attendee trying to register after the registration closing date has passed should be refused</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr">
+      <c r="G216" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s registration closing date (01/12/2026) has passed</t>
         </is>
       </c>
-      <c r="H211" s="2" t="inlineStr">
+      <c r="H216" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Attempt to register for "Community Meetup"</t>
         </is>
       </c>
-      <c r="I211" s="2" t="inlineStr">
+      <c r="I216" s="2" t="inlineStr">
         <is>
           <t>Closing date: 01/12/2026 (passed)</t>
         </is>
       </c>
-      <c r="J211" s="2" t="inlineStr">
+      <c r="J216" s="2" t="inlineStr">
         <is>
           <t>Registration is refused, since the closing date has passed</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="2" t="n">
+    <row r="217">
+      <c r="A217" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B212" s="2" t="inlineStr">
+      <c r="B217" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C212" s="2" t="inlineStr">
+      <c r="C217" s="2" t="inlineStr">
         <is>
           <t>E09-S03 - Scenario 3 (Closing date after event start warned)</t>
         </is>
       </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_05</t>
         </is>
       </c>
-      <c r="F212" s="2" t="inlineStr">
+      <c r="F217" s="2" t="inlineStr">
         <is>
           <t>Verify that setting a registration closing date that falls after the event has started should warn the Organiser and ask them to confirm</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr">
+      <c r="G217" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is editing event "Community Meetup", which starts on 15/11/2026</t>
         </is>
       </c>
-      <c r="H212" s="2" t="inlineStr">
+      <c r="H217" s="2" t="inlineStr">
         <is>
           <t>1. Set Registration Closes: 20/11/2026 (after the event's start date)
   2. Click "Save"</t>
         </is>
       </c>
-      <c r="I212" s="2" t="inlineStr">
+      <c r="I217" s="2" t="inlineStr">
         <is>
           <t>Closing date: 20/11/2026 (after event start 15/11/2026)</t>
         </is>
       </c>
-      <c r="J212" s="2" t="inlineStr">
+      <c r="J217" s="2" t="inlineStr">
         <is>
           <t>A warning is shown asking the Organiser to confirm this is intended, before the closing date is saved</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="2" t="n">
+    <row r="218">
+      <c r="A218" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B213" s="2" t="inlineStr">
+      <c r="B218" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C213" s="2" t="inlineStr">
+      <c r="C218" s="2" t="inlineStr">
         <is>
           <t>E09-S03 - Scenario 4 (Waiting list enabled)</t>
         </is>
       </c>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_06</t>
         </is>
       </c>
-      <c r="F213" s="2" t="inlineStr">
+      <c r="F218" s="2" t="inlineStr">
         <is>
           <t>Verify that enabling the waiting list for an event should offer it to Attendees once a event becomes full</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr">
+      <c r="G218" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is about to enable the waiting list for event "Community Meetup"</t>
         </is>
       </c>
-      <c r="H213" s="2" t="inlineStr">
+      <c r="H218" s="2" t="inlineStr">
         <is>
           <t>1. Open event "Community Meetup"
   2. Toggle "Enable Waiting List" on
@@ -11607,363 +11867,363 @@
   4. Fill the event to capacity and attempt a further registration</t>
         </is>
       </c>
-      <c r="I213" s="2" t="inlineStr">
+      <c r="I218" s="2" t="inlineStr">
         <is>
           <t>Waiting List: Enabled</t>
         </is>
       </c>
-      <c r="J213" s="2" t="inlineStr">
+      <c r="J218" s="2" t="inlineStr">
         <is>
           <t>Once the event is full, the further registration attempt is offered the waiting list instead of being simply refused</t>
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="2" t="n">
+    <row r="219">
+      <c r="A219" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B214" s="2" t="inlineStr">
+      <c r="B219" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C214" s="2" t="inlineStr">
+      <c r="C219" s="2" t="inlineStr">
         <is>
           <t>E09-S03 · Scenario 1 (Before registration opens)</t>
         </is>
       </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="D219" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_07</t>
         </is>
       </c>
-      <c r="F214" s="2" t="inlineStr">
+      <c r="F219" s="2" t="inlineStr">
         <is>
           <t>Verify that registration succeeds at the exact opening timestamp</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr">
+      <c r="G219" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with registration opening at 2026-10-01 09:00:00 +08:00. Attendee attendee_a@example.com is signed in. Event EVT-2001 has places remaining</t>
         </is>
       </c>
-      <c r="H214" s="2" t="inlineStr">
+      <c r="H219" s="2" t="inlineStr">
         <is>
           <t>1. Set the system clock to exactly 2026-10-01 09:00:00 +08:00
  2. Open event EVT-2001
  3. Select event EVT-2001 and submit registration</t>
         </is>
       </c>
-      <c r="I214" s="2" t="inlineStr">
+      <c r="I219" s="2" t="inlineStr">
         <is>
           <t>Registration opens: 2026-10-01 09:00:00 +08:00 · Attempt at: 2026-10-01 09:00:00 +08:00</t>
         </is>
       </c>
-      <c r="J214" s="2" t="inlineStr">
+      <c r="J219" s="2" t="inlineStr">
         <is>
           <t>Registration succeeds and a place is reserved. The opening moment is inclusive: registration is open at, not after, the opening timestamp</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="2" t="n">
+    <row r="220">
+      <c r="A220" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B215" s="2" t="inlineStr">
+      <c r="B220" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C215" s="2" t="inlineStr">
+      <c r="C220" s="2" t="inlineStr">
         <is>
           <t>E09-S03 · Scenario 2 (After registration closes)</t>
         </is>
       </c>
-      <c r="D215" s="2" t="inlineStr">
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_08</t>
         </is>
       </c>
-      <c r="F215" s="2" t="inlineStr">
+      <c r="F220" s="2" t="inlineStr">
         <is>
           <t>Verify that registration still succeeds at the exact closing timestamp</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr">
+      <c r="G220" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with registration closing at 2026-10-20 17:00:00 +08:00. Attendee attendee_b@example.com is signed in. Event EVT-2001 has places remaining</t>
         </is>
       </c>
-      <c r="H215" s="2" t="inlineStr">
+      <c r="H220" s="2" t="inlineStr">
         <is>
           <t>1. Set the system clock to exactly 2026-10-20 17:00:00 +08:00
  2. Open event EVT-2001
  3. Select event EVT-2001 and submit registration</t>
         </is>
       </c>
-      <c r="I215" s="2" t="inlineStr">
+      <c r="I220" s="2" t="inlineStr">
         <is>
           <t>Registration closes: 2026-10-20 17:00:00 +08:00 · Attempt at: 2026-10-20 17:00:00 +08:00</t>
         </is>
       </c>
-      <c r="J215" s="2" t="inlineStr">
+      <c r="J220" s="2" t="inlineStr">
         <is>
           <t>Registration succeeds. The acceptance criterion refuses registration once the closing date "has passed", so at the exact closing instant it has not yet passed. One second later the same attempt must be refused
 ## E09-S04</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2" t="n">
+    <row r="221">
+      <c r="A221" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B216" s="2" t="inlineStr">
+      <c r="B221" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C216" s="2" t="inlineStr">
+      <c r="C221" s="2" t="inlineStr">
         <is>
           <t>E09-S04 - Scenario 1 (Joined a full event's list)</t>
         </is>
       </c>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_01</t>
         </is>
       </c>
-      <c r="F216" s="2" t="inlineStr">
+      <c r="F221" s="2" t="inlineStr">
         <is>
           <t>Verify that joining the waiting list for a full event with the list enabled should add the Attendee and confirm their position</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr">
+      <c r="G221" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s event is full; the waiting list is enabled and currently empty</t>
         </is>
       </c>
-      <c r="H216" s="2" t="inlineStr">
+      <c r="H221" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_i@example.com
   2. Open the registration page for "Community Meetup"
   3. Click "Join Waiting List"</t>
         </is>
       </c>
-      <c r="I216" s="2" t="inlineStr">
+      <c r="I221" s="2" t="inlineStr">
         <is>
           <t>Waiting list: enabled, currently empty</t>
         </is>
       </c>
-      <c r="J216" s="2" t="inlineStr">
+      <c r="J221" s="2" t="inlineStr">
         <is>
           <t>attendee_i@example.com is added to the waiting list and shown their position (e.g. "Position 1")</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="2" t="n">
+    <row r="222">
+      <c r="A222" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B217" s="2" t="inlineStr">
+      <c r="B222" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C217" s="2" t="inlineStr">
+      <c r="C222" s="2" t="inlineStr">
         <is>
           <t>E09-S04 - Scenario 2 (Released place notified to all)</t>
         </is>
       </c>
-      <c r="D217" s="2" t="inlineStr">
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_02</t>
         </is>
       </c>
-      <c r="F217" s="2" t="inlineStr">
+      <c r="F222" s="2" t="inlineStr">
         <is>
           <t>Verify that when a place is released in a event with a waiting list, all waitlisted Attendees should be notified and the place claimed on a first-come, first-served basis</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr">
+      <c r="G222" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s waiting list has attendee_i@example.com (position 1) and attendee_j@example.com (position 2)</t>
         </is>
       </c>
-      <c r="H217" s="2" t="inlineStr">
+      <c r="H222" s="2" t="inlineStr">
         <is>
           <t>1. Have registered Attendee attendee_m@example.com withdraw from "Community Meetup", releasing one place
   2. Check notifications for attendee_i@example.com and attendee_j@example.com
   3. Have attendee_i@example.com claim the released place first</t>
         </is>
       </c>
-      <c r="I217" s="2" t="inlineStr">
+      <c r="I222" s="2" t="inlineStr">
         <is>
           <t>Waiting list: attendee_i@example.com (1st), attendee_j@example.com (2nd)</t>
         </is>
       </c>
-      <c r="J217" s="2" t="inlineStr">
+      <c r="J222" s="2" t="inlineStr">
         <is>
           <t>Both waitlisted Attendees are notified of the released place; attendee_i@example.com successfully claims it since they acted first</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="2" t="n">
+    <row r="223">
+      <c r="A223" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B218" s="2" t="inlineStr">
+      <c r="B223" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C218" s="2" t="inlineStr">
+      <c r="C223" s="2" t="inlineStr">
         <is>
           <t>E09-S04 - Scenario 3 (Claimed place leaves the list)</t>
         </is>
       </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="D223" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_03</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr">
+      <c r="F223" s="2" t="inlineStr">
         <is>
           <t>Verify that claiming a released place should remove the Attendee from the waiting list for that event</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr">
+      <c r="G223" s="2" t="inlineStr">
         <is>
           <t>attendee_i@example.com has just claimed a released place in "Community Meetup"'s event</t>
         </is>
       </c>
-      <c r="H218" s="2" t="inlineStr">
+      <c r="H223" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_i@example.com
   2. Check the waiting list for "Community Meetup"'s event</t>
         </is>
       </c>
-      <c r="I218" s="2" t="inlineStr">
+      <c r="I223" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_i@example.com (just claimed a place)</t>
         </is>
       </c>
-      <c r="J218" s="2" t="inlineStr">
+      <c r="J223" s="2" t="inlineStr">
         <is>
           <t>attendee_i@example.com no longer appears on the waiting list for that event, since they are now registered</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="2" t="n">
+    <row r="224">
+      <c r="A224" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B219" s="2" t="inlineStr">
+      <c r="B224" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C219" s="2" t="inlineStr">
+      <c r="C224" s="2" t="inlineStr">
         <is>
           <t>E09-S04 - Scenario 4 (Disabled list offers nothing)</t>
         </is>
       </c>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="D224" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_04</t>
         </is>
       </c>
-      <c r="F219" s="2" t="inlineStr">
+      <c r="F224" s="2" t="inlineStr">
         <is>
           <t>Verify that a full event should not offer a waiting list when the Organiser has disabled it</t>
         </is>
       </c>
-      <c r="G219" s="2" t="inlineStr">
+      <c r="G224" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has the waiting list disabled; the event is full</t>
         </is>
       </c>
-      <c r="H219" s="2" t="inlineStr">
+      <c r="H224" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_k@example.com
   2. Open the registration page for the event of "Tech Conference 2026"</t>
         </is>
       </c>
-      <c r="I219" s="2" t="inlineStr">
+      <c r="I224" s="2" t="inlineStr">
         <is>
           <t>Waiting list: disabled | the event: full</t>
         </is>
       </c>
-      <c r="J219" s="2" t="inlineStr">
+      <c r="J224" s="2" t="inlineStr">
         <is>
           <t>No waiting list option is offered; registration is simply shown as closed</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="2" t="n">
+    <row r="225">
+      <c r="A225" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B220" s="2" t="inlineStr">
+      <c r="B225" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C220" s="2" t="inlineStr">
+      <c r="C225" s="2" t="inlineStr">
         <is>
           <t>E09-S04 (checklist: leave the waiting list)</t>
         </is>
       </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_05</t>
         </is>
       </c>
-      <c r="F220" s="2" t="inlineStr">
+      <c r="F225" s="2" t="inlineStr">
         <is>
           <t>Verify that an Attendee should be able to voluntarily leave the waiting list before a place is released</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr">
+      <c r="G225" s="2" t="inlineStr">
         <is>
           <t>attendee_j@example.com is on the waiting list for "Community Meetup"'s event, position 2</t>
         </is>
       </c>
-      <c r="H220" s="2" t="inlineStr">
+      <c r="H225" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_j@example.com
   2. Open the waiting list status for "Community Meetup"
@@ -11971,622 +12231,622 @@
   4. Confirm</t>
         </is>
       </c>
-      <c r="I220" s="2" t="inlineStr">
+      <c r="I225" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_j@example.com</t>
         </is>
       </c>
-      <c r="J220" s="2" t="inlineStr">
+      <c r="J225" s="2" t="inlineStr">
         <is>
           <t>attendee_j@example.com is removed from the waiting list and no longer receives notifications about released places for that event
 ## E09-S05</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="2" t="n">
+    <row r="226">
+      <c r="A226" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B221" s="2" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="C221" s="2" t="inlineStr">
+      <c r="C226" s="2" t="inlineStr">
         <is>
           <t>E09-S05 - Scenario 1 (Registration withdrawn)</t>
         </is>
       </c>
-      <c r="D221" s="2" t="inlineStr">
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E221" s="2" t="inlineStr">
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>TC_E09S05_01</t>
         </is>
       </c>
-      <c r="F221" s="2" t="inlineStr">
+      <c r="F226" s="2" t="inlineStr">
         <is>
           <t>Verify that withdrawing from a single event before the withdrawal deadline should cancel that registration and release the place, leaving other events unaffected</t>
         </is>
       </c>
-      <c r="G221" s="2" t="inlineStr">
+      <c r="G226" s="2" t="inlineStr">
         <is>
           <t>attendee_d@example.com is registered for both the event and the event of "Tech Conference 2026"; the withdrawal deadline has not passed</t>
         </is>
       </c>
-      <c r="H221" s="2" t="inlineStr">
+      <c r="H226" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_d@example.com
   2. Open "My Registrations"
   3. Withdraw from the event only</t>
         </is>
       </c>
-      <c r="I221" s="2" t="inlineStr">
+      <c r="I226" s="2" t="inlineStr">
         <is>
           <t>Withdrawing from: the event only</t>
         </is>
       </c>
-      <c r="J221" s="2" t="inlineStr">
+      <c r="J226" s="2" t="inlineStr">
         <is>
           <t>The the event registration is cancelled and its place becomes available again; attendee_d@example.com remains registered for the event</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="2" t="n">
+    <row r="227">
+      <c r="A227" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B222" s="2" t="inlineStr">
+      <c r="B227" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="C222" s="2" t="inlineStr">
+      <c r="C227" s="2" t="inlineStr">
         <is>
           <t>E09-S05 - Scenario 2 (Withdrawal after deadline refused)</t>
         </is>
       </c>
-      <c r="D222" s="2" t="inlineStr">
+      <c r="D227" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>TC_E09S05_03</t>
         </is>
       </c>
-      <c r="F222" s="2" t="inlineStr">
+      <c r="F227" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to withdraw after the withdrawal deadline has passed should be refused, with a contact provided for assistance</t>
         </is>
       </c>
-      <c r="G222" s="2" t="inlineStr">
+      <c r="G227" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s withdrawal deadline (10/12/2026) has passed</t>
         </is>
       </c>
-      <c r="H222" s="2" t="inlineStr">
+      <c r="H227" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Attempt to withdraw from "Community Meetup"</t>
         </is>
       </c>
-      <c r="I222" s="2" t="inlineStr">
+      <c r="I227" s="2" t="inlineStr">
         <is>
           <t>Withdrawal deadline: 10/12/2026 (passed)</t>
         </is>
       </c>
-      <c r="J222" s="2" t="inlineStr">
+      <c r="J227" s="2" t="inlineStr">
         <is>
           <t>Withdrawal is refused with the message "Withdrawal has closed" and a contact is provided for assistance</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="2" t="n">
+    <row r="228">
+      <c r="A228" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B223" s="2" t="inlineStr">
+      <c r="B228" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="C223" s="2" t="inlineStr">
+      <c r="C228" s="2" t="inlineStr">
         <is>
           <t>E09-S05 · Scenario 2 (Withdrawal after deadline refused)</t>
         </is>
       </c>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>TC_E09S05_04</t>
         </is>
       </c>
-      <c r="F223" s="2" t="inlineStr">
+      <c r="F228" s="2" t="inlineStr">
         <is>
           <t>Verify that withdrawal succeeds at the exact withdrawal deadline</t>
         </is>
       </c>
-      <c r="G223" s="2" t="inlineStr">
+      <c r="G228" s="2" t="inlineStr">
         <is>
           <t>Attendee attendee_a@example.com is registered for event EVT-2001. The withdrawal deadline for event EVT-2001 is 2026-10-25 23:59:59 +08:00</t>
         </is>
       </c>
-      <c r="H223" s="2" t="inlineStr">
+      <c r="H228" s="2" t="inlineStr">
         <is>
           <t>1. Set the system clock to exactly 2026-10-25 23:59:59 +08:00
  2. Sign in as attendee_a@example.com
  3. Open the registration for EVT-2001 and select Withdraw</t>
         </is>
       </c>
-      <c r="I223" s="2" t="inlineStr">
+      <c r="I228" s="2" t="inlineStr">
         <is>
           <t>Withdrawal deadline: 2026-10-25 23:59:59 +08:00 · Attempt at: 2026-10-25 23:59:59 +08:00</t>
         </is>
       </c>
-      <c r="J223" s="2" t="inlineStr">
+      <c r="J228" s="2" t="inlineStr">
         <is>
           <t>The withdrawal succeeds, the registration status becomes Withdrawn and the place is released. Every waitlisted Attendee for EVT-2001 is notified that a place is available
 ## E09-S06</t>
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="2" t="n">
+    <row r="229">
+      <c r="A229" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B224" s="2" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="C224" s="2" t="inlineStr">
+      <c r="C229" s="2" t="inlineStr">
         <is>
           <t>E09-S06 - Scenario 1 (Attendance marked after completion)</t>
         </is>
       </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>TC_E09S06_01</t>
         </is>
       </c>
-      <c r="F224" s="2" t="inlineStr">
+      <c r="F229" s="2" t="inlineStr">
         <is>
           <t>Verify that marking a registered Attendee as attended for a event after the event is Completed should update their record without changing the registration figure</t>
         </is>
       </c>
-      <c r="G224" s="2" t="inlineStr">
+      <c r="G229" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has status "Completed" (per TC_E08S05_01); attendee_a@example.com is registered for its event</t>
         </is>
       </c>
-      <c r="H224" s="2" t="inlineStr">
+      <c r="H229" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the completed event "Charity Run"
   3. Mark attendee_a@example.com as "Attended"</t>
         </is>
       </c>
-      <c r="I224" s="2" t="inlineStr">
+      <c r="I229" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_a@example.com</t>
         </is>
       </c>
-      <c r="J224" s="2" t="inlineStr">
+      <c r="J229" s="2" t="inlineStr">
         <is>
           <t>attendee_a@example.com's record shows "Attended"; the total registration figure for the event remains unchanged</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="2" t="n">
+    <row r="230">
+      <c r="A230" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B225" s="2" t="inlineStr">
+      <c r="B230" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="C225" s="2" t="inlineStr">
+      <c r="C230" s="2" t="inlineStr">
         <is>
           <t>E09-S06 - Scenario 2 (Registered but not attended)</t>
         </is>
       </c>
-      <c r="D225" s="2" t="inlineStr">
+      <c r="D230" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="E230" s="2" t="inlineStr">
         <is>
           <t>TC_E09S06_02</t>
         </is>
       </c>
-      <c r="F225" s="2" t="inlineStr">
+      <c r="F230" s="2" t="inlineStr">
         <is>
           <t>Verify that a registered Attendee who did not attend should be shown as registered but not attended once the event is Completed</t>
         </is>
       </c>
-      <c r="G225" s="2" t="inlineStr">
+      <c r="G230" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has status "Completed"; attendee_b@example.com was registered but has not been marked attended</t>
         </is>
       </c>
-      <c r="H225" s="2" t="inlineStr">
+      <c r="H230" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the completed event "Charity Run"
   3. Check attendee_b@example.com's status</t>
         </is>
       </c>
-      <c r="I225" s="2" t="inlineStr">
+      <c r="I230" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_b@example.com (registered, not marked attended)</t>
         </is>
       </c>
-      <c r="J225" s="2" t="inlineStr">
+      <c r="J230" s="2" t="inlineStr">
         <is>
           <t>attendee_b@example.com is shown as "Registered but not attended"</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="2" t="n">
+    <row r="231">
+      <c r="A231" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B226" s="2" t="inlineStr">
+      <c r="B231" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="C226" s="2" t="inlineStr">
+      <c r="C231" s="2" t="inlineStr">
         <is>
           <t>E09-S06 - Scenario 3 (Recording before completion blocked)</t>
         </is>
       </c>
-      <c r="D226" s="2" t="inlineStr">
+      <c r="D231" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="E231" s="2" t="inlineStr">
         <is>
           <t>TC_E09S06_03</t>
         </is>
       </c>
-      <c r="F226" s="2" t="inlineStr">
+      <c r="F231" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to record attendance before the event is Completed should be blocked</t>
         </is>
       </c>
-      <c r="G226" s="2" t="inlineStr">
+      <c r="G231" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has status "Confirmed" (not yet Completed)</t>
         </is>
       </c>
-      <c r="H226" s="2" t="inlineStr">
+      <c r="H231" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Tech Conference 2026"
   3. Attempt to mark an Attendee as attended</t>
         </is>
       </c>
-      <c r="I226" s="2" t="inlineStr">
+      <c r="I231" s="2" t="inlineStr">
         <is>
           <t>Event status: Confirmed (not Completed)</t>
         </is>
       </c>
-      <c r="J226" s="2" t="inlineStr">
+      <c r="J231" s="2" t="inlineStr">
         <is>
           <t>The action is blocked; attendance cannot be recorded before the event is Completed</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="2" t="n">
+    <row r="232">
+      <c r="A232" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B227" s="2" t="inlineStr">
+      <c r="B232" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="C227" s="2" t="inlineStr">
+      <c r="C232" s="2" t="inlineStr">
         <is>
           <t>E09-S06 (checklist: registration/attendance counts viewable side by side)</t>
         </is>
       </c>
-      <c r="D227" s="2" t="inlineStr">
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>TC_E09S06_04</t>
         </is>
       </c>
-      <c r="F227" s="2" t="inlineStr">
+      <c r="F232" s="2" t="inlineStr">
         <is>
           <t>Verify that registration and attendance counts should be viewable side by side for each event</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr">
+      <c r="G232" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has status "Completed"; its event had 5 registrations and 4 marked attended</t>
         </is>
       </c>
-      <c r="H227" s="2" t="inlineStr">
+      <c r="H232" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the completed event "Charity Run"
   3. View the event's registration and attendance summary</t>
         </is>
       </c>
-      <c r="I227" s="2" t="inlineStr">
+      <c r="I232" s="2" t="inlineStr">
         <is>
           <t>Registered: 5 | Attended: 4</t>
         </is>
       </c>
-      <c r="J227" s="2" t="inlineStr">
+      <c r="J232" s="2" t="inlineStr">
         <is>
           <t>The summary shows "Registered: 5" and "Attended: 4" together, side by side
 ## E09-S07</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="2" t="n">
+    <row r="233">
+      <c r="A233" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B228" s="2" t="inlineStr">
+      <c r="B233" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="C228" s="2" t="inlineStr">
+      <c r="C233" s="2" t="inlineStr">
         <is>
           <t>E09-S07 - Scenario 1 (Registrations grouped by event)</t>
         </is>
       </c>
-      <c r="D228" s="2" t="inlineStr">
+      <c r="D233" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t>TC_E09S07_01</t>
         </is>
       </c>
-      <c r="F228" s="2" t="inlineStr">
+      <c r="F233" s="2" t="inlineStr">
         <is>
           <t>Verify that opening the registration list for an event with registered Attendees should show each Attendee's name, email address and contact number</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr">
+      <c r="G233" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has attendee_a@example.com and attendee_b@example.com registered, each with a name, email address and contact number on file</t>
         </is>
       </c>
-      <c r="H228" s="2" t="inlineStr">
+      <c r="H233" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the registration list for "Tech Conference 2026"</t>
         </is>
       </c>
-      <c r="I228" s="2" t="inlineStr">
+      <c r="I233" s="2" t="inlineStr">
         <is>
           <t>attendee_a@example.com: +65 9123 4567 | attendee_b@example.com: +65 9234 5678</t>
         </is>
       </c>
-      <c r="J228" s="2" t="inlineStr">
+      <c r="J233" s="2" t="inlineStr">
         <is>
           <t>The list shows each Attendee's name, email address and contact number: attendee_a@example.com and attendee_b@example.com both appear with their full contact details</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="2" t="n">
+    <row r="234">
+      <c r="A234" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B229" s="2" t="inlineStr">
+      <c r="B234" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="C229" s="2" t="inlineStr">
+      <c r="C234" s="2" t="inlineStr">
         <is>
           <t>E09-S07 - Scenario 2 (Counts and remaining capacity)</t>
         </is>
       </c>
-      <c r="D229" s="2" t="inlineStr">
+      <c r="D234" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E229" s="2" t="inlineStr">
+      <c r="E234" s="2" t="inlineStr">
         <is>
           <t>TC_E09S07_02</t>
         </is>
       </c>
-      <c r="F229" s="2" t="inlineStr">
+      <c r="F234" s="2" t="inlineStr">
         <is>
           <t>Verify that the registration list should show the registered count and remaining capacity per event</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr">
+      <c r="G234" s="2" t="inlineStr">
         <is>
           <t>"Tech Conference 2026" the event has 100 registered out of a capacity of 150</t>
         </is>
       </c>
-      <c r="H229" s="2" t="inlineStr">
+      <c r="H234" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the registration list for "Tech Conference 2026"</t>
         </is>
       </c>
-      <c r="I229" s="2" t="inlineStr">
+      <c r="I234" s="2" t="inlineStr">
         <is>
           <t>the event: 100 registered, capacity 150</t>
         </is>
       </c>
-      <c r="J229" s="2" t="inlineStr">
+      <c r="J234" s="2" t="inlineStr">
         <is>
           <t>the event shows "100 registered" and "50 remaining"</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="2" t="n">
+    <row r="235">
+      <c r="A235" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B230" s="2" t="inlineStr">
+      <c r="B235" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="C230" s="2" t="inlineStr">
+      <c r="C235" s="2" t="inlineStr">
         <is>
           <t>E09-S07 - Scenario 3 (Unmanaged event refused)</t>
         </is>
       </c>
-      <c r="D230" s="2" t="inlineStr">
+      <c r="D235" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E230" s="2" t="inlineStr">
+      <c r="E235" s="2" t="inlineStr">
         <is>
           <t>TC_E09S07_03</t>
         </is>
       </c>
-      <c r="F230" s="2" t="inlineStr">
+      <c r="F235" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to open the registration list for an event that does not belong to the Organiser's client organisation should be refused</t>
         </is>
       </c>
-      <c r="G230" s="2" t="inlineStr">
+      <c r="G235" s="2" t="inlineStr">
         <is>
           <t>organiser_b@clienta.com is linked to Client B; event "Annual Tech Summit" belongs to Client A</t>
         </is>
       </c>
-      <c r="H230" s="2" t="inlineStr">
+      <c r="H235" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_b@clienta.com
   2. Attempt to open the registration list for "Annual Tech Summit"</t>
         </is>
       </c>
-      <c r="I230" s="2" t="inlineStr">
+      <c r="I235" s="2" t="inlineStr">
         <is>
           <t>Acting user: organiser_b@clienta.com | Event: Annual Tech Summit (Client A)</t>
         </is>
       </c>
-      <c r="J230" s="2" t="inlineStr">
+      <c r="J235" s="2" t="inlineStr">
         <is>
           <t>Access is refused, since "Annual Tech Summit" does not belong to organiser_b@clienta.com's client organisation</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="2" t="n">
+    <row r="236">
+      <c r="A236" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B231" s="2" t="inlineStr">
+      <c r="B236" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="C231" s="2" t="inlineStr">
+      <c r="C236" s="2" t="inlineStr">
         <is>
           <t>E09-S07 - Scenario 4 (Waitlist shown separately)</t>
         </is>
       </c>
-      <c r="D231" s="2" t="inlineStr">
+      <c r="D236" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E231" s="2" t="inlineStr">
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>TC_E09S07_04</t>
         </is>
       </c>
-      <c r="F231" s="2" t="inlineStr">
+      <c r="F236" s="2" t="inlineStr">
         <is>
           <t>Verify that waitlisted Attendees should be shown separately from registered Attendees on the registration list</t>
         </is>
       </c>
-      <c r="G231" s="2" t="inlineStr">
+      <c r="G236" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s event has 5 registered Attendees and 2 on the waiting list</t>
         </is>
       </c>
-      <c r="H231" s="2" t="inlineStr">
+      <c r="H236" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the registration list for "Community Meetup"</t>
         </is>
       </c>
-      <c r="I231" s="2" t="inlineStr">
+      <c r="I236" s="2" t="inlineStr">
         <is>
           <t>Registered: 5 | Waitlisted: 2</t>
         </is>
       </c>
-      <c r="J231" s="2" t="inlineStr">
+      <c r="J236" s="2" t="inlineStr">
         <is>
           <t>The 5 registered Attendees and the 2 waitlisted Attendees are shown in clearly separate sections/lists</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="2" t="n">
+    <row r="237">
+      <c r="A237" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B232" s="2" t="inlineStr">
+      <c r="B237" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C232" s="2" t="inlineStr">
+      <c r="C237" s="2" t="inlineStr">
         <is>
           <t>E10-S01 - Scenario 1 (Change request recorded)</t>
         </is>
       </c>
-      <c r="D232" s="2" t="inlineStr">
+      <c r="D237" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E232" s="2" t="inlineStr">
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_01</t>
         </is>
       </c>
-      <c r="F232" s="2" t="inlineStr">
+      <c r="F237" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting a change request on an approved or confirmed event should notify the assigned Coordinator and record the request against the event</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr">
+      <c r="G237" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" has status "Confirmed"</t>
         </is>
       </c>
-      <c r="H232" s="2" t="inlineStr">
+      <c r="H237" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Community Meetup"
@@ -12595,155 +12855,155 @@
   5. Submit</t>
         </is>
       </c>
-      <c r="I232" s="2" t="inlineStr">
+      <c r="I237" s="2" t="inlineStr">
         <is>
           <t>Change description: "Increase expected attendance to 10"</t>
         </is>
       </c>
-      <c r="J232" s="2" t="inlineStr">
+      <c r="J237" s="2" t="inlineStr">
         <is>
           <t>coordinator_1@connectsphere.com is notified, and the change request is recorded against "Community Meetup"</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="2" t="n">
+    <row r="238">
+      <c r="A238" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B233" s="2" t="inlineStr">
+      <c r="B238" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C233" s="2" t="inlineStr">
+      <c r="C238" s="2" t="inlineStr">
         <is>
           <t>E10-S01 - Scenario 2 (Confirmed details shown alongside)</t>
         </is>
       </c>
-      <c r="D233" s="2" t="inlineStr">
+      <c r="D238" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E233" s="2" t="inlineStr">
+      <c r="E238" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_02</t>
         </is>
       </c>
-      <c r="F233" s="2" t="inlineStr">
+      <c r="F238" s="2" t="inlineStr">
         <is>
           <t>Verify that viewing an event with a pending change request should still show the currently confirmed details alongside the pending request</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr">
+      <c r="G238" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" has a pending change request; its confirmed details (venue, date, time) remain unchanged</t>
         </is>
       </c>
-      <c r="H233" s="2" t="inlineStr">
+      <c r="H238" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Community Meetup"</t>
         </is>
       </c>
-      <c r="I233" s="2" t="inlineStr">
+      <c r="I238" s="2" t="inlineStr">
         <is>
           <t>Pending request: Increase expected attendance to 10</t>
         </is>
       </c>
-      <c r="J233" s="2" t="inlineStr">
+      <c r="J238" s="2" t="inlineStr">
         <is>
           <t>The page shows both the currently confirmed details and the pending change request together</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="2" t="n">
+    <row r="239">
+      <c r="A239" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B234" s="2" t="inlineStr">
+      <c r="B239" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C234" s="2" t="inlineStr">
+      <c r="C239" s="2" t="inlineStr">
         <is>
           <t>E10-S01 - Scenario 3 (Refused edit offers the form)</t>
         </is>
       </c>
-      <c r="D234" s="2" t="inlineStr">
+      <c r="D239" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_03</t>
         </is>
       </c>
-      <c r="F234" s="2" t="inlineStr">
+      <c r="F239" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to directly edit a restricted field after approval should be refused and offered the change request form pre-filled with that field</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr">
+      <c r="G239" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" has status "Confirmed"</t>
         </is>
       </c>
-      <c r="H234" s="2" t="inlineStr">
+      <c r="H239" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Community Meetup"
   3. Attempt to directly edit the Expected Attendance field</t>
         </is>
       </c>
-      <c r="I234" s="2" t="inlineStr">
+      <c r="I239" s="2" t="inlineStr">
         <is>
           <t>Field attempted: Expected Attendance</t>
         </is>
       </c>
-      <c r="J234" s="2" t="inlineStr">
+      <c r="J239" s="2" t="inlineStr">
         <is>
           <t>Direct editing is refused; organiser_a@clienta.com is offered the change request form, pre-filled with the Expected Attendance field</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="2" t="n">
+    <row r="240">
+      <c r="A240" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B235" s="2" t="inlineStr">
+      <c r="B240" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C235" s="2" t="inlineStr">
+      <c r="C240" s="2" t="inlineStr">
         <is>
           <t>E10-S01 - Scenario 4 (Approved change applied)</t>
         </is>
       </c>
-      <c r="D235" s="2" t="inlineStr">
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_04</t>
         </is>
       </c>
-      <c r="F235" s="2" t="inlineStr">
+      <c r="F240" s="2" t="inlineStr">
         <is>
           <t>Verify that when the Coordinator approves a change request, the event should be updated and the Organiser notified</t>
         </is>
       </c>
-      <c r="G235" s="2" t="inlineStr">
+      <c r="G240" s="2" t="inlineStr">
         <is>
           <t>A change request on "Community Meetup" (increase expected attendance to 10) is pending Coordinator approval</t>
         </is>
       </c>
-      <c r="H235" s="2" t="inlineStr">
+      <c r="H240" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the pending change request
@@ -12751,52 +13011,52 @@
   4. Log in as organiser_a@clienta.com and check the event and notifications</t>
         </is>
       </c>
-      <c r="I235" s="2" t="inlineStr">
+      <c r="I240" s="2" t="inlineStr">
         <is>
           <t>Change: Expected Attendance -&gt; 10</t>
         </is>
       </c>
-      <c r="J235" s="2" t="inlineStr">
+      <c r="J240" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s Expected Attendance is updated to 10, and organiser_a@clienta.com is notified that the change was applied</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="2" t="n">
+    <row r="241">
+      <c r="A241" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B236" s="2" t="inlineStr">
+      <c r="B241" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C236" s="2" t="inlineStr">
+      <c r="C241" s="2" t="inlineStr">
         <is>
           <t>E10-S01 (checklist: notified when Coordinator approves or declines)</t>
         </is>
       </c>
-      <c r="D236" s="2" t="inlineStr">
+      <c r="D241" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_05</t>
         </is>
       </c>
-      <c r="F236" s="2" t="inlineStr">
+      <c r="F241" s="2" t="inlineStr">
         <is>
           <t>Verify that when the Coordinator declines a change request, the Organiser should be notified</t>
         </is>
       </c>
-      <c r="G236" s="2" t="inlineStr">
+      <c r="G241" s="2" t="inlineStr">
         <is>
           <t>A change request on "Community Meetup" is pending Coordinator approval</t>
         </is>
       </c>
-      <c r="H236" s="2" t="inlineStr">
+      <c r="H241" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the pending change request
@@ -12805,105 +13065,105 @@
   5. Log in as organiser_a@clienta.com and check notifications</t>
         </is>
       </c>
-      <c r="I236" s="2" t="inlineStr">
+      <c r="I241" s="2" t="inlineStr">
         <is>
           <t>Decision: Declined</t>
         </is>
       </c>
-      <c r="J236" s="2" t="inlineStr">
+      <c r="J241" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is notified that the change request was declined, and the event remains unchanged
 ## E10-S02</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="2" t="n">
+    <row r="242">
+      <c r="A242" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B237" s="2" t="inlineStr">
+      <c r="B242" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C237" s="2" t="inlineStr">
+      <c r="C242" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 1 (Attendance beyond capacity flagged)</t>
         </is>
       </c>
-      <c r="D237" s="2" t="inlineStr">
+      <c r="D242" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="E242" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_01</t>
         </is>
       </c>
-      <c r="F237" s="2" t="inlineStr">
+      <c r="F242" s="2" t="inlineStr">
         <is>
           <t>Verify that increasing a event's expected attendance beyond its confirmed venue's capacity should flag the venue booking for review and notify Venue Staff</t>
         </is>
       </c>
-      <c r="G237" s="2" t="inlineStr">
+      <c r="G242" s="2" t="inlineStr">
         <is>
           <t>A event of "Tech Conference 2026" has a confirmed venue "Riverside Hall" with capacity 200</t>
         </is>
       </c>
-      <c r="H237" s="2" t="inlineStr">
+      <c r="H242" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Increase the event's Expected Attendance to 250
   3. Save</t>
         </is>
       </c>
-      <c r="I237" s="2" t="inlineStr">
+      <c r="I242" s="2" t="inlineStr">
         <is>
           <t>Expected Attendance: 200 -&gt; 250 (venue capacity: 200)</t>
         </is>
       </c>
-      <c r="J237" s="2" t="inlineStr">
+      <c r="J242" s="2" t="inlineStr">
         <is>
           <t>The venue booking for "Riverside Hall" is flagged for review, and venue_staff_1@connectsphere.com is notified</t>
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="2" t="n">
+    <row r="243">
+      <c r="A243" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B238" s="2" t="inlineStr">
+      <c r="B243" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C238" s="2" t="inlineStr">
+      <c r="C243" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 2 (Description-only edit flags nothing)</t>
         </is>
       </c>
-      <c r="D238" s="2" t="inlineStr">
+      <c r="D243" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="E243" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_02</t>
         </is>
       </c>
-      <c r="F238" s="2" t="inlineStr">
+      <c r="F243" s="2" t="inlineStr">
         <is>
           <t>Verify that editing only the event description on an event with confirmed venue and equipment should flag nothing</t>
         </is>
       </c>
-      <c r="G238" s="2" t="inlineStr">
+      <c r="G243" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has a confirmed venue and equipment</t>
         </is>
       </c>
-      <c r="H238" s="2" t="inlineStr">
+      <c r="H243" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Edit only the Description field
@@ -12911,208 +13171,208 @@
   4. Check for any flagged arrangements</t>
         </is>
       </c>
-      <c r="I238" s="2" t="inlineStr">
+      <c r="I243" s="2" t="inlineStr">
         <is>
           <t>Field changed: Description only</t>
         </is>
       </c>
-      <c r="J238" s="2" t="inlineStr">
+      <c r="J243" s="2" t="inlineStr">
         <is>
           <t>No arrangements are flagged as a result of this edit</t>
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="2" t="n">
+    <row r="244">
+      <c r="A244" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B239" s="2" t="inlineStr">
+      <c r="B244" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C239" s="2" t="inlineStr">
+      <c r="C244" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 3 (Affected arrangements shown first)</t>
         </is>
       </c>
-      <c r="D239" s="2" t="inlineStr">
+      <c r="D244" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr">
+      <c r="E244" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_03</t>
         </is>
       </c>
-      <c r="F239" s="2" t="inlineStr">
+      <c r="F244" s="2" t="inlineStr">
         <is>
           <t>Verify that saving a change that affects confirmed arrangements should show which arrangements are affected before the change takes effect</t>
         </is>
       </c>
-      <c r="G239" s="2" t="inlineStr">
+      <c r="G244" s="2" t="inlineStr">
         <is>
           <t>A pending edit to "Tech Conference 2026" would affect its confirmed venue booking</t>
         </is>
       </c>
-      <c r="H239" s="2" t="inlineStr">
+      <c r="H244" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Make the edit that affects the venue booking
   3. Click "Save"</t>
         </is>
       </c>
-      <c r="I239" s="2" t="inlineStr">
+      <c r="I244" s="2" t="inlineStr">
         <is>
           <t>Edit: affects the confirmed venue booking</t>
         </is>
       </c>
-      <c r="J239" s="2" t="inlineStr">
+      <c r="J244" s="2" t="inlineStr">
         <is>
           <t>Before the change is applied, a confirmation screen lists the affected arrangement (venue booking) for review</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="2" t="n">
+    <row r="245">
+      <c r="A245" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B240" s="2" t="inlineStr">
+      <c r="B245" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C240" s="2" t="inlineStr">
+      <c r="C245" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 4 (Over-subscription warns only)</t>
         </is>
       </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_04</t>
         </is>
       </c>
-      <c r="F240" s="2" t="inlineStr">
+      <c r="F245" s="2" t="inlineStr">
         <is>
           <t>Verify that a venue change that reduces a event's capacity below its registration count should warn the Coordinator and show the over-subscription without automatically removing or waitlisting anyone</t>
         </is>
       </c>
-      <c r="G240" s="2" t="inlineStr">
+      <c r="G245" s="2" t="inlineStr">
         <is>
           <t>A event of "Tech Conference 2026" has 100 registered; a venue change is about to reduce its capacity to 80</t>
         </is>
       </c>
-      <c r="H240" s="2" t="inlineStr">
+      <c r="H245" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Change the event's venue to one with capacity 80
   3. Save</t>
         </is>
       </c>
-      <c r="I240" s="2" t="inlineStr">
+      <c r="I245" s="2" t="inlineStr">
         <is>
           <t>New capacity: 80; Registered: 100</t>
         </is>
       </c>
-      <c r="J240" s="2" t="inlineStr">
+      <c r="J245" s="2" t="inlineStr">
         <is>
           <t>coordinator_1@connectsphere.com is warned and shown the over-subscription (100 vs 80); no Attendee is automatically removed or waitlisted</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="2" t="n">
+    <row r="246">
+      <c r="A246" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B241" s="2" t="inlineStr">
+      <c r="B246" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C241" s="2" t="inlineStr">
+      <c r="C246" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 5 (Date change flags venue and equipment)</t>
         </is>
       </c>
-      <c r="D241" s="2" t="inlineStr">
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E241" s="2" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_05</t>
         </is>
       </c>
-      <c r="F241" s="2" t="inlineStr">
+      <c r="F246" s="2" t="inlineStr">
         <is>
           <t>Verify that changing a event's date or time should flag its venue booking and equipment reservations as requiring reconfirmation</t>
         </is>
       </c>
-      <c r="G241" s="2" t="inlineStr">
+      <c r="G246" s="2" t="inlineStr">
         <is>
           <t>A event of "Tech Conference 2026" has a confirmed venue and reserved equipment</t>
         </is>
       </c>
-      <c r="H241" s="2" t="inlineStr">
+      <c r="H246" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Change the event's date from 15/11/2026 to 20/11/2026
   3. Save</t>
         </is>
       </c>
-      <c r="I241" s="2" t="inlineStr">
+      <c r="I246" s="2" t="inlineStr">
         <is>
           <t>Date: 15/11/2026 -&gt; 20/11/2026</t>
         </is>
       </c>
-      <c r="J241" s="2" t="inlineStr">
+      <c r="J246" s="2" t="inlineStr">
         <is>
           <t>Both the venue booking and the equipment reservations for this event are flagged as requiring reconfirmation</t>
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="2" t="n">
+    <row r="247">
+      <c r="A247" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B242" s="2" t="inlineStr">
+      <c r="B247" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C242" s="2" t="inlineStr">
+      <c r="C247" s="2" t="inlineStr">
         <is>
           <t>E10-S02 (checklist: Venue Staff and Technical Support Staff both notified)</t>
         </is>
       </c>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="D247" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting (notification consistency)</t>
         </is>
       </c>
-      <c r="E242" s="2" t="inlineStr">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_06</t>
         </is>
       </c>
-      <c r="F242" s="2" t="inlineStr">
+      <c r="F247" s="2" t="inlineStr">
         <is>
           <t>Verify that when a date or time change flags arrangements for reconfirmation, the assigned Technical Support Staff should also be notified, not just Venue Staff</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr">
+      <c r="G247" s="2" t="inlineStr">
         <is>
           <t>A event of "Tech Conference 2026" has a confirmed venue, reserved equipment, and tech_support_1@connectsphere.com assigned for on-site support</t>
         </is>
       </c>
-      <c r="H242" s="2" t="inlineStr">
+      <c r="H247" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Change the event's date
@@ -13120,52 +13380,52 @@
   4. Check notifications for both venue_staff_1@connectsphere.com and tech_support_1@connectsphere.com</t>
         </is>
       </c>
-      <c r="I242" s="2" t="inlineStr">
+      <c r="I247" s="2" t="inlineStr">
         <is>
           <t>Changed field: Date</t>
         </is>
       </c>
-      <c r="J242" s="2" t="inlineStr">
+      <c r="J247" s="2" t="inlineStr">
         <is>
           <t>Both venue_staff_1@connectsphere.com and tech_support_1@connectsphere.com receive a notification about the change requiring reconfirmation</t>
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="2" t="n">
+    <row r="248">
+      <c r="A248" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B243" s="2" t="inlineStr">
+      <c r="B248" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C243" s="2" t="inlineStr">
+      <c r="C248" s="2" t="inlineStr">
         <is>
           <t>E10-S02 — Scenario 1 (Attendance beyond capacity flagged); assumes O-27</t>
         </is>
       </c>
-      <c r="D243" s="2" t="inlineStr">
+      <c r="D248" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E243" s="2" t="inlineStr">
+      <c r="E248" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_07</t>
         </is>
       </c>
-      <c r="F243" s="2" t="inlineStr">
+      <c r="F248" s="2" t="inlineStr">
         <is>
           <t>Verify that increasing expected attendance on a multi-venue event should flag only the venue bookings whose governing headcount now exceeds capacity</t>
         </is>
       </c>
-      <c r="G243" s="2" t="inlineStr">
+      <c r="G248" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Summit" is Confirmed with "Grand Auditorium" (capacity 600, booking headcount not set) and "Seminar Room A" (capacity 60, booking headcount 50); expected attendance is 500; coordinator_1@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H243" s="2" t="inlineStr">
+      <c r="H248" s="2" t="inlineStr">
         <is>
           <t>1. Change expected attendance to 600 and save
   2. Read the arrangement flags
@@ -13173,53 +13433,53 @@
   4. Read the arrangement flags</t>
         </is>
       </c>
-      <c r="I243" s="2" t="inlineStr">
+      <c r="I248" s="2" t="inlineStr">
         <is>
           <t>Auditorium governed by event attendance (600 = exactly at capacity, 601 = above); Seminar Room A governed by its own headcount 50</t>
         </is>
       </c>
-      <c r="J243" s="2" t="inlineStr">
+      <c r="J248" s="2" t="inlineStr">
         <is>
           <t>After step 1 no booking is flagged; after step 3 only "Grand Auditorium" is flagged for review and "Seminar Room A" is not, because its booking headcount of 50 is unchanged
 ## E10-S04</t>
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="2" t="n">
+    <row r="249">
+      <c r="A249" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B244" s="2" t="inlineStr">
+      <c r="B249" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="C244" s="2" t="inlineStr">
+      <c r="C249" s="2" t="inlineStr">
         <is>
           <t>E10-S04 - Scenario 1 (Event cancelled, arrangements released)</t>
         </is>
       </c>
-      <c r="D244" s="2" t="inlineStr">
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E244" s="2" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>TC_E10S04_01</t>
         </is>
       </c>
-      <c r="F244" s="2" t="inlineStr">
+      <c r="F249" s="2" t="inlineStr">
         <is>
           <t>Verify that cancelling an event and recording a reason should release its venue bookings and equipment reservations, update the venue calendars, and notify affected staff</t>
         </is>
       </c>
-      <c r="G244" s="2" t="inlineStr">
+      <c r="G249" s="2" t="inlineStr">
         <is>
           <t>Event "Product Launch Night" has status "Confirmed" with a confirmed venue "Small Room" and reserved equipment</t>
         </is>
       </c>
-      <c r="H244" s="2" t="inlineStr">
+      <c r="H249" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Product Launch Night"
@@ -13228,156 +13488,156 @@
   5. Confirm</t>
         </is>
       </c>
-      <c r="I244" s="2" t="inlineStr">
+      <c r="I249" s="2" t="inlineStr">
         <is>
           <t>Cancellation reason: "Insufficient sponsor funding"</t>
         </is>
       </c>
-      <c r="J244" s="2" t="inlineStr">
+      <c r="J249" s="2" t="inlineStr">
         <is>
           <t>The status becomes "Cancelled"; "Small Room"'s booking and the reserved equipment are released, the venue calendar is updated, and affected staff are notified</t>
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="2" t="n">
+    <row r="250">
+      <c r="A250" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B245" s="2" t="inlineStr">
+      <c r="B250" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="C245" s="2" t="inlineStr">
+      <c r="C250" s="2" t="inlineStr">
         <is>
           <t>E10-S04 - Scenario 2 (Attendees and waitlist notified)</t>
         </is>
       </c>
-      <c r="D245" s="2" t="inlineStr">
+      <c r="D250" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E245" s="2" t="inlineStr">
+      <c r="E250" s="2" t="inlineStr">
         <is>
           <t>TC_E10S04_03</t>
         </is>
       </c>
-      <c r="F245" s="2" t="inlineStr">
+      <c r="F250" s="2" t="inlineStr">
         <is>
           <t>Verify that cancelling a event should notify all of its registered and waitlisted Attendees</t>
         </is>
       </c>
-      <c r="G245" s="2" t="inlineStr">
+      <c r="G250" s="2" t="inlineStr">
         <is>
           <t>The event of "Tech Conference 2026" being cancelled has attendee_a@example.com registered and attendee_l@example.com waitlisted</t>
         </is>
       </c>
-      <c r="H245" s="2" t="inlineStr">
+      <c r="H250" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Cancel the event
   3. Check notifications for attendee_a@example.com and attendee_l@example.com</t>
         </is>
       </c>
-      <c r="I245" s="2" t="inlineStr">
+      <c r="I250" s="2" t="inlineStr">
         <is>
           <t>Registered: attendee_a@example.com | Waitlisted: attendee_l@example.com</t>
         </is>
       </c>
-      <c r="J245" s="2" t="inlineStr">
+      <c r="J250" s="2" t="inlineStr">
         <is>
           <t>Both attendee_a@example.com and attendee_l@example.com receive a notification of the cancellation</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="2" t="n">
+    <row r="251">
+      <c r="A251" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B246" s="2" t="inlineStr">
+      <c r="B251" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="C246" s="2" t="inlineStr">
+      <c r="C251" s="2" t="inlineStr">
         <is>
           <t>E10-S04 - Scenario 3 (Cancelled event read-only)</t>
         </is>
       </c>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="D251" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>TC_E10S04_04</t>
         </is>
       </c>
-      <c r="F246" s="2" t="inlineStr">
+      <c r="F251" s="2" t="inlineStr">
         <is>
           <t>Verify that a cancelled event should be read-only and show its cancellation reason and date to any viewer</t>
         </is>
       </c>
-      <c r="G246" s="2" t="inlineStr">
+      <c r="G251" s="2" t="inlineStr">
         <is>
           <t>Event "Product Launch Night" was cancelled on 12/09/2026 with reason "Insufficient sponsor funding" (per TC_E10S04_01)</t>
         </is>
       </c>
-      <c r="H246" s="2" t="inlineStr">
+      <c r="H251" s="2" t="inlineStr">
         <is>
           <t>1. Log in as any user with access (e.g. organiser_a@clienta.com)
   2. Open the cancelled event "Product Launch Night"
   3. Attempt to edit any field</t>
         </is>
       </c>
-      <c r="I246" s="2" t="inlineStr">
+      <c r="I251" s="2" t="inlineStr">
         <is>
           <t>Cancellation reason: "Insufficient sponsor funding" | Date: 12/09/2026</t>
         </is>
       </c>
-      <c r="J246" s="2" t="inlineStr">
+      <c r="J251" s="2" t="inlineStr">
         <is>
           <t>The event shows "Cancelled on 12 September 2026 - Insufficient sponsor funding"; all fields are read-only</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="2" t="n">
+    <row r="252">
+      <c r="A252" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B247" s="2" t="inlineStr">
+      <c r="B252" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="C247" s="2" t="inlineStr">
+      <c r="C252" s="2" t="inlineStr">
         <is>
           <t>E10-S04 - Scenario 4 (Organiser cancellation becomes a request)</t>
         </is>
       </c>
-      <c r="D247" s="2" t="inlineStr">
+      <c r="D252" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E247" s="2" t="inlineStr">
+      <c r="E252" s="2" t="inlineStr">
         <is>
           <t>TC_E10S04_05</t>
         </is>
       </c>
-      <c r="F247" s="2" t="inlineStr">
+      <c r="F252" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Organiser attempting to cancel directly should have the action recorded as a cancellation request for the Coordinator to action</t>
         </is>
       </c>
-      <c r="G247" s="2" t="inlineStr">
+      <c r="G252" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" has status "Confirmed", assigned to coordinator_1@connectsphere.com</t>
         </is>
       </c>
-      <c r="H247" s="2" t="inlineStr">
+      <c r="H252" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Community Meetup"
@@ -13385,308 +13645,308 @@
   4. Enter a reason and submit</t>
         </is>
       </c>
-      <c r="I247" s="2" t="inlineStr">
+      <c r="I252" s="2" t="inlineStr">
         <is>
           <t>Reason: "No longer needed"</t>
         </is>
       </c>
-      <c r="J247" s="2" t="inlineStr">
+      <c r="J252" s="2" t="inlineStr">
         <is>
           <t>The event is NOT immediately cancelled; instead, a cancellation request is recorded and coordinator_1@connectsphere.com is notified to action it</t>
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="2" t="n">
+    <row r="253">
+      <c r="A253" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B248" s="2" t="inlineStr">
+      <c r="B253" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C248" s="2" t="inlineStr">
+      <c r="C253" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 1 (Status change notified)</t>
         </is>
       </c>
-      <c r="D248" s="2" t="inlineStr">
+      <c r="D253" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E248" s="2" t="inlineStr">
+      <c r="E253" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_01</t>
         </is>
       </c>
-      <c r="F248" s="2" t="inlineStr">
+      <c r="F253" s="2" t="inlineStr">
         <is>
           <t>Verify that a user linked to an event should be notified when its status changes or a booking decision is made, with details of what/when/which event</t>
         </is>
       </c>
-      <c r="G248" s="2" t="inlineStr">
+      <c r="G253" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is linked to event "Annual Tech Summit", currently "Under Review"</t>
         </is>
       </c>
-      <c r="H248" s="2" t="inlineStr">
+      <c r="H253" s="2" t="inlineStr">
         <is>
           <t>1. As coordinator_1@connectsphere.com, approve request "Annual Tech Summit" (status -&gt; Approved)
   2. Log in as organiser_a@clienta.com and open notifications</t>
         </is>
       </c>
-      <c r="I248" s="2" t="inlineStr">
+      <c r="I253" s="2" t="inlineStr">
         <is>
           <t>Event: Annual Tech Summit | Change: Under Review -&gt; Approved</t>
         </is>
       </c>
-      <c r="J248" s="2" t="inlineStr">
+      <c r="J253" s="2" t="inlineStr">
         <is>
           <t>A notification is received stating the status changed to "Approved", the time of the change, and that it concerns "Annual Tech Summit"</t>
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="2" t="n">
+    <row r="254">
+      <c r="A254" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B249" s="2" t="inlineStr">
+      <c r="B254" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C249" s="2" t="inlineStr">
+      <c r="C254" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 2 (All affected parties notified)</t>
         </is>
       </c>
-      <c r="D249" s="2" t="inlineStr">
+      <c r="D254" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E249" s="2" t="inlineStr">
+      <c r="E254" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_02</t>
         </is>
       </c>
-      <c r="F249" s="2" t="inlineStr">
+      <c r="F254" s="2" t="inlineStr">
         <is>
           <t>Verify that effective date, time or venue changes follow the approved recipient matrix</t>
         </is>
       </c>
-      <c r="G249" s="2" t="inlineStr">
+      <c r="G254" s="2" t="inlineStr">
         <is>
           <t>Event "Annual Tech Summit" the event has organiser_a@clienta.com, venue_staff_1@connectsphere.com, and tech_support_1@connectsphere.com assigned, and attendee_a@example.com registered; attendee_b@example.com is waitlisted and coordinator_1@connectsphere.com is the assigned Coordinator</t>
         </is>
       </c>
-      <c r="H249" s="2" t="inlineStr">
+      <c r="H254" s="2" t="inlineStr">
         <is>
           <t>1. As coordinator_1@connectsphere.com, change the event's venue
   2. Check notifications for organiser_a@clienta.com, venue_staff_1@connectsphere.com, tech_support_1@connectsphere.com, and attendee_a@example.com</t>
         </is>
       </c>
-      <c r="I249" s="2" t="inlineStr">
+      <c r="I254" s="2" t="inlineStr">
         <is>
           <t>Changed field: Venue</t>
         </is>
       </c>
-      <c r="J249" s="2" t="inlineStr">
+      <c r="J254" s="2" t="inlineStr">
         <is>
           <t>The Organiser, assigned Venue Staff, assigned Technical Support Staff, registered Attendee and waitlisted Attendee receive a notification. The acting Coordinator receives no self-notification. If another authorized actor or a system operation makes the change, the assigned Coordinator is included. Venue-move tests include responsible staff for both the old and new venues. Backend resolver fixtures are not evidence that the venue-assignment workflow is implemented.</t>
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="2" t="n">
+    <row r="255">
+      <c r="A255" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B250" s="2" t="inlineStr">
+      <c r="B255" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C250" s="2" t="inlineStr">
+      <c r="C255" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 3 (Unaffected users not notified)</t>
         </is>
       </c>
-      <c r="D250" s="2" t="inlineStr">
+      <c r="D255" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E250" s="2" t="inlineStr">
+      <c r="E255" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_03</t>
         </is>
       </c>
-      <c r="F250" s="2" t="inlineStr">
+      <c r="F255" s="2" t="inlineStr">
         <is>
           <t>Verify that a user whose responsibilities are unaffected by a change should not be notified</t>
         </is>
       </c>
-      <c r="G250" s="2" t="inlineStr">
+      <c r="G255" s="2" t="inlineStr">
         <is>
           <t>Event "Annual Tech Summit" the event's Description field is about to be edited; venue_staff_1@connectsphere.com has no responsibility tied to the Description field</t>
         </is>
       </c>
-      <c r="H250" s="2" t="inlineStr">
+      <c r="H255" s="2" t="inlineStr">
         <is>
           <t>1. As organiser_a@clienta.com, edit the Description field only
   2. Check venue_staff_1@connectsphere.com's notifications</t>
         </is>
       </c>
-      <c r="I250" s="2" t="inlineStr">
+      <c r="I255" s="2" t="inlineStr">
         <is>
           <t>Changed field: Description only</t>
         </is>
       </c>
-      <c r="J250" s="2" t="inlineStr">
+      <c r="J255" s="2" t="inlineStr">
         <is>
           <t>venue_staff_1@connectsphere.com receives no notification, since the Description change does not affect their responsibilities</t>
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="2" t="n">
+    <row r="256">
+      <c r="A256" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B251" s="2" t="inlineStr">
+      <c r="B256" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C251" s="2" t="inlineStr">
+      <c r="C256" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 4 (Delivered in-app and by email)</t>
         </is>
       </c>
-      <c r="D251" s="2" t="inlineStr">
+      <c r="D256" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E251" s="2" t="inlineStr">
+      <c r="E256" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_05</t>
         </is>
       </c>
-      <c r="F251" s="2" t="inlineStr">
+      <c r="F256" s="2" t="inlineStr">
         <is>
           <t>Verify that a generated notification should appear in the system and also be sent to the user's registered email address</t>
         </is>
       </c>
-      <c r="G251" s="2" t="inlineStr">
+      <c r="G256" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com's registered email is organiser_a@clienta.com; a notification-triggering status change is about to occur on their event</t>
         </is>
       </c>
-      <c r="H251" s="2" t="inlineStr">
+      <c r="H256" s="2" t="inlineStr">
         <is>
           <t>1. Trigger a status change on organiser_a@clienta.com's event
   2. Log in as organiser_a@clienta.com and check the in-app notification list
   3. Check the inbox for organiser_a@clienta.com</t>
         </is>
       </c>
-      <c r="I251" s="2" t="inlineStr">
+      <c r="I256" s="2" t="inlineStr">
         <is>
           <t>Registered email: organiser_a@clienta.com</t>
         </is>
       </c>
-      <c r="J251" s="2" t="inlineStr">
+      <c r="J256" s="2" t="inlineStr">
         <is>
           <t>The notification appears in the in-app notification list, and an equivalent email is also delivered to organiser_a@clienta.com's inbox</t>
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="2" t="n">
+    <row r="257">
+      <c r="A257" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B252" s="2" t="inlineStr">
+      <c r="B257" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C252" s="2" t="inlineStr">
+      <c r="C257" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 5 (Unread notifications distinguished)</t>
         </is>
       </c>
-      <c r="D252" s="2" t="inlineStr">
+      <c r="D257" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="E257" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_06</t>
         </is>
       </c>
-      <c r="F252" s="2" t="inlineStr">
+      <c r="F257" s="2" t="inlineStr">
         <is>
           <t>Verify that opening the notification list with several unread notifications should show them newest first with unread ones distinguished</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr">
+      <c r="G257" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com has 3 notifications on 09/09/2026: 08:00 (read), 10:00 (unread), 14:00 (unread)</t>
         </is>
       </c>
-      <c r="H252" s="2" t="inlineStr">
+      <c r="H257" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the notification list</t>
         </is>
       </c>
-      <c r="I252" s="2" t="inlineStr">
+      <c r="I257" s="2" t="inlineStr">
         <is>
           <t>Notifications: 08:00 (read), 10:00 (unread), 14:00 (unread)</t>
         </is>
       </c>
-      <c r="J252" s="2" t="inlineStr">
+      <c r="J257" s="2" t="inlineStr">
         <is>
           <t>Notifications are listed newest first (14:00, then 10:00, then 08:00), with the 14:00 and 10:00 entries visually marked as unread and 08:00 shown as read</t>
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="2" t="n">
+    <row r="258">
+      <c r="A258" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B253" s="2" t="inlineStr">
+      <c r="B258" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C253" s="2" t="inlineStr">
+      <c r="C258" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 6 (Marked as read)</t>
         </is>
       </c>
-      <c r="D253" s="2" t="inlineStr">
+      <c r="D258" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E253" s="2" t="inlineStr">
+      <c r="E258" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_07</t>
         </is>
       </c>
-      <c r="F253" s="2" t="inlineStr">
+      <c r="F258" s="2" t="inlineStr">
         <is>
           <t>Verify that opening an unread notification should mark it as read</t>
         </is>
       </c>
-      <c r="G253" s="2" t="inlineStr">
+      <c r="G258" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com has an unread notification from 10:00 on 09/09/2026</t>
         </is>
       </c>
-      <c r="H253" s="2" t="inlineStr">
+      <c r="H258" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the notification list
@@ -13694,52 +13954,52 @@
   4. Return to the notification list</t>
         </is>
       </c>
-      <c r="I253" s="2" t="inlineStr">
+      <c r="I258" s="2" t="inlineStr">
         <is>
           <t>Notification: 10:00 on 09/09/2026 (initially unread)</t>
         </is>
       </c>
-      <c r="J253" s="2" t="inlineStr">
+      <c r="J258" s="2" t="inlineStr">
         <is>
           <t>The 10:00 notification is now shown as read (no longer marked unread) in the list</t>
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="2" t="n">
+    <row r="259">
+      <c r="A259" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B254" s="2" t="inlineStr">
+      <c r="B259" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C254" s="2" t="inlineStr">
+      <c r="C259" s="2" t="inlineStr">
         <is>
           <t>E11-S01 · Scenario 5 (Delivered in-app and by email) · ADR-006</t>
         </is>
       </c>
-      <c r="D254" s="2" t="inlineStr">
+      <c r="D259" s="2" t="inlineStr">
         <is>
           <t>4 - Negative (third-party unavailable)</t>
         </is>
       </c>
-      <c r="E254" s="2" t="inlineStr">
+      <c r="E259" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_08</t>
         </is>
       </c>
-      <c r="F254" s="2" t="inlineStr">
+      <c r="F259" s="2" t="inlineStr">
         <is>
           <t>Verify that an unreachable email provider does not affect the business change or the in-app notification</t>
         </is>
       </c>
-      <c r="G254" s="2" t="inlineStr">
+      <c r="G259" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2003 has an assigned Coordinator coord_a@connectsphere.com. The email provider endpoint is configured to an unreachable host so every SMTP attempt fails</t>
         </is>
       </c>
-      <c r="H254" s="2" t="inlineStr">
+      <c r="H259" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Venue Staff and approve the pending venue booking for EVT-2003
  2. Confirm the booking status has changed
@@ -13747,52 +14007,52 @@
  4. Inspect the delivery records for that notification</t>
         </is>
       </c>
-      <c r="I254" s="2" t="inlineStr">
+      <c r="I259" s="2" t="inlineStr">
         <is>
           <t>SMTP host: unreachable · Notification: venue booking approved</t>
         </is>
       </c>
-      <c r="J254" s="2" t="inlineStr">
+      <c r="J259" s="2" t="inlineStr">
         <is>
           <t>The booking is Confirmed and the change persists. The in-app notification appears for the Coordinator. The email delivery row is marked failed with a recorded reason. The business transaction is not rolled back by the email failure</t>
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" s="2" t="n">
+    <row r="260">
+      <c r="A260" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B255" s="2" t="inlineStr">
+      <c r="B260" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C255" s="2" t="inlineStr">
+      <c r="C260" s="2" t="inlineStr">
         <is>
           <t>E11-S01 · Scenario 1 (Status change notified) · ADR-006 outbox guarantee</t>
         </is>
       </c>
-      <c r="D255" s="2" t="inlineStr">
+      <c r="D260" s="2" t="inlineStr">
         <is>
           <t>4 - Negative (transaction rollback)</t>
         </is>
       </c>
-      <c r="E255" s="2" t="inlineStr">
+      <c r="E260" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_09</t>
         </is>
       </c>
-      <c r="F255" s="2" t="inlineStr">
+      <c r="F260" s="2" t="inlineStr">
         <is>
           <t>Verify that a rolled-back business transaction publishes no notification</t>
         </is>
       </c>
-      <c r="G255" s="2" t="inlineStr">
+      <c r="G260" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2004 is at status Under Review. A fault is injected so that the approval transaction fails after the notification delivery rows are written but before commit</t>
         </is>
       </c>
-      <c r="H255" s="2" t="inlineStr">
+      <c r="H260" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as the assigned Event Coordinator
  2. Approve EVT-2004, triggering the injected failure
@@ -13800,264 +14060,14 @@
  4. Inspect the job queue and the Organiser's notification list</t>
         </is>
       </c>
-      <c r="I255" s="2" t="inlineStr">
+      <c r="I260" s="2" t="inlineStr">
         <is>
           <t>Event: EVT-2004 · Injected failure point: after delivery rows written, before commit</t>
         </is>
       </c>
-      <c r="J255" s="2" t="inlineStr">
+      <c r="J260" s="2" t="inlineStr">
         <is>
           <t>The event remains at Under Review. No delivery row is persisted, nothing is published to the queue, and the Organiser receives no in-app notification and no email. Only committed deliveries are ever published</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B256" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01</t>
-        </is>
-      </c>
-      <c r="C256" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
-        </is>
-      </c>
-      <c r="D256" s="2" t="inlineStr">
-        <is>
-          <t>3 - Integration / regression</t>
-        </is>
-      </c>
-      <c r="E256" s="2" t="inlineStr">
-        <is>
-          <t>TC_E11S01_10</t>
-        </is>
-      </c>
-      <c r="F256" s="2" t="inlineStr">
-        <is>
-          <t>Apply the approved role/change recipient matrix</t>
-        </is>
-      </c>
-      <c r="G256" s="2" t="inlineStr">
-        <is>
-          <t>The event has active links to all six recipient groups and a public snapshot.</t>
-        </is>
-      </c>
-      <c r="H256" s="2" t="inlineStr">
-        <is>
-          <t>1. Trigger each internal status, booking, equipment, public status, arrangement, place-release and description-only change through the selector.</t>
-        </is>
-      </c>
-      <c r="I256" s="2" t="inlineStr">
-        <is>
-          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
-        </is>
-      </c>
-      <c r="J256" s="2" t="inlineStr">
-        <is>
-          <t>Recipient sets match the E11-S01 matrix; internal decisions do not reach Attendees; initial Planning differs from Confirmed-to-Planning.</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B257" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01</t>
-        </is>
-      </c>
-      <c r="C257" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
-        </is>
-      </c>
-      <c r="D257" s="2" t="inlineStr">
-        <is>
-          <t>3 - Integration / regression</t>
-        </is>
-      </c>
-      <c r="E257" s="2" t="inlineStr">
-        <is>
-          <t>TC_E11S01_11</t>
-        </is>
-      </c>
-      <c r="F257" s="2" t="inlineStr">
-        <is>
-          <t>Suppress self-notifications and duplicate recipient links</t>
-        </is>
-      </c>
-      <c r="G257" s="2" t="inlineStr">
-        <is>
-          <t>A user is both the actor and a candidate recipient; duplicated staff links exist.</t>
-        </is>
-      </c>
-      <c r="H257" s="2" t="inlineStr">
-        <is>
-          <t>1. Select recipients for an arrangement change and an actor-made booking decision.</t>
-        </is>
-      </c>
-      <c r="I257" s="2" t="inlineStr">
-        <is>
-          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
-        </is>
-      </c>
-      <c r="J257" s="2" t="inlineStr">
-        <is>
-          <t>The actor receives no routine self-notification; every remaining user appears once; system changes have no excluded actor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B258" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01</t>
-        </is>
-      </c>
-      <c r="C258" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
-        </is>
-      </c>
-      <c r="D258" s="2" t="inlineStr">
-        <is>
-          <t>3 - Integration / regression</t>
-        </is>
-      </c>
-      <c r="E258" s="2" t="inlineStr">
-        <is>
-          <t>TC_E11S01_12</t>
-        </is>
-      </c>
-      <c r="F258" s="2" t="inlineStr">
-        <is>
-          <t>Preserve before/after recipients during cancellation and venue moves</t>
-        </is>
-      </c>
-      <c r="G258" s="2" t="inlineStr">
-        <is>
-          <t>An event has active bookings, assigned staff, registered and waitlisted Attendees.</t>
-        </is>
-      </c>
-      <c r="H258" s="2" t="inlineStr">
-        <is>
-          <t>1. Capture its audience, release links during cancellation or replace the venue, then call the hook with both snapshots.</t>
-        </is>
-      </c>
-      <c r="I258" s="2" t="inlineStr">
-        <is>
-          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
-        </is>
-      </c>
-      <c r="J258" s="2" t="inlineStr">
-        <is>
-          <t>Cancellation notifies the pre-release audience. Venue moves include responsible staff at both venues. These are hook-contract tests until the owning workflows integrate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B259" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01</t>
-        </is>
-      </c>
-      <c r="C259" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
-        </is>
-      </c>
-      <c r="D259" s="2" t="inlineStr">
-        <is>
-          <t>3 - Integration / regression</t>
-        </is>
-      </c>
-      <c r="E259" s="2" t="inlineStr">
-        <is>
-          <t>TC_E11S01_13</t>
-        </is>
-      </c>
-      <c r="F259" s="2" t="inlineStr">
-        <is>
-          <t>Expose missing Venue Staff assignments without an unsafe fallback</t>
-        </is>
-      </c>
-      <c r="G259" s="2" t="inlineStr">
-        <is>
-          <t>No explicit venue assignment adapter is available; a booking has a decided_by actor and unrelated Venue Staff accounts exist.</t>
-        </is>
-      </c>
-      <c r="H259" s="2" t="inlineStr">
-        <is>
-          <t>1. Capture the audience and select booking-request recipients.</t>
-        </is>
-      </c>
-      <c r="I259" s="2" t="inlineStr">
-        <is>
-          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
-        </is>
-      </c>
-      <c r="J259" s="2" t="inlineStr">
-        <is>
-          <t>Venue Staff recipients are unresolved, the venue IDs are reported, and neither decided_by nor all Venue Staff is substituted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B260" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01</t>
-        </is>
-      </c>
-      <c r="C260" s="2" t="inlineStr">
-        <is>
-          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
-        </is>
-      </c>
-      <c r="D260" s="2" t="inlineStr">
-        <is>
-          <t>3 - Integration / regression</t>
-        </is>
-      </c>
-      <c r="E260" s="2" t="inlineStr">
-        <is>
-          <t>TC_E11S01_14</t>
-        </is>
-      </c>
-      <c r="F260" s="2" t="inlineStr">
-        <is>
-          <t>Protect attendee notification content and membership boundaries</t>
-        </is>
-      </c>
-      <c r="G260" s="2" t="inlineStr">
-        <is>
-          <t>The internal event title differs from its publication; registered, waitlisted, withdrawn, inactive and unrelated users exist.</t>
-        </is>
-      </c>
-      <c r="H260" s="2" t="inlineStr">
-        <is>
-          <t>1. Apply an effective date change; inspect notification messages and retained email payloads. Also select recipients for an unpublished event.</t>
-        </is>
-      </c>
-      <c r="I260" s="2" t="inlineStr">
-        <is>
-          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
-        </is>
-      </c>
-      <c r="J260" s="2" t="inlineStr">
-        <is>
-          <t>Only eligible linked active users are selected. Attendees receive the published event name and fixed public change description; no internal title/reason/comment leaks. Unpublished events produce no attendee notice.</t>
         </is>
       </c>
     </row>
@@ -14082,22 +14092,22 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>TC_E11S01_15</t>
+          <t>TC_E11S01_10</t>
         </is>
       </c>
       <c r="F261" s="2" t="inlineStr">
         <is>
-          <t>Deduplicate concurrent notification-hook retries</t>
+          <t>Apply the approved role/change recipient matrix</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>Two transactions use the same event, stable change ID and recipient snapshot.</t>
+          <t>The event has active links to all six recipient groups and a public snapshot.</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>1. Call the notification hook concurrently and commit both attempts.</t>
+          <t>1. Trigger each internal status, booking, equipment, public status, arrangement, place-release and description-only change through the selector.</t>
         </is>
       </c>
       <c r="I261" s="2" t="inlineStr">
@@ -14107,7 +14117,7 @@
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
-          <t>Exactly one in-app row and one email-delivery row exist per recipient for the logical change. A new change ID identifies a different business change.</t>
+          <t>Recipient sets match the E11-S01 matrix; internal decisions do not reach Attendees; initial Planning differs from Confirmed-to-Planning.</t>
         </is>
       </c>
     </row>
@@ -14132,22 +14142,22 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>TC_E11S01_16</t>
+          <t>TC_E11S01_11</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>Keep uncommitted notifications invisible and roll back all writes</t>
+          <t>Suppress self-notifications and duplicate recipient links</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>A business transaction has inserted notifications and prepared email delivery rows but has not committed.</t>
+          <t>A user is both the actor and a candidate recipient; duplicated staff links exist.</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>1. Read from another connection, then force the business transaction to roll back.</t>
+          <t>1. Select recipients for an arrangement change and an actor-made booking decision.</t>
         </is>
       </c>
       <c r="I262" s="2" t="inlineStr">
@@ -14157,253 +14167,503 @@
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
-          <t>The other connection cannot observe the uncommitted messages. After rollback no notification or email-delivery row remains.</t>
+          <t>The actor receives no routine self-notification; every remaining user appears once; system changes have no excluded actor.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>3 - Integration / regression</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>TC_E11S01_12</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>Preserve before/after recipients during cancellation and venue moves</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>An event has active bookings, assigned staff, registered and waitlisted Attendees.</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>1. Capture its audience, release links during cancellation or replace the venue, then call the hook with both snapshots.</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="inlineStr">
+        <is>
+          <t>Cancellation notifies the pre-release audience. Venue moves include responsible staff at both venues. These are hook-contract tests until the owning workflows integrate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>3 - Integration / regression</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>TC_E11S01_13</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>Expose missing Venue Staff assignments without an unsafe fallback</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>No explicit venue assignment adapter is available; a booking has a decided_by actor and unrelated Venue Staff accounts exist.</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>1. Capture the audience and select booking-request recipients.</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
+        </is>
+      </c>
+      <c r="J264" s="2" t="inlineStr">
+        <is>
+          <t>Venue Staff recipients are unresolved, the venue IDs are reported, and neither decided_by nor all Venue Staff is substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>3 - Integration / regression</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>TC_E11S01_14</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>Protect attendee notification content and membership boundaries</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>The internal event title differs from its publication; registered, waitlisted, withdrawn, inactive and unrelated users exist.</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>1. Apply an effective date change; inspect notification messages and retained email payloads. Also select recipients for an unpublished event.</t>
+        </is>
+      </c>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
+        </is>
+      </c>
+      <c r="J265" s="2" t="inlineStr">
+        <is>
+          <t>Only eligible linked active users are selected. Attendees receive the published event name and fixed public change description; no internal title/reason/comment leaks. Unpublished events produce no attendee notice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>3 - Integration / regression</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>TC_E11S01_15</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>Deduplicate concurrent notification-hook retries</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>Two transactions use the same event, stable change ID and recipient snapshot.</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>1. Call the notification hook concurrently and commit both attempts.</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
+        </is>
+      </c>
+      <c r="J266" s="2" t="inlineStr">
+        <is>
+          <t>Exactly one in-app row and one email-delivery row exist per recipient for the logical change. A new change ID identifies a different business change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>3 - Integration / regression</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>TC_E11S01_16</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>Keep uncommitted notifications invisible and roll back all writes</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>A business transaction has inserted notifications and prepared email delivery rows but has not committed.</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>1. Read from another connection, then force the business transaction to roll back.</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr">
+        <is>
+          <t>The other connection cannot observe the uncommitted messages. After rollback no notification or email-delivery row remains.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B263" s="2" t="inlineStr">
+      <c r="B268" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C263" s="2" t="inlineStr">
+      <c r="C268" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 1 (Status change recorded)</t>
         </is>
       </c>
-      <c r="D263" s="2" t="inlineStr">
+      <c r="D268" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E263" s="2" t="inlineStr">
+      <c r="E268" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_01</t>
         </is>
       </c>
-      <c r="F263" s="2" t="inlineStr">
+      <c r="F268" s="2" t="inlineStr">
         <is>
           <t>Verify that an event status change should be recorded with the actor, action, affected event, and time</t>
         </is>
       </c>
-      <c r="G263" s="2" t="inlineStr">
+      <c r="G268" s="2" t="inlineStr">
         <is>
           <t>Request "Annual Tech Summit" has status "Under Review"</t>
         </is>
       </c>
-      <c r="H263" s="2" t="inlineStr">
+      <c r="H268" s="2" t="inlineStr">
         <is>
           <t>1. As coordinator_1@connectsphere.com, approve the request (status -&gt; Approved)
   2. Log in as a System Administrator
   3. Open the Activity Log and locate the entry</t>
         </is>
       </c>
-      <c r="I263" s="2" t="inlineStr">
+      <c r="I268" s="2" t="inlineStr">
         <is>
           <t>Event: Annual Tech Summit | Action: Approve</t>
         </is>
       </c>
-      <c r="J263" s="2" t="inlineStr">
+      <c r="J268" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded with actor = coordinator_1@connectsphere.com, action = "Status changed to Approved", event = Annual Tech Summit, and a timestamp</t>
         </is>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" s="2" t="n">
+    <row r="269">
+      <c r="A269" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B264" s="2" t="inlineStr">
+      <c r="B269" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C264" s="2" t="inlineStr">
+      <c r="C269" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 2 (Access denial recorded)</t>
         </is>
       </c>
-      <c r="D264" s="2" t="inlineStr">
+      <c r="D269" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E264" s="2" t="inlineStr">
+      <c r="E269" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_02</t>
         </is>
       </c>
-      <c r="F264" s="2" t="inlineStr">
+      <c r="F269" s="2" t="inlineStr">
         <is>
           <t>Verify that a denied access attempt should be recorded with the user, target, and time</t>
         </is>
       </c>
-      <c r="G264" s="2" t="inlineStr">
+      <c r="G269" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is linked to Client A; event EVT-B01 belongs to Client B</t>
         </is>
       </c>
-      <c r="H264" s="2" t="inlineStr">
+      <c r="H269" s="2" t="inlineStr">
         <is>
           <t>1. As organiser_a@clienta.com, attempt to access EVT-B01 directly
   2. Log in as a System Administrator
   3. Check the Activity Log</t>
         </is>
       </c>
-      <c r="I264" s="2" t="inlineStr">
+      <c r="I269" s="2" t="inlineStr">
         <is>
           <t>User: organiser_a@clienta.com | Target: EVT-B01</t>
         </is>
       </c>
-      <c r="J264" s="2" t="inlineStr">
+      <c r="J269" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded with user = organiser_a@clienta.com, target = EVT-B01, action = "Access Denied", and a timestamp</t>
         </is>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" s="2" t="n">
+    <row r="270">
+      <c r="A270" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B265" s="2" t="inlineStr">
+      <c r="B270" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C265" s="2" t="inlineStr">
+      <c r="C270" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 3 (Booking decision recorded)</t>
         </is>
       </c>
-      <c r="D265" s="2" t="inlineStr">
+      <c r="D270" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E265" s="2" t="inlineStr">
+      <c r="E270" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_03</t>
         </is>
       </c>
-      <c r="F265" s="2" t="inlineStr">
+      <c r="F270" s="2" t="inlineStr">
         <is>
           <t>Verify that an approved venue booking should be recorded with the actor, action, affected records, and time</t>
         </is>
       </c>
-      <c r="G265" s="2" t="inlineStr">
+      <c r="G270" s="2" t="inlineStr">
         <is>
           <t>A booking request for Venue Z is pending</t>
         </is>
       </c>
-      <c r="H265" s="2" t="inlineStr">
+      <c r="H270" s="2" t="inlineStr">
         <is>
           <t>1. As Venue Staff, approve the booking request
   2. Log in as a System Administrator
   3. Check the Activity Log</t>
         </is>
       </c>
-      <c r="I265" s="2" t="inlineStr">
+      <c r="I270" s="2" t="inlineStr">
         <is>
           <t>Venue: Venue Z | Action: Approve Booking</t>
         </is>
       </c>
-      <c r="J265" s="2" t="inlineStr">
+      <c r="J270" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded with the actor, action ("Booking Approved"), the affected booking/event, and a timestamp</t>
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" s="2" t="n">
+    <row r="271">
+      <c r="A271" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B266" s="2" t="inlineStr">
+      <c r="B271" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C266" s="2" t="inlineStr">
+      <c r="C271" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 4 (Deactivation recorded)</t>
         </is>
       </c>
-      <c r="D266" s="2" t="inlineStr">
+      <c r="D271" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E266" s="2" t="inlineStr">
+      <c r="E271" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_04</t>
         </is>
       </c>
-      <c r="F266" s="2" t="inlineStr">
+      <c r="F271" s="2" t="inlineStr">
         <is>
           <t>Verify that an account deactivation should be recorded in the activity log</t>
         </is>
       </c>
-      <c r="G266" s="2" t="inlineStr">
+      <c r="G271" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is signed in</t>
         </is>
       </c>
-      <c r="H266" s="2" t="inlineStr">
+      <c r="H271" s="2" t="inlineStr">
         <is>
           <t>1. Deactivate the account
   2. Log in as a System Administrator
   3. Check the Activity Log</t>
         </is>
       </c>
-      <c r="I266" s="2" t="inlineStr">
+      <c r="I271" s="2" t="inlineStr">
         <is>
           <t>Account: organiser_a@clienta.com</t>
         </is>
       </c>
-      <c r="J266" s="2" t="inlineStr">
+      <c r="J271" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded showing the account deactivation with actor and timestamp</t>
         </is>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" s="2" t="n">
+    <row r="272">
+      <c r="A272" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B267" s="2" t="inlineStr">
+      <c r="B272" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C267" s="2" t="inlineStr">
+      <c r="C272" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 5 (Log entries immutable)</t>
         </is>
       </c>
-      <c r="D267" s="2" t="inlineStr">
+      <c r="D272" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E267" s="2" t="inlineStr">
+      <c r="E272" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_05</t>
         </is>
       </c>
-      <c r="F267" s="2" t="inlineStr">
+      <c r="F272" s="2" t="inlineStr">
         <is>
           <t>Verify that any attempt to edit or delete an activity log entry should be refused</t>
         </is>
       </c>
-      <c r="G267" s="2" t="inlineStr">
+      <c r="G272" s="2" t="inlineStr">
         <is>
           <t>A log entry exists: Event = Annual Tech Summit, Action = "Status changed to Approved", Actor = coordinator_1@connectsphere.com (created in TC_E14S02_01)</t>
         </is>
       </c>
-      <c r="H267" s="2" t="inlineStr">
+      <c r="H272" s="2" t="inlineStr">
         <is>
           <t>1. Log in as a System Administrator
   2. Open the Activity Log and locate the entry for Event = Annual Tech Summit, Action = "Status changed to Approved"
@@ -14412,272 +14672,272 @@
   5. If no UI path exists for either action, attempt the same edit and delete via a direct API call to the log entry's ID</t>
         </is>
       </c>
-      <c r="I267" s="2" t="inlineStr">
+      <c r="I272" s="2" t="inlineStr">
         <is>
           <t>Target log entry: Event = Annual Tech Summit, Action = "Status changed to Approved" | Attempted edit: Action -&gt; "Status changed to Rejected"</t>
         </is>
       </c>
-      <c r="J267" s="2" t="inlineStr">
+      <c r="J272" s="2" t="inlineStr">
         <is>
           <t>Both the edit and delete attempts are refused; no UI control exists to modify or remove a log entry, and the direct API call returns an authorization/forbidden error with the entry left unchanged</t>
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" s="2" t="n">
+    <row r="273">
+      <c r="A273" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B268" s="2" t="inlineStr">
+      <c r="B273" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C268" s="2" t="inlineStr">
+      <c r="C273" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 3 (Booking decision recorded)</t>
         </is>
       </c>
-      <c r="D268" s="2" t="inlineStr">
+      <c r="D273" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E268" s="2" t="inlineStr">
+      <c r="E273" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_06</t>
         </is>
       </c>
-      <c r="F268" s="2" t="inlineStr">
+      <c r="F273" s="2" t="inlineStr">
         <is>
           <t>Verify that a rejected venue booking should be recorded with the actor, action, affected records, and time</t>
         </is>
       </c>
-      <c r="G268" s="2" t="inlineStr">
+      <c r="G273" s="2" t="inlineStr">
         <is>
           <t>A booking request for Venue Z is pending</t>
         </is>
       </c>
-      <c r="H268" s="2" t="inlineStr">
+      <c r="H273" s="2" t="inlineStr">
         <is>
           <t>1. As Venue Staff, reject the booking request with reason "Venue unavailable for maintenance"
   2. Log in as a System Administrator
   3. Check the Activity Log</t>
         </is>
       </c>
-      <c r="I268" s="2" t="inlineStr">
+      <c r="I273" s="2" t="inlineStr">
         <is>
           <t>Venue: Venue Z | Action: Reject Booking | Reason: Venue unavailable for maintenance</t>
         </is>
       </c>
-      <c r="J268" s="2" t="inlineStr">
+      <c r="J273" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded with the actor, action ("Booking Rejected"), the affected booking/event, and a timestamp</t>
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" s="2" t="n">
+    <row r="274">
+      <c r="A274" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B269" s="2" t="inlineStr">
+      <c r="B274" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C269" s="2" t="inlineStr">
+      <c r="C274" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 3 (Booking decision recorded)</t>
         </is>
       </c>
-      <c r="D269" s="2" t="inlineStr">
+      <c r="D274" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E269" s="2" t="inlineStr">
+      <c r="E274" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_07</t>
         </is>
       </c>
-      <c r="F269" s="2" t="inlineStr">
+      <c r="F274" s="2" t="inlineStr">
         <is>
           <t>Verify that a released venue booking should be recorded with the actor, action, affected records, and time</t>
         </is>
       </c>
-      <c r="G269" s="2" t="inlineStr">
+      <c r="G274" s="2" t="inlineStr">
         <is>
           <t>Venue Z has a confirmed booking for event "Annual Tech Summit"</t>
         </is>
       </c>
-      <c r="H269" s="2" t="inlineStr">
+      <c r="H274" s="2" t="inlineStr">
         <is>
           <t>1. As Venue Staff or Coordinator, release the confirmed booking for Venue Z (e.g. due to event cancellation)
   2. Log in as a System Administrator
   3. Check the Activity Log</t>
         </is>
       </c>
-      <c r="I269" s="2" t="inlineStr">
+      <c r="I274" s="2" t="inlineStr">
         <is>
           <t>Venue: Venue Z | Action: Release Booking | Event: Annual Tech Summit</t>
         </is>
       </c>
-      <c r="J269" s="2" t="inlineStr">
+      <c r="J274" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded with the actor, action ("Booking Released"), the affected booking/event, and a timestamp</t>
         </is>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" s="2" t="n">
+    <row r="275">
+      <c r="A275" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B270" s="2" t="inlineStr">
+      <c r="B275" s="2" t="inlineStr">
         <is>
           <t>Definition of Done</t>
         </is>
       </c>
-      <c r="C270" s="2" t="inlineStr">
+      <c r="C275" s="2" t="inlineStr">
         <is>
           <t>Definition of Done · BDR T-51 · Week 1 §8a</t>
         </is>
       </c>
-      <c r="D270" s="2" t="inlineStr">
+      <c r="D275" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting</t>
         </is>
       </c>
-      <c r="E270" s="2" t="inlineStr">
+      <c r="E275" s="2" t="inlineStr">
         <is>
           <t>TC_PERF_01</t>
         </is>
       </c>
-      <c r="F270" s="2" t="inlineStr">
+      <c r="F275" s="2" t="inlineStr">
         <is>
           <t>Verify a venue search returns within the 3-second target on a realistic catalogue</t>
         </is>
       </c>
-      <c r="G270" s="2" t="inlineStr">
+      <c r="G275" s="2" t="inlineStr">
         <is>
           <t>The venue catalogue holds 50 venues with layouts, accessibility features and facilities. 200 confirmed bookings exist across the next 90 days. Coordinator coord_a@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H270" s="2" t="inlineStr">
+      <c r="H275" s="2" t="inlineStr">
         <is>
           <t>1. Open the venue search
  2. Enter date 2026-12-01, time 09:00–11:00, expected attendance 120, layout Theatre, accessibility Step-free access
  3. Start a timer on submit and stop it when results render</t>
         </is>
       </c>
-      <c r="I270" s="2" t="inlineStr">
+      <c r="I275" s="2" t="inlineStr">
         <is>
           <t>50 venues · 200 bookings · elapsed time measured client-side</t>
         </is>
       </c>
-      <c r="J270" s="2" t="inlineStr">
+      <c r="J275" s="2" t="inlineStr">
         <is>
           <t>Results render in under 3 seconds. Record the measured time; if it exceeds 3 seconds the story does not meet the Definition of Done</t>
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" s="2" t="n">
+    <row r="276">
+      <c r="A276" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B271" s="2" t="inlineStr">
+      <c r="B276" s="2" t="inlineStr">
         <is>
           <t>Definition of Done</t>
         </is>
       </c>
-      <c r="C271" s="2" t="inlineStr">
+      <c r="C276" s="2" t="inlineStr">
         <is>
           <t>Definition of Done · BDR T-51 · Week 1 §8a</t>
         </is>
       </c>
-      <c r="D271" s="2" t="inlineStr">
+      <c r="D276" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting</t>
         </is>
       </c>
-      <c r="E271" s="2" t="inlineStr">
+      <c r="E276" s="2" t="inlineStr">
         <is>
           <t>TC_PERF_02</t>
         </is>
       </c>
-      <c r="F271" s="2" t="inlineStr">
+      <c r="F276" s="2" t="inlineStr">
         <is>
           <t>Verify the venue availability calendar loads within the 3-second target for a busy month</t>
         </is>
       </c>
-      <c r="G271" s="2" t="inlineStr">
+      <c r="G276" s="2" t="inlineStr">
         <is>
           <t>Orchid Hall has 40 confirmed bookings, 5 tentative holds and 3 maintenance blocks within 2026-12-01 to 2026-12-31</t>
         </is>
       </c>
-      <c r="H271" s="2" t="inlineStr">
+      <c r="H276" s="2" t="inlineStr">
         <is>
           <t>1. Open Orchid Hall in the venue catalogue
  2. Select the calendar for December 2026
  3. Start a timer on selection and stop it when all states have rendered</t>
         </is>
       </c>
-      <c r="I271" s="2" t="inlineStr">
+      <c r="I276" s="2" t="inlineStr">
         <is>
           <t>48 calendar entries in one month · elapsed time measured client-side</t>
         </is>
       </c>
-      <c r="J271" s="2" t="inlineStr">
+      <c r="J276" s="2" t="inlineStr">
         <is>
           <t>The calendar renders all Free, Tentative, Confirmed and Blocked states in under 3 seconds</t>
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" s="2" t="n">
+    <row r="277">
+      <c r="A277" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B272" s="2" t="inlineStr">
+      <c r="B277" s="2" t="inlineStr">
         <is>
           <t>Definition of Done</t>
         </is>
       </c>
-      <c r="C272" s="2" t="inlineStr">
+      <c r="C277" s="2" t="inlineStr">
         <is>
           <t>Definition of Done · BDR T-51 · Week 1 §8a</t>
         </is>
       </c>
-      <c r="D272" s="2" t="inlineStr">
+      <c r="D277" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting</t>
         </is>
       </c>
-      <c r="E272" s="2" t="inlineStr">
+      <c r="E277" s="2" t="inlineStr">
         <is>
           <t>TC_PERF_03</t>
         </is>
       </c>
-      <c r="F272" s="2" t="inlineStr">
+      <c r="F277" s="2" t="inlineStr">
         <is>
           <t>Verify a registration submission completes within the 3-second target near capacity</t>
         </is>
       </c>
-      <c r="G272" s="2" t="inlineStr">
+      <c r="G277" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with Orchid Hall booked, venue capacity 200, and 198 registrations recorded. Attendee attendee_b@example.com is signed in</t>
         </is>
       </c>
-      <c r="H272" s="2" t="inlineStr">
+      <c r="H277" s="2" t="inlineStr">
         <is>
           <t>1. Open event EVT-2001
  2. Submit a registration
  3. Start a timer on submit and stop it when confirmation renders</t>
         </is>
       </c>
-      <c r="I272" s="2" t="inlineStr">
+      <c r="I277" s="2" t="inlineStr">
         <is>
           <t>198 existing registrations · capacity 200 · elapsed time measured client-side</t>
         </is>
       </c>
-      <c r="J272" s="2" t="inlineStr">
+      <c r="J277" s="2" t="inlineStr">
         <is>
           <t>The registration is created and confirmation renders in under 3 seconds, including the capacity check against the booked venue</t>
         </is>

--- a/docs/testing/PROJECT TEST CASES CAA 031026.xlsx
+++ b/docs/testing/PROJECT TEST CASES CAA 031026.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J293"/>
+  <dimension ref="A1:J302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11239,46 +11239,151 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>The event becomes Confirmed and organiser_1 is notified; the Organiser's view lists all three venues with their purpose and period
-## E08-S04</t>
+          <t>The event becomes Confirmed and organiser_1 is notified; the Organiser's view lists all three venues with their purpose and period</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>E08-S03</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>E08-S03 — Scenario 1 (All arrangements complete, event submitted for safety review); assumes O-39, O-40</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>TC_E08S03_08</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>Verify that submitting a fully arranged event for its Operational Safety Check should move it to Safety Review and notify the Safety Officer and Organiser</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>Event "Charity Run" is in Planning with every venue booking Confirmed, equipment fully reserved and technical support assigned; coordinator_1@connectsphere.com is signed in; safety_1@connectsphere.com is a pre-seeded Safety Officer</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>1. Open "Charity Run" and click "Submit for safety check"
+  2. Read the event's status
+  3. Sign in as safety_1@connectsphere.com and open the inbox and the safety review queue
+  4. Sign in as organiser_1@connectsphere.com and open the inbox</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>All readiness checks satisfied</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t>The status is Safety Review, not Confirmed; the Safety Officer has a notification and sees the event in the queue; the Organiser has a notification that the event is awaiting its safety check</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>E08-S03</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>E08-S03 — Scenario 2 (Missing venue blocks submission); Scenario 7 (Confirmed is reached only through approval)</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>4 - Negative (business rule)</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>TC_E08S03_09</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>Verify that submission for safety review should be blocked while a readiness item is outstanding and that no one but a Safety Officer can set Confirmed</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>Event "Alumni Dinner" has one venue booking still Pending; event "Charity Run" is in Safety Review; coordinator_1@connectsphere.com is signed in; lead_1@connectsphere.com is available</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>1. Open "Alumni Dinner" and click "Submit for safety check"
+  2. Issue a set-status-Confirmed action for "Charity Run" against the API as coordinator_1
+  3. Repeat step 2 as lead_1</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>One blocked submission, two unauthorised confirmations</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>Step 1 is blocked and lists the Pending booking by venue; steps 2 and 3 are refused, "Charity Run" stays in Safety Review, and both attempts are in the activity log
+## E08-S04</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B207" s="2" t="inlineStr">
+      <c r="B209" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="C207" s="2" t="inlineStr">
+      <c r="C209" s="2" t="inlineStr">
         <is>
           <t>E08-S04 - Scenario 1 (Reverted with a recorded reason)</t>
         </is>
       </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="D209" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>TC_E08S04_01</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="F209" s="2" t="inlineStr">
         <is>
           <t>Verify that reverting a Confirmed event to Planning with a recorded reason should update its status and notify the Organiser with the reason</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr">
         <is>
           <t>Event "Leadership Summit" has status "Confirmed"</t>
         </is>
       </c>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="H209" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Leadership Summit"
@@ -11287,52 +11392,52 @@
   5. Confirm</t>
         </is>
       </c>
-      <c r="I207" s="2" t="inlineStr">
+      <c r="I209" s="2" t="inlineStr">
         <is>
           <t>Reason: "Venue reported a plumbing issue"</t>
         </is>
       </c>
-      <c r="J207" s="2" t="inlineStr">
+      <c r="J209" s="2" t="inlineStr">
         <is>
           <t>The status changes to "Planning", and organiser_a@clienta.com is notified with the reason "Venue reported a plumbing issue"</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="n">
+    <row r="210">
+      <c r="A210" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B208" s="2" t="inlineStr">
+      <c r="B210" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="C208" s="2" t="inlineStr">
+      <c r="C210" s="2" t="inlineStr">
         <is>
           <t>E08-S04 - Scenario 2 (Registered Attendees notified)</t>
         </is>
       </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>TC_E08S04_02</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>Verify that reverting a Confirmed event with registered Attendees should notify them that arrangements are being revised</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr">
+      <c r="G210" s="2" t="inlineStr">
         <is>
           <t>Event "Leadership Summit" has status "Confirmed" with attendee_a@example.com registered</t>
         </is>
       </c>
-      <c r="H208" s="2" t="inlineStr">
+      <c r="H210" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Leadership Summit"
@@ -11340,169 +11445,66 @@
   4. Check attendee_a@example.com's notifications</t>
         </is>
       </c>
-      <c r="I208" s="2" t="inlineStr">
+      <c r="I210" s="2" t="inlineStr">
         <is>
           <t>Registered Attendee: attendee_a@example.com</t>
         </is>
       </c>
-      <c r="J208" s="2" t="inlineStr">
+      <c r="J210" s="2" t="inlineStr">
         <is>
           <t>attendee_a@example.com receives a notification that arrangements for "Leadership Summit" are being revised</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2" t="n">
+    <row r="211">
+      <c r="A211" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B209" s="2" t="inlineStr">
+      <c r="B211" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="C209" s="2" t="inlineStr">
+      <c r="C211" s="2" t="inlineStr">
         <is>
           <t>E08-S04 - Scenario 3 (No automatic reversion)</t>
         </is>
       </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>TC_E08S04_03</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>Verify that an arrangement breaking on a Confirmed event should not automatically revert its status; the affected arrangement should instead be flagged</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr">
+      <c r="G211" s="2" t="inlineStr">
         <is>
           <t>Event "Leadership Summit" has status "Confirmed"; its venue booking has just been flagged due to a broken arrangement, but no one has reverted the event</t>
         </is>
       </c>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="H211" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Leadership Summit"
   3. Check the event status and the flagged arrangement</t>
         </is>
       </c>
-      <c r="I209" s="2" t="inlineStr">
+      <c r="I211" s="2" t="inlineStr">
         <is>
           <t>Flagged arrangement: venue booking</t>
         </is>
       </c>
-      <c r="J209" s="2" t="inlineStr">
+      <c r="J211" s="2" t="inlineStr">
         <is>
           <t>The event status remains "Confirmed"; the affected venue booking is shown flagged, but no automatic status change has occurred</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>E08-S04</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>E08-S04 (checklist: reversion recorded in activity log)</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="inlineStr">
-        <is>
-          <t>3 - Cross-cutting (audit logging)</t>
-        </is>
-      </c>
-      <c r="E210" s="2" t="inlineStr">
-        <is>
-          <t>TC_E08S04_04</t>
-        </is>
-      </c>
-      <c r="F210" s="2" t="inlineStr">
-        <is>
-          <t>Verify that a reversion from Confirmed to Planning should be recorded in the activity log</t>
-        </is>
-      </c>
-      <c r="G210" s="2" t="inlineStr">
-        <is>
-          <t>Event "Leadership Summit" has just been reverted from "Confirmed" to "Planning" by coordinator_1@connectsphere.com</t>
-        </is>
-      </c>
-      <c r="H210" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in as a System Administrator
-  2. Open the Activity Log and search for "Leadership Summit"</t>
-        </is>
-      </c>
-      <c r="I210" s="2" t="inlineStr">
-        <is>
-          <t>Event: Leadership Summit</t>
-        </is>
-      </c>
-      <c r="J210" s="2" t="inlineStr">
-        <is>
-          <t>An activity log entry exists recording the reversion, with actor = coordinator_1@connectsphere.com, action = "Reverted to Planning", and a timestamp
-## E08-S05</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>E08-S05</t>
-        </is>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>E08-S05 - Scenario 1 (Auto-completed after the end time)</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
-        <is>
-          <t>2 - Happy Path</t>
-        </is>
-      </c>
-      <c r="E211" s="2" t="inlineStr">
-        <is>
-          <t>TC_E08S05_01</t>
-        </is>
-      </c>
-      <c r="F211" s="2" t="inlineStr">
-        <is>
-          <t>Verify that a Confirmed event should automatically become Completed once its last event's end time has passed</t>
-        </is>
-      </c>
-      <c r="G211" s="2" t="inlineStr">
-        <is>
-          <t>Event "Charity Run" has status "Confirmed"; its only event ended at 17:00 on 15/01/2027, which has now passed</t>
-        </is>
-      </c>
-      <c r="H211" s="2" t="inlineStr">
-        <is>
-          <t>1. Wait for (or trigger) the system's next scheduled evaluation after 17:00 on 15/01/2027
-  2. Open event "Charity Run" and check its status</t>
-        </is>
-      </c>
-      <c r="I211" s="2" t="inlineStr">
-        <is>
-          <t>Event end time: 17:00, 15/01/2027 (passed)</t>
-        </is>
-      </c>
-      <c r="J211" s="2" t="inlineStr">
-        <is>
-          <t>The event status has automatically changed to "Completed"</t>
         </is>
       </c>
     </row>
@@ -11512,241 +11514,396 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
+          <t>E08-S04</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>E08-S04 (checklist: reversion recorded in activity log)</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>3 - Cross-cutting (audit logging)</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>TC_E08S04_04</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>Verify that a reversion from Confirmed to Planning should be recorded in the activity log</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>Event "Leadership Summit" has just been reverted from "Confirmed" to "Planning" by coordinator_1@connectsphere.com</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in as a System Administrator
+  2. Open the Activity Log and search for "Leadership Summit"</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>Event: Leadership Summit</t>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr">
+        <is>
+          <t>An activity log entry exists recording the reversion, with actor = coordinator_1@connectsphere.com, action = "Reverted to Planning", and a timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>E08-S04</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>E08-S04 — Scenario 4 (Reverted event passes the safety check again)</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>3 - Integration / regression</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>TC_E08S04_05</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>Verify that a reverted event should pass the Operational Safety Check again before it is Confirmed again</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>Event "Charity Run" was Confirmed through a safety approval, then reverted to Planning by coordinator_1 with a reason; its arrangements are complete again</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>1. As coordinator_1, click "Submit for safety check"
+  2. Read the status and the activity log
+  3. As safety_1@connectsphere.com, approve the event</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>Second pass through the gate</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>After step 1 the status is Safety Review and the log shows both the earlier approval and the new submission; the event is not Confirmed until step 3 completes
+## E08-S05</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C212" s="2" t="inlineStr">
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>E08-S05 - Scenario 1 (Auto-completed after the end time)</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>TC_E08S05_01</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>Verify that a Confirmed event should automatically become Completed once its last event's end time has passed</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>Event "Charity Run" has status "Confirmed"; its only event ended at 17:00 on 15/01/2027, which has now passed</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>1. Wait for (or trigger) the system's next scheduled evaluation after 17:00 on 15/01/2027
+  2. Open event "Charity Run" and check its status</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>Event end time: 17:00, 15/01/2027 (passed)</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr">
+        <is>
+          <t>The event status has automatically changed to "Completed"</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>E08-S05</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
         <is>
           <t>E08-S05 - Scenario 2 (Marked complete manually)</t>
         </is>
       </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="D215" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="E215" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_02</t>
         </is>
       </c>
-      <c r="F212" s="2" t="inlineStr">
+      <c r="F215" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Coordinator should be able to manually mark a Confirmed event complete once its last event has started</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr">
+      <c r="G215" s="2" t="inlineStr">
         <is>
           <t>Event "Volunteer Training Day" has status "Confirmed"; its last (only) event started at 09:00 today and is still in progress</t>
         </is>
       </c>
-      <c r="H212" s="2" t="inlineStr">
+      <c r="H215" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Volunteer Training Day"
   3. Click "Mark Complete"</t>
         </is>
       </c>
-      <c r="I212" s="2" t="inlineStr">
+      <c r="I215" s="2" t="inlineStr">
         <is>
           <t>Event started: 09:00 today</t>
         </is>
       </c>
-      <c r="J212" s="2" t="inlineStr">
+      <c r="J215" s="2" t="inlineStr">
         <is>
           <t>The event status changes to "Completed"</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="2" t="n">
+    <row r="216">
+      <c r="A216" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B213" s="2" t="inlineStr">
+      <c r="B216" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C213" s="2" t="inlineStr">
+      <c r="C216" s="2" t="inlineStr">
         <is>
           <t>E08-S05 - Scenario 3 (Premature completion blocked)</t>
         </is>
       </c>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="D216" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_03</t>
         </is>
       </c>
-      <c r="F213" s="2" t="inlineStr">
+      <c r="F216" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to mark an event complete before its first event has started should be blocked</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr">
+      <c r="G216" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has status "Confirmed"; its first event has not yet started</t>
         </is>
       </c>
-      <c r="H213" s="2" t="inlineStr">
+      <c r="H216" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Tech Conference 2026"
   3. Attempt to click "Mark Complete"</t>
         </is>
       </c>
-      <c r="I213" s="2" t="inlineStr">
+      <c r="I216" s="2" t="inlineStr">
         <is>
           <t>First event: not yet started</t>
         </is>
       </c>
-      <c r="J213" s="2" t="inlineStr">
+      <c r="J216" s="2" t="inlineStr">
         <is>
           <t>The action is blocked; the event cannot be marked complete before it has started</t>
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="2" t="n">
+    <row r="217">
+      <c r="A217" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B214" s="2" t="inlineStr">
+      <c r="B217" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C214" s="2" t="inlineStr">
+      <c r="C217" s="2" t="inlineStr">
         <is>
           <t>E08-S05 - Scenario 4 (Cancelled event never auto-completes)</t>
         </is>
       </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_04</t>
         </is>
       </c>
-      <c r="F214" s="2" t="inlineStr">
+      <c r="F217" s="2" t="inlineStr">
         <is>
           <t>Verify that a Cancelled event should never auto-complete, even after its original end time passes</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr">
+      <c r="G217" s="2" t="inlineStr">
         <is>
           <t>Event "Product Launch Night" has status "Cancelled" (per TC_E10S04_01); its original end time has now passed</t>
         </is>
       </c>
-      <c r="H214" s="2" t="inlineStr">
+      <c r="H217" s="2" t="inlineStr">
         <is>
           <t>1. Wait for (or trigger) the system's next scheduled evaluation after "Product Launch Night"'s original end time
   2. Open event "Product Launch Night" and check its status</t>
         </is>
       </c>
-      <c r="I214" s="2" t="inlineStr">
+      <c r="I217" s="2" t="inlineStr">
         <is>
           <t>Original end time: passed</t>
         </is>
       </c>
-      <c r="J214" s="2" t="inlineStr">
+      <c r="J217" s="2" t="inlineStr">
         <is>
           <t>The event status remains "Cancelled"; it has not been auto-completed</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="2" t="n">
+    <row r="218">
+      <c r="A218" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B215" s="2" t="inlineStr">
+      <c r="B218" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C215" s="2" t="inlineStr">
+      <c r="C218" s="2" t="inlineStr">
         <is>
           <t>E08-S05 (checklist: transition to Completed logged)</t>
         </is>
       </c>
-      <c r="D215" s="2" t="inlineStr">
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting (audit logging)</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_05</t>
         </is>
       </c>
-      <c r="F215" s="2" t="inlineStr">
+      <c r="F218" s="2" t="inlineStr">
         <is>
           <t>Verify that an event's transition to Completed should be recorded in the activity log</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr">
+      <c r="G218" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has just transitioned to "Completed" (per TC_E08S05_01)</t>
         </is>
       </c>
-      <c r="H215" s="2" t="inlineStr">
+      <c r="H218" s="2" t="inlineStr">
         <is>
           <t>1. Log in as a System Administrator
   2. Open the Activity Log and search for "Charity Run"</t>
         </is>
       </c>
-      <c r="I215" s="2" t="inlineStr">
+      <c r="I218" s="2" t="inlineStr">
         <is>
           <t>Event: Charity Run</t>
         </is>
       </c>
-      <c r="J215" s="2" t="inlineStr">
+      <c r="J218" s="2" t="inlineStr">
         <is>
           <t>An activity log entry exists recording the transition to "Completed", with the time it occurred</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2" t="n">
+    <row r="219">
+      <c r="A219" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B216" s="2" t="inlineStr">
+      <c r="B219" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="C216" s="2" t="inlineStr">
+      <c r="C219" s="2" t="inlineStr">
         <is>
           <t>E08-S05 · Scenario 1 (Auto-completed after the end time)</t>
         </is>
       </c>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="D219" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>TC_E08S05_06</t>
         </is>
       </c>
-      <c r="F216" s="2" t="inlineStr">
+      <c r="F219" s="2" t="inlineStr">
         <is>
           <t>Verify that an event auto-completes at the exact end time and not before</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr">
+      <c r="G219" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2002 is Confirmed and its end time is 2026-11-02 17:00:00 +08:00</t>
         </is>
       </c>
-      <c r="H216" s="2" t="inlineStr">
+      <c r="H219" s="2" t="inlineStr">
         <is>
           <t>1. Set the system clock to 2026-11-02 16:59:59 +08:00 and trigger the completion evaluation
  2. Record the event status
@@ -11754,52 +11911,367 @@
  4. Record the event status</t>
         </is>
       </c>
-      <c r="I216" s="2" t="inlineStr">
+      <c r="I219" s="2" t="inlineStr">
         <is>
           <t>Event ends: 2026-11-02 17:00:00 +08:00 · Evaluations at 16:59:59 and 17:00:00</t>
         </is>
       </c>
-      <c r="J216" s="2" t="inlineStr">
-        <is>
-          <t>At 16:59:59 the status remains Confirmed. At 17:00:00 the status becomes Completed and the transition is recorded in the activity log</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="J219" s="2" t="inlineStr">
+        <is>
+          <t>At 16:59:59 the status remains Confirmed. At 17:00:00 the status becomes Completed and the transition is recorded in the activity log
+## E08-S06</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>E08-S06</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>E08-S06 — Scenario 1 (Events awaiting review listed with what the check needs)</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>TC_E08S06_01</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>Verify that the safety review queue should show each waiting event with the information the listed factors need, oldest first</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>Two events entered Safety Review at 10:00 and 11:00; the first has two confirmed venues and a projector reservation; safety_1@connectsphere.com is signed in</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the safety review queue
+  2. Open the 10:00 event</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>Event with two venues, accessibility requirement "wheelchair access", expected attendance 500</t>
+        </is>
+      </c>
+      <c r="J220" s="2" t="inlineStr">
+        <is>
+          <t>The 10:00 event is listed first; its page shows date and time, both venues with capacity, layout and known restrictions, expected attendance 500, the accessibility requirement, the equipment and its placement, and the time it entered Safety Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>E08-S06</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>E08-S06 — Scenario 2 (Structured review of the listed factors); Scenario 3 (Approval confirms the event); Scenario 10 (Every decision is auditable); assumes O-42</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>2 - Happy Path</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>TC_E08S06_02</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>Verify that approving an event after recording every factor as satisfactory should make it Confirmed, notify the Organiser and Coordinator, and log the decision with the checklist</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>"Charity Run" is in Safety Review; safety_1@connectsphere.com is signed in</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>1. Open "Charity Run" from the queue
+  2. Mark each of the seven factors satisfactory with a short comment
+  3. Click "Approve"
+  4. Read the event status, the inboxes of organiser_1 and coordinator_1, and the activity log</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>Seven factors, all satisfactory</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr">
+        <is>
+          <t>The status is Confirmed; organiser_1 and coordinator_1 each have a notification with the confirmed details; the activity log has an entry "safety check approved" by safety_1 with the time and the seven-factor checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>E08-S06</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>E08-S06 — Scenario 4 (Requesting changes returns the event to planning); assumes O-41</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>4 - Negative (business rule)</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>TC_E08S06_03</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>Verify that requesting changes should return the event to Planning with the items to address, flag the affected arrangements and keep it from being Confirmed until resubmitted and approved</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>"Charity Run" is in Safety Review with venue "Riverside Hall" and a stage rig reserved; safety_1@connectsphere.com is signed in</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>1. Mark "equipment placement" unsatisfactory with comment "Stage rig blocks the east exit"
+  2. Click "Request changes" and record the reason
+  3. Read the event status and flags; open coordinator_1's and organiser_1's inboxes
+  4. As coordinator_1, attempt to set the event Confirmed</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>One unsatisfactory factor</t>
+        </is>
+      </c>
+      <c r="J222" s="2" t="inlineStr">
+        <is>
+          <t>The status is Planning; the technical arrangement is flagged for re-review and the venue is not; both inboxes have a notification naming the item; the log records "safety check changes requested"; step 4 is refused</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>E08-S06</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>E08-S06 — Scenario 5 (Rejecting the safety arrangement does not cancel the event); assumes O-41</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>4 - Negative (business rule)</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>TC_E08S06_04</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>Verify that rejecting the safety arrangement should return the event to Planning with a rejection flag without cancelling it</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>"Charity Run" is in Safety Review; safety_1@connectsphere.com is signed in</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>1. Click "Reject safety arrangement" and record the reason "Capacity exceeds safe egress for the layout"
+  2. Read the event status and flags
+  3. As coordinator_1, open the event</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>Overall rejection</t>
+        </is>
+      </c>
+      <c r="J223" s="2" t="inlineStr">
+        <is>
+          <t>The status is Planning, not Cancelled; the event shows "safety arrangement rejected" with the reason; registrations, bookings and reservations are untouched; coordinator_1 and organiser_1 are notified; coordinator_1 can rework and resubmit or cancel through E10-S04</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>E08-S06</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>E08-S06 — Scenario 6 (Reason required for reject or request changes); Scenario 7 (Only a Safety Officer decides)</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>4 - Negative</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>TC_E08S06_05</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>Verify that reject and request changes should require a reason and that no role other than Safety Officer can decide</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>"Charity Run" is in Safety Review; safety_1@connectsphere.com, coordinator_1 and lead_1 are available</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>1. As safety_1, click "Request changes" with an empty reason
+  2. As safety_1, click "Reject safety arrangement" with an empty reason
+  3. As coordinator_1, issue the approve action against the API
+  4. As lead_1, issue the approve action against the API</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>Two empty reasons, two unauthorised actors</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr">
+        <is>
+          <t>Steps 1 and 2 are refused until a reason is given and the status stays Safety Review; steps 3 and 4 are refused and both attempts are logged</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>E08-S06</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>E08-S06 — Scenario 8 (Events confirmed before this story are not re-reviewed); Scenario 9 (Status display and deactivation treat Safety Review as active); regression on E03-S05 and E01-S11 per T-74; assumes O-43</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>3 - Integration / regression</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>TC_E08S06_06</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>Verify that events confirmed before the safety check existed should be untouched and that Safety Review should count as an active status for the tracker and for deactivation</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>"Legacy Gala" was Confirmed before this story; "Charity Run" is in Safety Review and assigned to coordinator_1</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>1. As organiser of "Legacy Gala", open it and its status history
+  2. As organiser_1, open "Charity Run" and its status history (E03-S05)
+  3. As coordinator_1, attempt to deactivate the account (E01-S11)</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>One pre-existing Confirmed event, one event in Safety Review</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="inlineStr">
+        <is>
+          <t>"Legacy Gala" is still Confirmed with no safety record and is not in the queue; "Charity Run" shows "Safety Review" in plain language with the date reached; deactivation is blocked naming "Charity Run" as an active event, so TC_E01S11 cases and TC_E03S05 cases continue to hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B217" s="2" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C217" s="2" t="inlineStr">
+      <c r="C226" s="2" t="inlineStr">
         <is>
           <t>E09-S01 - Scenario 1 (Place reserved in an open event)</t>
         </is>
       </c>
-      <c r="D217" s="2" t="inlineStr">
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_01</t>
         </is>
       </c>
-      <c r="F217" s="2" t="inlineStr">
+      <c r="F226" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting the required registration information for an open event with places remaining should reserve a place and provide a confirmation</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr">
+      <c r="G226" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" is Confirmed, registration is open, and 3 of 5 places remain in its event</t>
         </is>
       </c>
-      <c r="H217" s="2" t="inlineStr">
+      <c r="H226" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Open event "Community Meetup"
@@ -11807,52 +12279,52 @@
   4. Submit registration</t>
         </is>
       </c>
-      <c r="I217" s="2" t="inlineStr">
+      <c r="I226" s="2" t="inlineStr">
         <is>
           <t>Name: Casey Tan | Email: attendee_c@example.com</t>
         </is>
       </c>
-      <c r="J217" s="2" t="inlineStr">
+      <c r="J226" s="2" t="inlineStr">
         <is>
           <t>attendee_c@example.com's place is reserved, and they receive a confirmation containing the event's details (date, time, venue)</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="2" t="n">
+    <row r="227">
+      <c r="A227" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B218" s="2" t="inlineStr">
+      <c r="B227" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C218" s="2" t="inlineStr">
+      <c r="C227" s="2" t="inlineStr">
         <is>
           <t>E09-S01 (checklist: choose events to attend in a multi-event event)</t>
         </is>
       </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="D227" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_02</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr">
+      <c r="F227" s="2" t="inlineStr">
         <is>
           <t>Verify that registering for a multi-event event should let the Attendee choose which events to attend, reserving a place in each chosen event</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr">
+      <c r="G227" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has the event and the event, both open for registration</t>
         </is>
       </c>
-      <c r="H218" s="2" t="inlineStr">
+      <c r="H227" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_d@example.com
   2. Open event "Tech Conference 2026"
@@ -11860,104 +12332,104 @@
   4. Submit registration</t>
         </is>
       </c>
-      <c r="I218" s="2" t="inlineStr">
+      <c r="I227" s="2" t="inlineStr">
         <is>
           <t>Selected: the event only</t>
         </is>
       </c>
-      <c r="J218" s="2" t="inlineStr">
+      <c r="J227" s="2" t="inlineStr">
         <is>
           <t>A place is reserved for attendee_d@example.com in the event only; they are not registered for the event</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="2" t="n">
+    <row r="228">
+      <c r="A228" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B219" s="2" t="inlineStr">
+      <c r="B228" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C219" s="2" t="inlineStr">
+      <c r="C228" s="2" t="inlineStr">
         <is>
           <t>E09-S01 - Scenario 2 (Duplicate registration prevented)</t>
         </is>
       </c>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_03</t>
         </is>
       </c>
-      <c r="F219" s="2" t="inlineStr">
+      <c r="F228" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to register again for a event already registered for should be told so, without creating a duplicate</t>
         </is>
       </c>
-      <c r="G219" s="2" t="inlineStr">
+      <c r="G228" s="2" t="inlineStr">
         <is>
           <t>attendee_c@example.com is already registered for "Community Meetup"'s event</t>
         </is>
       </c>
-      <c r="H219" s="2" t="inlineStr">
+      <c r="H228" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Open event "Community Meetup"
   3. Attempt to register again</t>
         </is>
       </c>
-      <c r="I219" s="2" t="inlineStr">
+      <c r="I228" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_c@example.com (already registered)</t>
         </is>
       </c>
-      <c r="J219" s="2" t="inlineStr">
+      <c r="J228" s="2" t="inlineStr">
         <is>
           <t>attendee_c@example.com is told they are already registered; no duplicate registration is created</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="2" t="n">
+    <row r="229">
+      <c r="A229" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B220" s="2" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C220" s="2" t="inlineStr">
+      <c r="C229" s="2" t="inlineStr">
         <is>
           <t>E09-S01 - Scenario 3 (Missing fields identified)</t>
         </is>
       </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_04</t>
         </is>
       </c>
-      <c r="F220" s="2" t="inlineStr">
+      <c r="F229" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting registration with a required field empty should block registration and identify the missing fields</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr">
+      <c r="G229" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" is open for registration</t>
         </is>
       </c>
-      <c r="H220" s="2" t="inlineStr">
+      <c r="H229" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_e@example.com
   2. Open event "Community Meetup"
@@ -11965,361 +12437,361 @@
   4. Submit registration</t>
         </is>
       </c>
-      <c r="I220" s="2" t="inlineStr">
+      <c r="I229" s="2" t="inlineStr">
         <is>
           <t>Name: filled | Email: (blank)</t>
         </is>
       </c>
-      <c r="J220" s="2" t="inlineStr">
+      <c r="J229" s="2" t="inlineStr">
         <is>
           <t>Registration is blocked, and the Email field is identified as missing</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="2" t="n">
+    <row r="230">
+      <c r="A230" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B221" s="2" t="inlineStr">
+      <c r="B230" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C221" s="2" t="inlineStr">
+      <c r="C230" s="2" t="inlineStr">
         <is>
           <t>E09-S01 - Scenario 4 (Unconfirmed event refused)</t>
         </is>
       </c>
-      <c r="D221" s="2" t="inlineStr">
+      <c r="D230" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E221" s="2" t="inlineStr">
+      <c r="E230" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_05</t>
         </is>
       </c>
-      <c r="F221" s="2" t="inlineStr">
+      <c r="F230" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to register for an event that is not Confirmed should be refused</t>
         </is>
       </c>
-      <c r="G221" s="2" t="inlineStr">
+      <c r="G230" s="2" t="inlineStr">
         <is>
           <t>Event "Draft Networking Event" has status "Planning" (not yet Confirmed)</t>
         </is>
       </c>
-      <c r="H221" s="2" t="inlineStr">
+      <c r="H230" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Attempt to open the registration form for "Draft Networking Event"</t>
         </is>
       </c>
-      <c r="I221" s="2" t="inlineStr">
+      <c r="I230" s="2" t="inlineStr">
         <is>
           <t>Event status: Planning</t>
         </is>
       </c>
-      <c r="J221" s="2" t="inlineStr">
+      <c r="J230" s="2" t="inlineStr">
         <is>
           <t>Registration is refused, since the event is not yet Confirmed</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="2" t="n">
+    <row r="231">
+      <c r="A231" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B222" s="2" t="inlineStr">
+      <c r="B231" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="C222" s="2" t="inlineStr">
+      <c r="C231" s="2" t="inlineStr">
         <is>
           <t>E09-S01 — Scenario 5 (One venue shown for a multi-venue event); assumes O-30</t>
         </is>
       </c>
-      <c r="D222" s="2" t="inlineStr">
+      <c r="D231" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="E231" s="2" t="inlineStr">
         <is>
           <t>TC_E09S01_06</t>
         </is>
       </c>
-      <c r="F222" s="2" t="inlineStr">
+      <c r="F231" s="2" t="inlineStr">
         <is>
           <t>Verify that an Attendee viewing a multi-venue event should see only the primary venue</t>
         </is>
       </c>
-      <c r="G222" s="2" t="inlineStr">
+      <c r="G231" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Summit" is Confirmed with three Confirmed venue bookings and "Grand Auditorium" marked primary; registration is open; attendee_1@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H222" s="2" t="inlineStr">
+      <c r="H231" s="2" t="inlineStr">
         <is>
           <t>1. Open "Tech Summit" from the attendee event list
   2. Read the venue shown
   3. Register</t>
         </is>
       </c>
-      <c r="I222" s="2" t="inlineStr">
+      <c r="I231" s="2" t="inlineStr">
         <is>
           <t>Primary: Grand Auditorium | Others: Seminar Room A, Seminar Room B</t>
         </is>
       </c>
-      <c r="J222" s="2" t="inlineStr">
+      <c r="J231" s="2" t="inlineStr">
         <is>
           <t>The event page shows "Grand Auditorium" as the venue; Seminar Rooms A and B are not offered as separate registration options; registration succeeds once as in TC_E09S01_01
 ## E09-S02</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="2" t="n">
+    <row r="232">
+      <c r="A232" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B223" s="2" t="inlineStr">
+      <c r="B232" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C223" s="2" t="inlineStr">
+      <c r="C232" s="2" t="inlineStr">
         <is>
           <t>E09-S02 (checklist: set a registration limit)</t>
         </is>
       </c>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_01</t>
         </is>
       </c>
-      <c r="F223" s="2" t="inlineStr">
+      <c r="F232" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Organiser should be able to set a registration limit for a event</t>
         </is>
       </c>
-      <c r="G223" s="2" t="inlineStr">
+      <c r="G232" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is signed in; event "Community Meetup"'s event has no registration limit set yet</t>
         </is>
       </c>
-      <c r="H223" s="2" t="inlineStr">
+      <c r="H232" s="2" t="inlineStr">
         <is>
           <t>1. Open event "Community Meetup"
   2. Set the Registration Limit for its event to 5
   3. Save</t>
         </is>
       </c>
-      <c r="I223" s="2" t="inlineStr">
+      <c r="I232" s="2" t="inlineStr">
         <is>
           <t>Registration Limit: 5</t>
         </is>
       </c>
-      <c r="J223" s="2" t="inlineStr">
+      <c r="J232" s="2" t="inlineStr">
         <is>
           <t>The event's registration limit is saved as 5</t>
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="2" t="n">
+    <row r="233">
+      <c r="A233" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B224" s="2" t="inlineStr">
+      <c r="B233" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C224" s="2" t="inlineStr">
+      <c r="C233" s="2" t="inlineStr">
         <is>
           <t>E09-S02 - Scenario 1 (Venue capacity enforced)</t>
         </is>
       </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="D233" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_02</t>
         </is>
       </c>
-      <c r="F224" s="2" t="inlineStr">
+      <c r="F233" s="2" t="inlineStr">
         <is>
           <t>Verify that registration should stop once the event reaches the lower of the Organiser's limit and the booked venue's capacity</t>
         </is>
       </c>
-      <c r="G224" s="2" t="inlineStr">
+      <c r="G233" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s event has an Organiser-set limit of 5 and a booked venue capacity of 8 (the limit is the lower value); 5 Attendees are already registered</t>
         </is>
       </c>
-      <c r="H224" s="2" t="inlineStr">
+      <c r="H233" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_f@example.com
   2. Attempt to register for "Community Meetup"</t>
         </is>
       </c>
-      <c r="I224" s="2" t="inlineStr">
+      <c r="I233" s="2" t="inlineStr">
         <is>
           <t>Registered so far: 5 (effective limit) | Venue capacity: 8</t>
         </is>
       </c>
-      <c r="J224" s="2" t="inlineStr">
+      <c r="J233" s="2" t="inlineStr">
         <is>
           <t>Registration is refused since the event has reached its effective capacity of 5</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="2" t="n">
+    <row r="234">
+      <c r="A234" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B225" s="2" t="inlineStr">
+      <c r="B234" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C225" s="2" t="inlineStr">
+      <c r="C234" s="2" t="inlineStr">
         <is>
           <t>E09-S02 - Scenario 2 (Simultaneous final registration)</t>
         </is>
       </c>
-      <c r="D225" s="2" t="inlineStr">
+      <c r="D234" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (last place, concurrency)</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="E234" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_03</t>
         </is>
       </c>
-      <c r="F225" s="2" t="inlineStr">
+      <c r="F234" s="2" t="inlineStr">
         <is>
           <t>Verify that when only one place remains, two simultaneous registration attempts should result in exactly one success</t>
         </is>
       </c>
-      <c r="G225" s="2" t="inlineStr">
+      <c r="G234" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s event has exactly 1 place remaining</t>
         </is>
       </c>
-      <c r="H225" s="2" t="inlineStr">
+      <c r="H234" s="2" t="inlineStr">
         <is>
           <t>1. Have attendee_g@example.com and attendee_h@example.com submit registration for the same event at the same moment
   2. Check both outcomes</t>
         </is>
       </c>
-      <c r="I225" s="2" t="inlineStr">
+      <c r="I234" s="2" t="inlineStr">
         <is>
           <t>1 place remaining | 2 simultaneous attempts</t>
         </is>
       </c>
-      <c r="J225" s="2" t="inlineStr">
+      <c r="J234" s="2" t="inlineStr">
         <is>
           <t>Exactly one of the two registrations succeeds; the other is told the event is full</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="2" t="n">
+    <row r="235">
+      <c r="A235" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B226" s="2" t="inlineStr">
+      <c r="B235" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C226" s="2" t="inlineStr">
+      <c r="C235" s="2" t="inlineStr">
         <is>
           <t>E09-S02 - Scenario 3 (Full event offers the waiting list)</t>
         </is>
       </c>
-      <c r="D226" s="2" t="inlineStr">
+      <c r="D235" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="E235" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_04</t>
         </is>
       </c>
-      <c r="F226" s="2" t="inlineStr">
+      <c r="F235" s="2" t="inlineStr">
         <is>
           <t>Verify that opening the registration page for a full event should close registration and offer the waiting list where enabled</t>
         </is>
       </c>
-      <c r="G226" s="2" t="inlineStr">
+      <c r="G235" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s event is full (5 of 5 places taken); the waiting list is enabled for this event</t>
         </is>
       </c>
-      <c r="H226" s="2" t="inlineStr">
+      <c r="H235" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_i@example.com
   2. Open the registration page for "Community Meetup"</t>
         </is>
       </c>
-      <c r="I226" s="2" t="inlineStr">
+      <c r="I235" s="2" t="inlineStr">
         <is>
           <t>Event: full | Waiting list: enabled</t>
         </is>
       </c>
-      <c r="J226" s="2" t="inlineStr">
+      <c r="J235" s="2" t="inlineStr">
         <is>
           <t>Registration is shown as closed, and the option to join the waiting list is offered</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="2" t="n">
+    <row r="236">
+      <c r="A236" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B227" s="2" t="inlineStr">
+      <c r="B236" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C227" s="2" t="inlineStr">
+      <c r="C236" s="2" t="inlineStr">
         <is>
           <t>E09-S02 · Scenario 4 (VIP added beyond normal registration)</t>
         </is>
       </c>
-      <c r="D227" s="2" t="inlineStr">
+      <c r="D236" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (just below venue capacity)</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_06</t>
         </is>
       </c>
-      <c r="F227" s="2" t="inlineStr">
+      <c r="F236" s="2" t="inlineStr">
         <is>
           <t>Verify that a VIP can be added manually when normal registration is full but venue capacity is not reached</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr">
+      <c r="G236" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with Orchid Hall booked, venue capacity 200. Normal registration has closed at 199 registrations. Coordinator coord_a@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H227" s="2" t="inlineStr">
+      <c r="H236" s="2" t="inlineStr">
         <is>
           <t>1. Open event EVT-2001
  2. Select Add attendee manually
@@ -12327,52 +12799,52 @@
  4. Confirm the addition</t>
         </is>
       </c>
-      <c r="I227" s="2" t="inlineStr">
+      <c r="I236" s="2" t="inlineStr">
         <is>
           <t>Venue capacity: 200 · Current registrations: 199 · Added: 1</t>
         </is>
       </c>
-      <c r="J227" s="2" t="inlineStr">
+      <c r="J236" s="2" t="inlineStr">
         <is>
           <t>The registration is created, total registrations reach 200, and the record is marked as a manual addition distinguishable from a normal registration</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="2" t="n">
+    <row r="237">
+      <c r="A237" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B228" s="2" t="inlineStr">
+      <c r="B237" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="C228" s="2" t="inlineStr">
+      <c r="C237" s="2" t="inlineStr">
         <is>
           <t>E09-S02 · Scenario 5 (VIP blocked at venue capacity)</t>
         </is>
       </c>
-      <c r="D228" s="2" t="inlineStr">
+      <c r="D237" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at venue capacity)</t>
         </is>
       </c>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t>TC_E09S02_07</t>
         </is>
       </c>
-      <c r="F228" s="2" t="inlineStr">
+      <c r="F237" s="2" t="inlineStr">
         <is>
           <t>Verify that a manual VIP addition is blocked once total registrations equal venue capacity</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr">
+      <c r="G237" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with Orchid Hall booked, venue capacity 200, and 200 registrations already recorded. Coordinator coord_a@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H228" s="2" t="inlineStr">
+      <c r="H237" s="2" t="inlineStr">
         <is>
           <t>1. Open event EVT-2001
  2. Select Add attendee manually
@@ -12380,310 +12852,310 @@
  4. Confirm the addition</t>
         </is>
       </c>
-      <c r="I228" s="2" t="inlineStr">
+      <c r="I237" s="2" t="inlineStr">
         <is>
           <t>Venue capacity: 200 · Current registrations: 200</t>
         </is>
       </c>
-      <c r="J228" s="2" t="inlineStr">
+      <c r="J237" s="2" t="inlineStr">
         <is>
           <t>The addition is blocked with a message stating the booked venue capacity has been reached. No registration is created
 ## E09-S03</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="2" t="n">
+    <row r="238">
+      <c r="A238" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B229" s="2" t="inlineStr">
+      <c r="B238" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C229" s="2" t="inlineStr">
+      <c r="C238" s="2" t="inlineStr">
         <is>
           <t>E09-S03 (checklist: set registration opening/closing dates)</t>
         </is>
       </c>
-      <c r="D229" s="2" t="inlineStr">
+      <c r="D238" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E229" s="2" t="inlineStr">
+      <c r="E238" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_01</t>
         </is>
       </c>
-      <c r="F229" s="2" t="inlineStr">
+      <c r="F238" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Organiser should be able to set the registration opening and closing dates for an event</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr">
+      <c r="G238" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is signed in; event "Community Meetup" has no registration dates set</t>
         </is>
       </c>
-      <c r="H229" s="2" t="inlineStr">
+      <c r="H238" s="2" t="inlineStr">
         <is>
           <t>1. Open event "Community Meetup"
   2. Set Registration Opens: 01/10/2026, Registration Closes: 01/12/2026
   3. Save</t>
         </is>
       </c>
-      <c r="I229" s="2" t="inlineStr">
+      <c r="I238" s="2" t="inlineStr">
         <is>
           <t>Opens: 01/10/2026 | Closes: 01/12/2026</t>
         </is>
       </c>
-      <c r="J229" s="2" t="inlineStr">
+      <c r="J238" s="2" t="inlineStr">
         <is>
           <t>The registration opening and closing dates are saved as entered</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="2" t="n">
+    <row r="239">
+      <c r="A239" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B230" s="2" t="inlineStr">
+      <c r="B239" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C230" s="2" t="inlineStr">
+      <c r="C239" s="2" t="inlineStr">
         <is>
           <t>E09-S03 (checklist: set a withdrawal deadline)</t>
         </is>
       </c>
-      <c r="D230" s="2" t="inlineStr">
+      <c r="D239" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E230" s="2" t="inlineStr">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_02</t>
         </is>
       </c>
-      <c r="F230" s="2" t="inlineStr">
+      <c r="F239" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Organiser should be able to set a withdrawal deadline for an event</t>
         </is>
       </c>
-      <c r="G230" s="2" t="inlineStr">
+      <c r="G239" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is signed in; event "Community Meetup" has no withdrawal deadline set</t>
         </is>
       </c>
-      <c r="H230" s="2" t="inlineStr">
+      <c r="H239" s="2" t="inlineStr">
         <is>
           <t>1. Open event "Community Meetup"
   2. Set Withdrawal Deadline: 10/12/2026
   3. Save</t>
         </is>
       </c>
-      <c r="I230" s="2" t="inlineStr">
+      <c r="I239" s="2" t="inlineStr">
         <is>
           <t>Withdrawal Deadline: 10/12/2026</t>
         </is>
       </c>
-      <c r="J230" s="2" t="inlineStr">
+      <c r="J239" s="2" t="inlineStr">
         <is>
           <t>The withdrawal deadline is saved as 10/12/2026</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="2" t="n">
+    <row r="240">
+      <c r="A240" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B231" s="2" t="inlineStr">
+      <c r="B240" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C231" s="2" t="inlineStr">
+      <c r="C240" s="2" t="inlineStr">
         <is>
           <t>E09-S03 - Scenario 1 (Before registration opens)</t>
         </is>
       </c>
-      <c r="D231" s="2" t="inlineStr">
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (before)</t>
         </is>
       </c>
-      <c r="E231" s="2" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_03</t>
         </is>
       </c>
-      <c r="F231" s="2" t="inlineStr">
+      <c r="F240" s="2" t="inlineStr">
         <is>
           <t>Verify that an Attendee viewing an event before its registration opening date should see registration as not yet open, with the opening date stated</t>
         </is>
       </c>
-      <c r="G231" s="2" t="inlineStr">
+      <c r="G240" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s registration opening date (01/10/2026) has not yet been reached</t>
         </is>
       </c>
-      <c r="H231" s="2" t="inlineStr">
+      <c r="H240" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Open event "Community Meetup"</t>
         </is>
       </c>
-      <c r="I231" s="2" t="inlineStr">
+      <c r="I240" s="2" t="inlineStr">
         <is>
           <t>Opening date: 01/10/2026 (not reached)</t>
         </is>
       </c>
-      <c r="J231" s="2" t="inlineStr">
+      <c r="J240" s="2" t="inlineStr">
         <is>
           <t>Registration is shown as "Not yet open", with the message stating it opens on 01/10/2026</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="2" t="n">
+    <row r="241">
+      <c r="A241" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B232" s="2" t="inlineStr">
+      <c r="B241" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C232" s="2" t="inlineStr">
+      <c r="C241" s="2" t="inlineStr">
         <is>
           <t>E09-S03 - Scenario 2 (After registration closes)</t>
         </is>
       </c>
-      <c r="D232" s="2" t="inlineStr">
+      <c r="D241" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (after)</t>
         </is>
       </c>
-      <c r="E232" s="2" t="inlineStr">
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_04</t>
         </is>
       </c>
-      <c r="F232" s="2" t="inlineStr">
+      <c r="F241" s="2" t="inlineStr">
         <is>
           <t>Verify that an Attendee trying to register after the registration closing date has passed should be refused</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr">
+      <c r="G241" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s registration closing date (01/12/2026) has passed</t>
         </is>
       </c>
-      <c r="H232" s="2" t="inlineStr">
+      <c r="H241" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Attempt to register for "Community Meetup"</t>
         </is>
       </c>
-      <c r="I232" s="2" t="inlineStr">
+      <c r="I241" s="2" t="inlineStr">
         <is>
           <t>Closing date: 01/12/2026 (passed)</t>
         </is>
       </c>
-      <c r="J232" s="2" t="inlineStr">
+      <c r="J241" s="2" t="inlineStr">
         <is>
           <t>Registration is refused, since the closing date has passed</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="2" t="n">
+    <row r="242">
+      <c r="A242" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B233" s="2" t="inlineStr">
+      <c r="B242" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C233" s="2" t="inlineStr">
+      <c r="C242" s="2" t="inlineStr">
         <is>
           <t>E09-S03 - Scenario 3 (Closing date after event start warned)</t>
         </is>
       </c>
-      <c r="D233" s="2" t="inlineStr">
+      <c r="D242" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E233" s="2" t="inlineStr">
+      <c r="E242" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_05</t>
         </is>
       </c>
-      <c r="F233" s="2" t="inlineStr">
+      <c r="F242" s="2" t="inlineStr">
         <is>
           <t>Verify that setting a registration closing date that falls after the event has started should warn the Organiser and ask them to confirm</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr">
+      <c r="G242" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is editing event "Community Meetup", which starts on 15/11/2026</t>
         </is>
       </c>
-      <c r="H233" s="2" t="inlineStr">
+      <c r="H242" s="2" t="inlineStr">
         <is>
           <t>1. Set Registration Closes: 20/11/2026 (after the event's start date)
   2. Click "Save"</t>
         </is>
       </c>
-      <c r="I233" s="2" t="inlineStr">
+      <c r="I242" s="2" t="inlineStr">
         <is>
           <t>Closing date: 20/11/2026 (after event start 15/11/2026)</t>
         </is>
       </c>
-      <c r="J233" s="2" t="inlineStr">
+      <c r="J242" s="2" t="inlineStr">
         <is>
           <t>A warning is shown asking the Organiser to confirm this is intended, before the closing date is saved</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="2" t="n">
+    <row r="243">
+      <c r="A243" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B234" s="2" t="inlineStr">
+      <c r="B243" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C234" s="2" t="inlineStr">
+      <c r="C243" s="2" t="inlineStr">
         <is>
           <t>E09-S03 - Scenario 4 (Waiting list enabled)</t>
         </is>
       </c>
-      <c r="D234" s="2" t="inlineStr">
+      <c r="D243" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="E243" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_06</t>
         </is>
       </c>
-      <c r="F234" s="2" t="inlineStr">
+      <c r="F243" s="2" t="inlineStr">
         <is>
           <t>Verify that enabling the waiting list for an event should offer it to Attendees once a event becomes full</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr">
+      <c r="G243" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is about to enable the waiting list for event "Community Meetup"</t>
         </is>
       </c>
-      <c r="H234" s="2" t="inlineStr">
+      <c r="H243" s="2" t="inlineStr">
         <is>
           <t>1. Open event "Community Meetup"
   2. Toggle "Enable Waiting List" on
@@ -12691,363 +13163,363 @@
   4. Fill the event to capacity and attempt a further registration</t>
         </is>
       </c>
-      <c r="I234" s="2" t="inlineStr">
+      <c r="I243" s="2" t="inlineStr">
         <is>
           <t>Waiting List: Enabled</t>
         </is>
       </c>
-      <c r="J234" s="2" t="inlineStr">
+      <c r="J243" s="2" t="inlineStr">
         <is>
           <t>Once the event is full, the further registration attempt is offered the waiting list instead of being simply refused</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="2" t="n">
+    <row r="244">
+      <c r="A244" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B235" s="2" t="inlineStr">
+      <c r="B244" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C235" s="2" t="inlineStr">
+      <c r="C244" s="2" t="inlineStr">
         <is>
           <t>E09-S03 · Scenario 1 (Before registration opens)</t>
         </is>
       </c>
-      <c r="D235" s="2" t="inlineStr">
+      <c r="D244" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="E244" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_07</t>
         </is>
       </c>
-      <c r="F235" s="2" t="inlineStr">
+      <c r="F244" s="2" t="inlineStr">
         <is>
           <t>Verify that registration succeeds at the exact opening timestamp</t>
         </is>
       </c>
-      <c r="G235" s="2" t="inlineStr">
+      <c r="G244" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with registration opening at 2026-10-01 09:00:00 +08:00. Attendee attendee_a@example.com is signed in. Event EVT-2001 has places remaining</t>
         </is>
       </c>
-      <c r="H235" s="2" t="inlineStr">
+      <c r="H244" s="2" t="inlineStr">
         <is>
           <t>1. Set the system clock to exactly 2026-10-01 09:00:00 +08:00
  2. Open event EVT-2001
  3. Select event EVT-2001 and submit registration</t>
         </is>
       </c>
-      <c r="I235" s="2" t="inlineStr">
+      <c r="I244" s="2" t="inlineStr">
         <is>
           <t>Registration opens: 2026-10-01 09:00:00 +08:00 · Attempt at: 2026-10-01 09:00:00 +08:00</t>
         </is>
       </c>
-      <c r="J235" s="2" t="inlineStr">
+      <c r="J244" s="2" t="inlineStr">
         <is>
           <t>Registration succeeds and a place is reserved. The opening moment is inclusive: registration is open at, not after, the opening timestamp</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="2" t="n">
+    <row r="245">
+      <c r="A245" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B236" s="2" t="inlineStr">
+      <c r="B245" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="C236" s="2" t="inlineStr">
+      <c r="C245" s="2" t="inlineStr">
         <is>
           <t>E09-S03 · Scenario 2 (After registration closes)</t>
         </is>
       </c>
-      <c r="D236" s="2" t="inlineStr">
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
         <is>
           <t>TC_E09S03_08</t>
         </is>
       </c>
-      <c r="F236" s="2" t="inlineStr">
+      <c r="F245" s="2" t="inlineStr">
         <is>
           <t>Verify that registration still succeeds at the exact closing timestamp</t>
         </is>
       </c>
-      <c r="G236" s="2" t="inlineStr">
+      <c r="G245" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with registration closing at 2026-10-20 17:00:00 +08:00. Attendee attendee_b@example.com is signed in. Event EVT-2001 has places remaining</t>
         </is>
       </c>
-      <c r="H236" s="2" t="inlineStr">
+      <c r="H245" s="2" t="inlineStr">
         <is>
           <t>1. Set the system clock to exactly 2026-10-20 17:00:00 +08:00
  2. Open event EVT-2001
  3. Select event EVT-2001 and submit registration</t>
         </is>
       </c>
-      <c r="I236" s="2" t="inlineStr">
+      <c r="I245" s="2" t="inlineStr">
         <is>
           <t>Registration closes: 2026-10-20 17:00:00 +08:00 · Attempt at: 2026-10-20 17:00:00 +08:00</t>
         </is>
       </c>
-      <c r="J236" s="2" t="inlineStr">
+      <c r="J245" s="2" t="inlineStr">
         <is>
           <t>Registration succeeds. The acceptance criterion refuses registration once the closing date "has passed", so at the exact closing instant it has not yet passed. One second later the same attempt must be refused
 ## E09-S04</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="2" t="n">
+    <row r="246">
+      <c r="A246" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B237" s="2" t="inlineStr">
+      <c r="B246" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C237" s="2" t="inlineStr">
+      <c r="C246" s="2" t="inlineStr">
         <is>
           <t>E09-S04 - Scenario 1 (Joined a full event's list)</t>
         </is>
       </c>
-      <c r="D237" s="2" t="inlineStr">
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_01</t>
         </is>
       </c>
-      <c r="F237" s="2" t="inlineStr">
+      <c r="F246" s="2" t="inlineStr">
         <is>
           <t>Verify that joining the waiting list for a full event with the list enabled should add the Attendee and confirm their position</t>
         </is>
       </c>
-      <c r="G237" s="2" t="inlineStr">
+      <c r="G246" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s event is full; the waiting list is enabled and currently empty</t>
         </is>
       </c>
-      <c r="H237" s="2" t="inlineStr">
+      <c r="H246" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_i@example.com
   2. Open the registration page for "Community Meetup"
   3. Click "Join Waiting List"</t>
         </is>
       </c>
-      <c r="I237" s="2" t="inlineStr">
+      <c r="I246" s="2" t="inlineStr">
         <is>
           <t>Waiting list: enabled, currently empty</t>
         </is>
       </c>
-      <c r="J237" s="2" t="inlineStr">
+      <c r="J246" s="2" t="inlineStr">
         <is>
           <t>attendee_i@example.com is added to the waiting list and shown their position (e.g. "Position 1")</t>
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="2" t="n">
+    <row r="247">
+      <c r="A247" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B238" s="2" t="inlineStr">
+      <c r="B247" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C238" s="2" t="inlineStr">
+      <c r="C247" s="2" t="inlineStr">
         <is>
           <t>E09-S04 - Scenario 2 (Released place notified to all)</t>
         </is>
       </c>
-      <c r="D238" s="2" t="inlineStr">
+      <c r="D247" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_02</t>
         </is>
       </c>
-      <c r="F238" s="2" t="inlineStr">
+      <c r="F247" s="2" t="inlineStr">
         <is>
           <t>Verify that when a place is released in a event with a waiting list, all waitlisted Attendees should be notified and the place claimed on a first-come, first-served basis</t>
         </is>
       </c>
-      <c r="G238" s="2" t="inlineStr">
+      <c r="G247" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s waiting list has attendee_i@example.com (position 1) and attendee_j@example.com (position 2)</t>
         </is>
       </c>
-      <c r="H238" s="2" t="inlineStr">
+      <c r="H247" s="2" t="inlineStr">
         <is>
           <t>1. Have registered Attendee attendee_m@example.com withdraw from "Community Meetup", releasing one place
   2. Check notifications for attendee_i@example.com and attendee_j@example.com
   3. Have attendee_i@example.com claim the released place first</t>
         </is>
       </c>
-      <c r="I238" s="2" t="inlineStr">
+      <c r="I247" s="2" t="inlineStr">
         <is>
           <t>Waiting list: attendee_i@example.com (1st), attendee_j@example.com (2nd)</t>
         </is>
       </c>
-      <c r="J238" s="2" t="inlineStr">
+      <c r="J247" s="2" t="inlineStr">
         <is>
           <t>Both waitlisted Attendees are notified of the released place; attendee_i@example.com successfully claims it since they acted first</t>
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="2" t="n">
+    <row r="248">
+      <c r="A248" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B239" s="2" t="inlineStr">
+      <c r="B248" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C239" s="2" t="inlineStr">
+      <c r="C248" s="2" t="inlineStr">
         <is>
           <t>E09-S04 - Scenario 3 (Claimed place leaves the list)</t>
         </is>
       </c>
-      <c r="D239" s="2" t="inlineStr">
+      <c r="D248" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr">
+      <c r="E248" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_03</t>
         </is>
       </c>
-      <c r="F239" s="2" t="inlineStr">
+      <c r="F248" s="2" t="inlineStr">
         <is>
           <t>Verify that claiming a released place should remove the Attendee from the waiting list for that event</t>
         </is>
       </c>
-      <c r="G239" s="2" t="inlineStr">
+      <c r="G248" s="2" t="inlineStr">
         <is>
           <t>attendee_i@example.com has just claimed a released place in "Community Meetup"'s event</t>
         </is>
       </c>
-      <c r="H239" s="2" t="inlineStr">
+      <c r="H248" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_i@example.com
   2. Check the waiting list for "Community Meetup"'s event</t>
         </is>
       </c>
-      <c r="I239" s="2" t="inlineStr">
+      <c r="I248" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_i@example.com (just claimed a place)</t>
         </is>
       </c>
-      <c r="J239" s="2" t="inlineStr">
+      <c r="J248" s="2" t="inlineStr">
         <is>
           <t>attendee_i@example.com no longer appears on the waiting list for that event, since they are now registered</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="2" t="n">
+    <row r="249">
+      <c r="A249" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B240" s="2" t="inlineStr">
+      <c r="B249" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C240" s="2" t="inlineStr">
+      <c r="C249" s="2" t="inlineStr">
         <is>
           <t>E09-S04 - Scenario 4 (Disabled list offers nothing)</t>
         </is>
       </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_04</t>
         </is>
       </c>
-      <c r="F240" s="2" t="inlineStr">
+      <c r="F249" s="2" t="inlineStr">
         <is>
           <t>Verify that a full event should not offer a waiting list when the Organiser has disabled it</t>
         </is>
       </c>
-      <c r="G240" s="2" t="inlineStr">
+      <c r="G249" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has the waiting list disabled; the event is full</t>
         </is>
       </c>
-      <c r="H240" s="2" t="inlineStr">
+      <c r="H249" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_k@example.com
   2. Open the registration page for the event of "Tech Conference 2026"</t>
         </is>
       </c>
-      <c r="I240" s="2" t="inlineStr">
+      <c r="I249" s="2" t="inlineStr">
         <is>
           <t>Waiting list: disabled | the event: full</t>
         </is>
       </c>
-      <c r="J240" s="2" t="inlineStr">
+      <c r="J249" s="2" t="inlineStr">
         <is>
           <t>No waiting list option is offered; registration is simply shown as closed</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="2" t="n">
+    <row r="250">
+      <c r="A250" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B241" s="2" t="inlineStr">
+      <c r="B250" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="C241" s="2" t="inlineStr">
+      <c r="C250" s="2" t="inlineStr">
         <is>
           <t>E09-S04 (checklist: leave the waiting list)</t>
         </is>
       </c>
-      <c r="D241" s="2" t="inlineStr">
+      <c r="D250" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E241" s="2" t="inlineStr">
+      <c r="E250" s="2" t="inlineStr">
         <is>
           <t>TC_E09S04_05</t>
         </is>
       </c>
-      <c r="F241" s="2" t="inlineStr">
+      <c r="F250" s="2" t="inlineStr">
         <is>
           <t>Verify that an Attendee should be able to voluntarily leave the waiting list before a place is released</t>
         </is>
       </c>
-      <c r="G241" s="2" t="inlineStr">
+      <c r="G250" s="2" t="inlineStr">
         <is>
           <t>attendee_j@example.com is on the waiting list for "Community Meetup"'s event, position 2</t>
         </is>
       </c>
-      <c r="H241" s="2" t="inlineStr">
+      <c r="H250" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_j@example.com
   2. Open the waiting list status for "Community Meetup"
@@ -13055,622 +13527,622 @@
   4. Confirm</t>
         </is>
       </c>
-      <c r="I241" s="2" t="inlineStr">
+      <c r="I250" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_j@example.com</t>
         </is>
       </c>
-      <c r="J241" s="2" t="inlineStr">
+      <c r="J250" s="2" t="inlineStr">
         <is>
           <t>attendee_j@example.com is removed from the waiting list and no longer receives notifications about released places for that event
 ## E09-S05</t>
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="2" t="n">
+    <row r="251">
+      <c r="A251" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B242" s="2" t="inlineStr">
+      <c r="B251" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="C242" s="2" t="inlineStr">
+      <c r="C251" s="2" t="inlineStr">
         <is>
           <t>E09-S05 - Scenario 1 (Registration withdrawn)</t>
         </is>
       </c>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="D251" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E242" s="2" t="inlineStr">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>TC_E09S05_01</t>
         </is>
       </c>
-      <c r="F242" s="2" t="inlineStr">
+      <c r="F251" s="2" t="inlineStr">
         <is>
           <t>Verify that withdrawing from a single event before the withdrawal deadline should cancel that registration and release the place, leaving other events unaffected</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr">
+      <c r="G251" s="2" t="inlineStr">
         <is>
           <t>attendee_d@example.com is registered for both the event and the event of "Tech Conference 2026"; the withdrawal deadline has not passed</t>
         </is>
       </c>
-      <c r="H242" s="2" t="inlineStr">
+      <c r="H251" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_d@example.com
   2. Open "My Registrations"
   3. Withdraw from the event only</t>
         </is>
       </c>
-      <c r="I242" s="2" t="inlineStr">
+      <c r="I251" s="2" t="inlineStr">
         <is>
           <t>Withdrawing from: the event only</t>
         </is>
       </c>
-      <c r="J242" s="2" t="inlineStr">
+      <c r="J251" s="2" t="inlineStr">
         <is>
           <t>The the event registration is cancelled and its place becomes available again; attendee_d@example.com remains registered for the event</t>
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="2" t="n">
+    <row r="252">
+      <c r="A252" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B243" s="2" t="inlineStr">
+      <c r="B252" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="C243" s="2" t="inlineStr">
+      <c r="C252" s="2" t="inlineStr">
         <is>
           <t>E09-S05 - Scenario 2 (Withdrawal after deadline refused)</t>
         </is>
       </c>
-      <c r="D243" s="2" t="inlineStr">
+      <c r="D252" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E243" s="2" t="inlineStr">
+      <c r="E252" s="2" t="inlineStr">
         <is>
           <t>TC_E09S05_03</t>
         </is>
       </c>
-      <c r="F243" s="2" t="inlineStr">
+      <c r="F252" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to withdraw after the withdrawal deadline has passed should be refused, with a contact provided for assistance</t>
         </is>
       </c>
-      <c r="G243" s="2" t="inlineStr">
+      <c r="G252" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s withdrawal deadline (10/12/2026) has passed</t>
         </is>
       </c>
-      <c r="H243" s="2" t="inlineStr">
+      <c r="H252" s="2" t="inlineStr">
         <is>
           <t>1. Log in as attendee_c@example.com
   2. Attempt to withdraw from "Community Meetup"</t>
         </is>
       </c>
-      <c r="I243" s="2" t="inlineStr">
+      <c r="I252" s="2" t="inlineStr">
         <is>
           <t>Withdrawal deadline: 10/12/2026 (passed)</t>
         </is>
       </c>
-      <c r="J243" s="2" t="inlineStr">
+      <c r="J252" s="2" t="inlineStr">
         <is>
           <t>Withdrawal is refused with the message "Withdrawal has closed" and a contact is provided for assistance</t>
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="2" t="n">
+    <row r="253">
+      <c r="A253" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B244" s="2" t="inlineStr">
+      <c r="B253" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="C244" s="2" t="inlineStr">
+      <c r="C253" s="2" t="inlineStr">
         <is>
           <t>E09-S05 · Scenario 2 (Withdrawal after deadline refused)</t>
         </is>
       </c>
-      <c r="D244" s="2" t="inlineStr">
+      <c r="D253" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E244" s="2" t="inlineStr">
+      <c r="E253" s="2" t="inlineStr">
         <is>
           <t>TC_E09S05_04</t>
         </is>
       </c>
-      <c r="F244" s="2" t="inlineStr">
+      <c r="F253" s="2" t="inlineStr">
         <is>
           <t>Verify that withdrawal succeeds at the exact withdrawal deadline</t>
         </is>
       </c>
-      <c r="G244" s="2" t="inlineStr">
+      <c r="G253" s="2" t="inlineStr">
         <is>
           <t>Attendee attendee_a@example.com is registered for event EVT-2001. The withdrawal deadline for event EVT-2001 is 2026-10-25 23:59:59 +08:00</t>
         </is>
       </c>
-      <c r="H244" s="2" t="inlineStr">
+      <c r="H253" s="2" t="inlineStr">
         <is>
           <t>1. Set the system clock to exactly 2026-10-25 23:59:59 +08:00
  2. Sign in as attendee_a@example.com
  3. Open the registration for EVT-2001 and select Withdraw</t>
         </is>
       </c>
-      <c r="I244" s="2" t="inlineStr">
+      <c r="I253" s="2" t="inlineStr">
         <is>
           <t>Withdrawal deadline: 2026-10-25 23:59:59 +08:00 · Attempt at: 2026-10-25 23:59:59 +08:00</t>
         </is>
       </c>
-      <c r="J244" s="2" t="inlineStr">
+      <c r="J253" s="2" t="inlineStr">
         <is>
           <t>The withdrawal succeeds, the registration status becomes Withdrawn and the place is released. Every waitlisted Attendee for EVT-2001 is notified that a place is available
 ## E09-S06</t>
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="2" t="n">
+    <row r="254">
+      <c r="A254" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B245" s="2" t="inlineStr">
+      <c r="B254" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="C245" s="2" t="inlineStr">
+      <c r="C254" s="2" t="inlineStr">
         <is>
           <t>E09-S06 - Scenario 1 (Attendance marked after completion)</t>
         </is>
       </c>
-      <c r="D245" s="2" t="inlineStr">
+      <c r="D254" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E245" s="2" t="inlineStr">
+      <c r="E254" s="2" t="inlineStr">
         <is>
           <t>TC_E09S06_01</t>
         </is>
       </c>
-      <c r="F245" s="2" t="inlineStr">
+      <c r="F254" s="2" t="inlineStr">
         <is>
           <t>Verify that marking a registered Attendee as attended for a event after the event is Completed should update their record without changing the registration figure</t>
         </is>
       </c>
-      <c r="G245" s="2" t="inlineStr">
+      <c r="G254" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has status "Completed" (per TC_E08S05_01); attendee_a@example.com is registered for its event</t>
         </is>
       </c>
-      <c r="H245" s="2" t="inlineStr">
+      <c r="H254" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the completed event "Charity Run"
   3. Mark attendee_a@example.com as "Attended"</t>
         </is>
       </c>
-      <c r="I245" s="2" t="inlineStr">
+      <c r="I254" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_a@example.com</t>
         </is>
       </c>
-      <c r="J245" s="2" t="inlineStr">
+      <c r="J254" s="2" t="inlineStr">
         <is>
           <t>attendee_a@example.com's record shows "Attended"; the total registration figure for the event remains unchanged</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="2" t="n">
+    <row r="255">
+      <c r="A255" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B246" s="2" t="inlineStr">
+      <c r="B255" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="C246" s="2" t="inlineStr">
+      <c r="C255" s="2" t="inlineStr">
         <is>
           <t>E09-S06 - Scenario 2 (Registered but not attended)</t>
         </is>
       </c>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="D255" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="E255" s="2" t="inlineStr">
         <is>
           <t>TC_E09S06_02</t>
         </is>
       </c>
-      <c r="F246" s="2" t="inlineStr">
+      <c r="F255" s="2" t="inlineStr">
         <is>
           <t>Verify that a registered Attendee who did not attend should be shown as registered but not attended once the event is Completed</t>
         </is>
       </c>
-      <c r="G246" s="2" t="inlineStr">
+      <c r="G255" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has status "Completed"; attendee_b@example.com was registered but has not been marked attended</t>
         </is>
       </c>
-      <c r="H246" s="2" t="inlineStr">
+      <c r="H255" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the completed event "Charity Run"
   3. Check attendee_b@example.com's status</t>
         </is>
       </c>
-      <c r="I246" s="2" t="inlineStr">
+      <c r="I255" s="2" t="inlineStr">
         <is>
           <t>Attendee: attendee_b@example.com (registered, not marked attended)</t>
         </is>
       </c>
-      <c r="J246" s="2" t="inlineStr">
+      <c r="J255" s="2" t="inlineStr">
         <is>
           <t>attendee_b@example.com is shown as "Registered but not attended"</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="2" t="n">
+    <row r="256">
+      <c r="A256" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B247" s="2" t="inlineStr">
+      <c r="B256" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="C247" s="2" t="inlineStr">
+      <c r="C256" s="2" t="inlineStr">
         <is>
           <t>E09-S06 - Scenario 3 (Recording before completion blocked)</t>
         </is>
       </c>
-      <c r="D247" s="2" t="inlineStr">
+      <c r="D256" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E247" s="2" t="inlineStr">
+      <c r="E256" s="2" t="inlineStr">
         <is>
           <t>TC_E09S06_03</t>
         </is>
       </c>
-      <c r="F247" s="2" t="inlineStr">
+      <c r="F256" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to record attendance before the event is Completed should be blocked</t>
         </is>
       </c>
-      <c r="G247" s="2" t="inlineStr">
+      <c r="G256" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has status "Confirmed" (not yet Completed)</t>
         </is>
       </c>
-      <c r="H247" s="2" t="inlineStr">
+      <c r="H256" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Tech Conference 2026"
   3. Attempt to mark an Attendee as attended</t>
         </is>
       </c>
-      <c r="I247" s="2" t="inlineStr">
+      <c r="I256" s="2" t="inlineStr">
         <is>
           <t>Event status: Confirmed (not Completed)</t>
         </is>
       </c>
-      <c r="J247" s="2" t="inlineStr">
+      <c r="J256" s="2" t="inlineStr">
         <is>
           <t>The action is blocked; attendance cannot be recorded before the event is Completed</t>
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="2" t="n">
+    <row r="257">
+      <c r="A257" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B248" s="2" t="inlineStr">
+      <c r="B257" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="C248" s="2" t="inlineStr">
+      <c r="C257" s="2" t="inlineStr">
         <is>
           <t>E09-S06 (checklist: registration/attendance counts viewable side by side)</t>
         </is>
       </c>
-      <c r="D248" s="2" t="inlineStr">
+      <c r="D257" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E248" s="2" t="inlineStr">
+      <c r="E257" s="2" t="inlineStr">
         <is>
           <t>TC_E09S06_04</t>
         </is>
       </c>
-      <c r="F248" s="2" t="inlineStr">
+      <c r="F257" s="2" t="inlineStr">
         <is>
           <t>Verify that registration and attendance counts should be viewable side by side for each event</t>
         </is>
       </c>
-      <c r="G248" s="2" t="inlineStr">
+      <c r="G257" s="2" t="inlineStr">
         <is>
           <t>Event "Charity Run" has status "Completed"; its event had 5 registrations and 4 marked attended</t>
         </is>
       </c>
-      <c r="H248" s="2" t="inlineStr">
+      <c r="H257" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the completed event "Charity Run"
   3. View the event's registration and attendance summary</t>
         </is>
       </c>
-      <c r="I248" s="2" t="inlineStr">
+      <c r="I257" s="2" t="inlineStr">
         <is>
           <t>Registered: 5 | Attended: 4</t>
         </is>
       </c>
-      <c r="J248" s="2" t="inlineStr">
+      <c r="J257" s="2" t="inlineStr">
         <is>
           <t>The summary shows "Registered: 5" and "Attended: 4" together, side by side
 ## E09-S07</t>
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="2" t="n">
+    <row r="258">
+      <c r="A258" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B249" s="2" t="inlineStr">
+      <c r="B258" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="C249" s="2" t="inlineStr">
+      <c r="C258" s="2" t="inlineStr">
         <is>
           <t>E09-S07 - Scenario 1 (Registrations grouped by event)</t>
         </is>
       </c>
-      <c r="D249" s="2" t="inlineStr">
+      <c r="D258" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E249" s="2" t="inlineStr">
+      <c r="E258" s="2" t="inlineStr">
         <is>
           <t>TC_E09S07_01</t>
         </is>
       </c>
-      <c r="F249" s="2" t="inlineStr">
+      <c r="F258" s="2" t="inlineStr">
         <is>
           <t>Verify that opening the registration list for an event with registered Attendees should show each Attendee's name, email address and contact number</t>
         </is>
       </c>
-      <c r="G249" s="2" t="inlineStr">
+      <c r="G258" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has attendee_a@example.com and attendee_b@example.com registered, each with a name, email address and contact number on file</t>
         </is>
       </c>
-      <c r="H249" s="2" t="inlineStr">
+      <c r="H258" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the registration list for "Tech Conference 2026"</t>
         </is>
       </c>
-      <c r="I249" s="2" t="inlineStr">
+      <c r="I258" s="2" t="inlineStr">
         <is>
           <t>attendee_a@example.com: +65 9123 4567 | attendee_b@example.com: +65 9234 5678</t>
         </is>
       </c>
-      <c r="J249" s="2" t="inlineStr">
+      <c r="J258" s="2" t="inlineStr">
         <is>
           <t>The list shows each Attendee's name, email address and contact number: attendee_a@example.com and attendee_b@example.com both appear with their full contact details</t>
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="2" t="n">
+    <row r="259">
+      <c r="A259" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B250" s="2" t="inlineStr">
+      <c r="B259" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="C250" s="2" t="inlineStr">
+      <c r="C259" s="2" t="inlineStr">
         <is>
           <t>E09-S07 - Scenario 2 (Counts and remaining capacity)</t>
         </is>
       </c>
-      <c r="D250" s="2" t="inlineStr">
+      <c r="D259" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E250" s="2" t="inlineStr">
+      <c r="E259" s="2" t="inlineStr">
         <is>
           <t>TC_E09S07_02</t>
         </is>
       </c>
-      <c r="F250" s="2" t="inlineStr">
+      <c r="F259" s="2" t="inlineStr">
         <is>
           <t>Verify that the registration list should show the registered count and remaining capacity per event</t>
         </is>
       </c>
-      <c r="G250" s="2" t="inlineStr">
+      <c r="G259" s="2" t="inlineStr">
         <is>
           <t>"Tech Conference 2026" the event has 100 registered out of a capacity of 150</t>
         </is>
       </c>
-      <c r="H250" s="2" t="inlineStr">
+      <c r="H259" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the registration list for "Tech Conference 2026"</t>
         </is>
       </c>
-      <c r="I250" s="2" t="inlineStr">
+      <c r="I259" s="2" t="inlineStr">
         <is>
           <t>the event: 100 registered, capacity 150</t>
         </is>
       </c>
-      <c r="J250" s="2" t="inlineStr">
+      <c r="J259" s="2" t="inlineStr">
         <is>
           <t>the event shows "100 registered" and "50 remaining"</t>
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="2" t="n">
+    <row r="260">
+      <c r="A260" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B251" s="2" t="inlineStr">
+      <c r="B260" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="C251" s="2" t="inlineStr">
+      <c r="C260" s="2" t="inlineStr">
         <is>
           <t>E09-S07 - Scenario 3 (Unmanaged event refused)</t>
         </is>
       </c>
-      <c r="D251" s="2" t="inlineStr">
+      <c r="D260" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E251" s="2" t="inlineStr">
+      <c r="E260" s="2" t="inlineStr">
         <is>
           <t>TC_E09S07_03</t>
         </is>
       </c>
-      <c r="F251" s="2" t="inlineStr">
+      <c r="F260" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to open the registration list for an event that does not belong to the Organiser's client organisation should be refused</t>
         </is>
       </c>
-      <c r="G251" s="2" t="inlineStr">
+      <c r="G260" s="2" t="inlineStr">
         <is>
           <t>organiser_b@clienta.com is linked to Client B; event "Annual Tech Summit" belongs to Client A</t>
         </is>
       </c>
-      <c r="H251" s="2" t="inlineStr">
+      <c r="H260" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_b@clienta.com
   2. Attempt to open the registration list for "Annual Tech Summit"</t>
         </is>
       </c>
-      <c r="I251" s="2" t="inlineStr">
+      <c r="I260" s="2" t="inlineStr">
         <is>
           <t>Acting user: organiser_b@clienta.com | Event: Annual Tech Summit (Client A)</t>
         </is>
       </c>
-      <c r="J251" s="2" t="inlineStr">
+      <c r="J260" s="2" t="inlineStr">
         <is>
           <t>Access is refused, since "Annual Tech Summit" does not belong to organiser_b@clienta.com's client organisation</t>
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="2" t="n">
+    <row r="261">
+      <c r="A261" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B252" s="2" t="inlineStr">
+      <c r="B261" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="C252" s="2" t="inlineStr">
+      <c r="C261" s="2" t="inlineStr">
         <is>
           <t>E09-S07 - Scenario 4 (Waitlist shown separately)</t>
         </is>
       </c>
-      <c r="D252" s="2" t="inlineStr">
+      <c r="D261" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="E261" s="2" t="inlineStr">
         <is>
           <t>TC_E09S07_04</t>
         </is>
       </c>
-      <c r="F252" s="2" t="inlineStr">
+      <c r="F261" s="2" t="inlineStr">
         <is>
           <t>Verify that waitlisted Attendees should be shown separately from registered Attendees on the registration list</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr">
+      <c r="G261" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s event has 5 registered Attendees and 2 on the waiting list</t>
         </is>
       </c>
-      <c r="H252" s="2" t="inlineStr">
+      <c r="H261" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the registration list for "Community Meetup"</t>
         </is>
       </c>
-      <c r="I252" s="2" t="inlineStr">
+      <c r="I261" s="2" t="inlineStr">
         <is>
           <t>Registered: 5 | Waitlisted: 2</t>
         </is>
       </c>
-      <c r="J252" s="2" t="inlineStr">
+      <c r="J261" s="2" t="inlineStr">
         <is>
           <t>The 5 registered Attendees and the 2 waitlisted Attendees are shown in clearly separate sections/lists</t>
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="2" t="n">
+    <row r="262">
+      <c r="A262" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B253" s="2" t="inlineStr">
+      <c r="B262" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C253" s="2" t="inlineStr">
+      <c r="C262" s="2" t="inlineStr">
         <is>
           <t>E10-S01 - Scenario 1 (Change request recorded)</t>
         </is>
       </c>
-      <c r="D253" s="2" t="inlineStr">
+      <c r="D262" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E253" s="2" t="inlineStr">
+      <c r="E262" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_01</t>
         </is>
       </c>
-      <c r="F253" s="2" t="inlineStr">
+      <c r="F262" s="2" t="inlineStr">
         <is>
           <t>Verify that submitting a change request on an approved or confirmed event should notify the assigned Coordinator and record the request against the event</t>
         </is>
       </c>
-      <c r="G253" s="2" t="inlineStr">
+      <c r="G262" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" has status "Confirmed"</t>
         </is>
       </c>
-      <c r="H253" s="2" t="inlineStr">
+      <c r="H262" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Community Meetup"
@@ -13679,155 +14151,155 @@
   5. Submit</t>
         </is>
       </c>
-      <c r="I253" s="2" t="inlineStr">
+      <c r="I262" s="2" t="inlineStr">
         <is>
           <t>Change description: "Increase expected attendance to 10"</t>
         </is>
       </c>
-      <c r="J253" s="2" t="inlineStr">
+      <c r="J262" s="2" t="inlineStr">
         <is>
           <t>coordinator_1@connectsphere.com is notified, and the change request is recorded against "Community Meetup"</t>
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="2" t="n">
+    <row r="263">
+      <c r="A263" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B254" s="2" t="inlineStr">
+      <c r="B263" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C254" s="2" t="inlineStr">
+      <c r="C263" s="2" t="inlineStr">
         <is>
           <t>E10-S01 - Scenario 2 (Confirmed details shown alongside)</t>
         </is>
       </c>
-      <c r="D254" s="2" t="inlineStr">
+      <c r="D263" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E254" s="2" t="inlineStr">
+      <c r="E263" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_02</t>
         </is>
       </c>
-      <c r="F254" s="2" t="inlineStr">
+      <c r="F263" s="2" t="inlineStr">
         <is>
           <t>Verify that viewing an event with a pending change request should still show the currently confirmed details alongside the pending request</t>
         </is>
       </c>
-      <c r="G254" s="2" t="inlineStr">
+      <c r="G263" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" has a pending change request; its confirmed details (venue, date, time) remain unchanged</t>
         </is>
       </c>
-      <c r="H254" s="2" t="inlineStr">
+      <c r="H263" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Community Meetup"</t>
         </is>
       </c>
-      <c r="I254" s="2" t="inlineStr">
+      <c r="I263" s="2" t="inlineStr">
         <is>
           <t>Pending request: Increase expected attendance to 10</t>
         </is>
       </c>
-      <c r="J254" s="2" t="inlineStr">
+      <c r="J263" s="2" t="inlineStr">
         <is>
           <t>The page shows both the currently confirmed details and the pending change request together</t>
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" s="2" t="n">
+    <row r="264">
+      <c r="A264" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B255" s="2" t="inlineStr">
+      <c r="B264" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C255" s="2" t="inlineStr">
+      <c r="C264" s="2" t="inlineStr">
         <is>
           <t>E10-S01 - Scenario 3 (Refused edit offers the form)</t>
         </is>
       </c>
-      <c r="D255" s="2" t="inlineStr">
+      <c r="D264" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E255" s="2" t="inlineStr">
+      <c r="E264" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_03</t>
         </is>
       </c>
-      <c r="F255" s="2" t="inlineStr">
+      <c r="F264" s="2" t="inlineStr">
         <is>
           <t>Verify that attempting to directly edit a restricted field after approval should be refused and offered the change request form pre-filled with that field</t>
         </is>
       </c>
-      <c r="G255" s="2" t="inlineStr">
+      <c r="G264" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" has status "Confirmed"</t>
         </is>
       </c>
-      <c r="H255" s="2" t="inlineStr">
+      <c r="H264" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Community Meetup"
   3. Attempt to directly edit the Expected Attendance field</t>
         </is>
       </c>
-      <c r="I255" s="2" t="inlineStr">
+      <c r="I264" s="2" t="inlineStr">
         <is>
           <t>Field attempted: Expected Attendance</t>
         </is>
       </c>
-      <c r="J255" s="2" t="inlineStr">
+      <c r="J264" s="2" t="inlineStr">
         <is>
           <t>Direct editing is refused; organiser_a@clienta.com is offered the change request form, pre-filled with the Expected Attendance field</t>
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" s="2" t="n">
+    <row r="265">
+      <c r="A265" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B256" s="2" t="inlineStr">
+      <c r="B265" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C256" s="2" t="inlineStr">
+      <c r="C265" s="2" t="inlineStr">
         <is>
           <t>E10-S01 - Scenario 4 (Approved change applied)</t>
         </is>
       </c>
-      <c r="D256" s="2" t="inlineStr">
+      <c r="D265" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E256" s="2" t="inlineStr">
+      <c r="E265" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_04</t>
         </is>
       </c>
-      <c r="F256" s="2" t="inlineStr">
+      <c r="F265" s="2" t="inlineStr">
         <is>
           <t>Verify that when the Coordinator approves a change request, the event should be updated and the Organiser notified</t>
         </is>
       </c>
-      <c r="G256" s="2" t="inlineStr">
+      <c r="G265" s="2" t="inlineStr">
         <is>
           <t>A change request on "Community Meetup" (increase expected attendance to 10) is pending Coordinator approval</t>
         </is>
       </c>
-      <c r="H256" s="2" t="inlineStr">
+      <c r="H265" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the pending change request
@@ -13835,52 +14307,52 @@
   4. Log in as organiser_a@clienta.com and check the event and notifications</t>
         </is>
       </c>
-      <c r="I256" s="2" t="inlineStr">
+      <c r="I265" s="2" t="inlineStr">
         <is>
           <t>Change: Expected Attendance -&gt; 10</t>
         </is>
       </c>
-      <c r="J256" s="2" t="inlineStr">
+      <c r="J265" s="2" t="inlineStr">
         <is>
           <t>"Community Meetup"'s Expected Attendance is updated to 10, and organiser_a@clienta.com is notified that the change was applied</t>
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="2" t="n">
+    <row r="266">
+      <c r="A266" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B257" s="2" t="inlineStr">
+      <c r="B266" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="C257" s="2" t="inlineStr">
+      <c r="C266" s="2" t="inlineStr">
         <is>
           <t>E10-S01 (checklist: notified when Coordinator approves or declines)</t>
         </is>
       </c>
-      <c r="D257" s="2" t="inlineStr">
+      <c r="D266" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E257" s="2" t="inlineStr">
+      <c r="E266" s="2" t="inlineStr">
         <is>
           <t>TC_E10S01_05</t>
         </is>
       </c>
-      <c r="F257" s="2" t="inlineStr">
+      <c r="F266" s="2" t="inlineStr">
         <is>
           <t>Verify that when the Coordinator declines a change request, the Organiser should be notified</t>
         </is>
       </c>
-      <c r="G257" s="2" t="inlineStr">
+      <c r="G266" s="2" t="inlineStr">
         <is>
           <t>A change request on "Community Meetup" is pending Coordinator approval</t>
         </is>
       </c>
-      <c r="H257" s="2" t="inlineStr">
+      <c r="H266" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open the pending change request
@@ -13889,105 +14361,105 @@
   5. Log in as organiser_a@clienta.com and check notifications</t>
         </is>
       </c>
-      <c r="I257" s="2" t="inlineStr">
+      <c r="I266" s="2" t="inlineStr">
         <is>
           <t>Decision: Declined</t>
         </is>
       </c>
-      <c r="J257" s="2" t="inlineStr">
+      <c r="J266" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is notified that the change request was declined, and the event remains unchanged
 ## E10-S02</t>
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" s="2" t="n">
+    <row r="267">
+      <c r="A267" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B258" s="2" t="inlineStr">
+      <c r="B267" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C258" s="2" t="inlineStr">
+      <c r="C267" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 1 (Attendance beyond capacity flagged)</t>
         </is>
       </c>
-      <c r="D258" s="2" t="inlineStr">
+      <c r="D267" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E258" s="2" t="inlineStr">
+      <c r="E267" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_01</t>
         </is>
       </c>
-      <c r="F258" s="2" t="inlineStr">
+      <c r="F267" s="2" t="inlineStr">
         <is>
           <t>Verify that increasing a event's expected attendance beyond its confirmed venue's capacity should flag the venue booking for review and notify Venue Staff</t>
         </is>
       </c>
-      <c r="G258" s="2" t="inlineStr">
+      <c r="G267" s="2" t="inlineStr">
         <is>
           <t>A event of "Tech Conference 2026" has a confirmed venue "Riverside Hall" with capacity 200</t>
         </is>
       </c>
-      <c r="H258" s="2" t="inlineStr">
+      <c r="H267" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Increase the event's Expected Attendance to 250
   3. Save</t>
         </is>
       </c>
-      <c r="I258" s="2" t="inlineStr">
+      <c r="I267" s="2" t="inlineStr">
         <is>
           <t>Expected Attendance: 200 -&gt; 250 (venue capacity: 200)</t>
         </is>
       </c>
-      <c r="J258" s="2" t="inlineStr">
+      <c r="J267" s="2" t="inlineStr">
         <is>
           <t>The venue booking for "Riverside Hall" is flagged for review, and venue_staff_1@connectsphere.com is notified</t>
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="2" t="n">
+    <row r="268">
+      <c r="A268" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B259" s="2" t="inlineStr">
+      <c r="B268" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C259" s="2" t="inlineStr">
+      <c r="C268" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 2 (Description-only edit flags nothing)</t>
         </is>
       </c>
-      <c r="D259" s="2" t="inlineStr">
+      <c r="D268" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E259" s="2" t="inlineStr">
+      <c r="E268" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_02</t>
         </is>
       </c>
-      <c r="F259" s="2" t="inlineStr">
+      <c r="F268" s="2" t="inlineStr">
         <is>
           <t>Verify that editing only the event description on an event with confirmed venue and equipment should flag nothing</t>
         </is>
       </c>
-      <c r="G259" s="2" t="inlineStr">
+      <c r="G268" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Conference 2026" has a confirmed venue and equipment</t>
         </is>
       </c>
-      <c r="H259" s="2" t="inlineStr">
+      <c r="H268" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Edit only the Description field
@@ -13995,208 +14467,208 @@
   4. Check for any flagged arrangements</t>
         </is>
       </c>
-      <c r="I259" s="2" t="inlineStr">
+      <c r="I268" s="2" t="inlineStr">
         <is>
           <t>Field changed: Description only</t>
         </is>
       </c>
-      <c r="J259" s="2" t="inlineStr">
+      <c r="J268" s="2" t="inlineStr">
         <is>
           <t>No arrangements are flagged as a result of this edit</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="2" t="n">
+    <row r="269">
+      <c r="A269" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B260" s="2" t="inlineStr">
+      <c r="B269" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C260" s="2" t="inlineStr">
+      <c r="C269" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 3 (Affected arrangements shown first)</t>
         </is>
       </c>
-      <c r="D260" s="2" t="inlineStr">
+      <c r="D269" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E260" s="2" t="inlineStr">
+      <c r="E269" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_03</t>
         </is>
       </c>
-      <c r="F260" s="2" t="inlineStr">
+      <c r="F269" s="2" t="inlineStr">
         <is>
           <t>Verify that saving a change that affects confirmed arrangements should show which arrangements are affected before the change takes effect</t>
         </is>
       </c>
-      <c r="G260" s="2" t="inlineStr">
+      <c r="G269" s="2" t="inlineStr">
         <is>
           <t>A pending edit to "Tech Conference 2026" would affect its confirmed venue booking</t>
         </is>
       </c>
-      <c r="H260" s="2" t="inlineStr">
+      <c r="H269" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Make the edit that affects the venue booking
   3. Click "Save"</t>
         </is>
       </c>
-      <c r="I260" s="2" t="inlineStr">
+      <c r="I269" s="2" t="inlineStr">
         <is>
           <t>Edit: affects the confirmed venue booking</t>
         </is>
       </c>
-      <c r="J260" s="2" t="inlineStr">
+      <c r="J269" s="2" t="inlineStr">
         <is>
           <t>Before the change is applied, a confirmation screen lists the affected arrangement (venue booking) for review</t>
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" s="2" t="n">
+    <row r="270">
+      <c r="A270" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B261" s="2" t="inlineStr">
+      <c r="B270" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C261" s="2" t="inlineStr">
+      <c r="C270" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 4 (Over-subscription warns only)</t>
         </is>
       </c>
-      <c r="D261" s="2" t="inlineStr">
+      <c r="D270" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E261" s="2" t="inlineStr">
+      <c r="E270" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_04</t>
         </is>
       </c>
-      <c r="F261" s="2" t="inlineStr">
+      <c r="F270" s="2" t="inlineStr">
         <is>
           <t>Verify that a venue change that reduces a event's capacity below its registration count should warn the Coordinator and show the over-subscription without automatically removing or waitlisting anyone</t>
         </is>
       </c>
-      <c r="G261" s="2" t="inlineStr">
+      <c r="G270" s="2" t="inlineStr">
         <is>
           <t>A event of "Tech Conference 2026" has 100 registered; a venue change is about to reduce its capacity to 80</t>
         </is>
       </c>
-      <c r="H261" s="2" t="inlineStr">
+      <c r="H270" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Change the event's venue to one with capacity 80
   3. Save</t>
         </is>
       </c>
-      <c r="I261" s="2" t="inlineStr">
+      <c r="I270" s="2" t="inlineStr">
         <is>
           <t>New capacity: 80; Registered: 100</t>
         </is>
       </c>
-      <c r="J261" s="2" t="inlineStr">
+      <c r="J270" s="2" t="inlineStr">
         <is>
           <t>coordinator_1@connectsphere.com is warned and shown the over-subscription (100 vs 80); no Attendee is automatically removed or waitlisted</t>
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" s="2" t="n">
+    <row r="271">
+      <c r="A271" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B262" s="2" t="inlineStr">
+      <c r="B271" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C262" s="2" t="inlineStr">
+      <c r="C271" s="2" t="inlineStr">
         <is>
           <t>E10-S02 - Scenario 5 (Date change flags venue and equipment)</t>
         </is>
       </c>
-      <c r="D262" s="2" t="inlineStr">
+      <c r="D271" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E262" s="2" t="inlineStr">
+      <c r="E271" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_05</t>
         </is>
       </c>
-      <c r="F262" s="2" t="inlineStr">
+      <c r="F271" s="2" t="inlineStr">
         <is>
           <t>Verify that changing a event's date or time should flag its venue booking and equipment reservations as requiring reconfirmation</t>
         </is>
       </c>
-      <c r="G262" s="2" t="inlineStr">
+      <c r="G271" s="2" t="inlineStr">
         <is>
           <t>A event of "Tech Conference 2026" has a confirmed venue and reserved equipment</t>
         </is>
       </c>
-      <c r="H262" s="2" t="inlineStr">
+      <c r="H271" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Change the event's date from 15/11/2026 to 20/11/2026
   3. Save</t>
         </is>
       </c>
-      <c r="I262" s="2" t="inlineStr">
+      <c r="I271" s="2" t="inlineStr">
         <is>
           <t>Date: 15/11/2026 -&gt; 20/11/2026</t>
         </is>
       </c>
-      <c r="J262" s="2" t="inlineStr">
+      <c r="J271" s="2" t="inlineStr">
         <is>
           <t>Both the venue booking and the equipment reservations for this event are flagged as requiring reconfirmation</t>
         </is>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" s="2" t="n">
+    <row r="272">
+      <c r="A272" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B263" s="2" t="inlineStr">
+      <c r="B272" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C263" s="2" t="inlineStr">
+      <c r="C272" s="2" t="inlineStr">
         <is>
           <t>E10-S02 (checklist: Venue Staff and Technical Support Staff both notified)</t>
         </is>
       </c>
-      <c r="D263" s="2" t="inlineStr">
+      <c r="D272" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting (notification consistency)</t>
         </is>
       </c>
-      <c r="E263" s="2" t="inlineStr">
+      <c r="E272" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_06</t>
         </is>
       </c>
-      <c r="F263" s="2" t="inlineStr">
+      <c r="F272" s="2" t="inlineStr">
         <is>
           <t>Verify that when a date or time change flags arrangements for reconfirmation, the assigned Technical Support Staff should also be notified, not just Venue Staff</t>
         </is>
       </c>
-      <c r="G263" s="2" t="inlineStr">
+      <c r="G272" s="2" t="inlineStr">
         <is>
           <t>A event of "Tech Conference 2026" has a confirmed venue, reserved equipment, and tech_support_1@connectsphere.com assigned for on-site support</t>
         </is>
       </c>
-      <c r="H263" s="2" t="inlineStr">
+      <c r="H272" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Change the event's date
@@ -14204,52 +14676,52 @@
   4. Check notifications for both venue_staff_1@connectsphere.com and tech_support_1@connectsphere.com</t>
         </is>
       </c>
-      <c r="I263" s="2" t="inlineStr">
+      <c r="I272" s="2" t="inlineStr">
         <is>
           <t>Changed field: Date</t>
         </is>
       </c>
-      <c r="J263" s="2" t="inlineStr">
+      <c r="J272" s="2" t="inlineStr">
         <is>
           <t>Both venue_staff_1@connectsphere.com and tech_support_1@connectsphere.com receive a notification about the change requiring reconfirmation</t>
         </is>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" s="2" t="n">
+    <row r="273">
+      <c r="A273" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B264" s="2" t="inlineStr">
+      <c r="B273" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="C264" s="2" t="inlineStr">
+      <c r="C273" s="2" t="inlineStr">
         <is>
           <t>E10-S02 — Scenario 1 (Attendance beyond capacity flagged); assumes O-27</t>
         </is>
       </c>
-      <c r="D264" s="2" t="inlineStr">
+      <c r="D273" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E264" s="2" t="inlineStr">
+      <c r="E273" s="2" t="inlineStr">
         <is>
           <t>TC_E10S02_07</t>
         </is>
       </c>
-      <c r="F264" s="2" t="inlineStr">
+      <c r="F273" s="2" t="inlineStr">
         <is>
           <t>Verify that increasing expected attendance on a multi-venue event should flag only the venue bookings whose governing headcount now exceeds capacity</t>
         </is>
       </c>
-      <c r="G264" s="2" t="inlineStr">
+      <c r="G273" s="2" t="inlineStr">
         <is>
           <t>Event "Tech Summit" is Confirmed with "Grand Auditorium" (capacity 600, booking headcount not set) and "Seminar Room A" (capacity 60, booking headcount 50); expected attendance is 500; coordinator_1@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H264" s="2" t="inlineStr">
+      <c r="H273" s="2" t="inlineStr">
         <is>
           <t>1. Change expected attendance to 600 and save
   2. Read the arrangement flags
@@ -14257,53 +14729,53 @@
   4. Read the arrangement flags</t>
         </is>
       </c>
-      <c r="I264" s="2" t="inlineStr">
+      <c r="I273" s="2" t="inlineStr">
         <is>
           <t>Auditorium governed by event attendance (600 = exactly at capacity, 601 = above); Seminar Room A governed by its own headcount 50</t>
         </is>
       </c>
-      <c r="J264" s="2" t="inlineStr">
+      <c r="J273" s="2" t="inlineStr">
         <is>
           <t>After step 1 no booking is flagged; after step 3 only "Grand Auditorium" is flagged for review and "Seminar Room A" is not, because its booking headcount of 50 is unchanged
 ## E10-S04</t>
         </is>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" s="2" t="n">
+    <row r="274">
+      <c r="A274" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B265" s="2" t="inlineStr">
+      <c r="B274" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="C265" s="2" t="inlineStr">
+      <c r="C274" s="2" t="inlineStr">
         <is>
           <t>E10-S04 - Scenario 1 (Event cancelled, arrangements released)</t>
         </is>
       </c>
-      <c r="D265" s="2" t="inlineStr">
+      <c r="D274" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E265" s="2" t="inlineStr">
+      <c r="E274" s="2" t="inlineStr">
         <is>
           <t>TC_E10S04_01</t>
         </is>
       </c>
-      <c r="F265" s="2" t="inlineStr">
+      <c r="F274" s="2" t="inlineStr">
         <is>
           <t>Verify that cancelling an event and recording a reason should release its venue bookings and equipment reservations, update the venue calendars, and notify affected staff</t>
         </is>
       </c>
-      <c r="G265" s="2" t="inlineStr">
+      <c r="G274" s="2" t="inlineStr">
         <is>
           <t>Event "Product Launch Night" has status "Confirmed" with a confirmed venue "Small Room" and reserved equipment</t>
         </is>
       </c>
-      <c r="H265" s="2" t="inlineStr">
+      <c r="H274" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Open event "Product Launch Night"
@@ -14312,156 +14784,156 @@
   5. Confirm</t>
         </is>
       </c>
-      <c r="I265" s="2" t="inlineStr">
+      <c r="I274" s="2" t="inlineStr">
         <is>
           <t>Cancellation reason: "Insufficient sponsor funding"</t>
         </is>
       </c>
-      <c r="J265" s="2" t="inlineStr">
+      <c r="J274" s="2" t="inlineStr">
         <is>
           <t>The status becomes "Cancelled"; "Small Room"'s booking and the reserved equipment are released, the venue calendar is updated, and affected staff are notified</t>
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" s="2" t="n">
+    <row r="275">
+      <c r="A275" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B266" s="2" t="inlineStr">
+      <c r="B275" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="C266" s="2" t="inlineStr">
+      <c r="C275" s="2" t="inlineStr">
         <is>
           <t>E10-S04 - Scenario 2 (Attendees and waitlist notified)</t>
         </is>
       </c>
-      <c r="D266" s="2" t="inlineStr">
+      <c r="D275" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E266" s="2" t="inlineStr">
+      <c r="E275" s="2" t="inlineStr">
         <is>
           <t>TC_E10S04_03</t>
         </is>
       </c>
-      <c r="F266" s="2" t="inlineStr">
+      <c r="F275" s="2" t="inlineStr">
         <is>
           <t>Verify that cancelling a event should notify all of its registered and waitlisted Attendees</t>
         </is>
       </c>
-      <c r="G266" s="2" t="inlineStr">
+      <c r="G275" s="2" t="inlineStr">
         <is>
           <t>The event of "Tech Conference 2026" being cancelled has attendee_a@example.com registered and attendee_l@example.com waitlisted</t>
         </is>
       </c>
-      <c r="H266" s="2" t="inlineStr">
+      <c r="H275" s="2" t="inlineStr">
         <is>
           <t>1. Log in as coordinator_1@connectsphere.com
   2. Cancel the event
   3. Check notifications for attendee_a@example.com and attendee_l@example.com</t>
         </is>
       </c>
-      <c r="I266" s="2" t="inlineStr">
+      <c r="I275" s="2" t="inlineStr">
         <is>
           <t>Registered: attendee_a@example.com | Waitlisted: attendee_l@example.com</t>
         </is>
       </c>
-      <c r="J266" s="2" t="inlineStr">
+      <c r="J275" s="2" t="inlineStr">
         <is>
           <t>Both attendee_a@example.com and attendee_l@example.com receive a notification of the cancellation</t>
         </is>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" s="2" t="n">
+    <row r="276">
+      <c r="A276" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B267" s="2" t="inlineStr">
+      <c r="B276" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="C267" s="2" t="inlineStr">
+      <c r="C276" s="2" t="inlineStr">
         <is>
           <t>E10-S04 - Scenario 3 (Cancelled event read-only)</t>
         </is>
       </c>
-      <c r="D267" s="2" t="inlineStr">
+      <c r="D276" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E267" s="2" t="inlineStr">
+      <c r="E276" s="2" t="inlineStr">
         <is>
           <t>TC_E10S04_04</t>
         </is>
       </c>
-      <c r="F267" s="2" t="inlineStr">
+      <c r="F276" s="2" t="inlineStr">
         <is>
           <t>Verify that a cancelled event should be read-only and show its cancellation reason and date to any viewer</t>
         </is>
       </c>
-      <c r="G267" s="2" t="inlineStr">
+      <c r="G276" s="2" t="inlineStr">
         <is>
           <t>Event "Product Launch Night" was cancelled on 12/09/2026 with reason "Insufficient sponsor funding" (per TC_E10S04_01)</t>
         </is>
       </c>
-      <c r="H267" s="2" t="inlineStr">
+      <c r="H276" s="2" t="inlineStr">
         <is>
           <t>1. Log in as any user with access (e.g. organiser_a@clienta.com)
   2. Open the cancelled event "Product Launch Night"
   3. Attempt to edit any field</t>
         </is>
       </c>
-      <c r="I267" s="2" t="inlineStr">
+      <c r="I276" s="2" t="inlineStr">
         <is>
           <t>Cancellation reason: "Insufficient sponsor funding" | Date: 12/09/2026</t>
         </is>
       </c>
-      <c r="J267" s="2" t="inlineStr">
+      <c r="J276" s="2" t="inlineStr">
         <is>
           <t>The event shows "Cancelled on 12 September 2026 - Insufficient sponsor funding"; all fields are read-only</t>
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" s="2" t="n">
+    <row r="277">
+      <c r="A277" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B268" s="2" t="inlineStr">
+      <c r="B277" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="C268" s="2" t="inlineStr">
+      <c r="C277" s="2" t="inlineStr">
         <is>
           <t>E10-S04 - Scenario 4 (Organiser cancellation becomes a request)</t>
         </is>
       </c>
-      <c r="D268" s="2" t="inlineStr">
+      <c r="D277" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E268" s="2" t="inlineStr">
+      <c r="E277" s="2" t="inlineStr">
         <is>
           <t>TC_E10S04_05</t>
         </is>
       </c>
-      <c r="F268" s="2" t="inlineStr">
+      <c r="F277" s="2" t="inlineStr">
         <is>
           <t>Verify that an Event Organiser attempting to cancel directly should have the action recorded as a cancellation request for the Coordinator to action</t>
         </is>
       </c>
-      <c r="G268" s="2" t="inlineStr">
+      <c r="G277" s="2" t="inlineStr">
         <is>
           <t>Event "Community Meetup" has status "Confirmed", assigned to coordinator_1@connectsphere.com</t>
         </is>
       </c>
-      <c r="H268" s="2" t="inlineStr">
+      <c r="H277" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open event "Community Meetup"
@@ -14469,308 +14941,308 @@
   4. Enter a reason and submit</t>
         </is>
       </c>
-      <c r="I268" s="2" t="inlineStr">
+      <c r="I277" s="2" t="inlineStr">
         <is>
           <t>Reason: "No longer needed"</t>
         </is>
       </c>
-      <c r="J268" s="2" t="inlineStr">
+      <c r="J277" s="2" t="inlineStr">
         <is>
           <t>The event is NOT immediately cancelled; instead, a cancellation request is recorded and coordinator_1@connectsphere.com is notified to action it</t>
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" s="2" t="n">
+    <row r="278">
+      <c r="A278" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B269" s="2" t="inlineStr">
+      <c r="B278" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C269" s="2" t="inlineStr">
+      <c r="C278" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 1 (Status change notified)</t>
         </is>
       </c>
-      <c r="D269" s="2" t="inlineStr">
+      <c r="D278" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E269" s="2" t="inlineStr">
+      <c r="E278" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_01</t>
         </is>
       </c>
-      <c r="F269" s="2" t="inlineStr">
+      <c r="F278" s="2" t="inlineStr">
         <is>
           <t>Verify that a user linked to an event should be notified when its status changes or a booking decision is made, with details of what/when/which event</t>
         </is>
       </c>
-      <c r="G269" s="2" t="inlineStr">
+      <c r="G278" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is linked to event "Annual Tech Summit", currently "Under Review"</t>
         </is>
       </c>
-      <c r="H269" s="2" t="inlineStr">
+      <c r="H278" s="2" t="inlineStr">
         <is>
           <t>1. As coordinator_1@connectsphere.com, approve request "Annual Tech Summit" (status -&gt; Approved)
   2. Log in as organiser_a@clienta.com and open notifications</t>
         </is>
       </c>
-      <c r="I269" s="2" t="inlineStr">
+      <c r="I278" s="2" t="inlineStr">
         <is>
           <t>Event: Annual Tech Summit | Change: Under Review -&gt; Approved</t>
         </is>
       </c>
-      <c r="J269" s="2" t="inlineStr">
+      <c r="J278" s="2" t="inlineStr">
         <is>
           <t>A notification is received stating the status changed to "Approved", the time of the change, and that it concerns "Annual Tech Summit"</t>
         </is>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" s="2" t="n">
+    <row r="279">
+      <c r="A279" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B270" s="2" t="inlineStr">
+      <c r="B279" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C270" s="2" t="inlineStr">
+      <c r="C279" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 2 (All affected parties notified)</t>
         </is>
       </c>
-      <c r="D270" s="2" t="inlineStr">
+      <c r="D279" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E270" s="2" t="inlineStr">
+      <c r="E279" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_02</t>
         </is>
       </c>
-      <c r="F270" s="2" t="inlineStr">
+      <c r="F279" s="2" t="inlineStr">
         <is>
           <t>Verify that effective date, time or venue changes follow the approved recipient matrix</t>
         </is>
       </c>
-      <c r="G270" s="2" t="inlineStr">
+      <c r="G279" s="2" t="inlineStr">
         <is>
           <t>Event "Annual Tech Summit" the event has organiser_a@clienta.com, venue_staff_1@connectsphere.com, and tech_support_1@connectsphere.com assigned, and attendee_a@example.com registered; attendee_b@example.com is waitlisted and coordinator_1@connectsphere.com is the assigned Coordinator</t>
         </is>
       </c>
-      <c r="H270" s="2" t="inlineStr">
+      <c r="H279" s="2" t="inlineStr">
         <is>
           <t>1. As coordinator_1@connectsphere.com, change the event's venue
   2. Check notifications for organiser_a@clienta.com, venue_staff_1@connectsphere.com, tech_support_1@connectsphere.com, and attendee_a@example.com</t>
         </is>
       </c>
-      <c r="I270" s="2" t="inlineStr">
+      <c r="I279" s="2" t="inlineStr">
         <is>
           <t>Changed field: Venue</t>
         </is>
       </c>
-      <c r="J270" s="2" t="inlineStr">
+      <c r="J279" s="2" t="inlineStr">
         <is>
           <t>The Organiser, assigned Venue Staff, assigned Technical Support Staff, registered Attendee and waitlisted Attendee receive a notification. The acting Coordinator receives no self-notification. If another authorized actor or a system operation makes the change, the assigned Coordinator is included. Venue-move tests include responsible staff for both the old and new venues. Backend resolver fixtures are not evidence that the venue-assignment workflow is implemented.</t>
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" s="2" t="n">
+    <row r="280">
+      <c r="A280" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B271" s="2" t="inlineStr">
+      <c r="B280" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C271" s="2" t="inlineStr">
+      <c r="C280" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 3 (Unaffected users not notified)</t>
         </is>
       </c>
-      <c r="D271" s="2" t="inlineStr">
+      <c r="D280" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E271" s="2" t="inlineStr">
+      <c r="E280" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_03</t>
         </is>
       </c>
-      <c r="F271" s="2" t="inlineStr">
+      <c r="F280" s="2" t="inlineStr">
         <is>
           <t>Verify that a user whose responsibilities are unaffected by a change should not be notified</t>
         </is>
       </c>
-      <c r="G271" s="2" t="inlineStr">
+      <c r="G280" s="2" t="inlineStr">
         <is>
           <t>Event "Annual Tech Summit" the event's Description field is about to be edited; venue_staff_1@connectsphere.com has no responsibility tied to the Description field</t>
         </is>
       </c>
-      <c r="H271" s="2" t="inlineStr">
+      <c r="H280" s="2" t="inlineStr">
         <is>
           <t>1. As organiser_a@clienta.com, edit the Description field only
   2. Check venue_staff_1@connectsphere.com's notifications</t>
         </is>
       </c>
-      <c r="I271" s="2" t="inlineStr">
+      <c r="I280" s="2" t="inlineStr">
         <is>
           <t>Changed field: Description only</t>
         </is>
       </c>
-      <c r="J271" s="2" t="inlineStr">
+      <c r="J280" s="2" t="inlineStr">
         <is>
           <t>venue_staff_1@connectsphere.com receives no notification, since the Description change does not affect their responsibilities</t>
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" s="2" t="n">
+    <row r="281">
+      <c r="A281" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B272" s="2" t="inlineStr">
+      <c r="B281" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C272" s="2" t="inlineStr">
+      <c r="C281" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 4 (Delivered in-app and by email)</t>
         </is>
       </c>
-      <c r="D272" s="2" t="inlineStr">
+      <c r="D281" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E272" s="2" t="inlineStr">
+      <c r="E281" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_05</t>
         </is>
       </c>
-      <c r="F272" s="2" t="inlineStr">
+      <c r="F281" s="2" t="inlineStr">
         <is>
           <t>Verify that a generated notification should appear in the system and also be sent to the user's registered email address</t>
         </is>
       </c>
-      <c r="G272" s="2" t="inlineStr">
+      <c r="G281" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com's registered email is organiser_a@clienta.com; a notification-triggering status change is about to occur on their event</t>
         </is>
       </c>
-      <c r="H272" s="2" t="inlineStr">
+      <c r="H281" s="2" t="inlineStr">
         <is>
           <t>1. Trigger a status change on organiser_a@clienta.com's event
   2. Log in as organiser_a@clienta.com and check the in-app notification list
   3. Check the inbox for organiser_a@clienta.com</t>
         </is>
       </c>
-      <c r="I272" s="2" t="inlineStr">
+      <c r="I281" s="2" t="inlineStr">
         <is>
           <t>Registered email: organiser_a@clienta.com</t>
         </is>
       </c>
-      <c r="J272" s="2" t="inlineStr">
+      <c r="J281" s="2" t="inlineStr">
         <is>
           <t>The notification appears in the in-app notification list, and an equivalent email is also delivered to organiser_a@clienta.com's inbox</t>
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="2" t="n">
+    <row r="282">
+      <c r="A282" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B273" s="2" t="inlineStr">
+      <c r="B282" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C273" s="2" t="inlineStr">
+      <c r="C282" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 5 (Unread notifications distinguished)</t>
         </is>
       </c>
-      <c r="D273" s="2" t="inlineStr">
+      <c r="D282" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E273" s="2" t="inlineStr">
+      <c r="E282" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_06</t>
         </is>
       </c>
-      <c r="F273" s="2" t="inlineStr">
+      <c r="F282" s="2" t="inlineStr">
         <is>
           <t>Verify that opening the notification list with several unread notifications should show them newest first with unread ones distinguished</t>
         </is>
       </c>
-      <c r="G273" s="2" t="inlineStr">
+      <c r="G282" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com has 3 notifications on 09/09/2026: 08:00 (read), 10:00 (unread), 14:00 (unread)</t>
         </is>
       </c>
-      <c r="H273" s="2" t="inlineStr">
+      <c r="H282" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the notification list</t>
         </is>
       </c>
-      <c r="I273" s="2" t="inlineStr">
+      <c r="I282" s="2" t="inlineStr">
         <is>
           <t>Notifications: 08:00 (read), 10:00 (unread), 14:00 (unread)</t>
         </is>
       </c>
-      <c r="J273" s="2" t="inlineStr">
+      <c r="J282" s="2" t="inlineStr">
         <is>
           <t>Notifications are listed newest first (14:00, then 10:00, then 08:00), with the 14:00 and 10:00 entries visually marked as unread and 08:00 shown as read</t>
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" s="2" t="n">
+    <row r="283">
+      <c r="A283" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B274" s="2" t="inlineStr">
+      <c r="B283" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C274" s="2" t="inlineStr">
+      <c r="C283" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - Scenario 6 (Marked as read)</t>
         </is>
       </c>
-      <c r="D274" s="2" t="inlineStr">
+      <c r="D283" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E274" s="2" t="inlineStr">
+      <c r="E283" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_07</t>
         </is>
       </c>
-      <c r="F274" s="2" t="inlineStr">
+      <c r="F283" s="2" t="inlineStr">
         <is>
           <t>Verify that opening an unread notification should mark it as read</t>
         </is>
       </c>
-      <c r="G274" s="2" t="inlineStr">
+      <c r="G283" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com has an unread notification from 10:00 on 09/09/2026</t>
         </is>
       </c>
-      <c r="H274" s="2" t="inlineStr">
+      <c r="H283" s="2" t="inlineStr">
         <is>
           <t>1. Log in as organiser_a@clienta.com
   2. Open the notification list
@@ -14778,52 +15250,52 @@
   4. Return to the notification list</t>
         </is>
       </c>
-      <c r="I274" s="2" t="inlineStr">
+      <c r="I283" s="2" t="inlineStr">
         <is>
           <t>Notification: 10:00 on 09/09/2026 (initially unread)</t>
         </is>
       </c>
-      <c r="J274" s="2" t="inlineStr">
+      <c r="J283" s="2" t="inlineStr">
         <is>
           <t>The 10:00 notification is now shown as read (no longer marked unread) in the list</t>
         </is>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" s="2" t="n">
+    <row r="284">
+      <c r="A284" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B275" s="2" t="inlineStr">
+      <c r="B284" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C275" s="2" t="inlineStr">
+      <c r="C284" s="2" t="inlineStr">
         <is>
           <t>E11-S01 · Scenario 5 (Delivered in-app and by email) · ADR-006</t>
         </is>
       </c>
-      <c r="D275" s="2" t="inlineStr">
+      <c r="D284" s="2" t="inlineStr">
         <is>
           <t>4 - Negative (third-party unavailable)</t>
         </is>
       </c>
-      <c r="E275" s="2" t="inlineStr">
+      <c r="E284" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_08</t>
         </is>
       </c>
-      <c r="F275" s="2" t="inlineStr">
+      <c r="F284" s="2" t="inlineStr">
         <is>
           <t>Verify that an unreachable email provider does not affect the business change or the in-app notification</t>
         </is>
       </c>
-      <c r="G275" s="2" t="inlineStr">
+      <c r="G284" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2003 has an assigned Coordinator coord_a@connectsphere.com. The email provider endpoint is configured to an unreachable host so every SMTP attempt fails</t>
         </is>
       </c>
-      <c r="H275" s="2" t="inlineStr">
+      <c r="H284" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as Venue Staff and approve the pending venue booking for EVT-2003
  2. Confirm the booking status has changed
@@ -14831,52 +15303,52 @@
  4. Inspect the delivery records for that notification</t>
         </is>
       </c>
-      <c r="I275" s="2" t="inlineStr">
+      <c r="I284" s="2" t="inlineStr">
         <is>
           <t>SMTP host: unreachable · Notification: venue booking approved</t>
         </is>
       </c>
-      <c r="J275" s="2" t="inlineStr">
+      <c r="J284" s="2" t="inlineStr">
         <is>
           <t>The booking is Confirmed and the change persists. The in-app notification appears for the Coordinator. The email delivery row is marked failed with a recorded reason. The business transaction is not rolled back by the email failure</t>
         </is>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" s="2" t="n">
+    <row r="285">
+      <c r="A285" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B276" s="2" t="inlineStr">
+      <c r="B285" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C276" s="2" t="inlineStr">
+      <c r="C285" s="2" t="inlineStr">
         <is>
           <t>E11-S01 · Scenario 1 (Status change notified) · ADR-006 outbox guarantee</t>
         </is>
       </c>
-      <c r="D276" s="2" t="inlineStr">
+      <c r="D285" s="2" t="inlineStr">
         <is>
           <t>4 - Negative (transaction rollback)</t>
         </is>
       </c>
-      <c r="E276" s="2" t="inlineStr">
+      <c r="E285" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_09</t>
         </is>
       </c>
-      <c r="F276" s="2" t="inlineStr">
+      <c r="F285" s="2" t="inlineStr">
         <is>
           <t>Verify that a rolled-back business transaction publishes no notification</t>
         </is>
       </c>
-      <c r="G276" s="2" t="inlineStr">
+      <c r="G285" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2004 is at status Under Review. A fault is injected so that the approval transaction fails after the notification delivery rows are written but before commit</t>
         </is>
       </c>
-      <c r="H276" s="2" t="inlineStr">
+      <c r="H285" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as the assigned Event Coordinator
  2. Approve EVT-2004, triggering the injected failure
@@ -14884,610 +15356,610 @@
  4. Inspect the job queue and the Organiser's notification list</t>
         </is>
       </c>
-      <c r="I276" s="2" t="inlineStr">
+      <c r="I285" s="2" t="inlineStr">
         <is>
           <t>Event: EVT-2004 · Injected failure point: after delivery rows written, before commit</t>
         </is>
       </c>
-      <c r="J276" s="2" t="inlineStr">
+      <c r="J285" s="2" t="inlineStr">
         <is>
           <t>The event remains at Under Review. No delivery row is persisted, nothing is published to the queue, and the Organiser receives no in-app notification and no email. Only committed deliveries are ever published</t>
         </is>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" s="2" t="n">
+    <row r="286">
+      <c r="A286" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B277" s="2" t="inlineStr">
+      <c r="B286" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C277" s="2" t="inlineStr">
+      <c r="C286" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
         </is>
       </c>
-      <c r="D277" s="2" t="inlineStr">
+      <c r="D286" s="2" t="inlineStr">
         <is>
           <t>3 - Integration / regression</t>
         </is>
       </c>
-      <c r="E277" s="2" t="inlineStr">
+      <c r="E286" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_10</t>
         </is>
       </c>
-      <c r="F277" s="2" t="inlineStr">
+      <c r="F286" s="2" t="inlineStr">
         <is>
           <t>Apply the approved role/change recipient matrix</t>
         </is>
       </c>
-      <c r="G277" s="2" t="inlineStr">
+      <c r="G286" s="2" t="inlineStr">
         <is>
           <t>The event has active links to all six recipient groups and a public snapshot.</t>
         </is>
       </c>
-      <c r="H277" s="2" t="inlineStr">
+      <c r="H286" s="2" t="inlineStr">
         <is>
           <t>1. Trigger each internal status, booking, equipment, public status, arrangement, place-release and description-only change through the selector.</t>
         </is>
       </c>
-      <c r="I277" s="2" t="inlineStr">
+      <c r="I286" s="2" t="inlineStr">
         <is>
           <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
         </is>
       </c>
-      <c r="J277" s="2" t="inlineStr">
+      <c r="J286" s="2" t="inlineStr">
         <is>
           <t>Recipient sets match the E11-S01 matrix; internal decisions do not reach Attendees; initial Planning differs from Confirmed-to-Planning.</t>
         </is>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" s="2" t="n">
+    <row r="287">
+      <c r="A287" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B278" s="2" t="inlineStr">
+      <c r="B287" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C278" s="2" t="inlineStr">
+      <c r="C287" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
         </is>
       </c>
-      <c r="D278" s="2" t="inlineStr">
+      <c r="D287" s="2" t="inlineStr">
         <is>
           <t>3 - Integration / regression</t>
         </is>
       </c>
-      <c r="E278" s="2" t="inlineStr">
+      <c r="E287" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_11</t>
         </is>
       </c>
-      <c r="F278" s="2" t="inlineStr">
+      <c r="F287" s="2" t="inlineStr">
         <is>
           <t>Suppress self-notifications and duplicate recipient links</t>
         </is>
       </c>
-      <c r="G278" s="2" t="inlineStr">
+      <c r="G287" s="2" t="inlineStr">
         <is>
           <t>A user is both the actor and a candidate recipient; duplicated staff links exist.</t>
         </is>
       </c>
-      <c r="H278" s="2" t="inlineStr">
+      <c r="H287" s="2" t="inlineStr">
         <is>
           <t>1. Select recipients for an arrangement change and an actor-made booking decision.</t>
         </is>
       </c>
-      <c r="I278" s="2" t="inlineStr">
+      <c r="I287" s="2" t="inlineStr">
         <is>
           <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
         </is>
       </c>
-      <c r="J278" s="2" t="inlineStr">
+      <c r="J287" s="2" t="inlineStr">
         <is>
           <t>The actor receives no routine self-notification; every remaining user appears once; system changes have no excluded actor.</t>
         </is>
       </c>
     </row>
-    <row r="279">
-      <c r="A279" s="2" t="n">
+    <row r="288">
+      <c r="A288" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B279" s="2" t="inlineStr">
+      <c r="B288" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C279" s="2" t="inlineStr">
+      <c r="C288" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
         </is>
       </c>
-      <c r="D279" s="2" t="inlineStr">
+      <c r="D288" s="2" t="inlineStr">
         <is>
           <t>3 - Integration / regression</t>
         </is>
       </c>
-      <c r="E279" s="2" t="inlineStr">
+      <c r="E288" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_12</t>
         </is>
       </c>
-      <c r="F279" s="2" t="inlineStr">
+      <c r="F288" s="2" t="inlineStr">
         <is>
           <t>Preserve before/after recipients during cancellation and venue moves</t>
         </is>
       </c>
-      <c r="G279" s="2" t="inlineStr">
+      <c r="G288" s="2" t="inlineStr">
         <is>
           <t>An event has active bookings, assigned staff, registered and waitlisted Attendees.</t>
         </is>
       </c>
-      <c r="H279" s="2" t="inlineStr">
+      <c r="H288" s="2" t="inlineStr">
         <is>
           <t>1. Capture its audience, release links during cancellation or replace the venue, then call the hook with both snapshots.</t>
         </is>
       </c>
-      <c r="I279" s="2" t="inlineStr">
+      <c r="I288" s="2" t="inlineStr">
         <is>
           <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
         </is>
       </c>
-      <c r="J279" s="2" t="inlineStr">
+      <c r="J288" s="2" t="inlineStr">
         <is>
           <t>Cancellation notifies the pre-release audience. Venue moves include responsible staff at both venues. These are hook-contract tests until the owning workflows integrate.</t>
         </is>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" s="2" t="n">
+    <row r="289">
+      <c r="A289" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B280" s="2" t="inlineStr">
+      <c r="B289" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C280" s="2" t="inlineStr">
+      <c r="C289" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
         </is>
       </c>
-      <c r="D280" s="2" t="inlineStr">
+      <c r="D289" s="2" t="inlineStr">
         <is>
           <t>3 - Integration / regression</t>
         </is>
       </c>
-      <c r="E280" s="2" t="inlineStr">
+      <c r="E289" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_13</t>
         </is>
       </c>
-      <c r="F280" s="2" t="inlineStr">
+      <c r="F289" s="2" t="inlineStr">
         <is>
           <t>Expose missing Venue Staff assignments without an unsafe fallback</t>
         </is>
       </c>
-      <c r="G280" s="2" t="inlineStr">
+      <c r="G289" s="2" t="inlineStr">
         <is>
           <t>No explicit venue assignment adapter is available; a booking has a decided_by actor and unrelated Venue Staff accounts exist.</t>
         </is>
       </c>
-      <c r="H280" s="2" t="inlineStr">
+      <c r="H289" s="2" t="inlineStr">
         <is>
           <t>1. Capture the audience and select booking-request recipients.</t>
         </is>
       </c>
-      <c r="I280" s="2" t="inlineStr">
+      <c r="I289" s="2" t="inlineStr">
         <is>
           <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
         </is>
       </c>
-      <c r="J280" s="2" t="inlineStr">
+      <c r="J289" s="2" t="inlineStr">
         <is>
           <t>Venue Staff recipients are unresolved, the venue IDs are reported, and neither decided_by nor all Venue Staff is substituted.</t>
         </is>
       </c>
     </row>
-    <row r="281">
-      <c r="A281" s="2" t="n">
+    <row r="290">
+      <c r="A290" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B281" s="2" t="inlineStr">
+      <c r="B290" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C281" s="2" t="inlineStr">
+      <c r="C290" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
         </is>
       </c>
-      <c r="D281" s="2" t="inlineStr">
+      <c r="D290" s="2" t="inlineStr">
         <is>
           <t>3 - Integration / regression</t>
         </is>
       </c>
-      <c r="E281" s="2" t="inlineStr">
+      <c r="E290" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_14</t>
         </is>
       </c>
-      <c r="F281" s="2" t="inlineStr">
+      <c r="F290" s="2" t="inlineStr">
         <is>
           <t>Protect attendee notification content and membership boundaries</t>
         </is>
       </c>
-      <c r="G281" s="2" t="inlineStr">
+      <c r="G290" s="2" t="inlineStr">
         <is>
           <t>The internal event title differs from its publication; registered, waitlisted, withdrawn, inactive and unrelated users exist.</t>
         </is>
       </c>
-      <c r="H281" s="2" t="inlineStr">
+      <c r="H290" s="2" t="inlineStr">
         <is>
           <t>1. Apply an effective date change; inspect notification messages and retained email payloads. Also select recipients for an unpublished event.</t>
         </is>
       </c>
-      <c r="I281" s="2" t="inlineStr">
+      <c r="I290" s="2" t="inlineStr">
         <is>
           <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
         </is>
       </c>
-      <c r="J281" s="2" t="inlineStr">
+      <c r="J290" s="2" t="inlineStr">
         <is>
           <t>Only eligible linked active users are selected. Attendees receive the published event name and fixed public change description; no internal title/reason/comment leaks. Unpublished events produce no attendee notice.</t>
         </is>
       </c>
     </row>
-    <row r="282">
-      <c r="A282" s="2" t="n">
+    <row r="291">
+      <c r="A291" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B282" s="2" t="inlineStr">
+      <c r="B291" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C282" s="2" t="inlineStr">
+      <c r="C291" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
         </is>
       </c>
-      <c r="D282" s="2" t="inlineStr">
+      <c r="D291" s="2" t="inlineStr">
         <is>
           <t>3 - Integration / regression</t>
         </is>
       </c>
-      <c r="E282" s="2" t="inlineStr">
+      <c r="E291" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_15</t>
         </is>
       </c>
-      <c r="F282" s="2" t="inlineStr">
+      <c r="F291" s="2" t="inlineStr">
         <is>
           <t>Deduplicate concurrent notification-hook retries</t>
         </is>
       </c>
-      <c r="G282" s="2" t="inlineStr">
+      <c r="G291" s="2" t="inlineStr">
         <is>
           <t>Two transactions use the same event, stable change ID and recipient snapshot.</t>
         </is>
       </c>
-      <c r="H282" s="2" t="inlineStr">
+      <c r="H291" s="2" t="inlineStr">
         <is>
           <t>1. Call the notification hook concurrently and commit both attempts.</t>
         </is>
       </c>
-      <c r="I282" s="2" t="inlineStr">
+      <c r="I291" s="2" t="inlineStr">
         <is>
           <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
         </is>
       </c>
-      <c r="J282" s="2" t="inlineStr">
+      <c r="J291" s="2" t="inlineStr">
         <is>
           <t>Exactly one in-app row and one email-delivery row exist per recipient for the logical change. A new change ID identifies a different business change.</t>
         </is>
       </c>
     </row>
-    <row r="283">
-      <c r="A283" s="2" t="n">
+    <row r="292">
+      <c r="A292" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B283" s="2" t="inlineStr">
+      <c r="B292" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="C283" s="2" t="inlineStr">
+      <c r="C292" s="2" t="inlineStr">
         <is>
           <t>E11-S01 - approved routing extension (T-64); ADR-006</t>
         </is>
       </c>
-      <c r="D283" s="2" t="inlineStr">
+      <c r="D292" s="2" t="inlineStr">
         <is>
           <t>3 - Integration / regression</t>
         </is>
       </c>
-      <c r="E283" s="2" t="inlineStr">
+      <c r="E292" s="2" t="inlineStr">
         <is>
           <t>TC_E11S01_16</t>
         </is>
       </c>
-      <c r="F283" s="2" t="inlineStr">
+      <c r="F292" s="2" t="inlineStr">
         <is>
           <t>Keep uncommitted notifications invisible and roll back all writes</t>
         </is>
       </c>
-      <c r="G283" s="2" t="inlineStr">
+      <c r="G292" s="2" t="inlineStr">
         <is>
           <t>A business transaction has inserted notifications and prepared email delivery rows but has not committed.</t>
         </is>
       </c>
-      <c r="H283" s="2" t="inlineStr">
+      <c r="H292" s="2" t="inlineStr">
         <is>
           <t>1. Read from another connection, then force the business transaction to roll back.</t>
         </is>
       </c>
-      <c r="I283" s="2" t="inlineStr">
+      <c r="I292" s="2" t="inlineStr">
         <is>
           <t>Synthetic linked-user fixtures in disposable PostgreSQL; no live email provider calls.</t>
         </is>
       </c>
-      <c r="J283" s="2" t="inlineStr">
+      <c r="J292" s="2" t="inlineStr">
         <is>
           <t>The other connection cannot observe the uncommitted messages. After rollback no notification or email-delivery row remains.</t>
         </is>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" s="2" t="n">
+    <row r="293">
+      <c r="A293" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B284" s="2" t="inlineStr">
+      <c r="B293" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C284" s="2" t="inlineStr">
+      <c r="C293" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 1 (Status change recorded)</t>
         </is>
       </c>
-      <c r="D284" s="2" t="inlineStr">
+      <c r="D293" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E284" s="2" t="inlineStr">
+      <c r="E293" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_01</t>
         </is>
       </c>
-      <c r="F284" s="2" t="inlineStr">
+      <c r="F293" s="2" t="inlineStr">
         <is>
           <t>Verify that an event status change should be recorded with the actor, action, affected event, and time</t>
         </is>
       </c>
-      <c r="G284" s="2" t="inlineStr">
+      <c r="G293" s="2" t="inlineStr">
         <is>
           <t>Request "Annual Tech Summit" has status "Under Review"</t>
         </is>
       </c>
-      <c r="H284" s="2" t="inlineStr">
+      <c r="H293" s="2" t="inlineStr">
         <is>
           <t>1. As coordinator_1@connectsphere.com, approve the request (status -&gt; Approved)
   2. Log in as a System Administrator
   3. Open the Activity Log and locate the entry</t>
         </is>
       </c>
-      <c r="I284" s="2" t="inlineStr">
+      <c r="I293" s="2" t="inlineStr">
         <is>
           <t>Event: Annual Tech Summit | Action: Approve</t>
         </is>
       </c>
-      <c r="J284" s="2" t="inlineStr">
+      <c r="J293" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded with actor = coordinator_1@connectsphere.com, action = "Status changed to Approved", event = Annual Tech Summit, and a timestamp</t>
         </is>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" s="2" t="n">
+    <row r="294">
+      <c r="A294" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B285" s="2" t="inlineStr">
+      <c r="B294" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C285" s="2" t="inlineStr">
+      <c r="C294" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 2 (Access denial recorded)</t>
         </is>
       </c>
-      <c r="D285" s="2" t="inlineStr">
+      <c r="D294" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E285" s="2" t="inlineStr">
+      <c r="E294" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_02</t>
         </is>
       </c>
-      <c r="F285" s="2" t="inlineStr">
+      <c r="F294" s="2" t="inlineStr">
         <is>
           <t>Verify that a denied access attempt should be recorded with the user, target, and time</t>
         </is>
       </c>
-      <c r="G285" s="2" t="inlineStr">
+      <c r="G294" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is linked to Client A; event EVT-B01 belongs to Client B</t>
         </is>
       </c>
-      <c r="H285" s="2" t="inlineStr">
+      <c r="H294" s="2" t="inlineStr">
         <is>
           <t>1. As organiser_a@clienta.com, attempt to access EVT-B01 directly
   2. Log in as a System Administrator
   3. Check the Activity Log</t>
         </is>
       </c>
-      <c r="I285" s="2" t="inlineStr">
+      <c r="I294" s="2" t="inlineStr">
         <is>
           <t>User: organiser_a@clienta.com | Target: EVT-B01</t>
         </is>
       </c>
-      <c r="J285" s="2" t="inlineStr">
+      <c r="J294" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded with user = organiser_a@clienta.com, target = EVT-B01, action = "Access Denied", and a timestamp</t>
         </is>
       </c>
     </row>
-    <row r="286">
-      <c r="A286" s="2" t="n">
+    <row r="295">
+      <c r="A295" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B286" s="2" t="inlineStr">
+      <c r="B295" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C286" s="2" t="inlineStr">
+      <c r="C295" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 3 (Booking decision recorded)</t>
         </is>
       </c>
-      <c r="D286" s="2" t="inlineStr">
+      <c r="D295" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E286" s="2" t="inlineStr">
+      <c r="E295" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_03</t>
         </is>
       </c>
-      <c r="F286" s="2" t="inlineStr">
+      <c r="F295" s="2" t="inlineStr">
         <is>
           <t>Verify that an approved venue booking should be recorded with the actor, action, affected records, and time</t>
         </is>
       </c>
-      <c r="G286" s="2" t="inlineStr">
+      <c r="G295" s="2" t="inlineStr">
         <is>
           <t>A booking request for Venue Z is pending</t>
         </is>
       </c>
-      <c r="H286" s="2" t="inlineStr">
+      <c r="H295" s="2" t="inlineStr">
         <is>
           <t>1. As Venue Staff, approve the booking request
   2. Log in as a System Administrator
   3. Check the Activity Log</t>
         </is>
       </c>
-      <c r="I286" s="2" t="inlineStr">
+      <c r="I295" s="2" t="inlineStr">
         <is>
           <t>Venue: Venue Z | Action: Approve Booking</t>
         </is>
       </c>
-      <c r="J286" s="2" t="inlineStr">
+      <c r="J295" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded with the actor, action ("Booking Approved"), the affected booking/event, and a timestamp</t>
         </is>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" s="2" t="n">
+    <row r="296">
+      <c r="A296" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B287" s="2" t="inlineStr">
+      <c r="B296" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C287" s="2" t="inlineStr">
+      <c r="C296" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 4 (Deactivation recorded)</t>
         </is>
       </c>
-      <c r="D287" s="2" t="inlineStr">
+      <c r="D296" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E287" s="2" t="inlineStr">
+      <c r="E296" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_04</t>
         </is>
       </c>
-      <c r="F287" s="2" t="inlineStr">
+      <c r="F296" s="2" t="inlineStr">
         <is>
           <t>Verify that an account deactivation should be recorded in the activity log</t>
         </is>
       </c>
-      <c r="G287" s="2" t="inlineStr">
+      <c r="G296" s="2" t="inlineStr">
         <is>
           <t>organiser_a@clienta.com is signed in</t>
         </is>
       </c>
-      <c r="H287" s="2" t="inlineStr">
+      <c r="H296" s="2" t="inlineStr">
         <is>
           <t>1. Deactivate the account
   2. Log in as a System Administrator
   3. Check the Activity Log</t>
         </is>
       </c>
-      <c r="I287" s="2" t="inlineStr">
+      <c r="I296" s="2" t="inlineStr">
         <is>
           <t>Account: organiser_a@clienta.com</t>
         </is>
       </c>
-      <c r="J287" s="2" t="inlineStr">
+      <c r="J296" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded showing the account deactivation with actor and timestamp</t>
         </is>
       </c>
     </row>
-    <row r="288">
-      <c r="A288" s="2" t="n">
+    <row r="297">
+      <c r="A297" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B288" s="2" t="inlineStr">
+      <c r="B297" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C288" s="2" t="inlineStr">
+      <c r="C297" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 5 (Log entries immutable)</t>
         </is>
       </c>
-      <c r="D288" s="2" t="inlineStr">
+      <c r="D297" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E288" s="2" t="inlineStr">
+      <c r="E297" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_05</t>
         </is>
       </c>
-      <c r="F288" s="2" t="inlineStr">
+      <c r="F297" s="2" t="inlineStr">
         <is>
           <t>Verify that any attempt to edit or delete an activity log entry should be refused</t>
         </is>
       </c>
-      <c r="G288" s="2" t="inlineStr">
+      <c r="G297" s="2" t="inlineStr">
         <is>
           <t>A log entry exists: Event = Annual Tech Summit, Action = "Status changed to Approved", Actor = coordinator_1@connectsphere.com (created in TC_E14S02_01)</t>
         </is>
       </c>
-      <c r="H288" s="2" t="inlineStr">
+      <c r="H297" s="2" t="inlineStr">
         <is>
           <t>1. Log in as a System Administrator
   2. Open the Activity Log and locate the entry for Event = Annual Tech Summit, Action = "Status changed to Approved"
@@ -15496,272 +15968,272 @@
   5. If no UI path exists for either action, attempt the same edit and delete via a direct API call to the log entry's ID</t>
         </is>
       </c>
-      <c r="I288" s="2" t="inlineStr">
+      <c r="I297" s="2" t="inlineStr">
         <is>
           <t>Target log entry: Event = Annual Tech Summit, Action = "Status changed to Approved" | Attempted edit: Action -&gt; "Status changed to Rejected"</t>
         </is>
       </c>
-      <c r="J288" s="2" t="inlineStr">
+      <c r="J297" s="2" t="inlineStr">
         <is>
           <t>Both the edit and delete attempts are refused; no UI control exists to modify or remove a log entry, and the direct API call returns an authorization/forbidden error with the entry left unchanged</t>
         </is>
       </c>
     </row>
-    <row r="289">
-      <c r="A289" s="2" t="n">
+    <row r="298">
+      <c r="A298" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B289" s="2" t="inlineStr">
+      <c r="B298" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C289" s="2" t="inlineStr">
+      <c r="C298" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 3 (Booking decision recorded)</t>
         </is>
       </c>
-      <c r="D289" s="2" t="inlineStr">
+      <c r="D298" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E289" s="2" t="inlineStr">
+      <c r="E298" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_06</t>
         </is>
       </c>
-      <c r="F289" s="2" t="inlineStr">
+      <c r="F298" s="2" t="inlineStr">
         <is>
           <t>Verify that a rejected venue booking should be recorded with the actor, action, affected records, and time</t>
         </is>
       </c>
-      <c r="G289" s="2" t="inlineStr">
+      <c r="G298" s="2" t="inlineStr">
         <is>
           <t>A booking request for Venue Z is pending</t>
         </is>
       </c>
-      <c r="H289" s="2" t="inlineStr">
+      <c r="H298" s="2" t="inlineStr">
         <is>
           <t>1. As Venue Staff, reject the booking request with reason "Venue unavailable for maintenance"
   2. Log in as a System Administrator
   3. Check the Activity Log</t>
         </is>
       </c>
-      <c r="I289" s="2" t="inlineStr">
+      <c r="I298" s="2" t="inlineStr">
         <is>
           <t>Venue: Venue Z | Action: Reject Booking | Reason: Venue unavailable for maintenance</t>
         </is>
       </c>
-      <c r="J289" s="2" t="inlineStr">
+      <c r="J298" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded with the actor, action ("Booking Rejected"), the affected booking/event, and a timestamp</t>
         </is>
       </c>
     </row>
-    <row r="290">
-      <c r="A290" s="2" t="n">
+    <row r="299">
+      <c r="A299" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B290" s="2" t="inlineStr">
+      <c r="B299" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="C290" s="2" t="inlineStr">
+      <c r="C299" s="2" t="inlineStr">
         <is>
           <t>E14-S02 - Scenario 3 (Booking decision recorded)</t>
         </is>
       </c>
-      <c r="D290" s="2" t="inlineStr">
+      <c r="D299" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E290" s="2" t="inlineStr">
+      <c r="E299" s="2" t="inlineStr">
         <is>
           <t>TC_E14S02_07</t>
         </is>
       </c>
-      <c r="F290" s="2" t="inlineStr">
+      <c r="F299" s="2" t="inlineStr">
         <is>
           <t>Verify that a released venue booking should be recorded with the actor, action, affected records, and time</t>
         </is>
       </c>
-      <c r="G290" s="2" t="inlineStr">
+      <c r="G299" s="2" t="inlineStr">
         <is>
           <t>Venue Z has a confirmed booking for event "Annual Tech Summit"</t>
         </is>
       </c>
-      <c r="H290" s="2" t="inlineStr">
+      <c r="H299" s="2" t="inlineStr">
         <is>
           <t>1. As Venue Staff or Coordinator, release the confirmed booking for Venue Z (e.g. due to event cancellation)
   2. Log in as a System Administrator
   3. Check the Activity Log</t>
         </is>
       </c>
-      <c r="I290" s="2" t="inlineStr">
+      <c r="I299" s="2" t="inlineStr">
         <is>
           <t>Venue: Venue Z | Action: Release Booking | Event: Annual Tech Summit</t>
         </is>
       </c>
-      <c r="J290" s="2" t="inlineStr">
+      <c r="J299" s="2" t="inlineStr">
         <is>
           <t>An entry is recorded with the actor, action ("Booking Released"), the affected booking/event, and a timestamp</t>
         </is>
       </c>
     </row>
-    <row r="291">
-      <c r="A291" s="2" t="n">
+    <row r="300">
+      <c r="A300" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B291" s="2" t="inlineStr">
+      <c r="B300" s="2" t="inlineStr">
         <is>
           <t>Definition of Done</t>
         </is>
       </c>
-      <c r="C291" s="2" t="inlineStr">
+      <c r="C300" s="2" t="inlineStr">
         <is>
           <t>Definition of Done · BDR T-51 · Week 1 §8a</t>
         </is>
       </c>
-      <c r="D291" s="2" t="inlineStr">
+      <c r="D300" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting</t>
         </is>
       </c>
-      <c r="E291" s="2" t="inlineStr">
+      <c r="E300" s="2" t="inlineStr">
         <is>
           <t>TC_PERF_01</t>
         </is>
       </c>
-      <c r="F291" s="2" t="inlineStr">
+      <c r="F300" s="2" t="inlineStr">
         <is>
           <t>Verify a venue search returns within the 3-second target on a realistic catalogue</t>
         </is>
       </c>
-      <c r="G291" s="2" t="inlineStr">
+      <c r="G300" s="2" t="inlineStr">
         <is>
           <t>The venue catalogue holds 50 venues with layouts, accessibility features and facilities. 200 confirmed bookings exist across the next 90 days. Coordinator coord_a@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H291" s="2" t="inlineStr">
+      <c r="H300" s="2" t="inlineStr">
         <is>
           <t>1. Open the venue search
  2. Enter date 2026-12-01, time 09:00–11:00, expected attendance 120, layout Theatre, accessibility Step-free access
  3. Start a timer on submit and stop it when results render</t>
         </is>
       </c>
-      <c r="I291" s="2" t="inlineStr">
+      <c r="I300" s="2" t="inlineStr">
         <is>
           <t>50 venues · 200 bookings · elapsed time measured client-side</t>
         </is>
       </c>
-      <c r="J291" s="2" t="inlineStr">
+      <c r="J300" s="2" t="inlineStr">
         <is>
           <t>Results render in under 3 seconds. Record the measured time; if it exceeds 3 seconds the story does not meet the Definition of Done</t>
         </is>
       </c>
     </row>
-    <row r="292">
-      <c r="A292" s="2" t="n">
+    <row r="301">
+      <c r="A301" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B292" s="2" t="inlineStr">
+      <c r="B301" s="2" t="inlineStr">
         <is>
           <t>Definition of Done</t>
         </is>
       </c>
-      <c r="C292" s="2" t="inlineStr">
+      <c r="C301" s="2" t="inlineStr">
         <is>
           <t>Definition of Done · BDR T-51 · Week 1 §8a</t>
         </is>
       </c>
-      <c r="D292" s="2" t="inlineStr">
+      <c r="D301" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting</t>
         </is>
       </c>
-      <c r="E292" s="2" t="inlineStr">
+      <c r="E301" s="2" t="inlineStr">
         <is>
           <t>TC_PERF_02</t>
         </is>
       </c>
-      <c r="F292" s="2" t="inlineStr">
+      <c r="F301" s="2" t="inlineStr">
         <is>
           <t>Verify the venue availability calendar loads within the 3-second target for a busy month</t>
         </is>
       </c>
-      <c r="G292" s="2" t="inlineStr">
+      <c r="G301" s="2" t="inlineStr">
         <is>
           <t>Orchid Hall has 40 confirmed bookings, 5 tentative holds and 3 maintenance blocks within 2026-12-01 to 2026-12-31</t>
         </is>
       </c>
-      <c r="H292" s="2" t="inlineStr">
+      <c r="H301" s="2" t="inlineStr">
         <is>
           <t>1. Open Orchid Hall in the venue catalogue
  2. Select the calendar for December 2026
  3. Start a timer on selection and stop it when all states have rendered</t>
         </is>
       </c>
-      <c r="I292" s="2" t="inlineStr">
+      <c r="I301" s="2" t="inlineStr">
         <is>
           <t>48 calendar entries in one month · elapsed time measured client-side</t>
         </is>
       </c>
-      <c r="J292" s="2" t="inlineStr">
+      <c r="J301" s="2" t="inlineStr">
         <is>
           <t>The calendar renders all Free, Tentative, Confirmed and Blocked states in under 3 seconds</t>
         </is>
       </c>
     </row>
-    <row r="293">
-      <c r="A293" s="2" t="n">
+    <row r="302">
+      <c r="A302" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B293" s="2" t="inlineStr">
+      <c r="B302" s="2" t="inlineStr">
         <is>
           <t>Definition of Done</t>
         </is>
       </c>
-      <c r="C293" s="2" t="inlineStr">
+      <c r="C302" s="2" t="inlineStr">
         <is>
           <t>Definition of Done · BDR T-51 · Week 1 §8a</t>
         </is>
       </c>
-      <c r="D293" s="2" t="inlineStr">
+      <c r="D302" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting</t>
         </is>
       </c>
-      <c r="E293" s="2" t="inlineStr">
+      <c r="E302" s="2" t="inlineStr">
         <is>
           <t>TC_PERF_03</t>
         </is>
       </c>
-      <c r="F293" s="2" t="inlineStr">
+      <c r="F302" s="2" t="inlineStr">
         <is>
           <t>Verify a registration submission completes within the 3-second target near capacity</t>
         </is>
       </c>
-      <c r="G293" s="2" t="inlineStr">
+      <c r="G302" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with Orchid Hall booked, venue capacity 200, and 198 registrations recorded. Attendee attendee_b@example.com is signed in</t>
         </is>
       </c>
-      <c r="H293" s="2" t="inlineStr">
+      <c r="H302" s="2" t="inlineStr">
         <is>
           <t>1. Open event EVT-2001
  2. Submit a registration
  3. Start a timer on submit and stop it when confirmation renders</t>
         </is>
       </c>
-      <c r="I293" s="2" t="inlineStr">
+      <c r="I302" s="2" t="inlineStr">
         <is>
           <t>198 existing registrations · capacity 200 · elapsed time measured client-side</t>
         </is>
       </c>
-      <c r="J293" s="2" t="inlineStr">
+      <c r="J302" s="2" t="inlineStr">
         <is>
           <t>The registration is created and confirmation renders in under 3 seconds, including the capacity check against the booked venue</t>
         </is>

--- a/docs/testing/PROJECT TEST CASES CAA 031026.xlsx
+++ b/docs/testing/PROJECT TEST CASES CAA 031026.xlsx
@@ -7457,8 +7457,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>Setup time and Turnaround time both read 0; every Confirmed, Tentative and Blocked period on the calendar matches the advertised times exactly, with no buffer portion shown, so TC_E05S03_01 to TC_E05S03_05 continue to pass unchanged
-## E05-S06</t>
+          <t>Setup time and Turnaround time both read 0; every Confirmed, Tentative and Blocked period on the calendar matches the advertised times exactly, with no buffer portion shown, so TC_E05S03_01 to TC_E05S03_05 continue to pass unchanged</t>
         </is>
       </c>
     </row>
@@ -7468,35 +7467,88 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
+          <t>E05-S05</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>E05-S05 — Scenario 7 (Buffered occupancy excludes a venue from search); regression on E06-S01 per T-74</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>4 - Negative (business rule)</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>TC_E05S05_07</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Verify that a venue whose existing booking overlaps the event only once its setup and turnaround time are applied should not appear as available in search</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Venue "Riverside Hall" has Setup time 30 and Turnaround time 45 and a Confirmed booking 15/01/2027 10:00-12:00; coordinator_1@connectsphere.com is signed in with an Approved event on 15/01/2027 12:30-14:00</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>1. Open venue search for the event
+  2. Search for "Riverside"
+  3. Inspect the result for "Riverside Hall"</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>Existing booking buffered window: 09:30-12:45 | Event period: 12:30-14:00</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>"Riverside Hall" is not offered as available for the event; where it is listed its unavailability names the 12:30-12:45 overlap with the other booking's turnaround
+## E05-S06</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>E05-S06</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
         <is>
           <t>E05-S06 — Scenario 1 (Unavailability recorded with a reason)</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>2 - Happy Path</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>TC_E05S06_01</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Verify that marking a venue unavailable with a reason category over a period with no bookings should save and show the period as Blocked</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>venue_staff_1@connectsphere.com is signed in; venue "Riverside Hall" has no bookings on 20/01/2027</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>1. Open venue "Riverside Hall" and click "Mark unavailable"
   2. Enter period 20/01/2027 08:00 to 20/01/2027 18:00
@@ -7505,52 +7557,52 @@
   5. Open the venue availability calendar for 20/01/2027</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr">
         <is>
           <t>Period: 20/01/2027 08:00-18:00 | Category: Equipment failure | Note: Projector rig fault</t>
         </is>
       </c>
-      <c r="J135" s="2" t="inlineStr">
+      <c r="J136" s="2" t="inlineStr">
         <is>
           <t>The unavailability is saved with period, category, note and venue_staff_1 as recorder; the calendar shows 20/01/2027 08:00-18:00 as Blocked</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
+    <row r="137">
+      <c r="A137" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>E05-S06</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
         <is>
           <t>E05-S06 — Scenario 2 (Overlapping bookings become Conflicting, not released); Scenario 3 (The event itself is untouched); assumes O-24</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>4 - Negative (business rule)</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>TC_E05S06_02</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Verify that marking a venue unavailable over a Pending request and a Confirmed booking should mark both Conflicting, list the affected events on save and release neither</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>Venue "Riverside Hall" has a Confirmed booking for "Charity Run" (status Confirmed, coordinator_1) on 15/01/2027 10:00-12:00 and a Pending request for "Alumni Dinner" (coordinator_2) on 15/01/2027 14:00-16:00; venue_staff_1@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>1. Open venue "Riverside Hall" and click "Mark unavailable"
   2. Enter period 15/01/2027 00:00 to 16/01/2027 00:00, category "Safety concern", note "Ceiling inspection"
@@ -7559,52 +7611,52 @@
   5. Open the venue availability calendar for 15/01/2027</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr">
+      <c r="I137" s="2" t="inlineStr">
         <is>
           <t>Two bookings inside the period: Charity Run (Confirmed), Alumni Dinner (Pending)</t>
         </is>
       </c>
-      <c r="J136" s="2" t="inlineStr">
+      <c r="J137" s="2" t="inlineStr">
         <is>
           <t>The save succeeds and lists "Charity Run" and "Alumni Dinner" as affected; both bookings are marked Conflicting and neither is released or cancelled; "Charity Run" still shows status Confirmed with all other arrangements intact and a venue-conflict flag reading "Safety concern"; the calendar shows the period Blocked with the two Conflicting bookings visible</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
+    <row r="138">
+      <c r="A138" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>E05-S06</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
         <is>
           <t>E05-S06 — Scenario 4 (Affected Coordinators informed); assumes O-25</t>
         </is>
       </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting (notification consistency)</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>TC_E05S06_03</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Verify that each Coordinator whose booking became Conflicting should receive an in-app and email notification naming the venue, period, reason and event</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>As TC_E05S06_02, with the notification outbox relay enabled against the intercepted email provider</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>1. Perform TC_E05S06_02 steps 1-3
   2. Sign in as coordinator_1@connectsphere.com and open the inbox
@@ -7613,104 +7665,104 @@
   5. Sign in as the Organiser of "Charity Run" and open the inbox</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr">
         <is>
           <t>Expected recipients: coordinator_1, coordinator_2 | Not expected: the Organiser, registered Attendees</t>
         </is>
       </c>
-      <c r="J137" s="2" t="inlineStr">
+      <c r="J138" s="2" t="inlineStr">
         <is>
           <t>Each Coordinator has exactly one in-app notification and one email naming "Riverside Hall", 15/01/2027, "Safety concern" and their event, stating that alternative arrangements are required; the Organiser has no notification about the venue loss</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
+    <row r="139">
+      <c r="A139" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>E05-S06</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
         <is>
           <t>E05-S06 — Scenario 5 (End date required and extendable); assumes O-23</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>TC_E05S06_04</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Verify that an unavailability with no end date and time should be refused</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>venue_staff_1@connectsphere.com is signed in on venue "Riverside Hall"</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>1. Click "Mark unavailable"
   2. Enter start 20/01/2027 08:00, leave the end empty, choose "Renovation"
   3. Click "Save"</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr">
         <is>
           <t>Start: 20/01/2027 08:00 | End: (empty)</t>
         </is>
       </c>
-      <c r="J138" s="2" t="inlineStr">
+      <c r="J139" s="2" t="inlineStr">
         <is>
           <t>The save is refused with a message that an end date and time is required; nothing is recorded and the calendar is unchanged</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
+    <row r="140">
+      <c r="A140" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>E05-S06</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
         <is>
           <t>E05-S06 — Scenario 5 (End date required and extendable); Scenario 6 (Unavailability shortened or ended early); assumes O-26</t>
         </is>
       </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>5 - Boundary (exactly at)</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>TC_E05S06_05</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Verify that extending an unavailability should flag bookings newly inside the longer period and that shortening it should clear the flag on bookings it no longer touches</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>Venue "Riverside Hall" has an unavailability 15/01/2027 08:00-12:00 and a Confirmed booking for "Alumni Dinner" 15/01/2027 12:00-14:00 that is not Conflicting; venue_staff_1@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>1. Edit the unavailability and set the end to 15/01/2027 12:01; save
   2. Open event "Alumni Dinner"
@@ -7718,116 +7770,65 @@
   4. Open event "Alumni Dinner" again</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr">
         <is>
           <t>Booking: 12:00-14:00 | End at 12:00 = adjacent, no overlap | End at 12:01 = one minute of overlap</t>
         </is>
       </c>
-      <c r="J139" s="2" t="inlineStr">
+      <c r="J140" s="2" t="inlineStr">
         <is>
           <t>After step 1 the booking is Conflicting and coordinator_2 is notified; after step 3 the Conflicting flag has cleared and the booking stands as Confirmed with no further action by the Coordinator</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="n">
+    <row r="141">
+      <c r="A141" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>E05-S06</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
         <is>
           <t>E05-S06 — Checklist (E05-S04 regression per T-74)</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>3 - Integration / regression</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>TC_E05S06_06</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Verify that E05-S04's block, shorten and remove behaviour still works for periods with no bookings after this story</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>Venue "Riverside Hall" has no bookings 05/01/2027-07/01/2027; venue_staff_1@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>1. Re-run TC_E05S04_01 (block a free period)
   2. Re-run TC_E05S04_04 (shorten and remove the block)</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr">
+      <c r="I141" s="2" t="inlineStr">
         <is>
           <t>As TC_E05S04_01 and TC_E05S04_04</t>
         </is>
       </c>
-      <c r="J140" s="2" t="inlineStr">
+      <c r="J141" s="2" t="inlineStr">
         <is>
           <t>Both cases pass unchanged: a block over a free period makes the venue unavailable, and shortening or removing it restores availability; the only E05-S04 behaviour this story changes is the refusal in TC_E05S04_02, which is superseded by TC_E05S06_02</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>E06-S01</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>E06-S01 - Scenario 1 (Matching venues listed)</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>2 - Happy Path</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>TC_E06S01_01</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>Verify that running a search where multiple criteria match an available venue should list it with its capacity, layouts and facilities</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>Venue "Grand Ballroom" is available on 15/11/2026, capacity 300, supports Theatre layout, has Wheelchair Access, and has no other confirmed/blocked booking for that date</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in as an Event Coordinator
- 2. Search venues with Date: 15/11/2026, Expected Attendance: 250, Layout: Theatre, Accessibility: Wheelchair Access</t>
-        </is>
-      </c>
-      <c r="I141" s="2" t="inlineStr">
-        <is>
-          <t>Date: 15/11/2026 | Attendance: 250 | Layout: Theatre | Accessibility: Wheelchair Access</t>
-        </is>
-      </c>
-      <c r="J141" s="2" t="inlineStr">
-        <is>
-          <t>"Grand Ballroom" appears in the results, listed with its capacity (300), supported layouts, and facilities</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7843,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>E06-S01 - Scenario 2 (Near matches show failing criteria)</t>
+          <t>E06-S01 - Scenario 1 (Matching venues listed)</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -7852,33 +7853,33 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>TC_E06S01_02</t>
+          <t>TC_E06S01_01</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Verify that when no venue matches every criterion, near matches should be returned instead of an empty result</t>
+          <t>Verify that running a search where multiple criteria match an available venue should list it with its capacity, layouts and facilities</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>No venue fully meets Date: 15/11/2026, Attendance: 250, Accessibility: Hearing Loop (no venue currently has a hearing loop)</t>
+          <t>Venue "Grand Ballroom" is available on 15/11/2026, capacity 300, supports Theatre layout, has Wheelchair Access, and has no other confirmed/blocked booking for that date</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
           <t>1. Log in as an Event Coordinator
- 2. Search venues with Date: 15/11/2026, Attendance: 250, Accessibility: Hearing Loop</t>
+ 2. Search venues with Date: 15/11/2026, Expected Attendance: 250, Layout: Theatre, Accessibility: Wheelchair Access</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>Date: 15/11/2026 | Attendance: 250 | Accessibility: Hearing Loop (no exact match exists)</t>
+          <t>Date: 15/11/2026 | Attendance: 250 | Layout: Theatre | Accessibility: Wheelchair Access</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>The search returns near-matching venues (e.g. "Grand Ballroom" without a hearing loop) rather than an empty list, with the failing criterion (Hearing Loop) indicated for each</t>
+          <t>"Grand Ballroom" appears in the results, listed with its capacity (300), supported layouts, and facilities</t>
         </is>
       </c>
     </row>
@@ -7893,43 +7894,43 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>E06-S01 - Scenario 3 (Undersized venue marked unsuitable)</t>
+          <t>E06-S01 - Scenario 2 (Near matches show failing criteria)</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>4 - Negative</t>
+          <t>2 - Happy Path</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>TC_E06S01_03</t>
+          <t>TC_E06S01_02</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Verify that a venue available but with capacity below the event's expected attendance should be excluded or marked unsuitable</t>
+          <t>Verify that when no venue matches every criterion, near matches should be returned instead of an empty result</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Venue "Small Room" (capacity 50) is available on 15/11/2026; the event's expected attendance is 100</t>
+          <t>No venue fully meets Date: 15/11/2026, Attendance: 250, Accessibility: Hearing Loop (no venue currently has a hearing loop)</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
           <t>1. Log in as an Event Coordinator
-  2. Search venues with Date: 15/11/2026, Expected Attendance: 100</t>
+ 2. Search venues with Date: 15/11/2026, Attendance: 250, Accessibility: Hearing Loop</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>Small Room capacity: 50 | Required attendance: 100</t>
+          <t>Date: 15/11/2026 | Attendance: 250 | Accessibility: Hearing Loop (no exact match exists)</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>"Small Room" is excluded from the results or clearly marked unsuitable due to insufficient capacity</t>
+          <t>The search returns near-matching venues (e.g. "Grand Ballroom" without a hearing loop) rather than an empty list, with the failing criterion (Hearing Loop) indicated for each</t>
         </is>
       </c>
     </row>
@@ -7944,95 +7945,94 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
+          <t>E06-S01 - Scenario 3 (Undersized venue marked unsuitable)</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>4 - Negative</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>TC_E06S01_03</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Verify that a venue available but with capacity below the event's expected attendance should be excluded or marked unsuitable</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Venue "Small Room" (capacity 50) is available on 15/11/2026; the event's expected attendance is 100</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in as an Event Coordinator
+  2. Search venues with Date: 15/11/2026, Expected Attendance: 100</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Small Room capacity: 50 | Required attendance: 100</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>"Small Room" is excluded from the results or clearly marked unsuitable due to insufficient capacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>E06-S01</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
           <t>E06-S01 - Scenario 4 (Blocked or booked venues excluded)</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>4 - Negative</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>TC_E06S01_04</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Verify that a venue that is blocked or already confirmed for the requested period should not appear as available</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>Venue "Grand Ballroom" is Confirmed for another event on 15/11/2026</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>1. Log in as an Event Coordinator
   2. Search venues with Date: 15/11/2026</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr">
+      <c r="I145" s="2" t="inlineStr">
         <is>
           <t>Date: 15/11/2026 | Grand Ballroom status: Confirmed (for another event)</t>
         </is>
       </c>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t>"Grand Ballroom" does not appear as available in the results for 15/11/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>E06-S01</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>E06-S01 — Scenario 5 (Buffered occupancy excludes a venue)</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>4 - Negative (business rule)</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
-          <t>TC_E06S01_05</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>Verify that a venue whose existing booking overlaps the event only once its setup and turnaround time are applied should not appear as available in search</t>
-        </is>
-      </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t>Venue "Riverside Hall" has Setup time 30 and Turnaround time 45 and a Confirmed booking 15/01/2027 10:00-12:00; coordinator_1@connectsphere.com is signed in with an Approved event on 15/01/2027 12:30-14:00</t>
-        </is>
-      </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>1. Open venue search for the event
-  2. Search for "Riverside"
-  3. Inspect the result for "Riverside Hall"</t>
-        </is>
-      </c>
-      <c r="I145" s="2" t="inlineStr">
-        <is>
-          <t>Existing booking buffered window: 09:30-12:45 | Event period: 12:30-14:00</t>
-        </is>
-      </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>"Riverside Hall" is not offered as available for the event; where it is listed its unavailability names the 12:30-12:45 overlap with the other booking's turnaround
+          <t>"Grand Ballroom" does not appear as available in the results for 15/11/2026
 ## E06-S02</t>
         </is>
       </c>
